--- a/cargo_packages_p1-5.xlsx
+++ b/cargo_packages_p1-5.xlsx
@@ -1602,7 +1602,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>13/09/2026</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">

--- a/cargo_packages_p1-5.xlsx
+++ b/cargo_packages_p1-5.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N101"/>
+  <dimension ref="A1:N81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>13/09/2026</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -6047,1382 +6047,6 @@
           <t>蘑菇钉补胎贴</t>
         </is>
       </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="n">
-        <v>5</v>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>435289604798722</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>UN-INV260807-00009</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>ธรรมดา
- รถ lot18462-3</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>31/07/2026</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>01/08/2026</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>06/08/2026</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>4.30</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>0.0029</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>64.50฿</t>
-        </is>
-      </c>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr">
-        <is>
-          <t>气门嘴</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="n">
-        <v>5</v>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>ZY202471573119#2</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>UN-INV260807-00009</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>ธรรมดา
- รถ lot18463-6</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>31/07/2026</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>31/07/2026</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>06/08/2026</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>8.70</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>0.0441</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>264.60฿</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" t="n">
-        <v>5</v>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>ZY202471573119</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>UN-INV260807-00009</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>ธรรมดา
- รถ lot18463-5</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>31/07/2026</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>31/07/2026</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>06/08/2026</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>11.90</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>0.0832</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L84" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>499.20฿</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr">
-        <is>
-          <t>蘑菇钉补胎</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="n">
-        <v>5</v>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>YT7635427281240</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>UN-INV260807-00009</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>ธรรมดา
- รถ lot18458-21</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>31/07/2026</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>31/07/2026</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>06/08/2026</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>0.0117</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>70.20฿</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr">
-        <is>
-          <t>气阀</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="n">
-        <v>5</v>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>79021262374216</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>UN-INV260804-00019</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>ธรรมดา
- รถ lot18435-5-73</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>28/07/2026</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>28/07/2026</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>02/08/2026</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>12.20</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>0.0352</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>211.20฿</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr">
-        <is>
-          <t>加长弯头</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="n">
-        <v>5</v>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>113162219964#3</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>UN-INV260804-00019</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>ธรรมดา
- รถ lot18434-9-28</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>27/07/2026</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>27/07/2026</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>02/08/2026</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>18.70</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>0.0443</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L87" t="inlineStr">
-        <is>
-          <t>280.50฿</t>
-        </is>
-      </c>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" t="n">
-        <v>5</v>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>113162219964#2</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>UN-INV260804-00019</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>ธรรมดา
- รถ lot18434-9-27</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>27/07/2026</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>27/07/2026</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>02/08/2026</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>22.90</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>0.0522</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L88" t="inlineStr">
-        <is>
-          <t>343.50฿</t>
-        </is>
-      </c>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" t="n">
-        <v>5</v>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>113162219964</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>UN-INV260804-00019</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>ธรรมดา
- รถ lot18434-9-26</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>27/07/2026</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>27/07/2026</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>02/08/2026</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>25.60</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>0.0574</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L89" t="inlineStr">
-        <is>
-          <t>384.00฿</t>
-        </is>
-      </c>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr">
-        <is>
-          <t>补胎胶片/3件</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="n">
-        <v>5</v>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>113158800045#2</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>UN-INV260804-00019</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>ธรรมดา
- รถ lot18427-7-3</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>26/07/2026</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>26/07/2026</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>31/07/2026</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>26.30</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>0.0377</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L90" t="inlineStr">
-        <is>
-          <t>394.50฿</t>
-        </is>
-      </c>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" t="n">
-        <v>5</v>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>113158800045</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>UN-INV260804-00019</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>ธรรมดา
- รถ lot18427-7-2</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>26/07/2026</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>26/07/2026</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>31/07/2026</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>26.50</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>0.0379</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L91" t="inlineStr">
-        <is>
-          <t>397.50฿</t>
-        </is>
-      </c>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N91" t="inlineStr">
-        <is>
-          <t>塑料配件/2件</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="n">
-        <v>5</v>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>YT2550516723148</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>UN-INV260804-00019</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>ธรรมดา
- รถ lot18398-3-10</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>22/07/2026</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>23/07/2026</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>30/07/2026</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>1.20</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>0.0127</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L92" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>76.20฿</t>
-        </is>
-      </c>
-      <c r="N92" t="inlineStr">
-        <is>
-          <t>硅胶风管</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="n">
-        <v>5</v>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>ZY202467269952#4</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>UN-INV260724-00013</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>ธรรมดา
- รถ lot18314-8-30</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>11/07/2026</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>12/07/2026</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>17/07/2026</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>15.50</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>0.0492</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L93" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>295.20฿</t>
-        </is>
-      </c>
-      <c r="N93" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" t="n">
-        <v>5</v>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>ZY202467269952#3</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>UN-INV260724-00013</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>ธรรมดา
- รถ lot18314-8-29</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>11/07/2026</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>12/07/2026</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>17/07/2026</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>12.50</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>0.0300</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L94" t="inlineStr">
-        <is>
-          <t>187.50฿</t>
-        </is>
-      </c>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N94" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" t="n">
-        <v>5</v>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>ZY202467269952#2</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>UN-INV260724-00013</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>ธรรมดา
- รถ lot18314-8-28</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>11/07/2026</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>12/07/2026</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>17/07/2026</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>15.50</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>0.0508</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L95" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>304.80฿</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" t="n">
-        <v>5</v>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>ZY202467269952</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>UN-INV260724-00013</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>ธรรมดา
- รถ lot18314-8-27</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>11/07/2026</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>12/07/2026</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>17/07/2026</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>10.50</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>0.0355</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L96" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>213.00฿</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr">
-        <is>
-          <t>补胎胶片/4件</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="n">
-        <v>5</v>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>773431041004504</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>UN-INV260724-00013</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>ธรรมดา
- รถ lot18314-5-13</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>11/07/2026</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>12/07/2026</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>17/07/2026</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>1.00</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>0.0044</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L97" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>26.40฿</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr">
-        <is>
-          <t>门底条</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="n">
-        <v>5</v>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>ZY202467269844#2</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>UN-INV260717-00013</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>ธรรมดา
- รถ lot18288-8-41</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>08/07/2026</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>09/07/2026</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>15/07/2026</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>21.00</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>0.0660</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L98" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>396.00฿</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" t="n">
-        <v>5</v>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>ZY202467269844#5</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>UN-INV260717-00013</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>ธรรมดา
- รถ lot18288-8-40</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>08/07/2026</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>09/07/2026</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>15/07/2026</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>27.90</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>0.0800</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L99" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>480.00฿</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" t="n">
-        <v>5</v>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>ZY202467269844#3</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>UN-INV260717-00013</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>ธรรมดา
- รถ lot18288-8-39</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>08/07/2026</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>09/07/2026</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>15/07/2026</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>15.60</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>0.0496</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L100" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>297.60฿</t>
-        </is>
-      </c>
-      <c r="N100" t="inlineStr"/>
-    </row>
-    <row r="101">
-      <c r="A101" t="n">
-        <v>5</v>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>ZY202467269844#4</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>UN-INV260717-00013</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>ธรรมดา
- รถ lot18288-8-38</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>08/07/2026</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>09/07/2026</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>15/07/2026</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>16.00</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>0.0504</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L101" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>302.40฿</t>
-        </is>
-      </c>
-      <c r="N101" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/cargo_packages_p1-5.xlsx
+++ b/cargo_packages_p1-5.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N81"/>
+  <dimension ref="A1:N101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>UN-INV260914-00014</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>UN-INV260914-00015</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>UN-INV260914-00014</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>UN-INV260914-00014</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>UN-INV260914-00014</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>UN-INV260914-00015</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>UN-INV260914-00015</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>UN-INV260914-00014</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -6047,6 +6047,1382 @@
           <t>蘑菇钉补胎贴</t>
         </is>
       </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>5</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>435289604798722</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>UN-INV260807-00009</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>ธรรมดา
+ รถ lot18462-3</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>06/08/2026</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>4.30</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>0.0029</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>64.50฿</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>气门嘴</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>5</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>ZY202471573119#2</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>UN-INV260807-00009</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>ธรรมดา
+ รถ lot18463-6</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>06/08/2026</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>8.70</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>0.0441</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>264.60฿</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>5</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>ZY202471573119</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>UN-INV260807-00009</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>ธรรมดา
+ รถ lot18463-5</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>06/08/2026</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>11.90</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>0.0832</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>499.20฿</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>蘑菇钉补胎</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>5</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>YT7635427281240</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>UN-INV260807-00009</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>ธรรมดา
+ รถ lot18458-21</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>06/08/2026</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>0.0117</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>70.20฿</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>气阀</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>5</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>79021262374216</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>UN-INV260804-00019</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>ธรรมดา
+ รถ lot18435-5-73</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>02/08/2026</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>12.20</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>0.0352</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>211.20฿</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>加长弯头</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>5</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>113162219964#3</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>UN-INV260804-00019</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>ธรรมดา
+ รถ lot18434-9-28</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>02/08/2026</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>18.70</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>0.0443</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>280.50฿</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>5</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>113162219964#2</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>UN-INV260804-00019</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>ธรรมดา
+ รถ lot18434-9-27</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>02/08/2026</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>22.90</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>0.0522</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>343.50฿</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>5</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>113162219964</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>UN-INV260804-00019</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>ธรรมดา
+ รถ lot18434-9-26</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>02/08/2026</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>25.60</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>0.0574</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>384.00฿</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>补胎胶片/3件</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>5</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>113158800045#2</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>UN-INV260804-00019</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>ธรรมดา
+ รถ lot18427-7-3</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>26/07/2026</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>26/07/2026</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>26.30</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>0.0377</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>394.50฿</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>5</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>113158800045</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>UN-INV260804-00019</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>ธรรมดา
+ รถ lot18427-7-2</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>26/07/2026</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>26/07/2026</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>26.50</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>0.0379</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>397.50฿</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>塑料配件/2件</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>5</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>YT2550516723148</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>UN-INV260804-00019</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>ธรรมดา
+ รถ lot18398-3-10</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>22/07/2026</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>23/07/2026</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>1.20</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>0.0127</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>76.20฿</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>硅胶风管</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>5</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>ZY202467269952#4</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>UN-INV260724-00013</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>ธรรมดา
+ รถ lot18314-8-30</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>11/07/2026</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>15.50</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>0.0492</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>295.20฿</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>5</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>ZY202467269952#3</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>UN-INV260724-00013</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>ธรรมดา
+ รถ lot18314-8-29</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>11/07/2026</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>12.50</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>0.0300</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>187.50฿</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>5</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>ZY202467269952#2</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>UN-INV260724-00013</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>ธรรมดา
+ รถ lot18314-8-28</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>11/07/2026</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>15.50</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>0.0508</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>304.80฿</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>5</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>ZY202467269952</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>UN-INV260724-00013</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>ธรรมดา
+ รถ lot18314-8-27</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>11/07/2026</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>10.50</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>0.0355</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>213.00฿</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>补胎胶片/4件</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>5</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>773431041004504</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>UN-INV260724-00013</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>ธรรมดา
+ รถ lot18314-5-13</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>11/07/2026</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>0.0044</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>26.40฿</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>门底条</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>5</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>ZY202467269844#2</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>UN-INV260717-00013</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>ธรรมดา
+ รถ lot18288-8-41</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>08/07/2026</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>15/07/2026</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>21.00</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>0.0660</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>396.00฿</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>5</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>ZY202467269844#5</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>UN-INV260717-00013</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>ธรรมดา
+ รถ lot18288-8-40</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>08/07/2026</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>15/07/2026</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>27.90</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>0.0800</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>480.00฿</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>5</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>ZY202467269844#3</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>UN-INV260717-00013</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>ธรรมดา
+ รถ lot18288-8-39</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>08/07/2026</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>15/07/2026</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>15.60</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>0.0496</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>297.60฿</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>5</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>ZY202467269844#4</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>UN-INV260717-00013</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>ธรรมดา
+ รถ lot18288-8-38</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>08/07/2026</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>15/07/2026</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>16.00</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>0.0504</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>302.40฿</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/cargo_packages_p1-5.xlsx
+++ b/cargo_packages_p1-5.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ZY202472578299</t>
+          <t>113348267192#2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -522,17 +522,17 @@
       <c r="E2" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18758-7-43</t>
+ รถ lot18795-2-7</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -542,34 +542,30 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>47.40</t>
+          <t>28.10</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.1603</t>
+          <t>0.0628</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>421.50฿</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>961.20฿</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>补胎贴，3件</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -577,7 +573,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>773440822655698</t>
+          <t>113348267192</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -593,17 +589,17 @@
       <c r="E3" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18758-4-31</t>
+ รถ lot18795-2-6</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -613,12 +609,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>19.50</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.0022</t>
+          <t>0.0505</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -628,17 +624,17 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>18.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>303.00฿</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>钻头</t>
+          <t>补胎胶片</t>
         </is>
       </c>
     </row>
@@ -648,7 +644,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>YT7642998390994</t>
+          <t>ZY202472578299</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -664,7 +660,7 @@
       <c r="E4" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18769-3-57</t>
+ รถ lot18758-7-43</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -674,7 +670,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -684,32 +680,32 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5.80</t>
+          <t>47.40</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.0070</t>
+          <t>0.1603</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>87.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>961.20฿</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>补胎贴，3件</t>
         </is>
       </c>
     </row>
@@ -719,7 +715,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DPK212614057101</t>
+          <t>773440822655698</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,17 +731,17 @@
       <c r="E5" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18749-4-3</t>
+ รถ lot18758-4-31</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -755,12 +751,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>9.60</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.0060</t>
+          <t>0.0022</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -770,7 +766,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>144.00฿</t>
+          <t>18.00฿</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -780,7 +776,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>轮胎气门嘴</t>
+          <t>钻头</t>
         </is>
       </c>
     </row>
@@ -790,7 +786,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>79031204783305</t>
+          <t>YT7642998390994</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -806,17 +802,17 @@
       <c r="E6" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18744-6-15</t>
+ รถ lot18769-3-57</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -826,12 +822,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>5.80</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.0020</t>
+          <t>0.0070</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -841,7 +837,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>39.00฿</t>
+          <t>87.00฿</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -861,7 +857,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>435342988112655</t>
+          <t>DPK212614057101</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -877,32 +873,32 @@
       <c r="E7" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18743-3-34</t>
+ รถ lot18749-4-3</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>9.60</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.0014</t>
+          <t>0.0060</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -912,17 +908,17 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>144.00฿</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>10.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>橡胶垫圈</t>
+          <t>轮胎气门嘴</t>
         </is>
       </c>
     </row>
@@ -932,7 +928,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>435343890137834</t>
+          <t>79031204783305</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -948,32 +944,32 @@
       <c r="E8" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18743-7-25</t>
+ รถ lot18744-6-15</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>21.40</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.0080</t>
+          <t>0.0020</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -983,7 +979,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>321.00฿</t>
+          <t>39.00฿</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -993,7 +989,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>扒胎机包胶撬棍</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -1003,7 +999,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>YT7642670434639</t>
+          <t>435342988112655</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1019,7 +1015,7 @@
       <c r="E9" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18743-2-8</t>
+ รถ lot18743-3-34</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1034,17 +1030,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.0010</t>
+          <t>0.0014</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1054,17 +1050,17 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>12.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10.00฿</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>片片</t>
+          <t>橡胶垫圈</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1070,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>93015797092</t>
+          <t>435343890137834</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1084,18 +1080,18 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>UN-INV260914-00014</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18735-4-40</t>
+ รถ lot18743-7-25</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1105,17 +1101,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>12/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>8.60</t>
+          <t>21.40</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.0148</t>
+          <t>0.0080</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1125,7 +1121,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>129.00฿</t>
+          <t>321.00฿</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1135,7 +1131,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>仪表</t>
+          <t>扒胎机包胶撬棍</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1141,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>YT7642390374765</t>
+          <t>YT7642670434639</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1155,18 +1151,18 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>UN-INV260914-00015</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18735-4-20</t>
+ รถ lot18743-2-8</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1176,17 +1172,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>12/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>20.80</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.0598</t>
+          <t>0.0010</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1196,17 +1192,17 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>12.00฿</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>358.80฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>打磨机</t>
+          <t>片片</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1212,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>435342255104130</t>
+          <t>93015797092</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1232,7 +1228,7 @@
       <c r="E12" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18735-43</t>
+ รถ lot18735-4-40</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1252,12 +1248,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4.90</t>
+          <t>8.60</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0.0172</t>
+          <t>0.0148</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1267,17 +1263,17 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>129.00฿</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>103.20฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>轮毂保护套</t>
+          <t>仪表</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1283,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>773440312345715</t>
+          <t>YT7642390374765</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1297,13 +1293,13 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>UN-INV260914-00014</t>
+          <t>UN-INV260914-00015</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18735-3-78</t>
+ รถ lot18735-4-20</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1323,12 +1319,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>20.80</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0.0013</t>
+          <t>0.0598</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1338,17 +1334,17 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>19.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>358.80฿</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>打磨机</t>
         </is>
       </c>
     </row>
@@ -1358,7 +1354,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>773440291470393</t>
+          <t>435342255104130</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1374,7 +1370,7 @@
       <c r="E14" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18735-34</t>
+ รถ lot18735-43</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1394,12 +1390,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>4.90</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.0029</t>
+          <t>0.0172</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1409,17 +1405,17 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>48.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>103.20฿</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>球阀</t>
+          <t>轮毂保护套</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1425,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>435342261175750</t>
+          <t>773440312345715</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1439,13 +1435,13 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>UN-INV260914-00015</t>
+          <t>UN-INV260914-00014</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18736-13</t>
+ รถ lot18735-3-78</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1455,7 +1451,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1465,12 +1461,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>13.90</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.0137</t>
+          <t>0.0013</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1480,7 +1476,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>208.50฿</t>
+          <t>19.50฿</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1500,7 +1496,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ZY202461195200</t>
+          <t>773440291470393</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1510,13 +1506,13 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>UN-INV260914-00015</t>
+          <t>UN-INV260914-00014</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18728-7-13</t>
+ รถ lot18735-34</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1526,22 +1522,22 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>13/09/2026</t>
+          <t>12/09/2026</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>47.40</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>0.0116</t>
+          <t>0.0029</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1551,7 +1547,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>711.00฿</t>
+          <t>48.00฿</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1561,7 +1557,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>球阀</t>
         </is>
       </c>
     </row>
@@ -1571,7 +1567,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>79030687835952</t>
+          <t>435342261175750</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1581,13 +1577,13 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>UN-INV260914-00014</t>
+          <t>UN-INV260914-00015</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18728-3-64</t>
+ รถ lot18736-13</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1602,17 +1598,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>13/09/2026</t>
+          <t>12/09/2026</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>4.30</t>
+          <t>13.90</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.0030</t>
+          <t>0.0137</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1622,7 +1618,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>64.50฿</t>
+          <t>208.50฿</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1632,7 +1628,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>接头配件</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -1642,7 +1638,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>LJ20722214#3</t>
+          <t>ZY202461195200</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1652,38 +1648,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>UN-INV260912-00011</t>
+          <t>UN-INV260914-00015</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18726-7-8</t>
+ รถ lot18728-7-13</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>13/09/2026</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>14.00</t>
+          <t>47.40</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>0.0171</t>
+          <t>0.0116</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1693,7 +1689,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>210.00฿</t>
+          <t>711.00฿</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1701,7 +1697,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>配件</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1709,7 +1709,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>LJ20722214#2</t>
+          <t>79030687835952</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1719,38 +1719,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>UN-INV260912-00011</t>
+          <t>UN-INV260914-00014</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18726-7-7</t>
+ รถ lot18728-3-64</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>13/09/2026</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>11.90</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>0.0089</t>
+          <t>0.0030</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>178.50฿</t>
+          <t>64.50฿</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1768,7 +1768,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>接头配件</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1776,7 +1780,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>LJ20722214</t>
+          <t>LJ20722214#3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1792,7 +1796,7 @@
       <c r="E20" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18726-7-6</t>
+ รถ lot18726-7-8</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1812,12 +1816,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>16.00</t>
+          <t>14.00</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0.0144</t>
+          <t>0.0171</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1827,7 +1831,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>240.00฿</t>
+          <t>210.00฿</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1835,11 +1839,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>电板套筒配件/3件</t>
-        </is>
-      </c>
+      <c r="N20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>YT7641966426761</t>
+          <t>LJ20722214#2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1863,17 +1863,17 @@
       <c r="E21" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18714-9-23</t>
+ รถ lot18726-7-7</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>13.60</t>
+          <t>11.90</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.0422</t>
+          <t>0.0089</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1898,19 +1898,15 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>178.50฿</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>253.20฿</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>带表汽车轮胎打气嘴</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1918,7 +1914,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ZY202471681117#2</t>
+          <t>LJ20722214</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1934,17 +1930,17 @@
       <c r="E22" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18714-9-8</t>
+ รถ lot18726-7-6</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1954,12 +1950,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>11.80</t>
+          <t>16.00</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.0832</t>
+          <t>0.0144</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1969,15 +1965,19 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>240.00฿</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>499.20฿</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>电板套筒配件/3件</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1985,7 +1985,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ZY202471681117</t>
+          <t>YT7641966426761</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2001,7 +2001,7 @@
       <c r="E23" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18714-9-7</t>
+ รถ lot18714-9-23</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2021,12 +2021,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>7.70</t>
+          <t>13.60</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.0493</t>
+          <t>0.0422</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2041,12 +2041,12 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>295.80฿</t>
+          <t>253.20฿</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>补胎胶片/2件</t>
+          <t>带表汽车轮胎打气嘴</t>
         </is>
       </c>
     </row>
@@ -2056,7 +2056,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>302285502767#2</t>
+          <t>ZY202471681117#2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2072,7 +2072,7 @@
       <c r="E24" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18714-8-10</t>
+ รถ lot18714-9-8</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2092,12 +2092,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>33.70</t>
+          <t>11.80</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.0145</t>
+          <t>0.0832</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2107,12 +2107,12 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>505.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>499.20฿</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>302285502767</t>
+          <t>ZY202471681117</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2139,7 +2139,7 @@
       <c r="E25" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18714-8-9</t>
+ รถ lot18714-9-7</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2159,12 +2159,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>23.40</t>
+          <t>7.70</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.0123</t>
+          <t>0.0493</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2174,17 +2174,17 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>351.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>295.80฿</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>扳手</t>
+          <t>补胎胶片/2件</t>
         </is>
       </c>
     </row>
@@ -2194,7 +2194,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>LJ20716178#2</t>
+          <t>302285502767#2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2204,18 +2204,18 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>UN-INV260911-00013</t>
+          <t>UN-INV260912-00011</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18713-6-65</t>
+ รถ lot18714-8-10</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2225,17 +2225,17 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>19.50</t>
+          <t>33.70</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>0.0075</t>
+          <t>0.0145</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2245,7 +2245,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>292.50฿</t>
+          <t>505.50฿</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2261,7 +2261,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>LJ20716178</t>
+          <t>302285502767</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2271,18 +2271,18 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>UN-INV260911-00013</t>
+          <t>UN-INV260912-00011</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18713-6-64</t>
+ รถ lot18714-8-9</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2292,17 +2292,17 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>19.60</t>
+          <t>23.40</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.0075</t>
+          <t>0.0123</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2312,7 +2312,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>294.00฿</t>
+          <t>351.00฿</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>扳手</t>
         </is>
       </c>
     </row>
@@ -2332,7 +2332,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>435338972466812</t>
+          <t>LJ20716178#2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2348,7 +2348,7 @@
       <c r="E28" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18710-6-35</t>
+ รถ lot18713-6-65</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2368,12 +2368,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>13.10</t>
+          <t>19.50</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.0624</t>
+          <t>0.0075</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2383,19 +2383,15 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>292.50฿</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>374.40฿</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>修补工具</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2403,7 +2399,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>435334324045675</t>
+          <t>LJ20716178</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2413,38 +2409,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>UN-INV260908-00009</t>
+          <t>UN-INV260911-00013</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18696-14</t>
+ รถ lot18713-6-64</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>10.80</t>
+          <t>19.60</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0.0088</t>
+          <t>0.0075</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2454,7 +2450,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>162.00฿</t>
+          <t>294.00฿</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2474,7 +2470,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>YT7641276428798</t>
+          <t>435338972466812</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2484,38 +2480,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>UN-INV260908-00009</t>
+          <t>UN-INV260911-00013</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18697-11</t>
+ รถ lot18710-6-35</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>9.50</t>
+          <t>13.10</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.0296</t>
+          <t>0.0624</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2530,12 +2526,12 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>177.60฿</t>
+          <t>374.40฿</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>修补工具</t>
         </is>
       </c>
     </row>
@@ -2545,7 +2541,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>79029430531776</t>
+          <t>435334324045675</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2555,18 +2551,18 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>UN-INV260907-00015</t>
+          <t>UN-INV260908-00009</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18689-26</t>
+ รถ lot18696-14</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2576,17 +2572,17 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>10.80</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.0135</t>
+          <t>0.0088</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2596,17 +2592,17 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>162.00฿</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>81.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>卡套</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -2616,7 +2612,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>113282578128#2</t>
+          <t>YT7641276428798</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2626,38 +2622,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>UN-INV260907-00015</t>
+          <t>UN-INV260908-00009</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18683-4</t>
+ รถ lot18697-11</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>38.00</t>
+          <t>9.50</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.1601</t>
+          <t>0.0296</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2672,10 +2668,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>960.60฿</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
+          <t>177.60฿</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>配件</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>113282578128</t>
+          <t>79029430531776</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2699,17 +2699,17 @@
       <c r="E33" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18683-3</t>
+ รถ lot18689-26</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>27.50</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.1566</t>
+          <t>0.0135</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>939.60฿</t>
+          <t>81.00฿</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>压条取出器 一票两件破损件</t>
+          <t>卡套</t>
         </is>
       </c>
     </row>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>82730128600#3</t>
+          <t>113282578128#2</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2770,12 +2770,12 @@
       <c r="E34" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18678-6-21</t>
+ รถ lot18683-4</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>30/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2790,12 +2790,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>33.00</t>
+          <t>38.00</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.0122</t>
+          <t>0.1601</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>495.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>960.60฿</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -2821,7 +2821,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>82730128600#2</t>
+          <t>113282578128</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2837,12 +2837,12 @@
       <c r="E35" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18678-6-20</t>
+ รถ lot18683-3</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>30/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>27.60</t>
+          <t>27.50</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.0095</t>
+          <t>0.1566</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2872,15 +2872,19 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>414.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
+          <t>939.60฿</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>压条取出器 一票两件破损件</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2888,7 +2892,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>82730128600</t>
+          <t>82730128600#3</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2904,7 +2908,7 @@
       <c r="E36" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18678-6-19</t>
+ รถ lot18678-6-21</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2924,12 +2928,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>28.10</t>
+          <t>33.00</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.0118</t>
+          <t>0.0122</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2939,7 +2943,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>421.50฿</t>
+          <t>495.00฿</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2947,11 +2951,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>五金配件/3件</t>
-        </is>
-      </c>
+      <c r="N36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>113278387839#3</t>
+          <t>82730128600#2</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2969,38 +2969,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>UN-INV260903-00023</t>
+          <t>UN-INV260907-00015</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18663-8-3</t>
+ รถ lot18678-6-20</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>30/08/2026</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>25.30</t>
+          <t>27.60</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.0404</t>
+          <t>0.0095</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -3010,7 +3010,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>379.50฿</t>
+          <t>414.00฿</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3026,7 +3026,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>113278387839#2</t>
+          <t>82730128600</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3036,38 +3036,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>UN-INV260903-00023</t>
+          <t>UN-INV260907-00015</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18663-8-2</t>
+ รถ lot18678-6-19</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>30/08/2026</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>26.10</t>
+          <t>28.10</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.0304</t>
+          <t>0.0118</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>391.50฿</t>
+          <t>421.50฿</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3085,7 +3085,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>五金配件/3件</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -3093,7 +3097,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>113278387839</t>
+          <t>113278387839#3</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3109,7 +3113,7 @@
       <c r="E39" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18663-8-1</t>
+ รถ lot18663-8-3</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -3129,12 +3133,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>9.10</t>
+          <t>25.30</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.0144</t>
+          <t>0.0404</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -3144,7 +3148,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>136.50฿</t>
+          <t>379.50฿</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3152,11 +3156,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>配件/3件</t>
-        </is>
-      </c>
+      <c r="N39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>113276098937#3</t>
+          <t>113278387839#2</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3174,38 +3174,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>UN-INV260901-00057</t>
+          <t>UN-INV260903-00023</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-45</t>
+ รถ lot18663-8-2</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>17.80</t>
+          <t>26.10</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.0302</t>
+          <t>0.0304</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -3215,7 +3215,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>267.00฿</t>
+          <t>391.50฿</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -3231,7 +3231,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>113276098937#2</t>
+          <t>113278387839</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3241,38 +3241,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>UN-INV260901-00057</t>
+          <t>UN-INV260903-00023</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-44</t>
+ รถ lot18663-8-1</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>10.90</t>
+          <t>9.10</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.0313</t>
+          <t>0.0144</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -3282,15 +3282,19 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>136.50฿</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>187.80฿</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>配件/3件</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -3298,7 +3302,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>113276098937</t>
+          <t>113276098937#3</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3314,7 +3318,7 @@
       <c r="E42" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-43</t>
+ รถ lot18655-9-45</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -3334,12 +3338,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>33.60</t>
+          <t>17.80</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.0825</t>
+          <t>0.0302</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3349,7 +3353,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>504.00฿</t>
+          <t>267.00฿</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3357,11 +3361,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>补胎胶片+配件/3件</t>
-        </is>
-      </c>
+      <c r="N42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -3369,7 +3369,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ZY202464580877#4</t>
+          <t>113276098937#2</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3385,7 +3385,7 @@
       <c r="E43" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-17</t>
+ รถ lot18655-9-44</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -3405,12 +3405,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>20.10</t>
+          <t>10.90</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.0466</t>
+          <t>0.0313</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>301.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>187.80฿</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -3436,7 +3436,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ZY202464580877#7</t>
+          <t>113276098937</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3452,7 +3452,7 @@
       <c r="E44" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-16</t>
+ รถ lot18655-9-43</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -3472,12 +3472,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>16.60</t>
+          <t>33.60</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.0430</t>
+          <t>0.0825</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3487,15 +3487,19 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>504.00฿</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>258.00฿</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>补胎胶片+配件/3件</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -3503,7 +3507,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ZY202464580877#2</t>
+          <t>ZY202464580877#4</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3519,7 +3523,7 @@
       <c r="E45" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-15</t>
+ รถ lot18655-9-17</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -3539,12 +3543,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>25.10</t>
+          <t>20.10</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.0483</t>
+          <t>0.0466</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3554,7 +3558,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>376.50฿</t>
+          <t>301.50฿</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3570,7 +3574,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ZY202464580877#8</t>
+          <t>ZY202464580877#7</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3586,7 +3590,7 @@
       <c r="E46" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-14</t>
+ รถ lot18655-9-16</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -3606,12 +3610,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>28.90</t>
+          <t>16.60</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>0.0800</t>
+          <t>0.0430</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3626,7 +3630,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>480.00฿</t>
+          <t>258.00฿</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
@@ -3637,7 +3641,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ZY202464580877#6</t>
+          <t>ZY202464580877#2</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3653,7 +3657,7 @@
       <c r="E47" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-13</t>
+ รถ lot18655-9-15</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -3673,12 +3677,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>20.90</t>
+          <t>25.10</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>0.0534</t>
+          <t>0.0483</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3688,12 +3692,12 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>376.50฿</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>320.40฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
@@ -3704,7 +3708,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>ZY202464580877#5</t>
+          <t>ZY202464580877#8</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3720,7 +3724,7 @@
       <c r="E48" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-12</t>
+ รถ lot18655-9-14</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -3740,12 +3744,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>26.20</t>
+          <t>28.90</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>0.0535</t>
+          <t>0.0800</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3755,12 +3759,12 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>393.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>480.00฿</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
@@ -3771,7 +3775,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ZY202464580877</t>
+          <t>ZY202464580877#6</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3787,7 +3791,7 @@
       <c r="E49" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-11</t>
+ รถ lot18655-9-13</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3807,12 +3811,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>20.70</t>
+          <t>20.90</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>0.0531</t>
+          <t>0.0534</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3827,7 +3831,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>318.60฿</t>
+          <t>320.40฿</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
@@ -3838,7 +3842,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ZY202464580877#9</t>
+          <t>ZY202464580877#5</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3854,7 +3858,7 @@
       <c r="E50" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-10</t>
+ รถ lot18655-9-12</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3874,12 +3878,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>27.70</t>
+          <t>26.20</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>0.0800</t>
+          <t>0.0535</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3889,12 +3893,12 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>393.00฿</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>480.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N50" t="inlineStr"/>
@@ -3905,7 +3909,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ZY202464580877#3</t>
+          <t>ZY202464580877</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3921,7 +3925,7 @@
       <c r="E51" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-9</t>
+ รถ lot18655-9-11</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -3941,12 +3945,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>27.10</t>
+          <t>20.70</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>0.0567</t>
+          <t>0.0531</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3956,19 +3960,15 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>406.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>补胎胶片/9件</t>
-        </is>
-      </c>
+          <t>318.60฿</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -3976,7 +3976,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>S71090288685</t>
+          <t>ZY202464580877#9</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3986,38 +3986,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>UN-INV260831-00017</t>
+          <t>UN-INV260901-00057</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18634-7-3</t>
+ รถ lot18655-9-10</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>29/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>12.10</t>
+          <t>27.70</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>0.0240</t>
+          <t>0.0800</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -4027,19 +4027,15 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>181.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>配件</t>
-        </is>
-      </c>
+          <t>480.00฿</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -4047,7 +4043,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>YT7638092409979</t>
+          <t>ZY202464580877#3</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -4057,38 +4053,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>UN-INV260822-00010</t>
+          <t>UN-INV260901-00057</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18569-7-7</t>
+ รถ lot18655-9-9</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>16/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>16/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>15.00</t>
+          <t>27.10</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>0.0140</t>
+          <t>0.0567</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -4098,7 +4094,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>225.00฿</t>
+          <t>406.50฿</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -4108,7 +4104,7 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>补胎胶片/9件</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4114,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>435308000517585</t>
+          <t>S71090288685</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -4128,38 +4124,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>UN-INV260822-00010</t>
+          <t>UN-INV260831-00017</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18550-6-11</t>
+ รถ lot18634-7-3</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>29/08/2026</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>12.10</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>0.0032</t>
+          <t>0.0240</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -4169,7 +4165,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>54.00฿</t>
+          <t>181.50฿</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -4179,7 +4175,7 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>气门嘴</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -4189,7 +4185,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>710094401487</t>
+          <t>YT7638092409979</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -4205,52 +4201,52 @@
       <c r="E55" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18544-8-14</t>
+ รถ lot18569-7-7</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>16/08/2026</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>16/08/2026</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>107.10</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>0.4536</t>
+          <t>0.0140</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>225.00฿</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2,721.60฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>空的高压充气罐/一票10件，仓库实收到9件，已确认收到的9件先发</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -4260,7 +4256,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>773435675083665</t>
+          <t>435308000517585</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -4270,38 +4266,38 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>UN-INV260815-00046</t>
+          <t>UN-INV260822-00010</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18526-6-17</t>
+ รถ lot18550-6-11</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>13.10</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>0.0214</t>
+          <t>0.0032</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -4311,7 +4307,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>196.50฿</t>
+          <t>54.00฿</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -4321,7 +4317,7 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>补胎工具</t>
+          <t>气门嘴</t>
         </is>
       </c>
     </row>
@@ -4331,7 +4327,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>YT7637032206975</t>
+          <t>710094401487</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -4341,43 +4337,43 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>UN-INV260819-00010</t>
+          <t>UN-INV260822-00010</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>มอก.
- รถ lot18523-6-30</t>
+          <t>ธรรมดา
+ รถ lot18544-8-14</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>16/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>9.60</t>
+          <t>107.10</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>0.0316</t>
+          <t>0.4536</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4387,12 +4383,12 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>214.88฿</t>
+          <t>2,721.60฿</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>气动模具研磨机+配件</t>
+          <t>空的高压充气罐/一票10件，仓库实收到9件，已确认收到的9件先发</t>
         </is>
       </c>
     </row>
@@ -4402,7 +4398,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ZY202466648481#5</t>
+          <t>773435675083665</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -4418,32 +4414,32 @@
       <c r="E58" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18519-6-17</t>
+ รถ lot18526-6-17</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>15/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>16.10</t>
+          <t>13.10</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>0.0493</t>
+          <t>0.0214</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -4453,15 +4449,19 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>196.50฿</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>295.80฿</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>补胎工具</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -4469,7 +4469,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ZY202466648481#4</t>
+          <t>YT7637032206975</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4479,13 +4479,13 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>UN-INV260815-00046</t>
+          <t>UN-INV260819-00010</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>ธรรมดา
- รถ lot18519-6-16</t>
+          <t>มอก.
+ รถ lot18523-6-30</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -4500,17 +4500,17 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>15/08/2026</t>
+          <t>16/08/2026</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>20.50</t>
+          <t>9.60</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>0.0656</t>
+          <t>0.0316</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4525,10 +4525,14 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>393.60฿</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
+          <t>214.88฿</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>气动模具研磨机+配件</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -4536,7 +4540,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ZY202466648481#3</t>
+          <t>ZY202466648481#5</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4552,7 +4556,7 @@
       <c r="E60" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18519-6-15</t>
+ รถ lot18519-6-17</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -4572,12 +4576,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>15.70</t>
+          <t>16.10</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>0.0508</t>
+          <t>0.0493</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -4592,7 +4596,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>304.80฿</t>
+          <t>295.80฿</t>
         </is>
       </c>
       <c r="N60" t="inlineStr"/>
@@ -4603,7 +4607,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>ZY202466648481#2</t>
+          <t>ZY202466648481#4</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4619,7 +4623,7 @@
       <c r="E61" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18519-6-14</t>
+ รถ lot18519-6-16</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -4639,12 +4643,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>20.20</t>
+          <t>20.50</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>0.0660</t>
+          <t>0.0656</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -4659,7 +4663,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>396.00฿</t>
+          <t>393.60฿</t>
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
@@ -4670,7 +4674,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>ZY202466648481</t>
+          <t>ZY202466648481#3</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4686,7 +4690,7 @@
       <c r="E62" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18519-6-13</t>
+ รถ lot18519-6-15</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -4706,12 +4710,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>15.80</t>
+          <t>15.70</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>0.0522</t>
+          <t>0.0508</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -4726,14 +4730,10 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>313.20฿</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>补胎胶条/5件</t>
-        </is>
-      </c>
+          <t>304.80฿</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -4741,7 +4741,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>113204676267#2</t>
+          <t>ZY202466648481#2</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4757,32 +4757,32 @@
       <c r="E63" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18518-5-3</t>
+ รถ lot18519-6-14</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>15/08/2026</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>24.60</t>
+          <t>20.20</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>0.0608</t>
+          <t>0.0660</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>369.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>396.00฿</t>
         </is>
       </c>
       <c r="N63" t="inlineStr"/>
@@ -4808,7 +4808,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>113204676267</t>
+          <t>ZY202466648481</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4824,32 +4824,32 @@
       <c r="E64" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18518-5-2</t>
+ รถ lot18519-6-13</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>15/08/2026</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>25.00</t>
+          <t>15.80</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>0.0566</t>
+          <t>0.0522</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -4859,17 +4859,17 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>375.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>313.20฿</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>真空胎冷补胶片</t>
+          <t>补胎胶条/5件</t>
         </is>
       </c>
     </row>
@@ -4879,7 +4879,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>910061892464#2</t>
+          <t>113204676267#2</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4895,32 +4895,32 @@
       <c r="E65" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18505-5-23</t>
+ รถ lot18518-5-3</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>30.40</t>
+          <t>24.60</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>0.0523</t>
+          <t>0.0608</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -4930,7 +4930,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>456.00฿</t>
+          <t>369.00฿</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>910061892464</t>
+          <t>113204676267</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4962,32 +4962,32 @@
       <c r="E66" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18505-5-22</t>
+ รถ lot18518-5-2</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>15.90</t>
+          <t>25.00</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>0.0353</t>
+          <t>0.0566</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>238.50฿</t>
+          <t>375.00฿</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -5007,7 +5007,7 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>记号蜡笔</t>
+          <t>真空胎冷补胶片</t>
         </is>
       </c>
     </row>
@@ -5017,7 +5017,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>773434709817985</t>
+          <t>910061892464#2</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -5027,38 +5027,38 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>UN-INV260819-00010</t>
+          <t>UN-INV260815-00046</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18535-8</t>
+ รถ lot18505-5-23</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>16/08/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>30.40</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>0.0184</t>
+          <t>0.0523</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -5068,19 +5068,15 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>456.00฿</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>110.40฿</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr">
-        <is>
-          <t>锅具 二次包装货物变形</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -5088,7 +5084,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>435295775627304</t>
+          <t>910061892464</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -5098,38 +5094,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>UN-INV260811-00012</t>
+          <t>UN-INV260815-00046</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18492-2</t>
+ รถ lot18505-5-22</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>5.30</t>
+          <t>15.90</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>0.0090</t>
+          <t>0.0353</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -5139,7 +5135,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>79.50฿</t>
+          <t>238.50฿</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -5149,7 +5145,7 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>配件 破损件</t>
+          <t>记号蜡笔</t>
         </is>
       </c>
     </row>
@@ -5159,7 +5155,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>YT7636332367470</t>
+          <t>773434709817985</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -5169,38 +5165,38 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>UN-INV260811-00012</t>
+          <t>UN-INV260819-00010</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18487-2-27</t>
+ รถ lot18535-8</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>16/08/2026</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>0.0004</t>
+          <t>0.0184</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -5215,12 +5211,12 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>10.00฿</t>
+          <t>110.40฿</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>立牌</t>
+          <t>锅具 二次包装货物变形</t>
         </is>
       </c>
     </row>
@@ -5230,7 +5226,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>S35386280517#2</t>
+          <t>435295775627304</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -5246,32 +5242,32 @@
       <c r="E70" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18475-24</t>
+ รถ lot18492-2</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>8.80</t>
+          <t>5.30</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>0.0045</t>
+          <t>0.0090</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -5281,7 +5277,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>132.00฿</t>
+          <t>79.50฿</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -5289,7 +5285,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N70" t="inlineStr"/>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>配件 破损件</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -5297,7 +5297,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>S35386280517</t>
+          <t>YT7636332367470</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -5313,52 +5313,52 @@
       <c r="E71" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18475-23</t>
+ รถ lot18487-2-27</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>103.50</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>0.2236</t>
+          <t>0.0004</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>1,552.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10.00฿</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>气门嘴 顺心捷达，一票16件</t>
+          <t>立牌</t>
         </is>
       </c>
     </row>
@@ -5368,7 +5368,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>YT7635787693833</t>
+          <t>S35386280517#2</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -5384,7 +5384,7 @@
       <c r="E72" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18473-6-41</t>
+ รถ lot18475-24</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -5399,17 +5399,17 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>13.80</t>
+          <t>8.80</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>0.0432</t>
+          <t>0.0045</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -5419,19 +5419,15 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>132.00฿</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>259.20฿</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr">
-        <is>
-          <t>气压表/面单没有代码</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -5439,7 +5435,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>ZY202465806614</t>
+          <t>S35386280517</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -5449,58 +5445,58 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>UN-INV260807-00009</t>
+          <t>UN-INV260811-00012</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>มอก.
- รถ lot18466-5-51</t>
+          <t>ธรรมดา
+ รถ lot18475-23</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>11.30</t>
+          <t>103.50</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>0.0655</t>
+          <t>0.2236</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1,552.50฿</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>445.40฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>电子数显胎压枪</t>
+          <t>气门嘴 顺心捷达，一票16件</t>
         </is>
       </c>
     </row>
@@ -5510,7 +5506,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>113177184579#7</t>
+          <t>YT7635787693833</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -5520,38 +5516,38 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>UN-INV260807-00009</t>
+          <t>UN-INV260811-00012</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-17</t>
+ รถ lot18473-6-41</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>9.70</t>
+          <t>13.80</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>0.0305</t>
+          <t>0.0432</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -5566,10 +5562,14 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>183.00฿</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr"/>
+          <t>259.20฿</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>气压表/面单没有代码</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>113177184579#5</t>
+          <t>ZY202465806614</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -5592,18 +5592,18 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>ธรรมดา
- รถ lot18463-16</t>
+          <t>มอก.
+ รถ lot18466-5-51</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>15.00</t>
+          <t>11.30</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>0.0137</t>
+          <t>0.0655</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -5628,15 +5628,19 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>225.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr"/>
+          <t>445.40฿</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>电子数显胎压枪</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -5644,7 +5648,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>113177184579#4</t>
+          <t>113177184579#7</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5660,7 +5664,7 @@
       <c r="E76" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-15</t>
+ รถ lot18463-17</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -5680,12 +5684,12 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>7.30</t>
+          <t>9.70</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>0.0235</t>
+          <t>0.0305</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -5700,7 +5704,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>141.00฿</t>
+          <t>183.00฿</t>
         </is>
       </c>
       <c r="N76" t="inlineStr"/>
@@ -5711,7 +5715,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>113177184579#3</t>
+          <t>113177184579#5</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -5727,7 +5731,7 @@
       <c r="E77" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-14</t>
+ รถ lot18463-16</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -5747,12 +5751,12 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>11.90</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>0.0302</t>
+          <t>0.0137</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -5762,12 +5766,12 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>225.00฿</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>181.20฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N77" t="inlineStr"/>
@@ -5778,7 +5782,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>113177184579#6</t>
+          <t>113177184579#4</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -5794,7 +5798,7 @@
       <c r="E78" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-13</t>
+ รถ lot18463-15</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -5814,12 +5818,12 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>26.10</t>
+          <t>7.30</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>0.0673</t>
+          <t>0.0235</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -5834,7 +5838,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>403.80฿</t>
+          <t>141.00฿</t>
         </is>
       </c>
       <c r="N78" t="inlineStr"/>
@@ -5845,7 +5849,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>435289604798626</t>
+          <t>113177184579#3</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -5861,7 +5865,7 @@
       <c r="E79" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18462-6-6</t>
+ รถ lot18463-14</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -5871,7 +5875,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5881,12 +5885,12 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>9.60</t>
+          <t>11.90</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>0.0090</t>
+          <t>0.0302</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -5896,19 +5900,15 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>144.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr">
-        <is>
-          <t>螺丝配件</t>
-        </is>
-      </c>
+          <t>181.20฿</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -5916,7 +5916,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>113177184579#2</t>
+          <t>113177184579#6</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -5932,7 +5932,7 @@
       <c r="E80" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-12</t>
+ รถ lot18463-13</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -5952,12 +5952,12 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>5.30</t>
+          <t>26.10</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>0.0635</t>
+          <t>0.0673</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -5972,7 +5972,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>381.00฿</t>
+          <t>403.80฿</t>
         </is>
       </c>
       <c r="N80" t="inlineStr"/>
@@ -5983,7 +5983,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>113177184579</t>
+          <t>435289604798626</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -5999,7 +5999,7 @@
       <c r="E81" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-11</t>
+ รถ lot18462-6-6</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -6009,7 +6009,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -6019,12 +6019,12 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>13.30</t>
+          <t>9.60</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>0.1176</t>
+          <t>0.0090</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -6034,17 +6034,17 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>144.00฿</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>705.60฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>蘑菇钉补胎贴</t>
+          <t>螺丝配件</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>435289604798722</t>
+          <t>113177184579#2</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -6070,7 +6070,7 @@
       <c r="E82" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18462-3</t>
+ รถ lot18463-12</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -6080,7 +6080,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -6090,12 +6090,12 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>4.30</t>
+          <t>5.30</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>0.0029</t>
+          <t>0.0635</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -6105,19 +6105,15 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>64.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr">
-        <is>
-          <t>气门嘴</t>
-        </is>
-      </c>
+          <t>381.00฿</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -6125,7 +6121,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>ZY202471573119#2</t>
+          <t>113177184579</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -6141,7 +6137,7 @@
       <c r="E83" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-6</t>
+ รถ lot18463-11</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -6161,12 +6157,12 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>8.70</t>
+          <t>13.30</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>0.0441</t>
+          <t>0.1176</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -6181,10 +6177,14 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>264.60฿</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr"/>
+          <t>705.60฿</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>蘑菇钉补胎贴</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -6192,7 +6192,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>ZY202471573119</t>
+          <t>435289604798722</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -6208,7 +6208,7 @@
       <c r="E84" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-5</t>
+ รถ lot18462-3</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -6218,7 +6218,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -6228,12 +6228,12 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>11.90</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>0.0832</t>
+          <t>0.0029</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -6243,17 +6243,17 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>64.50฿</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>499.20฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>蘑菇钉补胎</t>
+          <t>气门嘴</t>
         </is>
       </c>
     </row>
@@ -6263,7 +6263,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>YT7635427281240</t>
+          <t>ZY202471573119#2</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -6279,7 +6279,7 @@
       <c r="E85" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18458-21</t>
+ รถ lot18463-6</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -6299,12 +6299,12 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>8.70</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>0.0117</t>
+          <t>0.0441</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -6319,14 +6319,10 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>70.20฿</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr">
-        <is>
-          <t>气阀</t>
-        </is>
-      </c>
+          <t>264.60฿</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -6334,7 +6330,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>79021262374216</t>
+          <t>ZY202471573119</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -6344,38 +6340,38 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>UN-INV260804-00019</t>
+          <t>UN-INV260807-00009</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18435-5-73</t>
+ รถ lot18463-5</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>12.20</t>
+          <t>11.90</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>0.0352</t>
+          <t>0.0832</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -6390,12 +6386,12 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>211.20฿</t>
+          <t>499.20฿</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>加长弯头</t>
+          <t>蘑菇钉补胎</t>
         </is>
       </c>
     </row>
@@ -6405,7 +6401,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>113162219964#3</t>
+          <t>YT7635427281240</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -6415,38 +6411,38 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>UN-INV260804-00019</t>
+          <t>UN-INV260807-00009</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18434-9-28</t>
+ รถ lot18458-21</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>18.70</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>0.0443</t>
+          <t>0.0117</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -6456,15 +6452,19 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>280.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr"/>
+          <t>70.20฿</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>气阀</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -6472,7 +6472,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>113162219964#2</t>
+          <t>79021262374216</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -6488,17 +6488,17 @@
       <c r="E88" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18434-9-27</t>
+ รถ lot18435-5-73</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>22.90</t>
+          <t>12.20</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>0.0522</t>
+          <t>0.0352</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -6523,15 +6523,19 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>343.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr"/>
+          <t>211.20฿</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>加长弯头</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -6539,7 +6543,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>113162219964</t>
+          <t>113162219964#3</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -6555,7 +6559,7 @@
       <c r="E89" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18434-9-26</t>
+ รถ lot18434-9-28</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -6575,12 +6579,12 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>25.60</t>
+          <t>18.70</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>0.0574</t>
+          <t>0.0443</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -6590,7 +6594,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>384.00฿</t>
+          <t>280.50฿</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -6598,11 +6602,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N89" t="inlineStr">
-        <is>
-          <t>补胎胶片/3件</t>
-        </is>
-      </c>
+      <c r="N89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -6610,7 +6610,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>113158800045#2</t>
+          <t>113162219964#2</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -6626,32 +6626,32 @@
       <c r="E90" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18427-7-3</t>
+ รถ lot18434-9-27</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>26/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>26/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>26.30</t>
+          <t>22.90</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>0.0377</t>
+          <t>0.0522</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -6661,7 +6661,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>394.50฿</t>
+          <t>343.50฿</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -6677,7 +6677,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>113158800045</t>
+          <t>113162219964</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -6693,32 +6693,32 @@
       <c r="E91" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18427-7-2</t>
+ รถ lot18434-9-26</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>26/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>26/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>26.50</t>
+          <t>25.60</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>0.0379</t>
+          <t>0.0574</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -6728,7 +6728,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>397.50฿</t>
+          <t>384.00฿</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -6738,7 +6738,7 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>塑料配件/2件</t>
+          <t>补胎胶片/3件</t>
         </is>
       </c>
     </row>
@@ -6748,7 +6748,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>YT2550516723148</t>
+          <t>113158800045#2</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -6764,32 +6764,32 @@
       <c r="E92" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18398-3-10</t>
+ รถ lot18427-7-3</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>22/07/2026</t>
+          <t>26/07/2026</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>23/07/2026</t>
+          <t>26/07/2026</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>26.30</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>0.0127</t>
+          <t>0.0377</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -6799,19 +6799,15 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>394.50฿</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>76.20฿</t>
-        </is>
-      </c>
-      <c r="N92" t="inlineStr">
-        <is>
-          <t>硅胶风管</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -6819,7 +6815,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>ZY202467269952#4</t>
+          <t>113158800045</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -6829,38 +6825,38 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>UN-INV260724-00013</t>
+          <t>UN-INV260804-00019</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18314-8-30</t>
+ รถ lot18427-7-2</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>11/07/2026</t>
+          <t>26/07/2026</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>12/07/2026</t>
+          <t>26/07/2026</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>15.50</t>
+          <t>26.50</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>0.0492</t>
+          <t>0.0379</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -6870,15 +6866,19 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>397.50฿</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>295.20฿</t>
-        </is>
-      </c>
-      <c r="N93" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>塑料配件/2件</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -6886,7 +6886,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>ZY202467269952#3</t>
+          <t>YT2550516723148</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -6896,38 +6896,38 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>UN-INV260724-00013</t>
+          <t>UN-INV260804-00019</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18314-8-29</t>
+ รถ lot18398-3-10</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>11/07/2026</t>
+          <t>22/07/2026</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>12/07/2026</t>
+          <t>23/07/2026</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>12.50</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>0.0300</t>
+          <t>0.0127</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -6937,15 +6937,19 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>187.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N94" t="inlineStr"/>
+          <t>76.20฿</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>硅胶风管</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -6953,7 +6957,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>ZY202467269952#2</t>
+          <t>ZY202467269952#4</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -6969,7 +6973,7 @@
       <c r="E95" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18314-8-28</t>
+ รถ lot18314-8-30</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -6994,7 +6998,7 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>0.0508</t>
+          <t>0.0492</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -7009,7 +7013,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>304.80฿</t>
+          <t>295.20฿</t>
         </is>
       </c>
       <c r="N95" t="inlineStr"/>
@@ -7020,7 +7024,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>ZY202467269952</t>
+          <t>ZY202467269952#3</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -7036,7 +7040,7 @@
       <c r="E96" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18314-8-27</t>
+ รถ lot18314-8-29</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -7056,12 +7060,12 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>10.50</t>
+          <t>12.50</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>0.0355</t>
+          <t>0.0300</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -7071,19 +7075,15 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>187.50฿</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>213.00฿</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr">
-        <is>
-          <t>补胎胶片/4件</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -7091,7 +7091,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>773431041004504</t>
+          <t>ZY202467269952#2</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -7107,7 +7107,7 @@
       <c r="E97" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18314-5-13</t>
+ รถ lot18314-8-28</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -7127,12 +7127,12 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>15.50</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>0.0044</t>
+          <t>0.0508</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -7147,14 +7147,10 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>26.40฿</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr">
-        <is>
-          <t>门底条</t>
-        </is>
-      </c>
+          <t>304.80฿</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -7162,7 +7158,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>ZY202467269844#2</t>
+          <t>ZY202467269952</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -7172,38 +7168,38 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>UN-INV260717-00013</t>
+          <t>UN-INV260724-00013</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18288-8-41</t>
+ รถ lot18314-8-27</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>11/07/2026</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>12/07/2026</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>21.00</t>
+          <t>10.50</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>0.0660</t>
+          <t>0.0355</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -7218,10 +7214,14 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>396.00฿</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr"/>
+          <t>213.00฿</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>补胎胶片/4件</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -7229,7 +7229,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>ZY202467269844#5</t>
+          <t>773431041004504</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -7239,38 +7239,38 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>UN-INV260717-00013</t>
+          <t>UN-INV260724-00013</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18288-8-40</t>
+ รถ lot18314-5-13</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>11/07/2026</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>12/07/2026</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>27.90</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>0.0800</t>
+          <t>0.0044</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -7285,10 +7285,14 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>480.00฿</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr"/>
+          <t>26.40฿</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>门底条</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -7296,7 +7300,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>ZY202467269844#3</t>
+          <t>ZY202467269844#2</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -7312,7 +7316,7 @@
       <c r="E100" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18288-8-39</t>
+ รถ lot18288-8-41</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -7332,12 +7336,12 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>15.60</t>
+          <t>21.00</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>0.0496</t>
+          <t>0.0660</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -7352,7 +7356,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>297.60฿</t>
+          <t>396.00฿</t>
         </is>
       </c>
       <c r="N100" t="inlineStr"/>
@@ -7363,7 +7367,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>ZY202467269844#4</t>
+          <t>ZY202467269844#5</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -7379,7 +7383,7 @@
       <c r="E101" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18288-8-38</t>
+ รถ lot18288-8-40</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -7399,12 +7403,12 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>16.00</t>
+          <t>27.90</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>0.0504</t>
+          <t>0.0800</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -7419,7 +7423,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>302.40฿</t>
+          <t>480.00฿</t>
         </is>
       </c>
       <c r="N101" t="inlineStr"/>

--- a/cargo_packages_p1-5.xlsx
+++ b/cargo_packages_p1-5.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>113348267192#2</t>
+          <t>760246657062</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -522,17 +522,17 @@
       <c r="E2" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18795-2-7</t>
+ รถ lot18799-7-3</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -542,12 +542,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>28.10</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.0628</t>
+          <t>0.0005</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -557,15 +557,19 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>421.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>10.00฿</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>气门嘴，轮胎修补工具，气门芯宣传册</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -573,7 +577,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>113348267192</t>
+          <t>113348267192#2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -589,7 +593,7 @@
       <c r="E3" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18795-2-6</t>
+ รถ lot18795-2-7</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -609,12 +613,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>19.50</t>
+          <t>28.10</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.0505</t>
+          <t>0.0628</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -624,19 +628,15 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>421.50฿</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>303.00฿</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>补胎胶片</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -644,7 +644,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ZY202472578299</t>
+          <t>113348267192</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -660,17 +660,17 @@
       <c r="E4" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18758-7-43</t>
+ รถ lot18795-2-6</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -680,17 +680,17 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>47.40</t>
+          <t>19.50</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.1603</t>
+          <t>0.0505</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -700,12 +700,12 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>961.20฿</t>
+          <t>303.00฿</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>补胎贴，3件</t>
+          <t>补胎胶片</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>773440822655698</t>
+          <t>ZY202472578299</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -731,7 +731,7 @@
       <c r="E5" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18758-4-31</t>
+ รถ lot18758-7-43</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -751,32 +751,32 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>47.40</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.0022</t>
+          <t>0.1603</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>18.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>961.20฿</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>钻头</t>
+          <t>补胎贴，3件</t>
         </is>
       </c>
     </row>
@@ -786,7 +786,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>YT7642998390994</t>
+          <t>773440822655698</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -802,7 +802,7 @@
       <c r="E6" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18769-3-57</t>
+ รถ lot18758-4-31</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -812,7 +812,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -822,12 +822,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5.80</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.0070</t>
+          <t>0.0022</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>87.00฿</t>
+          <t>18.00฿</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>钻头</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DPK212614057101</t>
+          <t>YT7642998390994</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -873,32 +873,32 @@
       <c r="E7" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18749-4-3</t>
+ รถ lot18769-3-57</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>9.60</t>
+          <t>5.80</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.0060</t>
+          <t>0.0070</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>144.00฿</t>
+          <t>87.00฿</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>轮胎气门嘴</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>79031204783305</t>
+          <t>DPK212614057101</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -944,7 +944,7 @@
       <c r="E8" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18744-6-15</t>
+ รถ lot18749-4-3</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -964,12 +964,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>9.60</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.0020</t>
+          <t>0.0060</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>39.00฿</t>
+          <t>144.00฿</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>轮胎气门嘴</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>435342988112655</t>
+          <t>79031204783305</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1015,17 +1015,17 @@
       <c r="E9" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18743-3-34</t>
+ รถ lot18744-6-15</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1035,12 +1035,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.0014</t>
+          <t>0.0020</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1050,17 +1050,17 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>39.00฿</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>10.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>橡胶垫圈</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -1070,7 +1070,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>435343890137834</t>
+          <t>435342988112655</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1086,7 +1086,7 @@
       <c r="E10" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18743-7-25</t>
+ รถ lot18743-3-34</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>21.40</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.0080</t>
+          <t>0.0014</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1121,17 +1121,17 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>321.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10.00฿</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>扒胎机包胶撬棍</t>
+          <t>橡胶垫圈</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>YT7642670434639</t>
+          <t>435343890137834</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1157,7 +1157,7 @@
       <c r="E11" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18743-2-8</t>
+ รถ lot18743-7-25</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1177,12 +1177,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>21.40</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.0010</t>
+          <t>0.0080</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>12.00฿</t>
+          <t>321.00฿</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>片片</t>
+          <t>扒胎机包胶撬棍</t>
         </is>
       </c>
     </row>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>93015797092</t>
+          <t>YT7642670434639</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1222,18 +1222,18 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>UN-INV260914-00014</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18735-4-40</t>
+ รถ lot18743-2-8</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1243,17 +1243,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>12/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>8.60</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0.0148</t>
+          <t>0.0010</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>129.00฿</t>
+          <t>12.00฿</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>仪表</t>
+          <t>片片</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>YT7642390374765</t>
+          <t>93015797092</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1293,13 +1293,13 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>UN-INV260914-00015</t>
+          <t>UN-INV260914-00014</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18735-4-20</t>
+ รถ lot18735-4-40</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>20.80</t>
+          <t>8.60</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0.0598</t>
+          <t>0.0148</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>129.00฿</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>358.80฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>打磨机</t>
+          <t>仪表</t>
         </is>
       </c>
     </row>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>435342255104130</t>
+          <t>YT7642390374765</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1364,13 +1364,13 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>UN-INV260914-00014</t>
+          <t>UN-INV260914-00015</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18735-43</t>
+ รถ lot18735-4-20</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1390,12 +1390,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>4.90</t>
+          <t>20.80</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.0172</t>
+          <t>0.0598</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1410,12 +1410,12 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>103.20฿</t>
+          <t>358.80฿</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>轮毂保护套</t>
+          <t>打磨机</t>
         </is>
       </c>
     </row>
@@ -1425,7 +1425,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>773440312345715</t>
+          <t>435342255104130</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1441,7 +1441,7 @@
       <c r="E15" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18735-3-78</t>
+ รถ lot18735-43</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1461,12 +1461,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>4.90</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.0013</t>
+          <t>0.0172</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1476,17 +1476,17 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>19.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>103.20฿</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>轮毂保护套</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>773440291470393</t>
+          <t>773440312345715</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1512,7 +1512,7 @@
       <c r="E16" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18735-34</t>
+ รถ lot18735-3-78</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1532,12 +1532,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>0.0029</t>
+          <t>0.0013</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>48.00฿</t>
+          <t>19.50฿</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>球阀</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -1567,7 +1567,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>435342261175750</t>
+          <t>773440291470393</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1577,13 +1577,13 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>UN-INV260914-00015</t>
+          <t>UN-INV260914-00014</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18736-13</t>
+ รถ lot18735-34</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1593,7 +1593,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1603,12 +1603,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>13.90</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.0137</t>
+          <t>0.0029</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>208.50฿</t>
+          <t>48.00฿</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>球阀</t>
         </is>
       </c>
     </row>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ZY202461195200</t>
+          <t>435342261175750</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1654,7 +1654,7 @@
       <c r="E18" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18728-7-13</t>
+ รถ lot18736-13</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1669,17 +1669,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>13/09/2026</t>
+          <t>12/09/2026</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>47.40</t>
+          <t>13.90</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>0.0116</t>
+          <t>0.0137</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>711.00฿</t>
+          <t>208.50฿</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1709,7 +1709,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>79030687835952</t>
+          <t>ZY202461195200</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1719,13 +1719,13 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>UN-INV260914-00014</t>
+          <t>UN-INV260914-00015</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18728-3-64</t>
+ รถ lot18728-7-13</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1745,12 +1745,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>4.30</t>
+          <t>47.40</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>0.0030</t>
+          <t>0.0116</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>64.50฿</t>
+          <t>711.00฿</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>接头配件</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>LJ20722214#3</t>
+          <t>79030687835952</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1790,38 +1790,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>UN-INV260912-00011</t>
+          <t>UN-INV260914-00014</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18726-7-8</t>
+ รถ lot18728-3-64</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>13/09/2026</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>14.00</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0.0171</t>
+          <t>0.0030</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1831,7 +1831,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>210.00฿</t>
+          <t>64.50฿</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1839,7 +1839,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>接头配件</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1847,7 +1851,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>LJ20722214#2</t>
+          <t>LJ20722214#3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1863,7 +1867,7 @@
       <c r="E21" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18726-7-7</t>
+ รถ lot18726-7-8</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1883,12 +1887,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>11.90</t>
+          <t>14.00</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.0089</t>
+          <t>0.0171</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1898,7 +1902,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>178.50฿</t>
+          <t>210.00฿</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1914,7 +1918,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>LJ20722214</t>
+          <t>LJ20722214#2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1930,7 +1934,7 @@
       <c r="E22" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18726-7-6</t>
+ รถ lot18726-7-7</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1950,12 +1954,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>16.00</t>
+          <t>11.90</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.0144</t>
+          <t>0.0089</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1965,7 +1969,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>240.00฿</t>
+          <t>178.50฿</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1973,11 +1977,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>电板套筒配件/3件</t>
-        </is>
-      </c>
+      <c r="N22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1985,7 +1985,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>YT7641966426761</t>
+          <t>LJ20722214</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2001,17 +2001,17 @@
       <c r="E23" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18714-9-23</t>
+ รถ lot18726-7-6</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2021,12 +2021,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>13.60</t>
+          <t>16.00</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.0422</t>
+          <t>0.0144</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2036,17 +2036,17 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>240.00฿</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>253.20฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>带表汽车轮胎打气嘴</t>
+          <t>电板套筒配件/3件</t>
         </is>
       </c>
     </row>
@@ -2056,7 +2056,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ZY202471681117#2</t>
+          <t>YT7641966426761</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2072,7 +2072,7 @@
       <c r="E24" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18714-9-8</t>
+ รถ lot18714-9-23</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2092,12 +2092,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>11.80</t>
+          <t>13.60</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.0832</t>
+          <t>0.0422</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2112,10 +2112,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>499.20฿</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
+          <t>253.20฿</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>带表汽车轮胎打气嘴</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -2123,7 +2127,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ZY202471681117</t>
+          <t>ZY202471681117#2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2139,7 +2143,7 @@
       <c r="E25" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18714-9-7</t>
+ รถ lot18714-9-8</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2159,12 +2163,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>7.70</t>
+          <t>11.80</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.0493</t>
+          <t>0.0832</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2179,14 +2183,10 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>295.80฿</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>补胎胶片/2件</t>
-        </is>
-      </c>
+          <t>499.20฿</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>302285502767#2</t>
+          <t>ZY202471681117</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2210,7 +2210,7 @@
       <c r="E26" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18714-8-10</t>
+ รถ lot18714-9-7</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>33.70</t>
+          <t>7.70</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>0.0145</t>
+          <t>0.0493</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2245,15 +2245,19 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>505.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
+          <t>295.80฿</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>补胎胶片/2件</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2261,7 +2265,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>302285502767</t>
+          <t>302285502767#2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2277,7 +2281,7 @@
       <c r="E27" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18714-8-9</t>
+ รถ lot18714-8-10</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2297,12 +2301,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>23.40</t>
+          <t>33.70</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.0123</t>
+          <t>0.0145</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2312,7 +2316,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>351.00฿</t>
+          <t>505.50฿</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2320,11 +2324,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>扳手</t>
-        </is>
-      </c>
+      <c r="N27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2332,7 +2332,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>LJ20716178#2</t>
+          <t>302285502767</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2342,18 +2342,18 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>UN-INV260911-00013</t>
+          <t>UN-INV260912-00011</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18713-6-65</t>
+ รถ lot18714-8-9</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2363,17 +2363,17 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>19.50</t>
+          <t>23.40</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.0075</t>
+          <t>0.0123</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2383,7 +2383,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>292.50฿</t>
+          <t>351.00฿</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2391,7 +2391,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>扳手</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2399,7 +2403,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>LJ20716178</t>
+          <t>LJ20716178#2</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2415,7 +2419,7 @@
       <c r="E29" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18713-6-64</t>
+ รถ lot18713-6-65</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2435,7 +2439,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>19.60</t>
+          <t>19.50</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2450,7 +2454,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>294.00฿</t>
+          <t>292.50฿</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2458,11 +2462,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>配件</t>
-        </is>
-      </c>
+      <c r="N29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>435338972466812</t>
+          <t>LJ20716178</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2486,7 +2486,7 @@
       <c r="E30" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18710-6-35</t>
+ รถ lot18713-6-64</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>13.10</t>
+          <t>19.60</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.0624</t>
+          <t>0.0075</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2521,17 +2521,17 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>294.00฿</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>374.40฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>修补工具</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -2541,7 +2541,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>435334324045675</t>
+          <t>435338972466812</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2551,38 +2551,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>UN-INV260908-00009</t>
+          <t>UN-INV260911-00013</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18696-14</t>
+ รถ lot18710-6-35</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>10.80</t>
+          <t>13.10</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.0088</t>
+          <t>0.0624</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2592,17 +2592,17 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>162.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>374.40฿</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>修补工具</t>
         </is>
       </c>
     </row>
@@ -2612,7 +2612,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>YT7641276428798</t>
+          <t>435334324045675</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2628,7 +2628,7 @@
       <c r="E32" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18697-11</t>
+ รถ lot18696-14</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2648,12 +2648,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>9.50</t>
+          <t>10.80</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.0296</t>
+          <t>0.0088</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2663,12 +2663,12 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>162.00฿</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>177.60฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>79029430531776</t>
+          <t>YT7641276428798</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2693,18 +2693,18 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>UN-INV260907-00015</t>
+          <t>UN-INV260908-00009</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18689-26</t>
+ รถ lot18697-11</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2714,17 +2714,17 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>9.50</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.0135</t>
+          <t>0.0296</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>81.00฿</t>
+          <t>177.60฿</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>卡套</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>113282578128#2</t>
+          <t>79029430531776</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2770,17 +2770,17 @@
       <c r="E34" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18683-4</t>
+ รถ lot18689-26</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2790,12 +2790,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>38.00</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.1601</t>
+          <t>0.0135</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2810,10 +2810,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>960.60฿</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
+          <t>81.00฿</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>卡套</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2821,7 +2825,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>113282578128</t>
+          <t>113282578128#2</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2837,7 +2841,7 @@
       <c r="E35" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18683-3</t>
+ รถ lot18683-4</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2857,12 +2861,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>27.50</t>
+          <t>38.00</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.1566</t>
+          <t>0.1601</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2877,14 +2881,10 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>939.60฿</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>压条取出器 一票两件破损件</t>
-        </is>
-      </c>
+          <t>960.60฿</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2892,7 +2892,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>82730128600#3</t>
+          <t>113282578128</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2908,12 +2908,12 @@
       <c r="E36" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18678-6-21</t>
+ รถ lot18683-3</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>30/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2928,12 +2928,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>33.00</t>
+          <t>27.50</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.0122</t>
+          <t>0.1566</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2943,15 +2943,19 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>495.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
+          <t>939.60฿</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>压条取出器 一票两件破损件</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2959,7 +2963,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>82730128600#2</t>
+          <t>82730128600#3</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2975,7 +2979,7 @@
       <c r="E37" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18678-6-20</t>
+ รถ lot18678-6-21</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2995,12 +2999,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>27.60</t>
+          <t>33.00</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.0095</t>
+          <t>0.0122</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -3010,7 +3014,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>414.00฿</t>
+          <t>495.00฿</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3026,7 +3030,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>82730128600</t>
+          <t>82730128600#2</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3042,7 +3046,7 @@
       <c r="E38" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18678-6-19</t>
+ รถ lot18678-6-20</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -3062,12 +3066,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>28.10</t>
+          <t>27.60</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.0118</t>
+          <t>0.0095</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -3077,7 +3081,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>421.50฿</t>
+          <t>414.00฿</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3085,11 +3089,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>五金配件/3件</t>
-        </is>
-      </c>
+      <c r="N38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>113278387839#3</t>
+          <t>82730128600</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3107,38 +3107,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>UN-INV260903-00023</t>
+          <t>UN-INV260907-00015</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18663-8-3</t>
+ รถ lot18678-6-19</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>30/08/2026</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>25.30</t>
+          <t>28.10</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.0404</t>
+          <t>0.0118</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>379.50฿</t>
+          <t>421.50฿</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3156,7 +3156,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>五金配件/3件</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -3164,7 +3168,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>113278387839#2</t>
+          <t>113278387839#3</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3180,7 +3184,7 @@
       <c r="E40" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18663-8-2</t>
+ รถ lot18663-8-3</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -3200,12 +3204,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>26.10</t>
+          <t>25.30</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.0304</t>
+          <t>0.0404</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -3215,7 +3219,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>391.50฿</t>
+          <t>379.50฿</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -3231,7 +3235,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>113278387839</t>
+          <t>113278387839#2</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3247,7 +3251,7 @@
       <c r="E41" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18663-8-1</t>
+ รถ lot18663-8-2</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -3267,12 +3271,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>9.10</t>
+          <t>26.10</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.0144</t>
+          <t>0.0304</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -3282,7 +3286,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>136.50฿</t>
+          <t>391.50฿</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -3290,11 +3294,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>配件/3件</t>
-        </is>
-      </c>
+      <c r="N41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -3302,7 +3302,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>113276098937#3</t>
+          <t>113278387839</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3312,38 +3312,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>UN-INV260901-00057</t>
+          <t>UN-INV260903-00023</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-45</t>
+ รถ lot18663-8-1</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>17.80</t>
+          <t>9.10</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.0302</t>
+          <t>0.0144</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3353,7 +3353,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>267.00฿</t>
+          <t>136.50฿</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3361,7 +3361,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>配件/3件</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -3369,7 +3373,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>113276098937#2</t>
+          <t>113276098937#3</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3385,7 +3389,7 @@
       <c r="E43" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-44</t>
+ รถ lot18655-9-45</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -3405,12 +3409,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>10.90</t>
+          <t>17.80</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.0313</t>
+          <t>0.0302</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3420,12 +3424,12 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>267.00฿</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>187.80฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -3436,7 +3440,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>113276098937</t>
+          <t>113276098937#2</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3452,7 +3456,7 @@
       <c r="E44" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-43</t>
+ รถ lot18655-9-44</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -3472,12 +3476,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>33.60</t>
+          <t>10.90</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.0825</t>
+          <t>0.0313</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3487,19 +3491,15 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>504.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>补胎胶片+配件/3件</t>
-        </is>
-      </c>
+          <t>187.80฿</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -3507,7 +3507,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ZY202464580877#4</t>
+          <t>113276098937</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3523,7 +3523,7 @@
       <c r="E45" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-17</t>
+ รถ lot18655-9-43</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>20.10</t>
+          <t>33.60</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.0466</t>
+          <t>0.0825</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3558,7 +3558,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>301.50฿</t>
+          <t>504.00฿</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3566,7 +3566,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>补胎胶片+配件/3件</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -3574,7 +3578,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ZY202464580877#7</t>
+          <t>ZY202464580877#4</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3590,7 +3594,7 @@
       <c r="E46" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-16</t>
+ รถ lot18655-9-17</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -3610,12 +3614,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>16.60</t>
+          <t>20.10</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>0.0430</t>
+          <t>0.0466</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3625,12 +3629,12 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>301.50฿</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>258.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
@@ -3641,7 +3645,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ZY202464580877#2</t>
+          <t>ZY202464580877#7</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3657,7 +3661,7 @@
       <c r="E47" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-15</t>
+ รถ lot18655-9-16</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -3677,12 +3681,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>25.10</t>
+          <t>16.60</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>0.0483</t>
+          <t>0.0430</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3692,12 +3696,12 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>376.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>258.00฿</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
@@ -3708,7 +3712,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>ZY202464580877#8</t>
+          <t>ZY202464580877#2</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3724,7 +3728,7 @@
       <c r="E48" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-14</t>
+ รถ lot18655-9-15</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -3744,12 +3748,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>28.90</t>
+          <t>25.10</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>0.0800</t>
+          <t>0.0483</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3759,12 +3763,12 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>376.50฿</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>480.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
@@ -3775,7 +3779,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ZY202464580877#6</t>
+          <t>ZY202464580877#8</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3791,7 +3795,7 @@
       <c r="E49" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-13</t>
+ รถ lot18655-9-14</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3811,12 +3815,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>20.90</t>
+          <t>28.90</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>0.0534</t>
+          <t>0.0800</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3831,7 +3835,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>320.40฿</t>
+          <t>480.00฿</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
@@ -3842,7 +3846,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ZY202464580877#5</t>
+          <t>ZY202464580877#6</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3858,7 +3862,7 @@
       <c r="E50" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-12</t>
+ รถ lot18655-9-13</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3878,12 +3882,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>26.20</t>
+          <t>20.90</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>0.0535</t>
+          <t>0.0534</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3893,12 +3897,12 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>393.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>320.40฿</t>
         </is>
       </c>
       <c r="N50" t="inlineStr"/>
@@ -3909,7 +3913,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ZY202464580877</t>
+          <t>ZY202464580877#5</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3925,7 +3929,7 @@
       <c r="E51" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-11</t>
+ รถ lot18655-9-12</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -3945,12 +3949,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>20.70</t>
+          <t>26.20</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>0.0531</t>
+          <t>0.0535</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3960,12 +3964,12 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>393.00฿</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>318.60฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N51" t="inlineStr"/>
@@ -3976,7 +3980,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ZY202464580877#9</t>
+          <t>ZY202464580877</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3992,7 +3996,7 @@
       <c r="E52" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-10</t>
+ รถ lot18655-9-11</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -4012,12 +4016,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>27.70</t>
+          <t>20.70</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>0.0800</t>
+          <t>0.0531</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -4032,7 +4036,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>480.00฿</t>
+          <t>318.60฿</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
@@ -4043,7 +4047,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ZY202464580877#3</t>
+          <t>ZY202464580877#9</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -4059,7 +4063,7 @@
       <c r="E53" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-9</t>
+ รถ lot18655-9-10</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -4079,12 +4083,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>27.10</t>
+          <t>27.70</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>0.0567</t>
+          <t>0.0800</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -4094,19 +4098,15 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>406.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>补胎胶片/9件</t>
-        </is>
-      </c>
+          <t>480.00฿</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -4114,7 +4114,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>S71090288685</t>
+          <t>ZY202464580877#3</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -4124,38 +4124,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>UN-INV260831-00017</t>
+          <t>UN-INV260901-00057</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18634-7-3</t>
+ รถ lot18655-9-9</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>29/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>12.10</t>
+          <t>27.10</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>0.0240</t>
+          <t>0.0567</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -4165,7 +4165,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>181.50฿</t>
+          <t>406.50฿</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -4175,7 +4175,7 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>补胎胶片/9件</t>
         </is>
       </c>
     </row>
@@ -4185,7 +4185,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>YT7638092409979</t>
+          <t>S71090288685</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -4195,38 +4195,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>UN-INV260822-00010</t>
+          <t>UN-INV260831-00017</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18569-7-7</t>
+ รถ lot18634-7-3</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>16/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>16/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>29/08/2026</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>15.00</t>
+          <t>12.10</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>0.0140</t>
+          <t>0.0240</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>225.00฿</t>
+          <t>181.50฿</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -4256,7 +4256,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>435308000517585</t>
+          <t>YT7638092409979</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -4272,32 +4272,32 @@
       <c r="E56" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18550-6-11</t>
+ รถ lot18569-7-7</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>16/08/2026</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>16/08/2026</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>0.0032</t>
+          <t>0.0140</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -4307,7 +4307,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>54.00฿</t>
+          <t>225.00฿</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -4317,7 +4317,7 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>气门嘴</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -4327,7 +4327,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>710094401487</t>
+          <t>435308000517585</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -4343,17 +4343,17 @@
       <c r="E57" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18544-8-14</t>
+ รถ lot18550-6-11</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4363,32 +4363,32 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>107.10</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>0.4536</t>
+          <t>0.0032</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>54.00฿</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>2,721.60฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>空的高压充气罐/一票10件，仓库实收到9件，已确认收到的9件先发</t>
+          <t>气门嘴</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>773435675083665</t>
+          <t>710094401487</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -4408,58 +4408,58 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>UN-INV260815-00046</t>
+          <t>UN-INV260822-00010</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18526-6-17</t>
+ รถ lot18544-8-14</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>13.10</t>
+          <t>107.10</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>0.0214</t>
+          <t>0.4536</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>196.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2,721.60฿</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>补胎工具</t>
+          <t>空的高压充气罐/一票10件，仓库实收到9件，已确认收到的9件先发</t>
         </is>
       </c>
     </row>
@@ -4469,7 +4469,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>YT7637032206975</t>
+          <t>773435675083665</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4479,38 +4479,38 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>UN-INV260819-00010</t>
+          <t>UN-INV260815-00046</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>มอก.
- รถ lot18523-6-30</t>
+          <t>ธรรมดา
+ รถ lot18526-6-17</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>16/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>9.60</t>
+          <t>13.10</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>0.0316</t>
+          <t>0.0214</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4520,17 +4520,17 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>196.50฿</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>214.88฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>气动模具研磨机+配件</t>
+          <t>补胎工具</t>
         </is>
       </c>
     </row>
@@ -4540,7 +4540,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ZY202466648481#5</t>
+          <t>YT7637032206975</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4550,13 +4550,13 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>UN-INV260815-00046</t>
+          <t>UN-INV260819-00010</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>ธรรมดา
- รถ lot18519-6-17</t>
+          <t>มอก.
+ รถ lot18523-6-30</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -4571,17 +4571,17 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>15/08/2026</t>
+          <t>16/08/2026</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>16.10</t>
+          <t>9.60</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>0.0493</t>
+          <t>0.0316</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -4596,10 +4596,14 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>295.80฿</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
+          <t>214.88฿</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>气动模具研磨机+配件</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -4607,7 +4611,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>ZY202466648481#4</t>
+          <t>ZY202466648481#5</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4623,7 +4627,7 @@
       <c r="E61" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18519-6-16</t>
+ รถ lot18519-6-17</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -4643,12 +4647,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>20.50</t>
+          <t>16.10</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>0.0656</t>
+          <t>0.0493</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -4663,7 +4667,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>393.60฿</t>
+          <t>295.80฿</t>
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
@@ -4674,7 +4678,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>ZY202466648481#3</t>
+          <t>ZY202466648481#4</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4690,7 +4694,7 @@
       <c r="E62" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18519-6-15</t>
+ รถ lot18519-6-16</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -4710,12 +4714,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>15.70</t>
+          <t>20.50</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>0.0508</t>
+          <t>0.0656</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -4730,7 +4734,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>304.80฿</t>
+          <t>393.60฿</t>
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
@@ -4741,7 +4745,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>ZY202466648481#2</t>
+          <t>ZY202466648481#3</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4757,7 +4761,7 @@
       <c r="E63" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18519-6-14</t>
+ รถ lot18519-6-15</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -4777,12 +4781,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>20.20</t>
+          <t>15.70</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>0.0660</t>
+          <t>0.0508</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -4797,7 +4801,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>396.00฿</t>
+          <t>304.80฿</t>
         </is>
       </c>
       <c r="N63" t="inlineStr"/>
@@ -4808,7 +4812,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>ZY202466648481</t>
+          <t>ZY202466648481#2</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4824,7 +4828,7 @@
       <c r="E64" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18519-6-13</t>
+ รถ lot18519-6-14</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -4844,12 +4848,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>15.80</t>
+          <t>20.20</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>0.0522</t>
+          <t>0.0660</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -4864,14 +4868,10 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>313.20฿</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr">
-        <is>
-          <t>补胎胶条/5件</t>
-        </is>
-      </c>
+          <t>396.00฿</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -4879,7 +4879,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>113204676267#2</t>
+          <t>ZY202466648481</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4895,32 +4895,32 @@
       <c r="E65" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18518-5-3</t>
+ รถ lot18519-6-13</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>15/08/2026</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>24.60</t>
+          <t>15.80</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>0.0608</t>
+          <t>0.0522</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -4930,15 +4930,19 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>369.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
+          <t>313.20฿</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>补胎胶条/5件</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -4946,7 +4950,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>113204676267</t>
+          <t>113204676267#2</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4962,7 +4966,7 @@
       <c r="E66" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18518-5-2</t>
+ รถ lot18518-5-3</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -4982,12 +4986,12 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>25.00</t>
+          <t>24.60</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>0.0566</t>
+          <t>0.0608</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -4997,7 +5001,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>375.00฿</t>
+          <t>369.00฿</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -5005,11 +5009,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N66" t="inlineStr">
-        <is>
-          <t>真空胎冷补胶片</t>
-        </is>
-      </c>
+      <c r="N66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -5017,7 +5017,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>910061892464#2</t>
+          <t>113204676267</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -5033,32 +5033,32 @@
       <c r="E67" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18505-5-23</t>
+ รถ lot18518-5-2</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>30.40</t>
+          <t>25.00</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>0.0523</t>
+          <t>0.0566</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -5068,7 +5068,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>456.00฿</t>
+          <t>375.00฿</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -5076,7 +5076,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N67" t="inlineStr"/>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>真空胎冷补胶片</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -5084,7 +5088,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>910061892464</t>
+          <t>910061892464#2</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -5100,7 +5104,7 @@
       <c r="E68" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18505-5-22</t>
+ รถ lot18505-5-23</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -5120,12 +5124,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>15.90</t>
+          <t>30.40</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>0.0353</t>
+          <t>0.0523</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -5135,7 +5139,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>238.50฿</t>
+          <t>456.00฿</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -5143,11 +5147,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>记号蜡笔</t>
-        </is>
-      </c>
+      <c r="N68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -5155,7 +5155,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>773434709817985</t>
+          <t>910061892464</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -5165,38 +5165,38 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>UN-INV260819-00010</t>
+          <t>UN-INV260815-00046</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18535-8</t>
+ รถ lot18505-5-22</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>16/08/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>15.90</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>0.0184</t>
+          <t>0.0353</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -5206,17 +5206,17 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>238.50฿</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>110.40฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>锅具 二次包装货物变形</t>
+          <t>记号蜡笔</t>
         </is>
       </c>
     </row>
@@ -5226,7 +5226,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>435295775627304</t>
+          <t>773434709817985</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -5236,38 +5236,38 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>UN-INV260811-00012</t>
+          <t>UN-INV260819-00010</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18492-2</t>
+ รถ lot18535-8</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>16/08/2026</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>5.30</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>0.0090</t>
+          <t>0.0184</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -5277,17 +5277,17 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>79.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>110.40฿</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>配件 破损件</t>
+          <t>锅具 二次包装货物变形</t>
         </is>
       </c>
     </row>
@@ -5297,7 +5297,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>YT7636332367470</t>
+          <t>435295775627304</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -5313,7 +5313,7 @@
       <c r="E71" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18487-2-27</t>
+ รถ lot18492-2</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>5.30</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>0.0004</t>
+          <t>0.0090</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -5348,17 +5348,17 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>79.50฿</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>10.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>立牌</t>
+          <t>配件 破损件</t>
         </is>
       </c>
     </row>
@@ -5368,7 +5368,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>S35386280517#2</t>
+          <t>YT7636332367470</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -5384,32 +5384,32 @@
       <c r="E72" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18475-24</t>
+ รถ lot18487-2-27</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>8.80</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>0.0045</t>
+          <t>0.0004</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -5419,15 +5419,19 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>132.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr"/>
+          <t>10.00฿</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>立牌</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -5435,7 +5439,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>S35386280517</t>
+          <t>S35386280517#2</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -5451,7 +5455,7 @@
       <c r="E73" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18475-23</t>
+ รถ lot18475-24</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -5471,22 +5475,22 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>103.50</t>
+          <t>8.80</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>0.2236</t>
+          <t>0.0045</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>1,552.50฿</t>
+          <t>132.00฿</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -5494,11 +5498,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t>气门嘴 顺心捷达，一票16件</t>
-        </is>
-      </c>
+      <c r="N73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -5506,7 +5506,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>YT7635787693833</t>
+          <t>S35386280517</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -5522,7 +5522,7 @@
       <c r="E74" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18473-6-41</t>
+ รถ lot18475-23</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -5537,37 +5537,37 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>13.80</t>
+          <t>103.50</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>0.0432</t>
+          <t>0.2236</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1,552.50฿</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>259.20฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>气压表/面单没有代码</t>
+          <t>气门嘴 顺心捷达，一票16件</t>
         </is>
       </c>
     </row>
@@ -5577,7 +5577,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>ZY202465806614</t>
+          <t>YT7635787693833</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -5587,38 +5587,38 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>UN-INV260807-00009</t>
+          <t>UN-INV260811-00012</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>มอก.
- รถ lot18466-5-51</t>
+          <t>ธรรมดา
+ รถ lot18473-6-41</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>11.30</t>
+          <t>13.80</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>0.0655</t>
+          <t>0.0432</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -5633,12 +5633,12 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>445.40฿</t>
+          <t>259.20฿</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>电子数显胎压枪</t>
+          <t>气压表/面单没有代码</t>
         </is>
       </c>
     </row>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>113177184579#7</t>
+          <t>ZY202465806614</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5663,18 +5663,18 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>ธรรมดา
- รถ lot18463-17</t>
+          <t>มอก.
+ รถ lot18466-5-51</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5684,12 +5684,12 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>9.70</t>
+          <t>11.30</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>0.0305</t>
+          <t>0.0655</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -5704,10 +5704,14 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>183.00฿</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr"/>
+          <t>445.40฿</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>电子数显胎压枪</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -5715,7 +5719,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>113177184579#5</t>
+          <t>113177184579#7</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -5731,7 +5735,7 @@
       <c r="E77" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-16</t>
+ รถ lot18463-17</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -5751,12 +5755,12 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>15.00</t>
+          <t>9.70</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>0.0137</t>
+          <t>0.0305</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -5766,12 +5770,12 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>225.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>183.00฿</t>
         </is>
       </c>
       <c r="N77" t="inlineStr"/>
@@ -5782,7 +5786,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>113177184579#4</t>
+          <t>113177184579#5</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -5798,7 +5802,7 @@
       <c r="E78" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-15</t>
+ รถ lot18463-16</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -5818,12 +5822,12 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>7.30</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>0.0235</t>
+          <t>0.0137</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -5833,12 +5837,12 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>225.00฿</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>141.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N78" t="inlineStr"/>
@@ -5849,7 +5853,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>113177184579#3</t>
+          <t>113177184579#4</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -5865,7 +5869,7 @@
       <c r="E79" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-14</t>
+ รถ lot18463-15</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -5885,12 +5889,12 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>11.90</t>
+          <t>7.30</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>0.0302</t>
+          <t>0.0235</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -5905,7 +5909,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>181.20฿</t>
+          <t>141.00฿</t>
         </is>
       </c>
       <c r="N79" t="inlineStr"/>
@@ -5916,7 +5920,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>113177184579#6</t>
+          <t>113177184579#3</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -5932,7 +5936,7 @@
       <c r="E80" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-13</t>
+ รถ lot18463-14</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -5952,12 +5956,12 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>26.10</t>
+          <t>11.90</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>0.0673</t>
+          <t>0.0302</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -5972,7 +5976,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>403.80฿</t>
+          <t>181.20฿</t>
         </is>
       </c>
       <c r="N80" t="inlineStr"/>
@@ -5983,7 +5987,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>435289604798626</t>
+          <t>113177184579#6</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -5999,7 +6003,7 @@
       <c r="E81" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18462-6-6</t>
+ รถ lot18463-13</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -6009,7 +6013,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -6019,12 +6023,12 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>9.60</t>
+          <t>26.10</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>0.0090</t>
+          <t>0.0673</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -6034,19 +6038,15 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>144.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr">
-        <is>
-          <t>螺丝配件</t>
-        </is>
-      </c>
+          <t>403.80฿</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -6054,7 +6054,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>113177184579#2</t>
+          <t>435289604798626</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -6070,7 +6070,7 @@
       <c r="E82" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-12</t>
+ รถ lot18462-6-6</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -6080,7 +6080,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -6090,12 +6090,12 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>5.30</t>
+          <t>9.60</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>0.0635</t>
+          <t>0.0090</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -6105,15 +6105,19 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>144.00฿</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>381.00฿</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>螺丝配件</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -6121,7 +6125,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>113177184579</t>
+          <t>113177184579#2</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -6137,7 +6141,7 @@
       <c r="E83" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-11</t>
+ รถ lot18463-12</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -6157,12 +6161,12 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>13.30</t>
+          <t>5.30</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>0.1176</t>
+          <t>0.0635</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -6177,14 +6181,10 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>705.60฿</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr">
-        <is>
-          <t>蘑菇钉补胎贴</t>
-        </is>
-      </c>
+          <t>381.00฿</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -6192,7 +6192,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>435289604798722</t>
+          <t>113177184579</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -6208,7 +6208,7 @@
       <c r="E84" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18462-3</t>
+ รถ lot18463-11</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -6218,7 +6218,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -6228,12 +6228,12 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>4.30</t>
+          <t>13.30</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>0.0029</t>
+          <t>0.1176</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -6243,17 +6243,17 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>64.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>705.60฿</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>气门嘴</t>
+          <t>蘑菇钉补胎贴</t>
         </is>
       </c>
     </row>
@@ -6263,7 +6263,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>ZY202471573119#2</t>
+          <t>435289604798722</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -6279,7 +6279,7 @@
       <c r="E85" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-6</t>
+ รถ lot18462-3</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -6289,7 +6289,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -6299,12 +6299,12 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>8.70</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>0.0441</t>
+          <t>0.0029</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -6314,15 +6314,19 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>64.50฿</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>264.60฿</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>气门嘴</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -6330,7 +6334,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>ZY202471573119</t>
+          <t>ZY202471573119#2</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -6346,7 +6350,7 @@
       <c r="E86" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-5</t>
+ รถ lot18463-6</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -6366,12 +6370,12 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>11.90</t>
+          <t>8.70</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>0.0832</t>
+          <t>0.0441</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -6386,14 +6390,10 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>499.20฿</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr">
-        <is>
-          <t>蘑菇钉补胎</t>
-        </is>
-      </c>
+          <t>264.60฿</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>YT7635427281240</t>
+          <t>ZY202471573119</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -6417,7 +6417,7 @@
       <c r="E87" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18458-21</t>
+ รถ lot18463-5</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -6437,12 +6437,12 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>11.90</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>0.0117</t>
+          <t>0.0832</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -6457,12 +6457,12 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>70.20฿</t>
+          <t>499.20฿</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>气阀</t>
+          <t>蘑菇钉补胎</t>
         </is>
       </c>
     </row>
@@ -6472,7 +6472,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>79021262374216</t>
+          <t>YT7635427281240</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -6482,38 +6482,38 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>UN-INV260804-00019</t>
+          <t>UN-INV260807-00009</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18435-5-73</t>
+ รถ lot18458-21</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>12.20</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>0.0352</t>
+          <t>0.0117</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -6528,12 +6528,12 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>211.20฿</t>
+          <t>70.20฿</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>加长弯头</t>
+          <t>气阀</t>
         </is>
       </c>
     </row>
@@ -6543,7 +6543,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>113162219964#3</t>
+          <t>79021262374216</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -6559,17 +6559,17 @@
       <c r="E89" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18434-9-28</t>
+ รถ lot18435-5-73</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -6579,12 +6579,12 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>18.70</t>
+          <t>12.20</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>0.0443</t>
+          <t>0.0352</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -6594,15 +6594,19 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>280.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr"/>
+          <t>211.20฿</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>加长弯头</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -6610,7 +6614,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>113162219964#2</t>
+          <t>113162219964#3</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -6626,7 +6630,7 @@
       <c r="E90" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18434-9-27</t>
+ รถ lot18434-9-28</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -6646,12 +6650,12 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>22.90</t>
+          <t>18.70</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>0.0522</t>
+          <t>0.0443</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -6661,7 +6665,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>343.50฿</t>
+          <t>280.50฿</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -6677,7 +6681,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>113162219964</t>
+          <t>113162219964#2</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -6693,7 +6697,7 @@
       <c r="E91" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18434-9-26</t>
+ รถ lot18434-9-27</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -6713,12 +6717,12 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>25.60</t>
+          <t>22.90</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>0.0574</t>
+          <t>0.0522</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -6728,7 +6732,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>384.00฿</t>
+          <t>343.50฿</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -6736,11 +6740,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N91" t="inlineStr">
-        <is>
-          <t>补胎胶片/3件</t>
-        </is>
-      </c>
+      <c r="N91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -6748,7 +6748,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>113158800045#2</t>
+          <t>113162219964</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -6764,32 +6764,32 @@
       <c r="E92" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18427-7-3</t>
+ รถ lot18434-9-26</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>26/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>26/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>26.30</t>
+          <t>25.60</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>0.0377</t>
+          <t>0.0574</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -6799,7 +6799,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>394.50฿</t>
+          <t>384.00฿</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -6807,7 +6807,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N92" t="inlineStr"/>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>补胎胶片/3件</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -6815,7 +6819,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>113158800045</t>
+          <t>113158800045#2</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -6831,7 +6835,7 @@
       <c r="E93" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18427-7-2</t>
+ รถ lot18427-7-3</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -6851,12 +6855,12 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>26.50</t>
+          <t>26.30</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>0.0379</t>
+          <t>0.0377</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -6866,7 +6870,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>397.50฿</t>
+          <t>394.50฿</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
@@ -6874,11 +6878,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N93" t="inlineStr">
-        <is>
-          <t>塑料配件/2件</t>
-        </is>
-      </c>
+      <c r="N93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -6886,7 +6886,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>YT2550516723148</t>
+          <t>113158800045</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -6902,32 +6902,32 @@
       <c r="E94" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18398-3-10</t>
+ รถ lot18427-7-2</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>22/07/2026</t>
+          <t>26/07/2026</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>23/07/2026</t>
+          <t>26/07/2026</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>26.50</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>0.0127</t>
+          <t>0.0379</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -6937,17 +6937,17 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>397.50฿</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>76.20฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>硅胶风管</t>
+          <t>塑料配件/2件</t>
         </is>
       </c>
     </row>
@@ -6957,7 +6957,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>ZY202467269952#4</t>
+          <t>YT2550516723148</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -6967,38 +6967,38 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>UN-INV260724-00013</t>
+          <t>UN-INV260804-00019</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18314-8-30</t>
+ รถ lot18398-3-10</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>11/07/2026</t>
+          <t>22/07/2026</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>12/07/2026</t>
+          <t>23/07/2026</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>15.50</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>0.0492</t>
+          <t>0.0127</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -7013,10 +7013,14 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>295.20฿</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr"/>
+          <t>76.20฿</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>硅胶风管</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -7024,7 +7028,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>ZY202467269952#3</t>
+          <t>ZY202467269952#4</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -7040,7 +7044,7 @@
       <c r="E96" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18314-8-29</t>
+ รถ lot18314-8-30</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -7060,12 +7064,12 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>12.50</t>
+          <t>15.50</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>0.0300</t>
+          <t>0.0492</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -7075,12 +7079,12 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>187.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>295.20฿</t>
         </is>
       </c>
       <c r="N96" t="inlineStr"/>
@@ -7091,7 +7095,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>ZY202467269952#2</t>
+          <t>ZY202467269952#3</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -7107,7 +7111,7 @@
       <c r="E97" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18314-8-28</t>
+ รถ lot18314-8-29</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -7127,12 +7131,12 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>15.50</t>
+          <t>12.50</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>0.0508</t>
+          <t>0.0300</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -7142,12 +7146,12 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>187.50฿</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>304.80฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N97" t="inlineStr"/>
@@ -7158,7 +7162,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>ZY202467269952</t>
+          <t>ZY202467269952#2</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -7174,7 +7178,7 @@
       <c r="E98" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18314-8-27</t>
+ รถ lot18314-8-28</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -7194,12 +7198,12 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>10.50</t>
+          <t>15.50</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>0.0355</t>
+          <t>0.0508</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -7214,14 +7218,10 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>213.00฿</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr">
-        <is>
-          <t>补胎胶片/4件</t>
-        </is>
-      </c>
+          <t>304.80฿</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -7229,7 +7229,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>773431041004504</t>
+          <t>ZY202467269952</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -7245,7 +7245,7 @@
       <c r="E99" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18314-5-13</t>
+ รถ lot18314-8-27</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>10.50</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>0.0044</t>
+          <t>0.0355</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>26.40฿</t>
+          <t>213.00฿</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>门底条</t>
+          <t>补胎胶片/4件</t>
         </is>
       </c>
     </row>
@@ -7300,7 +7300,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>ZY202467269844#2</t>
+          <t>773431041004504</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -7310,38 +7310,38 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>UN-INV260717-00013</t>
+          <t>UN-INV260724-00013</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18288-8-41</t>
+ รถ lot18314-5-13</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>11/07/2026</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>12/07/2026</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>21.00</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>0.0660</t>
+          <t>0.0044</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -7356,10 +7356,14 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>396.00฿</t>
-        </is>
-      </c>
-      <c r="N100" t="inlineStr"/>
+          <t>26.40฿</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>门底条</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -7367,7 +7371,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>ZY202467269844#5</t>
+          <t>ZY202467269844#2</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -7383,7 +7387,7 @@
       <c r="E101" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18288-8-40</t>
+ รถ lot18288-8-41</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -7403,12 +7407,12 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>27.90</t>
+          <t>21.00</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>0.0800</t>
+          <t>0.0660</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -7423,7 +7427,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>480.00฿</t>
+          <t>396.00฿</t>
         </is>
       </c>
       <c r="N101" t="inlineStr"/>

--- a/cargo_packages_p1-5.xlsx
+++ b/cargo_packages_p1-5.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>760246657062</t>
+          <t>113350746029#4</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -522,7 +522,7 @@
       <c r="E2" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18799-7-3</t>
+ รถ lot18799-6-32</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -532,7 +532,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -542,12 +542,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>27.70</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.0005</t>
+          <t>0.0800</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -562,14 +562,10 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>10.00฿</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>气门嘴，轮胎修补工具，气门芯宣传册</t>
-        </is>
-      </c>
+          <t>480.00฿</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -577,7 +573,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>113348267192#2</t>
+          <t>113350746029#3</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -593,17 +589,17 @@
       <c r="E3" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18795-2-7</t>
+ รถ lot18799-6-31</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -613,12 +609,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>28.10</t>
+          <t>10.90</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.0628</t>
+          <t>0.0377</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -628,12 +624,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>421.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>226.20฿</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -644,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>113348267192</t>
+          <t>113350746029#2</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -660,17 +656,17 @@
       <c r="E4" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18795-2-6</t>
+ รถ lot18799-6-30</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -680,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>19.50</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.0505</t>
+          <t>0.0101</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -695,19 +691,15 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>225.00฿</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>303.00฿</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>补胎胶片</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -715,7 +707,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ZY202472578299</t>
+          <t>113350746029</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -731,17 +723,17 @@
       <c r="E5" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18758-7-43</t>
+ รถ lot18799-6-29</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -751,32 +743,32 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>47.40</t>
+          <t>16.50</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.1603</t>
+          <t>0.0127</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>247.50฿</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>961.20฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>补胎贴，3件</t>
+          <t>真空胎加固修理补片</t>
         </is>
       </c>
     </row>
@@ -786,7 +778,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>773440822655698</t>
+          <t>760246657062</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -802,17 +794,17 @@
       <c r="E6" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18758-4-31</t>
+ รถ lot18799-7-3</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -822,12 +814,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.0022</t>
+          <t>0.0005</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -837,17 +829,17 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>18.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10.00฿</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>钻头</t>
+          <t>气门嘴，轮胎修补工具，气门芯宣传册</t>
         </is>
       </c>
     </row>
@@ -857,7 +849,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>YT7642998390994</t>
+          <t>113348267192#2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -873,17 +865,17 @@
       <c r="E7" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18769-3-57</t>
+ รถ lot18795-2-7</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -893,12 +885,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5.80</t>
+          <t>28.10</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.0070</t>
+          <t>0.0628</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -908,7 +900,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>87.00฿</t>
+          <t>421.50฿</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -916,11 +908,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>配件</t>
-        </is>
-      </c>
+      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -928,7 +916,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DPK212614057101</t>
+          <t>113348267192</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -944,32 +932,32 @@
       <c r="E8" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18749-4-3</t>
+ รถ lot18795-2-6</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>9.60</t>
+          <t>19.50</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.0060</t>
+          <t>0.0505</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -979,17 +967,17 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>144.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>303.00฿</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>轮胎气门嘴</t>
+          <t>补胎胶片</t>
         </is>
       </c>
     </row>
@@ -999,7 +987,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>79031204783305</t>
+          <t>ZY202472578299</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1015,52 +1003,52 @@
       <c r="E9" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18744-6-15</t>
+ รถ lot18758-7-43</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>47.40</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.0020</t>
+          <t>0.1603</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>39.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>961.20฿</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>补胎贴，3件</t>
         </is>
       </c>
     </row>
@@ -1070,7 +1058,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>435342988112655</t>
+          <t>773440822655698</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1086,32 +1074,32 @@
       <c r="E10" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18743-3-34</t>
+ รถ lot18758-4-31</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.0014</t>
+          <t>0.0022</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1121,17 +1109,17 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>18.00฿</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>10.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>橡胶垫圈</t>
+          <t>钻头</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1129,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>435343890137834</t>
+          <t>YT7642998390994</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1157,32 +1145,32 @@
       <c r="E11" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18743-7-25</t>
+ รถ lot18769-3-57</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>21.40</t>
+          <t>5.80</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.0080</t>
+          <t>0.0070</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1192,7 +1180,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>321.00฿</t>
+          <t>87.00฿</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1202,7 +1190,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>扒胎机包胶撬棍</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -1212,7 +1200,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>YT7642670434639</t>
+          <t>DPK212614057101</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1228,17 +1216,17 @@
       <c r="E12" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18743-2-8</t>
+ รถ lot18749-4-3</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1248,12 +1236,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>9.60</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0.0010</t>
+          <t>0.0060</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1263,7 +1251,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>12.00฿</t>
+          <t>144.00฿</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1273,7 +1261,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>片片</t>
+          <t>轮胎气门嘴</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1271,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>93015797092</t>
+          <t>79031204783305</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1293,38 +1281,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>UN-INV260914-00014</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18735-4-40</t>
+ รถ lot18744-6-15</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>12/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>8.60</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0.0148</t>
+          <t>0.0020</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1334,7 +1322,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>129.00฿</t>
+          <t>39.00฿</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1344,7 +1332,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>仪表</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -1354,7 +1342,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>YT7642390374765</t>
+          <t>435342988112655</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1364,18 +1352,18 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>UN-INV260914-00015</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18735-4-20</t>
+ รถ lot18743-3-34</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1385,17 +1373,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>12/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>20.80</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.0598</t>
+          <t>0.0014</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1410,12 +1398,12 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>358.80฿</t>
+          <t>10.00฿</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>打磨机</t>
+          <t>橡胶垫圈</t>
         </is>
       </c>
     </row>
@@ -1425,7 +1413,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>435342255104130</t>
+          <t>435343890137834</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1435,18 +1423,18 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>UN-INV260914-00014</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18735-43</t>
+ รถ lot18743-7-25</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1456,17 +1444,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>12/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>4.90</t>
+          <t>21.40</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.0172</t>
+          <t>0.0080</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1476,17 +1464,17 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>321.00฿</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>103.20฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>轮毂保护套</t>
+          <t>扒胎机包胶撬棍</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1484,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>773440312345715</t>
+          <t>YT7642670434639</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1506,18 +1494,18 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>UN-INV260914-00014</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18735-3-78</t>
+ รถ lot18743-2-8</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1527,17 +1515,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>12/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>0.0013</t>
+          <t>0.0010</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1547,7 +1535,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>19.50฿</t>
+          <t>12.00฿</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1557,7 +1545,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>片片</t>
         </is>
       </c>
     </row>
@@ -1567,7 +1555,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>773440291470393</t>
+          <t>93015797092</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1583,7 +1571,7 @@
       <c r="E17" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18735-34</t>
+ รถ lot18735-4-40</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1603,12 +1591,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>8.60</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.0029</t>
+          <t>0.0148</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1618,7 +1606,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>48.00฿</t>
+          <t>129.00฿</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1628,7 +1616,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>球阀</t>
+          <t>仪表</t>
         </is>
       </c>
     </row>
@@ -1638,7 +1626,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>435342261175750</t>
+          <t>YT7642390374765</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1654,7 +1642,7 @@
       <c r="E18" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18736-13</t>
+ รถ lot18735-4-20</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1664,7 +1652,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1674,12 +1662,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>13.90</t>
+          <t>20.80</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>0.0137</t>
+          <t>0.0598</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1689,17 +1677,17 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>208.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>358.80฿</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>打磨机</t>
         </is>
       </c>
     </row>
@@ -1709,7 +1697,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ZY202461195200</t>
+          <t>435342255104130</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1719,13 +1707,13 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>UN-INV260914-00015</t>
+          <t>UN-INV260914-00014</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18728-7-13</t>
+ รถ lot18735-43</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1735,22 +1723,22 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>13/09/2026</t>
+          <t>12/09/2026</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>47.40</t>
+          <t>4.90</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>0.0116</t>
+          <t>0.0172</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1760,17 +1748,17 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>711.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>103.20฿</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>轮毂保护套</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1768,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>79030687835952</t>
+          <t>773440312345715</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1796,7 +1784,7 @@
       <c r="E20" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18728-3-64</t>
+ รถ lot18735-3-78</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1806,22 +1794,22 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>13/09/2026</t>
+          <t>12/09/2026</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>4.30</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0.0030</t>
+          <t>0.0013</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1831,7 +1819,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>64.50฿</t>
+          <t>19.50฿</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1841,7 +1829,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>接头配件</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1839,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>LJ20722214#3</t>
+          <t>773440291470393</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1861,38 +1849,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>UN-INV260912-00011</t>
+          <t>UN-INV260914-00014</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18726-7-8</t>
+ รถ lot18735-34</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>12/09/2026</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>14.00</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.0171</t>
+          <t>0.0029</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1902,7 +1890,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>210.00฿</t>
+          <t>48.00฿</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1910,7 +1898,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>球阀</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1918,7 +1910,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>LJ20722214#2</t>
+          <t>435342261175750</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1928,38 +1920,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>UN-INV260912-00011</t>
+          <t>UN-INV260914-00015</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18726-7-7</t>
+ รถ lot18736-13</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>12/09/2026</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>11.90</t>
+          <t>13.90</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.0089</t>
+          <t>0.0137</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1969,7 +1961,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>178.50฿</t>
+          <t>208.50฿</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1977,7 +1969,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>配件</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1985,7 +1981,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>LJ20722214</t>
+          <t>ZY202461195200</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1995,38 +1991,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>UN-INV260912-00011</t>
+          <t>UN-INV260914-00015</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18726-7-6</t>
+ รถ lot18728-7-13</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>13/09/2026</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>16.00</t>
+          <t>47.40</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.0144</t>
+          <t>0.0116</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2036,7 +2032,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>240.00฿</t>
+          <t>711.00฿</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2046,7 +2042,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>电板套筒配件/3件</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -2056,7 +2052,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>YT7641966426761</t>
+          <t>79030687835952</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2066,38 +2062,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>UN-INV260912-00011</t>
+          <t>UN-INV260914-00014</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18714-9-23</t>
+ รถ lot18728-3-64</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>13/09/2026</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>13.60</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.0422</t>
+          <t>0.0030</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2107,17 +2103,17 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>64.50฿</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>253.20฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>带表汽车轮胎打气嘴</t>
+          <t>接头配件</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2123,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ZY202471681117#2</t>
+          <t>LJ20722214#3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2143,17 +2139,17 @@
       <c r="E25" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18714-9-8</t>
+ รถ lot18726-7-8</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2163,12 +2159,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>11.80</t>
+          <t>14.00</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.0832</t>
+          <t>0.0171</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2178,12 +2174,12 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>210.00฿</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>499.20฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -2194,7 +2190,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ZY202471681117</t>
+          <t>LJ20722214#2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2210,17 +2206,17 @@
       <c r="E26" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18714-9-7</t>
+ รถ lot18726-7-7</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2230,12 +2226,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>7.70</t>
+          <t>11.90</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>0.0493</t>
+          <t>0.0089</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2245,19 +2241,15 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>178.50฿</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>295.80฿</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>补胎胶片/2件</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2265,7 +2257,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>302285502767#2</t>
+          <t>LJ20722214</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2281,17 +2273,17 @@
       <c r="E27" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18714-8-10</t>
+ รถ lot18726-7-6</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2301,12 +2293,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>33.70</t>
+          <t>16.00</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.0145</t>
+          <t>0.0144</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2316,7 +2308,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>505.50฿</t>
+          <t>240.00฿</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2324,7 +2316,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>电板套筒配件/3件</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2332,7 +2328,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>302285502767</t>
+          <t>YT7641966426761</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2348,7 +2344,7 @@
       <c r="E28" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18714-8-9</t>
+ รถ lot18714-9-23</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2368,12 +2364,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>23.40</t>
+          <t>13.60</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.0123</t>
+          <t>0.0422</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2383,17 +2379,17 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>351.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>253.20฿</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>扳手</t>
+          <t>带表汽车轮胎打气嘴</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2399,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>LJ20716178#2</t>
+          <t>ZY202471681117#2</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2413,18 +2409,18 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>UN-INV260911-00013</t>
+          <t>UN-INV260912-00011</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18713-6-65</t>
+ รถ lot18714-9-8</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2434,17 +2430,17 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>19.50</t>
+          <t>11.80</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0.0075</t>
+          <t>0.0832</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2454,12 +2450,12 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>292.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>499.20฿</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -2470,7 +2466,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>LJ20716178</t>
+          <t>ZY202471681117</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2480,18 +2476,18 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>UN-INV260911-00013</t>
+          <t>UN-INV260912-00011</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18713-6-64</t>
+ รถ lot18714-9-7</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2501,17 +2497,17 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>19.60</t>
+          <t>7.70</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.0075</t>
+          <t>0.0493</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2521,17 +2517,17 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>294.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>295.80฿</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>补胎胶片/2件</t>
         </is>
       </c>
     </row>
@@ -2541,7 +2537,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>435338972466812</t>
+          <t>302285502767#2</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2551,38 +2547,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>UN-INV260911-00013</t>
+          <t>UN-INV260912-00011</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18710-6-35</t>
+ รถ lot18714-8-10</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>13.10</t>
+          <t>33.70</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.0624</t>
+          <t>0.0145</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2592,19 +2588,15 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>505.50฿</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>374.40฿</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>修补工具</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2612,7 +2604,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>435334324045675</t>
+          <t>302285502767</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2622,38 +2614,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>UN-INV260908-00009</t>
+          <t>UN-INV260912-00011</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18696-14</t>
+ รถ lot18714-8-9</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>10.80</t>
+          <t>23.40</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.0088</t>
+          <t>0.0123</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2663,7 +2655,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>162.00฿</t>
+          <t>351.00฿</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2673,7 +2665,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>扳手</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2675,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>YT7641276428798</t>
+          <t>LJ20716178#2</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2693,38 +2685,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>UN-INV260908-00009</t>
+          <t>UN-INV260911-00013</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18697-11</t>
+ รถ lot18713-6-65</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>9.50</t>
+          <t>19.50</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.0296</t>
+          <t>0.0075</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2734,19 +2726,15 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>292.50฿</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>177.60฿</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>配件</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2754,7 +2742,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>79029430531776</t>
+          <t>LJ20716178</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2764,38 +2752,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>UN-INV260907-00015</t>
+          <t>UN-INV260911-00013</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18689-26</t>
+ รถ lot18713-6-64</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>19.60</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.0135</t>
+          <t>0.0075</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2805,17 +2793,17 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>294.00฿</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>81.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>卡套</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -2825,7 +2813,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>113282578128#2</t>
+          <t>435338972466812</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2835,38 +2823,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>UN-INV260907-00015</t>
+          <t>UN-INV260911-00013</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18683-4</t>
+ รถ lot18710-6-35</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>38.00</t>
+          <t>13.10</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.1601</t>
+          <t>0.0624</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2881,10 +2869,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>960.60฿</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
+          <t>374.40฿</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>修补工具</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2892,7 +2884,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>113282578128</t>
+          <t>435334324045675</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2902,38 +2894,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>UN-INV260907-00015</t>
+          <t>UN-INV260908-00009</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18683-3</t>
+ รถ lot18696-14</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>27.50</t>
+          <t>10.80</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.1566</t>
+          <t>0.0088</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2943,17 +2935,17 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>162.00฿</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>939.60฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>压条取出器 一票两件破损件</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2955,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>82730128600#3</t>
+          <t>YT7641276428798</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2973,38 +2965,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>UN-INV260907-00015</t>
+          <t>UN-INV260908-00009</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18678-6-21</t>
+ รถ lot18697-11</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>30/08/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>33.00</t>
+          <t>9.50</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.0122</t>
+          <t>0.0296</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -3014,15 +3006,19 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>495.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
+          <t>177.60฿</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>配件</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -3030,7 +3026,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>82730128600#2</t>
+          <t>79029430531776</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3046,17 +3042,17 @@
       <c r="E38" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18678-6-20</t>
+ รถ lot18689-26</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>30/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3066,12 +3062,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>27.60</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.0095</t>
+          <t>0.0135</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -3081,15 +3077,19 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>414.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
+          <t>81.00฿</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>卡套</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>82730128600</t>
+          <t>113282578128#2</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3113,12 +3113,12 @@
       <c r="E39" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18678-6-19</t>
+ รถ lot18683-4</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>30/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>28.10</t>
+          <t>38.00</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.0118</t>
+          <t>0.1601</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -3148,19 +3148,15 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>421.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>五金配件/3件</t>
-        </is>
-      </c>
+          <t>960.60฿</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -3168,7 +3164,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>113278387839#3</t>
+          <t>113282578128</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3178,38 +3174,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>UN-INV260903-00023</t>
+          <t>UN-INV260907-00015</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18663-8-3</t>
+ รถ lot18683-3</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>25.30</t>
+          <t>27.50</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.0404</t>
+          <t>0.1566</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -3219,15 +3215,19 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>379.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
+          <t>939.60฿</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>压条取出器 一票两件破损件</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -3235,7 +3235,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>113278387839#2</t>
+          <t>82730128600#3</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3245,38 +3245,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>UN-INV260903-00023</t>
+          <t>UN-INV260907-00015</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18663-8-2</t>
+ รถ lot18678-6-21</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>30/08/2026</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>26.10</t>
+          <t>33.00</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.0304</t>
+          <t>0.0122</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>391.50฿</t>
+          <t>495.00฿</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -3302,7 +3302,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>113278387839</t>
+          <t>82730128600#2</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3312,38 +3312,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>UN-INV260903-00023</t>
+          <t>UN-INV260907-00015</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18663-8-1</t>
+ รถ lot18678-6-20</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>30/08/2026</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>9.10</t>
+          <t>27.60</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.0144</t>
+          <t>0.0095</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3353,7 +3353,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>136.50฿</t>
+          <t>414.00฿</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3361,11 +3361,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>配件/3件</t>
-        </is>
-      </c>
+      <c r="N42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -3373,7 +3369,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>113276098937#3</t>
+          <t>82730128600</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3383,38 +3379,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>UN-INV260901-00057</t>
+          <t>UN-INV260907-00015</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-45</t>
+ รถ lot18678-6-19</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>30/08/2026</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>17.80</t>
+          <t>28.10</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.0302</t>
+          <t>0.0118</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3424,7 +3420,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>267.00฿</t>
+          <t>421.50฿</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3432,7 +3428,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>五金配件/3件</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>113276098937#2</t>
+          <t>113278387839#3</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3450,38 +3450,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>UN-INV260901-00057</t>
+          <t>UN-INV260903-00023</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-44</t>
+ รถ lot18663-8-3</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>10.90</t>
+          <t>25.30</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.0313</t>
+          <t>0.0404</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3491,12 +3491,12 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>379.50฿</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>187.80฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
@@ -3507,7 +3507,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>113276098937</t>
+          <t>113278387839#2</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3517,38 +3517,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>UN-INV260901-00057</t>
+          <t>UN-INV260903-00023</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-43</t>
+ รถ lot18663-8-2</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>33.60</t>
+          <t>26.10</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.0825</t>
+          <t>0.0304</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3558,7 +3558,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>504.00฿</t>
+          <t>391.50฿</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3566,11 +3566,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>补胎胶片+配件/3件</t>
-        </is>
-      </c>
+      <c r="N45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -3578,7 +3574,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ZY202464580877#4</t>
+          <t>113278387839</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3588,38 +3584,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>UN-INV260901-00057</t>
+          <t>UN-INV260903-00023</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-17</t>
+ รถ lot18663-8-1</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>20.10</t>
+          <t>9.10</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>0.0466</t>
+          <t>0.0144</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3629,7 +3625,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>301.50฿</t>
+          <t>136.50฿</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3637,7 +3633,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>配件/3件</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -3645,7 +3645,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ZY202464580877#7</t>
+          <t>113276098937#3</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3661,7 +3661,7 @@
       <c r="E47" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-16</t>
+ รถ lot18655-9-45</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -3681,12 +3681,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>16.60</t>
+          <t>17.80</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>0.0430</t>
+          <t>0.0302</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3696,12 +3696,12 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>267.00฿</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>258.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
@@ -3712,7 +3712,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>ZY202464580877#2</t>
+          <t>113276098937#2</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3728,7 +3728,7 @@
       <c r="E48" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-15</t>
+ รถ lot18655-9-44</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -3748,12 +3748,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>25.10</t>
+          <t>10.90</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>0.0483</t>
+          <t>0.0313</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3763,12 +3763,12 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>376.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>187.80฿</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
@@ -3779,7 +3779,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ZY202464580877#8</t>
+          <t>113276098937</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3795,7 +3795,7 @@
       <c r="E49" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-14</t>
+ รถ lot18655-9-43</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3815,12 +3815,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>28.90</t>
+          <t>33.60</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>0.0800</t>
+          <t>0.0825</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3830,15 +3830,19 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>504.00฿</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>480.00฿</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>补胎胶片+配件/3件</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -3846,7 +3850,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ZY202464580877#6</t>
+          <t>ZY202464580877#4</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3862,7 +3866,7 @@
       <c r="E50" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-13</t>
+ รถ lot18655-9-17</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3882,12 +3886,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>20.90</t>
+          <t>20.10</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>0.0534</t>
+          <t>0.0466</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3897,12 +3901,12 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>301.50฿</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>320.40฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N50" t="inlineStr"/>
@@ -3913,7 +3917,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ZY202464580877#5</t>
+          <t>ZY202464580877#7</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3929,7 +3933,7 @@
       <c r="E51" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-12</t>
+ รถ lot18655-9-16</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -3949,12 +3953,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>26.20</t>
+          <t>16.60</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>0.0535</t>
+          <t>0.0430</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3964,12 +3968,12 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>393.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>258.00฿</t>
         </is>
       </c>
       <c r="N51" t="inlineStr"/>
@@ -3980,7 +3984,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ZY202464580877</t>
+          <t>ZY202464580877#2</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3996,7 +4000,7 @@
       <c r="E52" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-11</t>
+ รถ lot18655-9-15</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -4016,12 +4020,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>20.70</t>
+          <t>25.10</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>0.0531</t>
+          <t>0.0483</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -4031,12 +4035,12 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>376.50฿</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>318.60฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
@@ -4047,7 +4051,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ZY202464580877#9</t>
+          <t>ZY202464580877#8</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -4063,7 +4067,7 @@
       <c r="E53" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-10</t>
+ รถ lot18655-9-14</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -4083,7 +4087,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>27.70</t>
+          <t>28.90</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -4114,7 +4118,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ZY202464580877#3</t>
+          <t>ZY202464580877#6</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -4130,7 +4134,7 @@
       <c r="E54" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-9</t>
+ รถ lot18655-9-13</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -4150,12 +4154,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>27.10</t>
+          <t>20.90</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>0.0567</t>
+          <t>0.0534</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -4165,19 +4169,15 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>406.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>补胎胶片/9件</t>
-        </is>
-      </c>
+          <t>320.40฿</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -4185,7 +4185,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>S71090288685</t>
+          <t>ZY202464580877#5</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -4195,38 +4195,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>UN-INV260831-00017</t>
+          <t>UN-INV260901-00057</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18634-7-3</t>
+ รถ lot18655-9-12</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>29/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>12.10</t>
+          <t>26.20</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>0.0240</t>
+          <t>0.0535</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>181.50฿</t>
+          <t>393.00฿</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -4244,11 +4244,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>配件</t>
-        </is>
-      </c>
+      <c r="N55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -4256,7 +4252,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>YT7638092409979</t>
+          <t>ZY202464580877</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -4266,38 +4262,38 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>UN-INV260822-00010</t>
+          <t>UN-INV260901-00057</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18569-7-7</t>
+ รถ lot18655-9-11</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>16/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>16/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>15.00</t>
+          <t>20.70</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>0.0140</t>
+          <t>0.0531</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -4307,19 +4303,15 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>225.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>配件</t>
-        </is>
-      </c>
+          <t>318.60฿</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -4327,7 +4319,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>435308000517585</t>
+          <t>ZY202464580877#9</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -4337,38 +4329,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>UN-INV260822-00010</t>
+          <t>UN-INV260901-00057</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18550-6-11</t>
+ รถ lot18655-9-10</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>27.70</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>0.0032</t>
+          <t>0.0800</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -4378,19 +4370,15 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>54.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>气门嘴</t>
-        </is>
-      </c>
+          <t>480.00฿</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -4398,7 +4386,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>710094401487</t>
+          <t>ZY202464580877#3</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -4408,58 +4396,58 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>UN-INV260822-00010</t>
+          <t>UN-INV260901-00057</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18544-8-14</t>
+ รถ lot18655-9-9</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>107.10</t>
+          <t>27.10</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>0.4536</t>
+          <t>0.0567</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>406.50฿</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>2,721.60฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>空的高压充气罐/一票10件，仓库实收到9件，已确认收到的9件先发</t>
+          <t>补胎胶片/9件</t>
         </is>
       </c>
     </row>
@@ -4469,7 +4457,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>773435675083665</t>
+          <t>S71090288685</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4479,38 +4467,38 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>UN-INV260815-00046</t>
+          <t>UN-INV260831-00017</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18526-6-17</t>
+ รถ lot18634-7-3</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>29/08/2026</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>13.10</t>
+          <t>12.10</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>0.0214</t>
+          <t>0.0240</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4520,7 +4508,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>196.50฿</t>
+          <t>181.50฿</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -4530,7 +4518,7 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>补胎工具</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -4540,7 +4528,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>YT7637032206975</t>
+          <t>YT7638092409979</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4550,38 +4538,38 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>UN-INV260819-00010</t>
+          <t>UN-INV260822-00010</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>มอก.
- รถ lot18523-6-30</t>
+          <t>ธรรมดา
+ รถ lot18569-7-7</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>16/08/2026</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>16/08/2026</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>16/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>9.60</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>0.0316</t>
+          <t>0.0140</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -4591,17 +4579,17 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>225.00฿</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>214.88฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>气动模具研磨机+配件</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -4611,7 +4599,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>ZY202466648481#5</t>
+          <t>435308000517585</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4621,38 +4609,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>UN-INV260815-00046</t>
+          <t>UN-INV260822-00010</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18519-6-17</t>
+ รถ lot18550-6-11</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>15/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>16.10</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>0.0493</t>
+          <t>0.0032</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -4662,15 +4650,19 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>54.00฿</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>295.80฿</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>气门嘴</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -4678,7 +4670,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>ZY202466648481#4</t>
+          <t>710094401487</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4688,43 +4680,43 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>UN-INV260815-00046</t>
+          <t>UN-INV260822-00010</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18519-6-16</t>
+ รถ lot18544-8-14</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>15/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>20.50</t>
+          <t>107.10</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>0.0656</t>
+          <t>0.4536</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4734,10 +4726,14 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>393.60฿</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
+          <t>2,721.60฿</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>空的高压充气罐/一票10件，仓库实收到9件，已确认收到的9件先发</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -4745,7 +4741,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>ZY202466648481#3</t>
+          <t>773435675083665</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4761,32 +4757,32 @@
       <c r="E63" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18519-6-15</t>
+ รถ lot18526-6-17</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>15/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>15.70</t>
+          <t>13.10</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>0.0508</t>
+          <t>0.0214</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -4796,15 +4792,19 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>196.50฿</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>304.80฿</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>补胎工具</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -4812,7 +4812,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>ZY202466648481#2</t>
+          <t>YT7637032206975</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4822,13 +4822,13 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>UN-INV260815-00046</t>
+          <t>UN-INV260819-00010</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>ธรรมดา
- รถ lot18519-6-14</t>
+          <t>มอก.
+ รถ lot18523-6-30</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -4843,17 +4843,17 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>15/08/2026</t>
+          <t>16/08/2026</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>20.20</t>
+          <t>9.60</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>0.0660</t>
+          <t>0.0316</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -4868,10 +4868,14 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>396.00฿</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr"/>
+          <t>214.88฿</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>气动模具研磨机+配件</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -4879,7 +4883,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>ZY202466648481</t>
+          <t>ZY202466648481#5</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4895,7 +4899,7 @@
       <c r="E65" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18519-6-13</t>
+ รถ lot18519-6-17</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -4915,12 +4919,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>15.80</t>
+          <t>16.10</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>0.0522</t>
+          <t>0.0493</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -4935,14 +4939,10 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>313.20฿</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr">
-        <is>
-          <t>补胎胶条/5件</t>
-        </is>
-      </c>
+          <t>295.80฿</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -4950,7 +4950,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>113204676267#2</t>
+          <t>ZY202466648481#4</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4966,32 +4966,32 @@
       <c r="E66" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18518-5-3</t>
+ รถ lot18519-6-16</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>15/08/2026</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>24.60</t>
+          <t>20.50</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>0.0608</t>
+          <t>0.0656</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -5001,12 +5001,12 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>369.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>393.60฿</t>
         </is>
       </c>
       <c r="N66" t="inlineStr"/>
@@ -5017,7 +5017,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>113204676267</t>
+          <t>ZY202466648481#3</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -5033,32 +5033,32 @@
       <c r="E67" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18518-5-2</t>
+ รถ lot18519-6-15</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>15/08/2026</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>25.00</t>
+          <t>15.70</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>0.0566</t>
+          <t>0.0508</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -5068,19 +5068,15 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>375.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr">
-        <is>
-          <t>真空胎冷补胶片</t>
-        </is>
-      </c>
+          <t>304.80฿</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -5088,7 +5084,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>910061892464#2</t>
+          <t>ZY202466648481#2</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -5104,32 +5100,32 @@
       <c r="E68" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18505-5-23</t>
+ รถ lot18519-6-14</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>15/08/2026</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>30.40</t>
+          <t>20.20</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>0.0523</t>
+          <t>0.0660</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -5139,12 +5135,12 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>456.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>396.00฿</t>
         </is>
       </c>
       <c r="N68" t="inlineStr"/>
@@ -5155,7 +5151,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>910061892464</t>
+          <t>ZY202466648481</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -5171,32 +5167,32 @@
       <c r="E69" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18505-5-22</t>
+ รถ lot18519-6-13</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>15/08/2026</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>15.90</t>
+          <t>15.80</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>0.0353</t>
+          <t>0.0522</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -5206,17 +5202,17 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>238.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>313.20฿</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>记号蜡笔</t>
+          <t>补胎胶条/5件</t>
         </is>
       </c>
     </row>
@@ -5226,7 +5222,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>773434709817985</t>
+          <t>113204676267#2</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -5236,38 +5232,38 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>UN-INV260819-00010</t>
+          <t>UN-INV260815-00046</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18535-8</t>
+ รถ lot18518-5-3</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>16/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>24.60</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>0.0184</t>
+          <t>0.0608</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -5277,19 +5273,15 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>369.00฿</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>110.40฿</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t>锅具 二次包装货物变形</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -5297,7 +5289,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>435295775627304</t>
+          <t>113204676267</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -5307,38 +5299,38 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>UN-INV260811-00012</t>
+          <t>UN-INV260815-00046</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18492-2</t>
+ รถ lot18518-5-2</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>5.30</t>
+          <t>25.00</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>0.0090</t>
+          <t>0.0566</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -5348,7 +5340,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>79.50฿</t>
+          <t>375.00฿</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -5358,7 +5350,7 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>配件 破损件</t>
+          <t>真空胎冷补胶片</t>
         </is>
       </c>
     </row>
@@ -5368,7 +5360,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>YT7636332367470</t>
+          <t>910061892464#2</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -5378,38 +5370,38 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>UN-INV260811-00012</t>
+          <t>UN-INV260815-00046</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18487-2-27</t>
+ รถ lot18505-5-23</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>30.40</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>0.0004</t>
+          <t>0.0523</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -5419,19 +5411,15 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>456.00฿</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>10.00฿</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr">
-        <is>
-          <t>立牌</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -5439,7 +5427,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>S35386280517#2</t>
+          <t>910061892464</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -5449,38 +5437,38 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>UN-INV260811-00012</t>
+          <t>UN-INV260815-00046</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18475-24</t>
+ รถ lot18505-5-22</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>8.80</t>
+          <t>15.90</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>0.0045</t>
+          <t>0.0353</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -5490,7 +5478,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>132.00฿</t>
+          <t>238.50฿</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -5498,7 +5486,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N73" t="inlineStr"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>记号蜡笔</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -5506,7 +5498,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>S35386280517</t>
+          <t>773434709817985</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -5516,58 +5508,58 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>UN-INV260811-00012</t>
+          <t>UN-INV260819-00010</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18475-23</t>
+ รถ lot18535-8</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>16/08/2026</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>103.50</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>0.2236</t>
+          <t>0.0184</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>1,552.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>110.40฿</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>气门嘴 顺心捷达，一票16件</t>
+          <t>锅具 二次包装货物变形</t>
         </is>
       </c>
     </row>
@@ -5577,7 +5569,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>YT7635787693833</t>
+          <t>435295775627304</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -5593,32 +5585,32 @@
       <c r="E75" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18473-6-41</t>
+ รถ lot18492-2</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>13.80</t>
+          <t>5.30</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>0.0432</t>
+          <t>0.0090</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -5628,17 +5620,17 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>79.50฿</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>259.20฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>气压表/面单没有代码</t>
+          <t>配件 破损件</t>
         </is>
       </c>
     </row>
@@ -5648,7 +5640,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>ZY202465806614</t>
+          <t>YT7636332367470</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5658,38 +5650,38 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>UN-INV260807-00009</t>
+          <t>UN-INV260811-00012</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>มอก.
- รถ lot18466-5-51</t>
+          <t>ธรรมดา
+ รถ lot18487-2-27</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>11.30</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>0.0655</t>
+          <t>0.0004</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -5704,12 +5696,12 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>445.40฿</t>
+          <t>10.00฿</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>电子数显胎压枪</t>
+          <t>立牌</t>
         </is>
       </c>
     </row>
@@ -5719,7 +5711,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>113177184579#7</t>
+          <t>S35386280517#2</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -5729,38 +5721,38 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>UN-INV260807-00009</t>
+          <t>UN-INV260811-00012</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-17</t>
+ รถ lot18475-24</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>9.70</t>
+          <t>8.80</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>0.0305</t>
+          <t>0.0045</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -5770,12 +5762,12 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>132.00฿</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>183.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N77" t="inlineStr"/>
@@ -5786,7 +5778,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>113177184579#5</t>
+          <t>S35386280517</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -5796,48 +5788,48 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>UN-INV260807-00009</t>
+          <t>UN-INV260811-00012</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-16</t>
+ รถ lot18475-23</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>15.00</t>
+          <t>103.50</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>0.0137</t>
+          <t>0.2236</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>225.00฿</t>
+          <t>1,552.50฿</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -5845,7 +5837,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N78" t="inlineStr"/>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>气门嘴 顺心捷达，一票16件</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -5853,7 +5849,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>113177184579#4</t>
+          <t>YT7635787693833</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -5863,38 +5859,38 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>UN-INV260807-00009</t>
+          <t>UN-INV260811-00012</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-15</t>
+ รถ lot18473-6-41</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>7.30</t>
+          <t>13.80</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>0.0235</t>
+          <t>0.0432</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -5909,10 +5905,14 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>141.00฿</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr"/>
+          <t>259.20฿</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>气压表/面单没有代码</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -5920,7 +5920,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>113177184579#3</t>
+          <t>ZY202465806614</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -5935,18 +5935,18 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>ธรรมดา
- รถ lot18463-14</t>
+          <t>มอก.
+ รถ lot18466-5-51</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5956,12 +5956,12 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>11.90</t>
+          <t>11.30</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>0.0302</t>
+          <t>0.0655</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -5976,10 +5976,14 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>181.20฿</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr"/>
+          <t>445.40฿</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>电子数显胎压枪</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -5987,7 +5991,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>113177184579#6</t>
+          <t>113177184579#7</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -6003,7 +6007,7 @@
       <c r="E81" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-13</t>
+ รถ lot18463-17</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -6023,12 +6027,12 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>26.10</t>
+          <t>9.70</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>0.0673</t>
+          <t>0.0305</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -6043,7 +6047,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>403.80฿</t>
+          <t>183.00฿</t>
         </is>
       </c>
       <c r="N81" t="inlineStr"/>
@@ -6054,7 +6058,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>435289604798626</t>
+          <t>113177184579#5</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -6070,7 +6074,7 @@
       <c r="E82" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18462-6-6</t>
+ รถ lot18463-16</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -6080,7 +6084,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -6090,12 +6094,12 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>9.60</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>0.0090</t>
+          <t>0.0137</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -6105,7 +6109,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>144.00฿</t>
+          <t>225.00฿</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -6113,11 +6117,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N82" t="inlineStr">
-        <is>
-          <t>螺丝配件</t>
-        </is>
-      </c>
+      <c r="N82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -6125,7 +6125,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>113177184579#2</t>
+          <t>113177184579#4</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -6141,7 +6141,7 @@
       <c r="E83" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-12</t>
+ รถ lot18463-15</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>5.30</t>
+          <t>7.30</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>0.0635</t>
+          <t>0.0235</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -6181,7 +6181,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>381.00฿</t>
+          <t>141.00฿</t>
         </is>
       </c>
       <c r="N83" t="inlineStr"/>
@@ -6192,7 +6192,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>113177184579</t>
+          <t>113177184579#3</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -6208,7 +6208,7 @@
       <c r="E84" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-11</t>
+ รถ lot18463-14</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -6228,12 +6228,12 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>13.30</t>
+          <t>11.90</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>0.1176</t>
+          <t>0.0302</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -6248,14 +6248,10 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>705.60฿</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr">
-        <is>
-          <t>蘑菇钉补胎贴</t>
-        </is>
-      </c>
+          <t>181.20฿</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -6263,7 +6259,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>435289604798722</t>
+          <t>113177184579#6</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -6279,7 +6275,7 @@
       <c r="E85" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18462-3</t>
+ รถ lot18463-13</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -6289,7 +6285,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -6299,12 +6295,12 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>4.30</t>
+          <t>26.10</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>0.0029</t>
+          <t>0.0673</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -6314,19 +6310,15 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>64.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr">
-        <is>
-          <t>气门嘴</t>
-        </is>
-      </c>
+          <t>403.80฿</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -6334,7 +6326,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>ZY202471573119#2</t>
+          <t>435289604798626</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -6350,7 +6342,7 @@
       <c r="E86" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-6</t>
+ รถ lot18462-6-6</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -6360,7 +6352,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -6370,12 +6362,12 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>8.70</t>
+          <t>9.60</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>0.0441</t>
+          <t>0.0090</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -6385,15 +6377,19 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>144.00฿</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>264.60฿</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>螺丝配件</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -6401,7 +6397,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>ZY202471573119</t>
+          <t>113177184579#2</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -6417,7 +6413,7 @@
       <c r="E87" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-5</t>
+ รถ lot18463-12</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -6437,12 +6433,12 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>11.90</t>
+          <t>5.30</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>0.0832</t>
+          <t>0.0635</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -6457,14 +6453,10 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>499.20฿</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr">
-        <is>
-          <t>蘑菇钉补胎</t>
-        </is>
-      </c>
+          <t>381.00฿</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -6472,7 +6464,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>YT7635427281240</t>
+          <t>113177184579</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -6488,7 +6480,7 @@
       <c r="E88" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18458-21</t>
+ รถ lot18463-11</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -6508,12 +6500,12 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>13.30</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>0.0117</t>
+          <t>0.1176</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -6528,12 +6520,12 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>70.20฿</t>
+          <t>705.60฿</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>气阀</t>
+          <t>蘑菇钉补胎贴</t>
         </is>
       </c>
     </row>
@@ -6543,7 +6535,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>79021262374216</t>
+          <t>435289604798722</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -6553,38 +6545,38 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>UN-INV260804-00019</t>
+          <t>UN-INV260807-00009</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18435-5-73</t>
+ รถ lot18462-3</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>12.20</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>0.0352</t>
+          <t>0.0029</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -6594,17 +6586,17 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>64.50฿</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>211.20฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>加长弯头</t>
+          <t>气门嘴</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6606,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>113162219964#3</t>
+          <t>ZY202471573119#2</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -6624,38 +6616,38 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>UN-INV260804-00019</t>
+          <t>UN-INV260807-00009</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18434-9-28</t>
+ รถ lot18463-6</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>18.70</t>
+          <t>8.70</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>0.0443</t>
+          <t>0.0441</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -6665,12 +6657,12 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>280.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>264.60฿</t>
         </is>
       </c>
       <c r="N90" t="inlineStr"/>
@@ -6681,7 +6673,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>113162219964#2</t>
+          <t>ZY202471573119</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -6691,38 +6683,38 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>UN-INV260804-00019</t>
+          <t>UN-INV260807-00009</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18434-9-27</t>
+ รถ lot18463-5</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>22.90</t>
+          <t>11.90</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>0.0522</t>
+          <t>0.0832</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -6732,15 +6724,19 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>343.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N91" t="inlineStr"/>
+          <t>499.20฿</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>蘑菇钉补胎</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -6748,7 +6744,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>113162219964</t>
+          <t>YT7635427281240</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -6758,38 +6754,38 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>UN-INV260804-00019</t>
+          <t>UN-INV260807-00009</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18434-9-26</t>
+ รถ lot18458-21</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>25.60</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>0.0574</t>
+          <t>0.0117</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -6799,17 +6795,17 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>384.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>70.20฿</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>补胎胶片/3件</t>
+          <t>气阀</t>
         </is>
       </c>
     </row>
@@ -6819,7 +6815,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>113158800045#2</t>
+          <t>79021262374216</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -6835,32 +6831,32 @@
       <c r="E93" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18427-7-3</t>
+ รถ lot18435-5-73</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>26/07/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>26/07/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>26.30</t>
+          <t>12.20</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>0.0377</t>
+          <t>0.0352</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -6870,15 +6866,19 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>394.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N93" t="inlineStr"/>
+          <t>211.20฿</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>加长弯头</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -6886,7 +6886,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>113158800045</t>
+          <t>113162219964#3</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -6902,32 +6902,32 @@
       <c r="E94" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18427-7-2</t>
+ รถ lot18434-9-28</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>26/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>26/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>26.50</t>
+          <t>18.70</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>0.0379</t>
+          <t>0.0443</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -6937,7 +6937,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>397.50฿</t>
+          <t>280.50฿</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -6945,11 +6945,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N94" t="inlineStr">
-        <is>
-          <t>塑料配件/2件</t>
-        </is>
-      </c>
+      <c r="N94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -6957,7 +6953,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>YT2550516723148</t>
+          <t>113162219964#2</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -6973,32 +6969,32 @@
       <c r="E95" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18398-3-10</t>
+ รถ lot18434-9-27</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>22/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>23/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>22.90</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>0.0127</t>
+          <t>0.0522</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -7008,19 +7004,15 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>343.50฿</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>76.20฿</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr">
-        <is>
-          <t>硅胶风管</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -7028,7 +7020,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>ZY202467269952#4</t>
+          <t>113162219964</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -7038,38 +7030,38 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>UN-INV260724-00013</t>
+          <t>UN-INV260804-00019</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18314-8-30</t>
+ รถ lot18434-9-26</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>11/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>12/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>15.50</t>
+          <t>25.60</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>0.0492</t>
+          <t>0.0574</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -7079,15 +7071,19 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>384.00฿</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>295.20฿</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>补胎胶片/3件</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -7095,7 +7091,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>ZY202467269952#3</t>
+          <t>113158800045#2</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -7105,38 +7101,38 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>UN-INV260724-00013</t>
+          <t>UN-INV260804-00019</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18314-8-29</t>
+ รถ lot18427-7-3</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>11/07/2026</t>
+          <t>26/07/2026</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>12/07/2026</t>
+          <t>26/07/2026</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>12.50</t>
+          <t>26.30</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>0.0300</t>
+          <t>0.0377</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -7146,7 +7142,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>187.50฿</t>
+          <t>394.50฿</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -7162,7 +7158,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>ZY202467269952#2</t>
+          <t>113158800045</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -7172,38 +7168,38 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>UN-INV260724-00013</t>
+          <t>UN-INV260804-00019</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18314-8-28</t>
+ รถ lot18427-7-2</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>11/07/2026</t>
+          <t>26/07/2026</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>12/07/2026</t>
+          <t>26/07/2026</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>15.50</t>
+          <t>26.50</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>0.0508</t>
+          <t>0.0379</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -7213,15 +7209,19 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>397.50฿</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>304.80฿</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>塑料配件/2件</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -7229,7 +7229,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>ZY202467269952</t>
+          <t>YT2550516723148</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -7239,38 +7239,38 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>UN-INV260724-00013</t>
+          <t>UN-INV260804-00019</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18314-8-27</t>
+ รถ lot18398-3-10</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>11/07/2026</t>
+          <t>22/07/2026</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>12/07/2026</t>
+          <t>23/07/2026</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>10.50</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>0.0355</t>
+          <t>0.0127</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>213.00฿</t>
+          <t>76.20฿</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>补胎胶片/4件</t>
+          <t>硅胶风管</t>
         </is>
       </c>
     </row>
@@ -7300,7 +7300,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>773431041004504</t>
+          <t>ZY202467269952#4</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -7316,7 +7316,7 @@
       <c r="E100" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18314-5-13</t>
+ รถ lot18314-8-30</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -7336,12 +7336,12 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>15.50</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>0.0044</t>
+          <t>0.0492</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -7356,14 +7356,10 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>26.40฿</t>
-        </is>
-      </c>
-      <c r="N100" t="inlineStr">
-        <is>
-          <t>门底条</t>
-        </is>
-      </c>
+          <t>295.20฿</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -7371,7 +7367,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>ZY202467269844#2</t>
+          <t>ZY202467269952#3</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -7381,38 +7377,38 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>UN-INV260717-00013</t>
+          <t>UN-INV260724-00013</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18288-8-41</t>
+ รถ lot18314-8-29</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>11/07/2026</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>12/07/2026</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>21.00</t>
+          <t>12.50</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>0.0660</t>
+          <t>0.0300</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -7422,12 +7418,12 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>187.50฿</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>396.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N101" t="inlineStr"/>

--- a/cargo_packages_p1-5.xlsx
+++ b/cargo_packages_p1-5.xlsx
@@ -1210,7 +1210,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>UN-INV260916-00003</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>UN-INV260916-00003</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>UN-INV260916-00003</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>UN-INV260916-00003</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>UN-INV260916-00003</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">

--- a/cargo_packages_p1-5.xlsx
+++ b/cargo_packages_p1-5.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>113350746029#4</t>
+          <t>S71195667064</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -522,17 +522,17 @@
       <c r="E2" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18799-6-32</t>
+ รถ lot18810-8-3</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -542,17 +542,17 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>27.70</t>
+          <t>165.00</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.0800</t>
+          <t>0.8568</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -562,10 +562,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>480.00฿</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>5,140.80฿</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>千斤顶，3件，客户不打木架发</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -573,7 +577,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>113350746029#3</t>
+          <t>113350746029#4</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -589,7 +593,7 @@
       <c r="E3" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18799-6-31</t>
+ รถ lot18799-6-32</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -609,12 +613,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10.90</t>
+          <t>27.70</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.0377</t>
+          <t>0.0800</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -629,7 +633,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>226.20฿</t>
+          <t>480.00฿</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -640,7 +644,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>113350746029#2</t>
+          <t>113350746029#3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -656,7 +660,7 @@
       <c r="E4" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18799-6-30</t>
+ รถ lot18799-6-31</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -676,12 +680,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>15.00</t>
+          <t>10.90</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.0101</t>
+          <t>0.0377</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -691,12 +695,12 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>225.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>226.20฿</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -707,7 +711,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>113350746029</t>
+          <t>113350746029#2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -723,7 +727,7 @@
       <c r="E5" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18799-6-29</t>
+ รถ lot18799-6-30</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -743,12 +747,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>16.50</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.0127</t>
+          <t>0.0101</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -758,7 +762,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>247.50฿</t>
+          <t>225.00฿</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -766,11 +770,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>真空胎加固修理补片</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -778,7 +778,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>760246657062</t>
+          <t>113350746029</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -794,7 +794,7 @@
       <c r="E6" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18799-7-3</t>
+ รถ lot18799-6-29</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -814,12 +814,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>16.50</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.0005</t>
+          <t>0.0127</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -829,17 +829,17 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>247.50฿</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>10.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>气门嘴，轮胎修补工具，气门芯宣传册</t>
+          <t>真空胎加固修理补片</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>113348267192#2</t>
+          <t>760246657062</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -865,17 +865,17 @@
       <c r="E7" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18795-2-7</t>
+ รถ lot18799-7-3</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -885,12 +885,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>28.10</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.0628</t>
+          <t>0.0005</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -900,15 +900,19 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>421.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>10.00฿</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>气门嘴，轮胎修补工具，气门芯宣传册</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -916,7 +920,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>113348267192</t>
+          <t>113348267192#2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -932,7 +936,7 @@
       <c r="E8" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18795-2-6</t>
+ รถ lot18795-2-7</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -952,12 +956,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>19.50</t>
+          <t>28.10</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.0505</t>
+          <t>0.0628</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -967,19 +971,15 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>421.50฿</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>303.00฿</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>补胎胶片</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -987,7 +987,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ZY202472578299</t>
+          <t>113348267192</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1003,17 +1003,17 @@
       <c r="E9" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18758-7-43</t>
+ รถ lot18795-2-6</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1023,17 +1023,17 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>47.40</t>
+          <t>19.50</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.1603</t>
+          <t>0.0505</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>961.20฿</t>
+          <t>303.00฿</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>补胎贴，3件</t>
+          <t>补胎胶片</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>773440822655698</t>
+          <t>ZY202472578299</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1074,7 +1074,7 @@
       <c r="E10" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18758-4-31</t>
+ รถ lot18758-7-43</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1094,32 +1094,32 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>47.40</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.0022</t>
+          <t>0.1603</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>18.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>961.20฿</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>钻头</t>
+          <t>补胎贴，3件</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>YT7642998390994</t>
+          <t>773440822655698</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1145,7 +1145,7 @@
       <c r="E11" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18769-3-57</t>
+ รถ lot18758-4-31</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>5.80</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.0070</t>
+          <t>0.0022</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>87.00฿</t>
+          <t>18.00฿</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>钻头</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DPK212614057101</t>
+          <t>YT7642998390994</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1210,38 +1210,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>UN-INV260916-00003</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18749-4-3</t>
+ รถ lot18769-3-57</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>9.60</t>
+          <t>5.80</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0.0060</t>
+          <t>0.0070</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>144.00฿</t>
+          <t>87.00฿</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>轮胎气门嘴</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>79031204783305</t>
+          <t>DPK212614057101</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1287,7 +1287,7 @@
       <c r="E13" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18744-6-15</t>
+ รถ lot18749-4-3</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1307,12 +1307,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>9.60</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0.0020</t>
+          <t>0.0060</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>39.00฿</t>
+          <t>144.00฿</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>轮胎气门嘴</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>435342988112655</t>
+          <t>79031204783305</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1358,17 +1358,17 @@
       <c r="E14" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18743-3-34</t>
+ รถ lot18744-6-15</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1378,12 +1378,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.0014</t>
+          <t>0.0020</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1393,17 +1393,17 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>39.00฿</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>10.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>橡胶垫圈</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -1413,7 +1413,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>435343890137834</t>
+          <t>435342988112655</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1429,7 +1429,7 @@
       <c r="E15" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18743-7-25</t>
+ รถ lot18743-3-34</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>21.40</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.0080</t>
+          <t>0.0014</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1464,17 +1464,17 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>321.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10.00฿</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>扒胎机包胶撬棍</t>
+          <t>橡胶垫圈</t>
         </is>
       </c>
     </row>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>YT7642670434639</t>
+          <t>435343890137834</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1500,7 +1500,7 @@
       <c r="E16" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18743-2-8</t>
+ รถ lot18743-7-25</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1520,12 +1520,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>21.40</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>0.0010</t>
+          <t>0.0080</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>12.00฿</t>
+          <t>321.00฿</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>片片</t>
+          <t>扒胎机包胶撬棍</t>
         </is>
       </c>
     </row>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>93015797092</t>
+          <t>YT7642670434639</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1565,18 +1565,18 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>UN-INV260914-00014</t>
+          <t>UN-INV260916-00003</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18735-4-40</t>
+ รถ lot18743-2-8</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1586,17 +1586,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>12/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>8.60</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.0148</t>
+          <t>0.0010</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>129.00฿</t>
+          <t>12.00฿</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>仪表</t>
+          <t>片片</t>
         </is>
       </c>
     </row>
@@ -1626,7 +1626,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>YT7642390374765</t>
+          <t>93015797092</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1636,13 +1636,13 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>UN-INV260914-00015</t>
+          <t>UN-INV260914-00014</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18735-4-20</t>
+ รถ lot18735-4-40</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1662,12 +1662,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>20.80</t>
+          <t>8.60</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>0.0598</t>
+          <t>0.0148</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1677,17 +1677,17 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>129.00฿</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>358.80฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>打磨机</t>
+          <t>仪表</t>
         </is>
       </c>
     </row>
@@ -1697,7 +1697,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>435342255104130</t>
+          <t>YT7642390374765</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1707,13 +1707,13 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>UN-INV260914-00014</t>
+          <t>UN-INV260914-00015</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18735-43</t>
+ รถ lot18735-4-20</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1733,12 +1733,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>4.90</t>
+          <t>20.80</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>0.0172</t>
+          <t>0.0598</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1753,12 +1753,12 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>103.20฿</t>
+          <t>358.80฿</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>轮毂保护套</t>
+          <t>打磨机</t>
         </is>
       </c>
     </row>
@@ -1768,7 +1768,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>773440312345715</t>
+          <t>435342255104130</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1784,7 +1784,7 @@
       <c r="E20" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18735-3-78</t>
+ รถ lot18735-43</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>4.90</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0.0013</t>
+          <t>0.0172</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1819,17 +1819,17 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>19.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>103.20฿</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>轮毂保护套</t>
         </is>
       </c>
     </row>
@@ -1839,7 +1839,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>773440291470393</t>
+          <t>773440312345715</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1855,7 +1855,7 @@
       <c r="E21" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18735-34</t>
+ รถ lot18735-3-78</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1875,12 +1875,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.0029</t>
+          <t>0.0013</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>48.00฿</t>
+          <t>19.50฿</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>球阀</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>435342261175750</t>
+          <t>773440291470393</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1920,13 +1920,13 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>UN-INV260914-00015</t>
+          <t>UN-INV260914-00014</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18736-13</t>
+ รถ lot18735-34</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1946,12 +1946,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>13.90</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.0137</t>
+          <t>0.0029</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>208.50฿</t>
+          <t>48.00฿</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1971,7 +1971,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>球阀</t>
         </is>
       </c>
     </row>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ZY202461195200</t>
+          <t>435342261175750</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1997,7 +1997,7 @@
       <c r="E23" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18728-7-13</t>
+ รถ lot18736-13</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2012,17 +2012,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>13/09/2026</t>
+          <t>12/09/2026</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>47.40</t>
+          <t>13.90</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.0116</t>
+          <t>0.0137</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>711.00฿</t>
+          <t>208.50฿</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>79030687835952</t>
+          <t>ZY202461195200</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2062,13 +2062,13 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>UN-INV260914-00014</t>
+          <t>UN-INV260914-00015</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18728-3-64</t>
+ รถ lot18728-7-13</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2088,12 +2088,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>4.30</t>
+          <t>47.40</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.0030</t>
+          <t>0.0116</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2103,7 +2103,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>64.50฿</t>
+          <t>711.00฿</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>接头配件</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>LJ20722214#3</t>
+          <t>79030687835952</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2133,38 +2133,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>UN-INV260912-00011</t>
+          <t>UN-INV260914-00014</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18726-7-8</t>
+ รถ lot18728-3-64</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>13/09/2026</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>14.00</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.0171</t>
+          <t>0.0030</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>210.00฿</t>
+          <t>64.50฿</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2182,7 +2182,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>接头配件</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -2190,7 +2194,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>LJ20722214#2</t>
+          <t>LJ20722214#3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2206,7 +2210,7 @@
       <c r="E26" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18726-7-7</t>
+ รถ lot18726-7-8</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2226,12 +2230,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>11.90</t>
+          <t>14.00</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>0.0089</t>
+          <t>0.0171</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2241,7 +2245,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>178.50฿</t>
+          <t>210.00฿</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2257,7 +2261,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>LJ20722214</t>
+          <t>LJ20722214#2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2273,7 +2277,7 @@
       <c r="E27" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18726-7-6</t>
+ รถ lot18726-7-7</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2293,12 +2297,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>16.00</t>
+          <t>11.90</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.0144</t>
+          <t>0.0089</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2308,7 +2312,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>240.00฿</t>
+          <t>178.50฿</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2316,11 +2320,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>电板套筒配件/3件</t>
-        </is>
-      </c>
+      <c r="N27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2328,7 +2328,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>YT7641966426761</t>
+          <t>LJ20722214</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2344,17 +2344,17 @@
       <c r="E28" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18714-9-23</t>
+ รถ lot18726-7-6</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>13.60</t>
+          <t>16.00</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.0422</t>
+          <t>0.0144</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2379,17 +2379,17 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>240.00฿</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>253.20฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>带表汽车轮胎打气嘴</t>
+          <t>电板套筒配件/3件</t>
         </is>
       </c>
     </row>
@@ -2399,7 +2399,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ZY202471681117#2</t>
+          <t>YT7641966426761</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2415,7 +2415,7 @@
       <c r="E29" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18714-9-8</t>
+ รถ lot18714-9-23</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2435,12 +2435,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>11.80</t>
+          <t>13.60</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0.0832</t>
+          <t>0.0422</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2455,10 +2455,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>499.20฿</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
+          <t>253.20฿</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>带表汽车轮胎打气嘴</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2466,7 +2470,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ZY202471681117</t>
+          <t>ZY202471681117#2</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2482,7 +2486,7 @@
       <c r="E30" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18714-9-7</t>
+ รถ lot18714-9-8</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2502,12 +2506,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>7.70</t>
+          <t>11.80</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.0493</t>
+          <t>0.0832</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2522,14 +2526,10 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>295.80฿</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>补胎胶片/2件</t>
-        </is>
-      </c>
+          <t>499.20฿</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>302285502767#2</t>
+          <t>ZY202471681117</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2553,7 +2553,7 @@
       <c r="E31" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18714-8-10</t>
+ รถ lot18714-9-7</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>33.70</t>
+          <t>7.70</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.0145</t>
+          <t>0.0493</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2588,15 +2588,19 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>505.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
+          <t>295.80฿</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>补胎胶片/2件</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2604,7 +2608,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>302285502767</t>
+          <t>302285502767#2</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2620,7 +2624,7 @@
       <c r="E32" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18714-8-9</t>
+ รถ lot18714-8-10</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2640,12 +2644,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>23.40</t>
+          <t>33.70</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.0123</t>
+          <t>0.0145</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2655,7 +2659,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>351.00฿</t>
+          <t>505.50฿</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2663,11 +2667,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>扳手</t>
-        </is>
-      </c>
+      <c r="N32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2675,7 +2675,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>LJ20716178#2</t>
+          <t>302285502767</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2685,18 +2685,18 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>UN-INV260911-00013</t>
+          <t>UN-INV260912-00011</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18713-6-65</t>
+ รถ lot18714-8-9</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2706,17 +2706,17 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>19.50</t>
+          <t>23.40</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.0075</t>
+          <t>0.0123</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>292.50฿</t>
+          <t>351.00฿</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2734,7 +2734,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>扳手</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2742,7 +2746,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>LJ20716178</t>
+          <t>LJ20716178#2</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2758,7 +2762,7 @@
       <c r="E34" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18713-6-64</t>
+ รถ lot18713-6-65</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2778,7 +2782,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>19.60</t>
+          <t>19.50</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2793,7 +2797,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>294.00฿</t>
+          <t>292.50฿</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2801,11 +2805,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>配件</t>
-        </is>
-      </c>
+      <c r="N34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>435338972466812</t>
+          <t>LJ20716178</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2829,7 +2829,7 @@
       <c r="E35" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18710-6-35</t>
+ รถ lot18713-6-64</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2839,7 +2839,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>13.10</t>
+          <t>19.60</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.0624</t>
+          <t>0.0075</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2864,17 +2864,17 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>294.00฿</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>374.40฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>修补工具</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>435334324045675</t>
+          <t>435338972466812</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2894,38 +2894,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>UN-INV260908-00009</t>
+          <t>UN-INV260911-00013</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18696-14</t>
+ รถ lot18710-6-35</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>10.80</t>
+          <t>13.10</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.0088</t>
+          <t>0.0624</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2935,17 +2935,17 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>162.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>374.40฿</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>修补工具</t>
         </is>
       </c>
     </row>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>YT7641276428798</t>
+          <t>435334324045675</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2971,7 +2971,7 @@
       <c r="E37" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18697-11</t>
+ รถ lot18696-14</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>9.50</t>
+          <t>10.80</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.0296</t>
+          <t>0.0088</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -3006,12 +3006,12 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>162.00฿</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>177.60฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3026,7 +3026,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>79029430531776</t>
+          <t>YT7641276428798</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3036,18 +3036,18 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>UN-INV260907-00015</t>
+          <t>UN-INV260908-00009</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18689-26</t>
+ รถ lot18697-11</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -3057,17 +3057,17 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>9.50</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.0135</t>
+          <t>0.0296</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -3082,12 +3082,12 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>81.00฿</t>
+          <t>177.60฿</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>卡套</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -3097,7 +3097,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>113282578128#2</t>
+          <t>79029430531776</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3113,17 +3113,17 @@
       <c r="E39" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18683-4</t>
+ รถ lot18689-26</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>38.00</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.1601</t>
+          <t>0.0135</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -3153,10 +3153,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>960.60฿</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
+          <t>81.00฿</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>卡套</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -3164,7 +3168,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>113282578128</t>
+          <t>113282578128#2</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3180,7 +3184,7 @@
       <c r="E40" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18683-3</t>
+ รถ lot18683-4</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -3200,12 +3204,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>27.50</t>
+          <t>38.00</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.1566</t>
+          <t>0.1601</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -3220,14 +3224,10 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>939.60฿</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>压条取出器 一票两件破损件</t>
-        </is>
-      </c>
+          <t>960.60฿</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -3235,7 +3235,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>82730128600#3</t>
+          <t>113282578128</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3251,12 +3251,12 @@
       <c r="E41" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18678-6-21</t>
+ รถ lot18683-3</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>30/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -3271,12 +3271,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>33.00</t>
+          <t>27.50</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.0122</t>
+          <t>0.1566</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -3286,15 +3286,19 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>495.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
+          <t>939.60฿</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>压条取出器 一票两件破损件</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -3302,7 +3306,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>82730128600#2</t>
+          <t>82730128600#3</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3318,7 +3322,7 @@
       <c r="E42" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18678-6-20</t>
+ รถ lot18678-6-21</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -3338,12 +3342,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>27.60</t>
+          <t>33.00</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.0095</t>
+          <t>0.0122</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3353,7 +3357,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>414.00฿</t>
+          <t>495.00฿</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3369,7 +3373,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>82730128600</t>
+          <t>82730128600#2</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3385,7 +3389,7 @@
       <c r="E43" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18678-6-19</t>
+ รถ lot18678-6-20</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -3405,12 +3409,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>28.10</t>
+          <t>27.60</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.0118</t>
+          <t>0.0095</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3420,7 +3424,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>421.50฿</t>
+          <t>414.00฿</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3428,11 +3432,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>五金配件/3件</t>
-        </is>
-      </c>
+      <c r="N43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>113278387839#3</t>
+          <t>82730128600</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3450,38 +3450,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>UN-INV260903-00023</t>
+          <t>UN-INV260907-00015</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18663-8-3</t>
+ รถ lot18678-6-19</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>30/08/2026</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>25.30</t>
+          <t>28.10</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.0404</t>
+          <t>0.0118</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>379.50฿</t>
+          <t>421.50฿</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3499,7 +3499,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>五金配件/3件</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -3507,7 +3511,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>113278387839#2</t>
+          <t>113278387839#3</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3523,7 +3527,7 @@
       <c r="E45" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18663-8-2</t>
+ รถ lot18663-8-3</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -3543,12 +3547,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>26.10</t>
+          <t>25.30</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.0304</t>
+          <t>0.0404</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3558,7 +3562,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>391.50฿</t>
+          <t>379.50฿</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3574,7 +3578,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>113278387839</t>
+          <t>113278387839#2</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3590,7 +3594,7 @@
       <c r="E46" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18663-8-1</t>
+ รถ lot18663-8-2</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -3610,12 +3614,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>9.10</t>
+          <t>26.10</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>0.0144</t>
+          <t>0.0304</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3625,7 +3629,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>136.50฿</t>
+          <t>391.50฿</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3633,11 +3637,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>配件/3件</t>
-        </is>
-      </c>
+      <c r="N46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -3645,7 +3645,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>113276098937#3</t>
+          <t>113278387839</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3655,38 +3655,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>UN-INV260901-00057</t>
+          <t>UN-INV260903-00023</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-45</t>
+ รถ lot18663-8-1</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>17.80</t>
+          <t>9.10</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>0.0302</t>
+          <t>0.0144</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>267.00฿</t>
+          <t>136.50฿</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3704,7 +3704,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>配件/3件</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -3712,7 +3716,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>113276098937#2</t>
+          <t>113276098937#3</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3728,7 +3732,7 @@
       <c r="E48" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-44</t>
+ รถ lot18655-9-45</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -3748,12 +3752,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>10.90</t>
+          <t>17.80</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>0.0313</t>
+          <t>0.0302</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3763,12 +3767,12 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>267.00฿</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>187.80฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
@@ -3779,7 +3783,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>113276098937</t>
+          <t>113276098937#2</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3795,7 +3799,7 @@
       <c r="E49" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-43</t>
+ รถ lot18655-9-44</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3815,12 +3819,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>33.60</t>
+          <t>10.90</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>0.0825</t>
+          <t>0.0313</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3830,19 +3834,15 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>504.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>补胎胶片+配件/3件</t>
-        </is>
-      </c>
+          <t>187.80฿</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ZY202464580877#4</t>
+          <t>113276098937</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3866,7 +3866,7 @@
       <c r="E50" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-17</t>
+ รถ lot18655-9-43</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3886,12 +3886,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>20.10</t>
+          <t>33.60</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>0.0466</t>
+          <t>0.0825</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3901,7 +3901,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>301.50฿</t>
+          <t>504.00฿</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -3909,7 +3909,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>补胎胶片+配件/3件</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -3917,7 +3921,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ZY202464580877#7</t>
+          <t>ZY202464580877#4</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3933,7 +3937,7 @@
       <c r="E51" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-16</t>
+ รถ lot18655-9-17</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -3953,12 +3957,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>16.60</t>
+          <t>20.10</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>0.0430</t>
+          <t>0.0466</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3968,12 +3972,12 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>301.50฿</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>258.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N51" t="inlineStr"/>
@@ -3984,7 +3988,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ZY202464580877#2</t>
+          <t>ZY202464580877#7</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -4000,7 +4004,7 @@
       <c r="E52" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-15</t>
+ รถ lot18655-9-16</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -4020,12 +4024,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>25.10</t>
+          <t>16.60</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>0.0483</t>
+          <t>0.0430</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -4035,12 +4039,12 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>376.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>258.00฿</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
@@ -4051,7 +4055,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ZY202464580877#8</t>
+          <t>ZY202464580877#2</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -4067,7 +4071,7 @@
       <c r="E53" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-14</t>
+ รถ lot18655-9-15</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -4087,12 +4091,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>28.90</t>
+          <t>25.10</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>0.0800</t>
+          <t>0.0483</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -4102,12 +4106,12 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>376.50฿</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>480.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
@@ -4118,7 +4122,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ZY202464580877#6</t>
+          <t>ZY202464580877#8</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -4134,7 +4138,7 @@
       <c r="E54" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-13</t>
+ รถ lot18655-9-14</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -4154,12 +4158,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>20.90</t>
+          <t>28.90</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>0.0534</t>
+          <t>0.0800</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -4174,7 +4178,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>320.40฿</t>
+          <t>480.00฿</t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
@@ -4185,7 +4189,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ZY202464580877#5</t>
+          <t>ZY202464580877#6</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -4201,7 +4205,7 @@
       <c r="E55" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-12</t>
+ รถ lot18655-9-13</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -4221,12 +4225,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>26.20</t>
+          <t>20.90</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>0.0535</t>
+          <t>0.0534</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -4236,12 +4240,12 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>393.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>320.40฿</t>
         </is>
       </c>
       <c r="N55" t="inlineStr"/>
@@ -4252,7 +4256,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ZY202464580877</t>
+          <t>ZY202464580877#5</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -4268,7 +4272,7 @@
       <c r="E56" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-11</t>
+ รถ lot18655-9-12</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -4288,12 +4292,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>20.70</t>
+          <t>26.20</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>0.0531</t>
+          <t>0.0535</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -4303,12 +4307,12 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>393.00฿</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>318.60฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
@@ -4319,7 +4323,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ZY202464580877#9</t>
+          <t>ZY202464580877</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -4335,7 +4339,7 @@
       <c r="E57" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-10</t>
+ รถ lot18655-9-11</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -4355,12 +4359,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>27.70</t>
+          <t>20.70</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>0.0800</t>
+          <t>0.0531</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -4375,7 +4379,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>480.00฿</t>
+          <t>318.60฿</t>
         </is>
       </c>
       <c r="N57" t="inlineStr"/>
@@ -4386,7 +4390,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ZY202464580877#3</t>
+          <t>ZY202464580877#9</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -4402,7 +4406,7 @@
       <c r="E58" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-9</t>
+ รถ lot18655-9-10</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -4422,12 +4426,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>27.10</t>
+          <t>27.70</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>0.0567</t>
+          <t>0.0800</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -4437,19 +4441,15 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>406.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>补胎胶片/9件</t>
-        </is>
-      </c>
+          <t>480.00฿</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>S71090288685</t>
+          <t>ZY202464580877#3</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4467,38 +4467,38 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>UN-INV260831-00017</t>
+          <t>UN-INV260901-00057</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18634-7-3</t>
+ รถ lot18655-9-9</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>29/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>12.10</t>
+          <t>27.10</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>0.0240</t>
+          <t>0.0567</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4508,7 +4508,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>181.50฿</t>
+          <t>406.50฿</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -4518,7 +4518,7 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>补胎胶片/9件</t>
         </is>
       </c>
     </row>
@@ -4528,7 +4528,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>YT7638092409979</t>
+          <t>S71090288685</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4538,38 +4538,38 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>UN-INV260822-00010</t>
+          <t>UN-INV260831-00017</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18569-7-7</t>
+ รถ lot18634-7-3</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>16/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>16/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>29/08/2026</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>15.00</t>
+          <t>12.10</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>0.0140</t>
+          <t>0.0240</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>225.00฿</t>
+          <t>181.50฿</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -4599,7 +4599,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>435308000517585</t>
+          <t>YT7638092409979</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4615,32 +4615,32 @@
       <c r="E61" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18550-6-11</t>
+ รถ lot18569-7-7</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>16/08/2026</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>16/08/2026</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>0.0032</t>
+          <t>0.0140</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -4650,7 +4650,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>54.00฿</t>
+          <t>225.00฿</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -4660,7 +4660,7 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>气门嘴</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -4670,7 +4670,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>710094401487</t>
+          <t>435308000517585</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4686,17 +4686,17 @@
       <c r="E62" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18544-8-14</t>
+ รถ lot18550-6-11</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4706,32 +4706,32 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>107.10</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>0.4536</t>
+          <t>0.0032</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>54.00฿</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>2,721.60฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>空的高压充气罐/一票10件，仓库实收到9件，已确认收到的9件先发</t>
+          <t>气门嘴</t>
         </is>
       </c>
     </row>
@@ -4741,7 +4741,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>773435675083665</t>
+          <t>710094401487</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4751,58 +4751,58 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>UN-INV260815-00046</t>
+          <t>UN-INV260822-00010</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18526-6-17</t>
+ รถ lot18544-8-14</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>13.10</t>
+          <t>107.10</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>0.0214</t>
+          <t>0.4536</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>196.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2,721.60฿</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>补胎工具</t>
+          <t>空的高压充气罐/一票10件，仓库实收到9件，已确认收到的9件先发</t>
         </is>
       </c>
     </row>
@@ -4812,7 +4812,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>YT7637032206975</t>
+          <t>773435675083665</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4822,38 +4822,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>UN-INV260819-00010</t>
+          <t>UN-INV260815-00046</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>มอก.
- รถ lot18523-6-30</t>
+          <t>ธรรมดา
+ รถ lot18526-6-17</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>16/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>9.60</t>
+          <t>13.10</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>0.0316</t>
+          <t>0.0214</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>196.50฿</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>214.88฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>气动模具研磨机+配件</t>
+          <t>补胎工具</t>
         </is>
       </c>
     </row>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>ZY202466648481#5</t>
+          <t>YT7637032206975</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4893,13 +4893,13 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>UN-INV260815-00046</t>
+          <t>UN-INV260819-00010</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>ธรรมดา
- รถ lot18519-6-17</t>
+          <t>มอก.
+ รถ lot18523-6-30</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -4914,17 +4914,17 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>15/08/2026</t>
+          <t>16/08/2026</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>16.10</t>
+          <t>9.60</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>0.0493</t>
+          <t>0.0316</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -4939,10 +4939,14 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>295.80฿</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
+          <t>214.88฿</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>气动模具研磨机+配件</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -4950,7 +4954,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>ZY202466648481#4</t>
+          <t>ZY202466648481#5</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4966,7 +4970,7 @@
       <c r="E66" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18519-6-16</t>
+ รถ lot18519-6-17</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -4986,12 +4990,12 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>20.50</t>
+          <t>16.10</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>0.0656</t>
+          <t>0.0493</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -5006,7 +5010,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>393.60฿</t>
+          <t>295.80฿</t>
         </is>
       </c>
       <c r="N66" t="inlineStr"/>
@@ -5017,7 +5021,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>ZY202466648481#3</t>
+          <t>ZY202466648481#4</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -5033,7 +5037,7 @@
       <c r="E67" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18519-6-15</t>
+ รถ lot18519-6-16</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -5053,12 +5057,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>15.70</t>
+          <t>20.50</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>0.0508</t>
+          <t>0.0656</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -5073,7 +5077,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>304.80฿</t>
+          <t>393.60฿</t>
         </is>
       </c>
       <c r="N67" t="inlineStr"/>
@@ -5084,7 +5088,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>ZY202466648481#2</t>
+          <t>ZY202466648481#3</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -5100,7 +5104,7 @@
       <c r="E68" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18519-6-14</t>
+ รถ lot18519-6-15</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -5120,12 +5124,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>20.20</t>
+          <t>15.70</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>0.0660</t>
+          <t>0.0508</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -5140,7 +5144,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>396.00฿</t>
+          <t>304.80฿</t>
         </is>
       </c>
       <c r="N68" t="inlineStr"/>
@@ -5151,7 +5155,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>ZY202466648481</t>
+          <t>ZY202466648481#2</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -5167,7 +5171,7 @@
       <c r="E69" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18519-6-13</t>
+ รถ lot18519-6-14</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -5187,12 +5191,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>15.80</t>
+          <t>20.20</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>0.0522</t>
+          <t>0.0660</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -5207,14 +5211,10 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>313.20฿</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr">
-        <is>
-          <t>补胎胶条/5件</t>
-        </is>
-      </c>
+          <t>396.00฿</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -5222,7 +5222,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>113204676267#2</t>
+          <t>ZY202466648481</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -5238,32 +5238,32 @@
       <c r="E70" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18518-5-3</t>
+ รถ lot18519-6-13</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>15/08/2026</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>24.60</t>
+          <t>15.80</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>0.0608</t>
+          <t>0.0522</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -5273,15 +5273,19 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>369.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
+          <t>313.20฿</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>补胎胶条/5件</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -5289,7 +5293,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>113204676267</t>
+          <t>113204676267#2</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -5305,7 +5309,7 @@
       <c r="E71" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18518-5-2</t>
+ รถ lot18518-5-3</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -5325,12 +5329,12 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>25.00</t>
+          <t>24.60</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>0.0566</t>
+          <t>0.0608</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -5340,7 +5344,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>375.00฿</t>
+          <t>369.00฿</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -5348,11 +5352,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N71" t="inlineStr">
-        <is>
-          <t>真空胎冷补胶片</t>
-        </is>
-      </c>
+      <c r="N71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -5360,7 +5360,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>910061892464#2</t>
+          <t>113204676267</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -5376,32 +5376,32 @@
       <c r="E72" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18505-5-23</t>
+ รถ lot18518-5-2</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>30.40</t>
+          <t>25.00</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>0.0523</t>
+          <t>0.0566</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -5411,7 +5411,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>456.00฿</t>
+          <t>375.00฿</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -5419,7 +5419,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N72" t="inlineStr"/>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>真空胎冷补胶片</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -5427,7 +5431,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>910061892464</t>
+          <t>910061892464#2</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -5443,7 +5447,7 @@
       <c r="E73" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18505-5-22</t>
+ รถ lot18505-5-23</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -5463,12 +5467,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>15.90</t>
+          <t>30.40</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>0.0353</t>
+          <t>0.0523</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -5478,7 +5482,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>238.50฿</t>
+          <t>456.00฿</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -5486,11 +5490,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t>记号蜡笔</t>
-        </is>
-      </c>
+      <c r="N73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -5498,7 +5498,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>773434709817985</t>
+          <t>910061892464</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -5508,38 +5508,38 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>UN-INV260819-00010</t>
+          <t>UN-INV260815-00046</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18535-8</t>
+ รถ lot18505-5-22</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>16/08/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>15.90</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>0.0184</t>
+          <t>0.0353</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -5549,17 +5549,17 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>238.50฿</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>110.40฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>锅具 二次包装货物变形</t>
+          <t>记号蜡笔</t>
         </is>
       </c>
     </row>
@@ -5569,7 +5569,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>435295775627304</t>
+          <t>773434709817985</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -5579,38 +5579,38 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>UN-INV260811-00012</t>
+          <t>UN-INV260819-00010</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18492-2</t>
+ รถ lot18535-8</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>16/08/2026</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>5.30</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>0.0090</t>
+          <t>0.0184</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -5620,17 +5620,17 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>79.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>110.40฿</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>配件 破损件</t>
+          <t>锅具 二次包装货物变形</t>
         </is>
       </c>
     </row>
@@ -5640,7 +5640,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>YT7636332367470</t>
+          <t>435295775627304</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5656,7 +5656,7 @@
       <c r="E76" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18487-2-27</t>
+ รถ lot18492-2</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -5676,12 +5676,12 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>5.30</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>0.0004</t>
+          <t>0.0090</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -5691,17 +5691,17 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>79.50฿</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>10.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>立牌</t>
+          <t>配件 破损件</t>
         </is>
       </c>
     </row>
@@ -5711,7 +5711,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>S35386280517#2</t>
+          <t>YT7636332367470</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -5727,32 +5727,32 @@
       <c r="E77" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18475-24</t>
+ รถ lot18487-2-27</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>8.80</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>0.0045</t>
+          <t>0.0004</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -5762,15 +5762,19 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>132.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr"/>
+          <t>10.00฿</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>立牌</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -5778,7 +5782,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>S35386280517</t>
+          <t>S35386280517#2</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -5794,7 +5798,7 @@
       <c r="E78" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18475-23</t>
+ รถ lot18475-24</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -5814,22 +5818,22 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>103.50</t>
+          <t>8.80</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>0.2236</t>
+          <t>0.0045</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>1,552.50฿</t>
+          <t>132.00฿</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -5837,11 +5841,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N78" t="inlineStr">
-        <is>
-          <t>气门嘴 顺心捷达，一票16件</t>
-        </is>
-      </c>
+      <c r="N78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -5849,7 +5849,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>YT7635787693833</t>
+          <t>S35386280517</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -5865,7 +5865,7 @@
       <c r="E79" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18473-6-41</t>
+ รถ lot18475-23</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -5880,37 +5880,37 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>13.80</t>
+          <t>103.50</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>0.0432</t>
+          <t>0.2236</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1,552.50฿</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>259.20฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>气压表/面单没有代码</t>
+          <t>气门嘴 顺心捷达，一票16件</t>
         </is>
       </c>
     </row>
@@ -5920,7 +5920,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>ZY202465806614</t>
+          <t>YT7635787693833</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -5930,38 +5930,38 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>UN-INV260807-00009</t>
+          <t>UN-INV260811-00012</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>มอก.
- รถ lot18466-5-51</t>
+          <t>ธรรมดา
+ รถ lot18473-6-41</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>11.30</t>
+          <t>13.80</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>0.0655</t>
+          <t>0.0432</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -5976,12 +5976,12 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>445.40฿</t>
+          <t>259.20฿</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>电子数显胎压枪</t>
+          <t>气压表/面单没有代码</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>113177184579#7</t>
+          <t>ZY202465806614</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -6006,18 +6006,18 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>ธรรมดา
- รถ lot18463-17</t>
+          <t>มอก.
+ รถ lot18466-5-51</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -6027,12 +6027,12 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>9.70</t>
+          <t>11.30</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>0.0305</t>
+          <t>0.0655</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -6047,10 +6047,14 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>183.00฿</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr"/>
+          <t>445.40฿</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>电子数显胎压枪</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -6058,7 +6062,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>113177184579#5</t>
+          <t>113177184579#7</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -6074,7 +6078,7 @@
       <c r="E82" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-16</t>
+ รถ lot18463-17</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -6094,12 +6098,12 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>15.00</t>
+          <t>9.70</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>0.0137</t>
+          <t>0.0305</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -6109,12 +6113,12 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>225.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>183.00฿</t>
         </is>
       </c>
       <c r="N82" t="inlineStr"/>
@@ -6125,7 +6129,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>113177184579#4</t>
+          <t>113177184579#5</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -6141,7 +6145,7 @@
       <c r="E83" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-15</t>
+ รถ lot18463-16</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -6161,12 +6165,12 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>7.30</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>0.0235</t>
+          <t>0.0137</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -6176,12 +6180,12 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>225.00฿</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>141.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N83" t="inlineStr"/>
@@ -6192,7 +6196,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>113177184579#3</t>
+          <t>113177184579#4</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -6208,7 +6212,7 @@
       <c r="E84" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-14</t>
+ รถ lot18463-15</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -6228,12 +6232,12 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>11.90</t>
+          <t>7.30</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>0.0302</t>
+          <t>0.0235</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -6248,7 +6252,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>181.20฿</t>
+          <t>141.00฿</t>
         </is>
       </c>
       <c r="N84" t="inlineStr"/>
@@ -6259,7 +6263,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>113177184579#6</t>
+          <t>113177184579#3</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -6275,7 +6279,7 @@
       <c r="E85" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-13</t>
+ รถ lot18463-14</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -6295,12 +6299,12 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>26.10</t>
+          <t>11.90</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>0.0673</t>
+          <t>0.0302</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -6315,7 +6319,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>403.80฿</t>
+          <t>181.20฿</t>
         </is>
       </c>
       <c r="N85" t="inlineStr"/>
@@ -6326,7 +6330,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>435289604798626</t>
+          <t>113177184579#6</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -6342,7 +6346,7 @@
       <c r="E86" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18462-6-6</t>
+ รถ lot18463-13</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -6352,7 +6356,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -6362,12 +6366,12 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>9.60</t>
+          <t>26.10</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>0.0090</t>
+          <t>0.0673</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -6377,19 +6381,15 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>144.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr">
-        <is>
-          <t>螺丝配件</t>
-        </is>
-      </c>
+          <t>403.80฿</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -6397,7 +6397,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>113177184579#2</t>
+          <t>435289604798626</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -6413,7 +6413,7 @@
       <c r="E87" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-12</t>
+ รถ lot18462-6-6</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -6423,7 +6423,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -6433,12 +6433,12 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>5.30</t>
+          <t>9.60</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>0.0635</t>
+          <t>0.0090</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -6448,15 +6448,19 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>144.00฿</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>381.00฿</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>螺丝配件</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -6464,7 +6468,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>113177184579</t>
+          <t>113177184579#2</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -6480,7 +6484,7 @@
       <c r="E88" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-11</t>
+ รถ lot18463-12</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -6500,12 +6504,12 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>13.30</t>
+          <t>5.30</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>0.1176</t>
+          <t>0.0635</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -6520,14 +6524,10 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>705.60฿</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr">
-        <is>
-          <t>蘑菇钉补胎贴</t>
-        </is>
-      </c>
+          <t>381.00฿</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -6535,7 +6535,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>435289604798722</t>
+          <t>113177184579</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -6551,7 +6551,7 @@
       <c r="E89" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18462-3</t>
+ รถ lot18463-11</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -6561,7 +6561,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -6571,12 +6571,12 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>4.30</t>
+          <t>13.30</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>0.0029</t>
+          <t>0.1176</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -6586,17 +6586,17 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>64.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>705.60฿</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>气门嘴</t>
+          <t>蘑菇钉补胎贴</t>
         </is>
       </c>
     </row>
@@ -6606,7 +6606,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>ZY202471573119#2</t>
+          <t>435289604798722</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -6622,7 +6622,7 @@
       <c r="E90" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-6</t>
+ รถ lot18462-3</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -6632,7 +6632,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -6642,12 +6642,12 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>8.70</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>0.0441</t>
+          <t>0.0029</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -6657,15 +6657,19 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>64.50฿</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>264.60฿</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>气门嘴</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -6673,7 +6677,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>ZY202471573119</t>
+          <t>ZY202471573119#2</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -6689,7 +6693,7 @@
       <c r="E91" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-5</t>
+ รถ lot18463-6</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -6709,12 +6713,12 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>11.90</t>
+          <t>8.70</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>0.0832</t>
+          <t>0.0441</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -6729,14 +6733,10 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>499.20฿</t>
-        </is>
-      </c>
-      <c r="N91" t="inlineStr">
-        <is>
-          <t>蘑菇钉补胎</t>
-        </is>
-      </c>
+          <t>264.60฿</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -6744,7 +6744,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>YT7635427281240</t>
+          <t>ZY202471573119</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -6760,7 +6760,7 @@
       <c r="E92" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18458-21</t>
+ รถ lot18463-5</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -6780,12 +6780,12 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>11.90</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>0.0117</t>
+          <t>0.0832</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -6800,12 +6800,12 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>70.20฿</t>
+          <t>499.20฿</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>气阀</t>
+          <t>蘑菇钉补胎</t>
         </is>
       </c>
     </row>
@@ -6815,7 +6815,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>79021262374216</t>
+          <t>YT7635427281240</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -6825,38 +6825,38 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>UN-INV260804-00019</t>
+          <t>UN-INV260807-00009</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18435-5-73</t>
+ รถ lot18458-21</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>12.20</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>0.0352</t>
+          <t>0.0117</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -6871,12 +6871,12 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>211.20฿</t>
+          <t>70.20฿</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>加长弯头</t>
+          <t>气阀</t>
         </is>
       </c>
     </row>
@@ -6886,7 +6886,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>113162219964#3</t>
+          <t>79021262374216</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -6902,17 +6902,17 @@
       <c r="E94" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18434-9-28</t>
+ รถ lot18435-5-73</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>18.70</t>
+          <t>12.20</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>0.0443</t>
+          <t>0.0352</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -6937,15 +6937,19 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>280.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N94" t="inlineStr"/>
+          <t>211.20฿</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>加长弯头</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -6953,7 +6957,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>113162219964#2</t>
+          <t>113162219964#3</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -6969,7 +6973,7 @@
       <c r="E95" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18434-9-27</t>
+ รถ lot18434-9-28</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -6989,12 +6993,12 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>22.90</t>
+          <t>18.70</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>0.0522</t>
+          <t>0.0443</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -7004,7 +7008,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>343.50฿</t>
+          <t>280.50฿</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -7020,7 +7024,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>113162219964</t>
+          <t>113162219964#2</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -7036,7 +7040,7 @@
       <c r="E96" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18434-9-26</t>
+ รถ lot18434-9-27</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -7056,12 +7060,12 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>25.60</t>
+          <t>22.90</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>0.0574</t>
+          <t>0.0522</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -7071,7 +7075,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>384.00฿</t>
+          <t>343.50฿</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -7079,11 +7083,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N96" t="inlineStr">
-        <is>
-          <t>补胎胶片/3件</t>
-        </is>
-      </c>
+      <c r="N96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -7091,7 +7091,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>113158800045#2</t>
+          <t>113162219964</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -7107,32 +7107,32 @@
       <c r="E97" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18427-7-3</t>
+ รถ lot18434-9-26</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>26/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>26/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>26.30</t>
+          <t>25.60</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>0.0377</t>
+          <t>0.0574</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -7142,7 +7142,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>394.50฿</t>
+          <t>384.00฿</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -7150,7 +7150,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N97" t="inlineStr"/>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>补胎胶片/3件</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -7158,7 +7162,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>113158800045</t>
+          <t>113158800045#2</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -7174,7 +7178,7 @@
       <c r="E98" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18427-7-2</t>
+ รถ lot18427-7-3</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -7194,12 +7198,12 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>26.50</t>
+          <t>26.30</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>0.0379</t>
+          <t>0.0377</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -7209,7 +7213,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>397.50฿</t>
+          <t>394.50฿</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -7217,11 +7221,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N98" t="inlineStr">
-        <is>
-          <t>塑料配件/2件</t>
-        </is>
-      </c>
+      <c r="N98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -7229,7 +7229,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>YT2550516723148</t>
+          <t>113158800045</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -7245,32 +7245,32 @@
       <c r="E99" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18398-3-10</t>
+ รถ lot18427-7-2</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>22/07/2026</t>
+          <t>26/07/2026</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>23/07/2026</t>
+          <t>26/07/2026</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>26.50</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>0.0127</t>
+          <t>0.0379</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -7280,17 +7280,17 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>397.50฿</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>76.20฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>硅胶风管</t>
+          <t>塑料配件/2件</t>
         </is>
       </c>
     </row>
@@ -7300,7 +7300,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>ZY202467269952#4</t>
+          <t>YT2550516723148</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -7310,38 +7310,38 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>UN-INV260724-00013</t>
+          <t>UN-INV260804-00019</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18314-8-30</t>
+ รถ lot18398-3-10</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>11/07/2026</t>
+          <t>22/07/2026</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>12/07/2026</t>
+          <t>23/07/2026</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>15.50</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>0.0492</t>
+          <t>0.0127</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -7356,10 +7356,14 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>295.20฿</t>
-        </is>
-      </c>
-      <c r="N100" t="inlineStr"/>
+          <t>76.20฿</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>硅胶风管</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -7367,7 +7371,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>ZY202467269952#3</t>
+          <t>ZY202467269952#4</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -7383,7 +7387,7 @@
       <c r="E101" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18314-8-29</t>
+ รถ lot18314-8-30</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -7403,12 +7407,12 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>12.50</t>
+          <t>15.50</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>0.0300</t>
+          <t>0.0492</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -7418,12 +7422,12 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>187.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>295.20฿</t>
         </is>
       </c>
       <c r="N101" t="inlineStr"/>

--- a/cargo_packages_p1-5.xlsx
+++ b/cargo_packages_p1-5.xlsx
@@ -522,7 +522,7 @@
       <c r="E2" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18810-8-3</t>
+ รถ lot18810-6-3</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -532,7 +532,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">

--- a/cargo_packages_p1-5.xlsx
+++ b/cargo_packages_p1-5.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>S71195667064</t>
+          <t>435358249576981</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -522,17 +522,17 @@
       <c r="E2" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18810-6-3</t>
+ รถ lot18815-4-6</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -542,32 +542,32 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>165.00</t>
+          <t>5.20</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.8568</t>
+          <t>0.0044</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>78.00฿</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>5,140.80฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>千斤顶，3件，客户不打木架发</t>
+          <t>气门嘴</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>113350746029#4</t>
+          <t>S71195667064</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -593,17 +593,17 @@
       <c r="E3" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18799-6-32</t>
+ รถ lot18810-6-3</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -613,17 +613,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>27.70</t>
+          <t>165.00</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.0800</t>
+          <t>0.8568</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -633,10 +633,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>480.00฿</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>5,140.80฿</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>千斤顶，3件，客户不打木架发</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -644,7 +648,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>113350746029#3</t>
+          <t>113350746029#4</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -660,7 +664,7 @@
       <c r="E4" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18799-6-31</t>
+ รถ lot18799-6-32</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -680,12 +684,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10.90</t>
+          <t>27.70</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.0377</t>
+          <t>0.0800</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -700,7 +704,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>226.20฿</t>
+          <t>480.00฿</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -711,7 +715,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>113350746029#2</t>
+          <t>113350746029#3</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -727,7 +731,7 @@
       <c r="E5" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18799-6-30</t>
+ รถ lot18799-6-31</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -747,12 +751,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>15.00</t>
+          <t>10.90</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.0101</t>
+          <t>0.0377</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -762,12 +766,12 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>225.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>226.20฿</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -778,7 +782,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>113350746029</t>
+          <t>113350746029#2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -794,7 +798,7 @@
       <c r="E6" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18799-6-29</t>
+ รถ lot18799-6-30</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -814,12 +818,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>16.50</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.0127</t>
+          <t>0.0101</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -829,7 +833,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>247.50฿</t>
+          <t>225.00฿</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -837,11 +841,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>真空胎加固修理补片</t>
-        </is>
-      </c>
+      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -849,7 +849,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>760246657062</t>
+          <t>113350746029</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -865,7 +865,7 @@
       <c r="E7" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18799-7-3</t>
+ รถ lot18799-6-29</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -885,12 +885,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>16.50</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.0005</t>
+          <t>0.0127</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -900,17 +900,17 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>247.50฿</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>10.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>气门嘴，轮胎修补工具，气门芯宣传册</t>
+          <t>真空胎加固修理补片</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>113348267192#2</t>
+          <t>760246657062</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -936,17 +936,17 @@
       <c r="E8" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18795-2-7</t>
+ รถ lot18799-7-3</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>28.10</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.0628</t>
+          <t>0.0005</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -971,15 +971,19 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>421.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>10.00฿</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>气门嘴，轮胎修补工具，气门芯宣传册</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -987,7 +991,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>113348267192</t>
+          <t>113348267192#2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1003,7 +1007,7 @@
       <c r="E9" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18795-2-6</t>
+ รถ lot18795-2-7</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1023,12 +1027,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>19.50</t>
+          <t>28.10</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.0505</t>
+          <t>0.0628</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1038,19 +1042,15 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>421.50฿</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>303.00฿</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>补胎胶片</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ZY202472578299</t>
+          <t>113348267192</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1074,17 +1074,17 @@
       <c r="E10" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18758-7-43</t>
+ รถ lot18795-2-6</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1094,17 +1094,17 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>47.40</t>
+          <t>19.50</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.1603</t>
+          <t>0.0505</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1114,12 +1114,12 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>961.20฿</t>
+          <t>303.00฿</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>补胎贴，3件</t>
+          <t>补胎胶片</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>773440822655698</t>
+          <t>ZY202472578299</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1145,7 +1145,7 @@
       <c r="E11" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18758-4-31</t>
+ รถ lot18758-7-43</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1160,37 +1160,37 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>47.40</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.0022</t>
+          <t>0.1603</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>18.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>961.20฿</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>钻头</t>
+          <t>补胎贴，3件</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>YT7642998390994</t>
+          <t>773440822655698</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1216,7 +1216,7 @@
       <c r="E12" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18769-3-57</t>
+ รถ lot18758-4-31</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1226,22 +1226,22 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>5.80</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0.0070</t>
+          <t>0.0022</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>87.00฿</t>
+          <t>18.00฿</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>钻头</t>
         </is>
       </c>
     </row>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>DPK212614057101</t>
+          <t>YT7642998390994</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1281,38 +1281,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>UN-INV260916-00003</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18749-4-3</t>
+ รถ lot18769-3-57</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>9.60</t>
+          <t>5.80</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0.0060</t>
+          <t>0.0070</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>144.00฿</t>
+          <t>87.00฿</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>轮胎气门嘴</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>79031204783305</t>
+          <t>DPK212614057101</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1358,7 +1358,7 @@
       <c r="E14" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18744-6-15</t>
+ รถ lot18749-4-3</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1378,12 +1378,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>9.60</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.0020</t>
+          <t>0.0060</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1393,7 +1393,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>39.00฿</t>
+          <t>144.00฿</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>轮胎气门嘴</t>
         </is>
       </c>
     </row>
@@ -1413,7 +1413,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>435342988112655</t>
+          <t>79031204783305</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1429,17 +1429,17 @@
       <c r="E15" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18743-3-34</t>
+ รถ lot18744-6-15</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.0014</t>
+          <t>0.0020</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1464,17 +1464,17 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>39.00฿</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>10.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>橡胶垫圈</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>435343890137834</t>
+          <t>435342988112655</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1500,7 +1500,7 @@
       <c r="E16" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18743-7-25</t>
+ รถ lot18743-3-34</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1520,12 +1520,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>21.40</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>0.0080</t>
+          <t>0.0014</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1535,17 +1535,17 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>321.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10.00฿</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>扒胎机包胶撬棍</t>
+          <t>橡胶垫圈</t>
         </is>
       </c>
     </row>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>YT7642670434639</t>
+          <t>435343890137834</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1571,7 +1571,7 @@
       <c r="E17" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18743-2-8</t>
+ รถ lot18743-7-25</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>21.40</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.0010</t>
+          <t>0.0080</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>12.00฿</t>
+          <t>321.00฿</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>片片</t>
+          <t>扒胎机包胶撬棍</t>
         </is>
       </c>
     </row>
@@ -1626,7 +1626,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>93015797092</t>
+          <t>YT7642670434639</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1636,18 +1636,18 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>UN-INV260914-00014</t>
+          <t>UN-INV260916-00003</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18735-4-40</t>
+ รถ lot18743-2-8</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1657,17 +1657,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>12/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>8.60</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>0.0148</t>
+          <t>0.0010</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>129.00฿</t>
+          <t>12.00฿</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1687,7 +1687,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>仪表</t>
+          <t>片片</t>
         </is>
       </c>
     </row>
@@ -1697,7 +1697,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>YT7642390374765</t>
+          <t>93015797092</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1707,13 +1707,13 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>UN-INV260914-00015</t>
+          <t>UN-INV260914-00014</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18735-4-20</t>
+ รถ lot18735-4-40</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1733,12 +1733,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>20.80</t>
+          <t>8.60</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>0.0598</t>
+          <t>0.0148</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1748,17 +1748,17 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>129.00฿</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>358.80฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>打磨机</t>
+          <t>仪表</t>
         </is>
       </c>
     </row>
@@ -1768,7 +1768,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>435342255104130</t>
+          <t>YT7642390374765</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1778,13 +1778,13 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>UN-INV260914-00014</t>
+          <t>UN-INV260914-00015</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18735-43</t>
+ รถ lot18735-4-20</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>4.90</t>
+          <t>20.80</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0.0172</t>
+          <t>0.0598</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>103.20฿</t>
+          <t>358.80฿</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>轮毂保护套</t>
+          <t>打磨机</t>
         </is>
       </c>
     </row>
@@ -1839,7 +1839,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>773440312345715</t>
+          <t>435342255104130</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1855,7 +1855,7 @@
       <c r="E21" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18735-3-78</t>
+ รถ lot18735-43</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1875,12 +1875,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>4.90</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.0013</t>
+          <t>0.0172</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1890,17 +1890,17 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>19.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>103.20฿</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>轮毂保护套</t>
         </is>
       </c>
     </row>
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>773440291470393</t>
+          <t>773440312345715</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1926,7 +1926,7 @@
       <c r="E22" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18735-34</t>
+ รถ lot18735-3-78</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1946,12 +1946,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.0029</t>
+          <t>0.0013</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>48.00฿</t>
+          <t>19.50฿</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1971,7 +1971,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>球阀</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>435342261175750</t>
+          <t>773440291470393</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1991,13 +1991,13 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>UN-INV260914-00015</t>
+          <t>UN-INV260914-00014</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18736-13</t>
+ รถ lot18735-34</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2017,12 +2017,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>13.90</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.0137</t>
+          <t>0.0029</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>208.50฿</t>
+          <t>48.00฿</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2042,7 +2042,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>球阀</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ZY202461195200</t>
+          <t>435342261175750</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2068,7 +2068,7 @@
       <c r="E24" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18728-7-13</t>
+ รถ lot18736-13</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2083,17 +2083,17 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>13/09/2026</t>
+          <t>12/09/2026</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>47.40</t>
+          <t>13.90</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.0116</t>
+          <t>0.0137</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2103,7 +2103,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>711.00฿</t>
+          <t>208.50฿</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>79030687835952</t>
+          <t>ZY202461195200</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2133,13 +2133,13 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>UN-INV260914-00014</t>
+          <t>UN-INV260914-00015</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18728-3-64</t>
+ รถ lot18728-7-13</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2159,12 +2159,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>4.30</t>
+          <t>47.40</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.0030</t>
+          <t>0.0116</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>64.50฿</t>
+          <t>711.00฿</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>接头配件</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -2194,7 +2194,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>LJ20722214#3</t>
+          <t>79030687835952</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2204,38 +2204,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>UN-INV260912-00011</t>
+          <t>UN-INV260914-00014</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18726-7-8</t>
+ รถ lot18728-3-64</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>13/09/2026</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>14.00</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>0.0171</t>
+          <t>0.0030</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2245,7 +2245,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>210.00฿</t>
+          <t>64.50฿</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2253,7 +2253,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>接头配件</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2261,7 +2265,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>LJ20722214#2</t>
+          <t>LJ20722214#3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2277,7 +2281,7 @@
       <c r="E27" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18726-7-7</t>
+ รถ lot18726-7-8</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2297,12 +2301,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>11.90</t>
+          <t>14.00</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.0089</t>
+          <t>0.0171</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2312,7 +2316,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>178.50฿</t>
+          <t>210.00฿</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2328,7 +2332,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>LJ20722214</t>
+          <t>LJ20722214#2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2344,7 +2348,7 @@
       <c r="E28" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18726-7-6</t>
+ รถ lot18726-7-7</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2364,12 +2368,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>16.00</t>
+          <t>11.90</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.0144</t>
+          <t>0.0089</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2379,7 +2383,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>240.00฿</t>
+          <t>178.50฿</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2387,11 +2391,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>电板套筒配件/3件</t>
-        </is>
-      </c>
+      <c r="N28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2399,7 +2399,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>YT7641966426761</t>
+          <t>LJ20722214</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2415,17 +2415,17 @@
       <c r="E29" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18714-9-23</t>
+ รถ lot18726-7-6</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2435,12 +2435,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>13.60</t>
+          <t>16.00</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0.0422</t>
+          <t>0.0144</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2450,17 +2450,17 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>240.00฿</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>253.20฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>带表汽车轮胎打气嘴</t>
+          <t>电板套筒配件/3件</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ZY202471681117#2</t>
+          <t>YT7641966426761</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2486,7 +2486,7 @@
       <c r="E30" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18714-9-8</t>
+ รถ lot18714-9-23</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>11.80</t>
+          <t>13.60</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.0832</t>
+          <t>0.0422</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2526,10 +2526,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>499.20฿</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
+          <t>253.20฿</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>带表汽车轮胎打气嘴</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2537,7 +2541,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ZY202471681117</t>
+          <t>ZY202471681117#2</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2553,7 +2557,7 @@
       <c r="E31" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18714-9-7</t>
+ รถ lot18714-9-8</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2573,12 +2577,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>7.70</t>
+          <t>11.80</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.0493</t>
+          <t>0.0832</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2593,14 +2597,10 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>295.80฿</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>补胎胶片/2件</t>
-        </is>
-      </c>
+          <t>499.20฿</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>302285502767#2</t>
+          <t>ZY202471681117</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2624,7 +2624,7 @@
       <c r="E32" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18714-8-10</t>
+ รถ lot18714-9-7</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2644,12 +2644,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>33.70</t>
+          <t>7.70</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.0145</t>
+          <t>0.0493</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2659,15 +2659,19 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>505.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
+          <t>295.80฿</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>补胎胶片/2件</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2675,7 +2679,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>302285502767</t>
+          <t>302285502767#2</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2691,7 +2695,7 @@
       <c r="E33" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18714-8-9</t>
+ รถ lot18714-8-10</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2711,12 +2715,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>23.40</t>
+          <t>33.70</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.0123</t>
+          <t>0.0145</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2726,7 +2730,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>351.00฿</t>
+          <t>505.50฿</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2734,11 +2738,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>扳手</t>
-        </is>
-      </c>
+      <c r="N33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>LJ20716178#2</t>
+          <t>302285502767</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2756,18 +2756,18 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>UN-INV260911-00013</t>
+          <t>UN-INV260912-00011</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18713-6-65</t>
+ รถ lot18714-8-9</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2777,17 +2777,17 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>19.50</t>
+          <t>23.40</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.0075</t>
+          <t>0.0123</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2797,7 +2797,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>292.50฿</t>
+          <t>351.00฿</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2805,7 +2805,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>扳手</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2813,7 +2817,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>LJ20716178</t>
+          <t>LJ20716178#2</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2829,7 +2833,7 @@
       <c r="E35" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18713-6-64</t>
+ รถ lot18713-6-65</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2849,7 +2853,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>19.60</t>
+          <t>19.50</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2864,7 +2868,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>294.00฿</t>
+          <t>292.50฿</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2872,11 +2876,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>配件</t>
-        </is>
-      </c>
+      <c r="N35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>435338972466812</t>
+          <t>LJ20716178</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2900,7 +2900,7 @@
       <c r="E36" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18710-6-35</t>
+ รถ lot18713-6-64</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2920,12 +2920,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>13.10</t>
+          <t>19.60</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.0624</t>
+          <t>0.0075</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2935,17 +2935,17 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>294.00฿</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>374.40฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>修补工具</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>435334324045675</t>
+          <t>435338972466812</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2965,38 +2965,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>UN-INV260908-00009</t>
+          <t>UN-INV260911-00013</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18696-14</t>
+ รถ lot18710-6-35</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>10.80</t>
+          <t>13.10</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.0088</t>
+          <t>0.0624</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -3006,17 +3006,17 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>162.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>374.40฿</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>修补工具</t>
         </is>
       </c>
     </row>
@@ -3026,7 +3026,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>YT7641276428798</t>
+          <t>435334324045675</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3042,7 +3042,7 @@
       <c r="E38" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18697-11</t>
+ รถ lot18696-14</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -3062,12 +3062,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>9.50</t>
+          <t>10.80</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.0296</t>
+          <t>0.0088</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -3077,12 +3077,12 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>162.00฿</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>177.60฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>79029430531776</t>
+          <t>YT7641276428798</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3107,18 +3107,18 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>UN-INV260907-00015</t>
+          <t>UN-INV260908-00009</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18689-26</t>
+ รถ lot18697-11</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -3128,17 +3128,17 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>9.50</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.0135</t>
+          <t>0.0296</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>81.00฿</t>
+          <t>177.60฿</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>卡套</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>113282578128#2</t>
+          <t>79029430531776</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3184,17 +3184,17 @@
       <c r="E40" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18683-4</t>
+ รถ lot18689-26</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>38.00</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.1601</t>
+          <t>0.0135</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -3224,10 +3224,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>960.60฿</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
+          <t>81.00฿</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>卡套</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -3235,7 +3239,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>113282578128</t>
+          <t>113282578128#2</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3251,7 +3255,7 @@
       <c r="E41" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18683-3</t>
+ รถ lot18683-4</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -3271,12 +3275,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>27.50</t>
+          <t>38.00</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.1566</t>
+          <t>0.1601</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -3291,14 +3295,10 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>939.60฿</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>压条取出器 一票两件破损件</t>
-        </is>
-      </c>
+          <t>960.60฿</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>82730128600#3</t>
+          <t>113282578128</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3322,12 +3322,12 @@
       <c r="E42" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18678-6-21</t>
+ รถ lot18683-3</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>30/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -3342,12 +3342,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>33.00</t>
+          <t>27.50</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.0122</t>
+          <t>0.1566</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3357,15 +3357,19 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>495.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
+          <t>939.60฿</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>压条取出器 一票两件破损件</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -3373,7 +3377,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>82730128600#2</t>
+          <t>82730128600#3</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3389,7 +3393,7 @@
       <c r="E43" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18678-6-20</t>
+ รถ lot18678-6-21</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -3409,12 +3413,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>27.60</t>
+          <t>33.00</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.0095</t>
+          <t>0.0122</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3424,7 +3428,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>414.00฿</t>
+          <t>495.00฿</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3440,7 +3444,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>82730128600</t>
+          <t>82730128600#2</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3456,7 +3460,7 @@
       <c r="E44" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18678-6-19</t>
+ รถ lot18678-6-20</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -3476,12 +3480,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>28.10</t>
+          <t>27.60</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.0118</t>
+          <t>0.0095</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3491,7 +3495,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>421.50฿</t>
+          <t>414.00฿</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3499,11 +3503,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>五金配件/3件</t>
-        </is>
-      </c>
+      <c r="N44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>113278387839#3</t>
+          <t>82730128600</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3521,38 +3521,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>UN-INV260903-00023</t>
+          <t>UN-INV260907-00015</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18663-8-3</t>
+ รถ lot18678-6-19</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>30/08/2026</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>25.30</t>
+          <t>28.10</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.0404</t>
+          <t>0.0118</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3562,7 +3562,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>379.50฿</t>
+          <t>421.50฿</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3570,7 +3570,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>五金配件/3件</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -3578,7 +3582,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>113278387839#2</t>
+          <t>113278387839#3</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3594,7 +3598,7 @@
       <c r="E46" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18663-8-2</t>
+ รถ lot18663-8-3</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -3614,12 +3618,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>26.10</t>
+          <t>25.30</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>0.0304</t>
+          <t>0.0404</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3629,7 +3633,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>391.50฿</t>
+          <t>379.50฿</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3645,7 +3649,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>113278387839</t>
+          <t>113278387839#2</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3661,7 +3665,7 @@
       <c r="E47" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18663-8-1</t>
+ รถ lot18663-8-2</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -3681,12 +3685,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>9.10</t>
+          <t>26.10</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>0.0144</t>
+          <t>0.0304</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3696,7 +3700,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>136.50฿</t>
+          <t>391.50฿</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3704,11 +3708,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>配件/3件</t>
-        </is>
-      </c>
+      <c r="N47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>113276098937#3</t>
+          <t>113278387839</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3726,38 +3726,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>UN-INV260901-00057</t>
+          <t>UN-INV260903-00023</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-45</t>
+ รถ lot18663-8-1</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>17.80</t>
+          <t>9.10</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>0.0302</t>
+          <t>0.0144</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>267.00฿</t>
+          <t>136.50฿</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3775,7 +3775,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>配件/3件</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -3783,7 +3787,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>113276098937#2</t>
+          <t>113276098937#3</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3799,7 +3803,7 @@
       <c r="E49" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-44</t>
+ รถ lot18655-9-45</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3819,12 +3823,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>10.90</t>
+          <t>17.80</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>0.0313</t>
+          <t>0.0302</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3834,12 +3838,12 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>267.00฿</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>187.80฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
@@ -3850,7 +3854,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>113276098937</t>
+          <t>113276098937#2</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3866,7 +3870,7 @@
       <c r="E50" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-43</t>
+ รถ lot18655-9-44</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3886,12 +3890,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>33.60</t>
+          <t>10.90</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>0.0825</t>
+          <t>0.0313</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3901,19 +3905,15 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>504.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>补胎胶片+配件/3件</t>
-        </is>
-      </c>
+          <t>187.80฿</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -3921,7 +3921,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ZY202464580877#4</t>
+          <t>113276098937</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3937,7 +3937,7 @@
       <c r="E51" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-17</t>
+ รถ lot18655-9-43</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>20.10</t>
+          <t>33.60</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>0.0466</t>
+          <t>0.0825</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3972,7 +3972,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>301.50฿</t>
+          <t>504.00฿</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -3980,7 +3980,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr"/>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>补胎胶片+配件/3件</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -3988,7 +3992,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ZY202464580877#7</t>
+          <t>ZY202464580877#4</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -4004,7 +4008,7 @@
       <c r="E52" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-16</t>
+ รถ lot18655-9-17</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -4024,12 +4028,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>16.60</t>
+          <t>20.10</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>0.0430</t>
+          <t>0.0466</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -4039,12 +4043,12 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>301.50฿</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>258.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
@@ -4055,7 +4059,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ZY202464580877#2</t>
+          <t>ZY202464580877#7</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -4071,7 +4075,7 @@
       <c r="E53" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-15</t>
+ รถ lot18655-9-16</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -4091,12 +4095,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>25.10</t>
+          <t>16.60</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>0.0483</t>
+          <t>0.0430</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -4106,12 +4110,12 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>376.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>258.00฿</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
@@ -4122,7 +4126,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ZY202464580877#8</t>
+          <t>ZY202464580877#2</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -4138,7 +4142,7 @@
       <c r="E54" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-14</t>
+ รถ lot18655-9-15</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -4158,12 +4162,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>28.90</t>
+          <t>25.10</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>0.0800</t>
+          <t>0.0483</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -4173,12 +4177,12 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>376.50฿</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>480.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
@@ -4189,7 +4193,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ZY202464580877#6</t>
+          <t>ZY202464580877#8</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -4205,7 +4209,7 @@
       <c r="E55" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-13</t>
+ รถ lot18655-9-14</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -4225,12 +4229,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>20.90</t>
+          <t>28.90</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>0.0534</t>
+          <t>0.0800</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -4245,7 +4249,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>320.40฿</t>
+          <t>480.00฿</t>
         </is>
       </c>
       <c r="N55" t="inlineStr"/>
@@ -4256,7 +4260,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ZY202464580877#5</t>
+          <t>ZY202464580877#6</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -4272,7 +4276,7 @@
       <c r="E56" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-12</t>
+ รถ lot18655-9-13</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -4292,12 +4296,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>26.20</t>
+          <t>20.90</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>0.0535</t>
+          <t>0.0534</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -4307,12 +4311,12 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>393.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>320.40฿</t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
@@ -4323,7 +4327,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ZY202464580877</t>
+          <t>ZY202464580877#5</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -4339,7 +4343,7 @@
       <c r="E57" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-11</t>
+ รถ lot18655-9-12</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -4359,12 +4363,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>20.70</t>
+          <t>26.20</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>0.0531</t>
+          <t>0.0535</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -4374,12 +4378,12 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>393.00฿</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>318.60฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N57" t="inlineStr"/>
@@ -4390,7 +4394,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ZY202464580877#9</t>
+          <t>ZY202464580877</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -4406,7 +4410,7 @@
       <c r="E58" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-10</t>
+ รถ lot18655-9-11</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -4426,12 +4430,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>27.70</t>
+          <t>20.70</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>0.0800</t>
+          <t>0.0531</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -4446,7 +4450,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>480.00฿</t>
+          <t>318.60฿</t>
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
@@ -4457,7 +4461,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ZY202464580877#3</t>
+          <t>ZY202464580877#9</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4473,7 +4477,7 @@
       <c r="E59" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-9</t>
+ รถ lot18655-9-10</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -4493,12 +4497,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>27.10</t>
+          <t>27.70</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>0.0567</t>
+          <t>0.0800</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4508,19 +4512,15 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>406.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>补胎胶片/9件</t>
-        </is>
-      </c>
+          <t>480.00฿</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -4528,7 +4528,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>S71090288685</t>
+          <t>ZY202464580877#3</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4538,38 +4538,38 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>UN-INV260831-00017</t>
+          <t>UN-INV260901-00057</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18634-7-3</t>
+ รถ lot18655-9-9</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>29/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>12.10</t>
+          <t>27.10</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>0.0240</t>
+          <t>0.0567</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>181.50฿</t>
+          <t>406.50฿</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -4589,7 +4589,7 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>补胎胶片/9件</t>
         </is>
       </c>
     </row>
@@ -4599,7 +4599,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>YT7638092409979</t>
+          <t>S71090288685</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4609,38 +4609,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>UN-INV260822-00010</t>
+          <t>UN-INV260831-00017</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18569-7-7</t>
+ รถ lot18634-7-3</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>16/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>16/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>29/08/2026</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>15.00</t>
+          <t>12.10</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>0.0140</t>
+          <t>0.0240</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -4650,7 +4650,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>225.00฿</t>
+          <t>181.50฿</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>435308000517585</t>
+          <t>YT7638092409979</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4686,32 +4686,32 @@
       <c r="E62" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18550-6-11</t>
+ รถ lot18569-7-7</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>16/08/2026</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>16/08/2026</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>0.0032</t>
+          <t>0.0140</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>54.00฿</t>
+          <t>225.00฿</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>气门嘴</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -4741,7 +4741,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>710094401487</t>
+          <t>435308000517585</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4757,17 +4757,17 @@
       <c r="E63" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18544-8-14</t>
+ รถ lot18550-6-11</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4777,32 +4777,32 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>107.10</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>0.4536</t>
+          <t>0.0032</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>54.00฿</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>2,721.60฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>空的高压充气罐/一票10件，仓库实收到9件，已确认收到的9件先发</t>
+          <t>气门嘴</t>
         </is>
       </c>
     </row>
@@ -4812,7 +4812,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>773435675083665</t>
+          <t>710094401487</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4822,58 +4822,58 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>UN-INV260815-00046</t>
+          <t>UN-INV260822-00010</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18526-6-17</t>
+ รถ lot18544-8-14</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>13.10</t>
+          <t>107.10</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>0.0214</t>
+          <t>0.4536</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>196.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2,721.60฿</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>补胎工具</t>
+          <t>空的高压充气罐/一票10件，仓库实收到9件，已确认收到的9件先发</t>
         </is>
       </c>
     </row>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>YT7637032206975</t>
+          <t>773435675083665</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4893,38 +4893,38 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>UN-INV260819-00010</t>
+          <t>UN-INV260815-00046</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>มอก.
- รถ lot18523-6-30</t>
+          <t>ธรรมดา
+ รถ lot18526-6-17</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>16/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>9.60</t>
+          <t>13.10</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>0.0316</t>
+          <t>0.0214</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -4934,17 +4934,17 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>196.50฿</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>214.88฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>气动模具研磨机+配件</t>
+          <t>补胎工具</t>
         </is>
       </c>
     </row>
@@ -4954,7 +4954,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>ZY202466648481#5</t>
+          <t>YT7637032206975</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4964,13 +4964,13 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>UN-INV260815-00046</t>
+          <t>UN-INV260819-00010</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>ธรรมดา
- รถ lot18519-6-17</t>
+          <t>มอก.
+ รถ lot18523-6-30</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -4985,17 +4985,17 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>15/08/2026</t>
+          <t>16/08/2026</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>16.10</t>
+          <t>9.60</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>0.0493</t>
+          <t>0.0316</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -5010,10 +5010,14 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>295.80฿</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr"/>
+          <t>214.88฿</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>气动模具研磨机+配件</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -5021,7 +5025,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>ZY202466648481#4</t>
+          <t>ZY202466648481#5</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -5037,7 +5041,7 @@
       <c r="E67" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18519-6-16</t>
+ รถ lot18519-6-17</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -5057,12 +5061,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>20.50</t>
+          <t>16.10</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>0.0656</t>
+          <t>0.0493</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -5077,7 +5081,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>393.60฿</t>
+          <t>295.80฿</t>
         </is>
       </c>
       <c r="N67" t="inlineStr"/>
@@ -5088,7 +5092,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>ZY202466648481#3</t>
+          <t>ZY202466648481#4</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -5104,7 +5108,7 @@
       <c r="E68" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18519-6-15</t>
+ รถ lot18519-6-16</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -5124,12 +5128,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>15.70</t>
+          <t>20.50</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>0.0508</t>
+          <t>0.0656</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -5144,7 +5148,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>304.80฿</t>
+          <t>393.60฿</t>
         </is>
       </c>
       <c r="N68" t="inlineStr"/>
@@ -5155,7 +5159,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>ZY202466648481#2</t>
+          <t>ZY202466648481#3</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -5171,7 +5175,7 @@
       <c r="E69" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18519-6-14</t>
+ รถ lot18519-6-15</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -5191,12 +5195,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>20.20</t>
+          <t>15.70</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>0.0660</t>
+          <t>0.0508</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -5211,7 +5215,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>396.00฿</t>
+          <t>304.80฿</t>
         </is>
       </c>
       <c r="N69" t="inlineStr"/>
@@ -5222,7 +5226,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>ZY202466648481</t>
+          <t>ZY202466648481#2</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -5238,7 +5242,7 @@
       <c r="E70" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18519-6-13</t>
+ รถ lot18519-6-14</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -5258,12 +5262,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>15.80</t>
+          <t>20.20</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>0.0522</t>
+          <t>0.0660</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -5278,14 +5282,10 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>313.20฿</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t>补胎胶条/5件</t>
-        </is>
-      </c>
+          <t>396.00฿</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -5293,7 +5293,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>113204676267#2</t>
+          <t>ZY202466648481</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -5309,32 +5309,32 @@
       <c r="E71" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18518-5-3</t>
+ รถ lot18519-6-13</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>15/08/2026</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>24.60</t>
+          <t>15.80</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>0.0608</t>
+          <t>0.0522</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -5344,15 +5344,19 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>369.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
+          <t>313.20฿</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>补胎胶条/5件</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -5360,7 +5364,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>113204676267</t>
+          <t>113204676267#2</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -5376,7 +5380,7 @@
       <c r="E72" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18518-5-2</t>
+ รถ lot18518-5-3</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -5396,12 +5400,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>25.00</t>
+          <t>24.60</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>0.0566</t>
+          <t>0.0608</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -5411,7 +5415,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>375.00฿</t>
+          <t>369.00฿</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -5419,11 +5423,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N72" t="inlineStr">
-        <is>
-          <t>真空胎冷补胶片</t>
-        </is>
-      </c>
+      <c r="N72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>910061892464#2</t>
+          <t>113204676267</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -5447,32 +5447,32 @@
       <c r="E73" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18505-5-23</t>
+ รถ lot18518-5-2</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>30.40</t>
+          <t>25.00</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>0.0523</t>
+          <t>0.0566</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -5482,7 +5482,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>456.00฿</t>
+          <t>375.00฿</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -5490,7 +5490,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N73" t="inlineStr"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>真空胎冷补胶片</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -5498,7 +5502,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>910061892464</t>
+          <t>910061892464#2</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -5514,7 +5518,7 @@
       <c r="E74" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18505-5-22</t>
+ รถ lot18505-5-23</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -5534,12 +5538,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>15.90</t>
+          <t>30.40</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>0.0353</t>
+          <t>0.0523</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -5549,7 +5553,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>238.50฿</t>
+          <t>456.00฿</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -5557,11 +5561,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N74" t="inlineStr">
-        <is>
-          <t>记号蜡笔</t>
-        </is>
-      </c>
+      <c r="N74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -5569,7 +5569,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>773434709817985</t>
+          <t>910061892464</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -5579,38 +5579,38 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>UN-INV260819-00010</t>
+          <t>UN-INV260815-00046</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18535-8</t>
+ รถ lot18505-5-22</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>16/08/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>15.90</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>0.0184</t>
+          <t>0.0353</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -5620,17 +5620,17 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>238.50฿</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>110.40฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>锅具 二次包装货物变形</t>
+          <t>记号蜡笔</t>
         </is>
       </c>
     </row>
@@ -5640,7 +5640,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>435295775627304</t>
+          <t>773434709817985</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5650,38 +5650,38 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>UN-INV260811-00012</t>
+          <t>UN-INV260819-00010</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18492-2</t>
+ รถ lot18535-8</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>16/08/2026</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>5.30</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>0.0090</t>
+          <t>0.0184</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -5691,17 +5691,17 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>79.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>110.40฿</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>配件 破损件</t>
+          <t>锅具 二次包装货物变形</t>
         </is>
       </c>
     </row>
@@ -5711,7 +5711,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>YT7636332367470</t>
+          <t>435295775627304</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -5727,7 +5727,7 @@
       <c r="E77" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18487-2-27</t>
+ รถ lot18492-2</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -5747,12 +5747,12 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>5.30</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>0.0004</t>
+          <t>0.0090</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -5762,17 +5762,17 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>79.50฿</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>10.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>立牌</t>
+          <t>配件 破损件</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>S35386280517#2</t>
+          <t>YT7636332367470</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -5798,32 +5798,32 @@
       <c r="E78" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18475-24</t>
+ รถ lot18487-2-27</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>8.80</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>0.0045</t>
+          <t>0.0004</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -5833,15 +5833,19 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>132.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr"/>
+          <t>10.00฿</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>立牌</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -5849,7 +5853,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>S35386280517</t>
+          <t>S35386280517#2</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -5865,7 +5869,7 @@
       <c r="E79" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18475-23</t>
+ รถ lot18475-24</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -5885,22 +5889,22 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>103.50</t>
+          <t>8.80</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>0.2236</t>
+          <t>0.0045</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>1,552.50฿</t>
+          <t>132.00฿</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -5908,11 +5912,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N79" t="inlineStr">
-        <is>
-          <t>气门嘴 顺心捷达，一票16件</t>
-        </is>
-      </c>
+      <c r="N79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -5920,7 +5920,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>YT7635787693833</t>
+          <t>S35386280517</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -5936,7 +5936,7 @@
       <c r="E80" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18473-6-41</t>
+ รถ lot18475-23</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -5951,37 +5951,37 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>13.80</t>
+          <t>103.50</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>0.0432</t>
+          <t>0.2236</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1,552.50฿</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>259.20฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>气压表/面单没有代码</t>
+          <t>气门嘴 顺心捷达，一票16件</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>ZY202465806614</t>
+          <t>YT7635787693833</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -6001,38 +6001,38 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>UN-INV260807-00009</t>
+          <t>UN-INV260811-00012</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>มอก.
- รถ lot18466-5-51</t>
+          <t>ธรรมดา
+ รถ lot18473-6-41</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>11.30</t>
+          <t>13.80</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>0.0655</t>
+          <t>0.0432</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -6047,12 +6047,12 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>445.40฿</t>
+          <t>259.20฿</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>电子数显胎压枪</t>
+          <t>气压表/面单没有代码</t>
         </is>
       </c>
     </row>
@@ -6062,7 +6062,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>113177184579#7</t>
+          <t>ZY202465806614</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -6077,18 +6077,18 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>ธรรมดา
- รถ lot18463-17</t>
+          <t>มอก.
+ รถ lot18466-5-51</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -6098,12 +6098,12 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>9.70</t>
+          <t>11.30</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>0.0305</t>
+          <t>0.0655</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -6118,10 +6118,14 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>183.00฿</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
+          <t>445.40฿</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>电子数显胎压枪</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -6129,7 +6133,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>113177184579#5</t>
+          <t>113177184579#7</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -6145,7 +6149,7 @@
       <c r="E83" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-16</t>
+ รถ lot18463-17</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -6165,12 +6169,12 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>15.00</t>
+          <t>9.70</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>0.0137</t>
+          <t>0.0305</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -6180,12 +6184,12 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>225.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>183.00฿</t>
         </is>
       </c>
       <c r="N83" t="inlineStr"/>
@@ -6196,7 +6200,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>113177184579#4</t>
+          <t>113177184579#5</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -6212,7 +6216,7 @@
       <c r="E84" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-15</t>
+ รถ lot18463-16</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -6232,12 +6236,12 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>7.30</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>0.0235</t>
+          <t>0.0137</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -6247,12 +6251,12 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>225.00฿</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>141.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N84" t="inlineStr"/>
@@ -6263,7 +6267,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>113177184579#3</t>
+          <t>113177184579#4</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -6279,7 +6283,7 @@
       <c r="E85" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-14</t>
+ รถ lot18463-15</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -6299,12 +6303,12 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>11.90</t>
+          <t>7.30</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>0.0302</t>
+          <t>0.0235</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -6319,7 +6323,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>181.20฿</t>
+          <t>141.00฿</t>
         </is>
       </c>
       <c r="N85" t="inlineStr"/>
@@ -6330,7 +6334,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>113177184579#6</t>
+          <t>113177184579#3</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -6346,7 +6350,7 @@
       <c r="E86" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-13</t>
+ รถ lot18463-14</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -6366,12 +6370,12 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>26.10</t>
+          <t>11.90</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>0.0673</t>
+          <t>0.0302</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -6386,7 +6390,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>403.80฿</t>
+          <t>181.20฿</t>
         </is>
       </c>
       <c r="N86" t="inlineStr"/>
@@ -6397,7 +6401,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>435289604798626</t>
+          <t>113177184579#6</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -6413,7 +6417,7 @@
       <c r="E87" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18462-6-6</t>
+ รถ lot18463-13</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -6423,7 +6427,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -6433,12 +6437,12 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>9.60</t>
+          <t>26.10</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>0.0090</t>
+          <t>0.0673</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -6448,19 +6452,15 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>144.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr">
-        <is>
-          <t>螺丝配件</t>
-        </is>
-      </c>
+          <t>403.80฿</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -6468,7 +6468,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>113177184579#2</t>
+          <t>435289604798626</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -6484,7 +6484,7 @@
       <c r="E88" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-12</t>
+ รถ lot18462-6-6</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -6494,7 +6494,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -6504,12 +6504,12 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>5.30</t>
+          <t>9.60</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>0.0635</t>
+          <t>0.0090</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -6519,15 +6519,19 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>144.00฿</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>381.00฿</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>螺丝配件</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -6535,7 +6539,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>113177184579</t>
+          <t>113177184579#2</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -6551,7 +6555,7 @@
       <c r="E89" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-11</t>
+ รถ lot18463-12</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -6571,12 +6575,12 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>13.30</t>
+          <t>5.30</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>0.1176</t>
+          <t>0.0635</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -6591,14 +6595,10 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>705.60฿</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr">
-        <is>
-          <t>蘑菇钉补胎贴</t>
-        </is>
-      </c>
+          <t>381.00฿</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -6606,7 +6606,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>435289604798722</t>
+          <t>113177184579</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -6622,7 +6622,7 @@
       <c r="E90" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18462-3</t>
+ รถ lot18463-11</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -6632,7 +6632,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -6642,12 +6642,12 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>4.30</t>
+          <t>13.30</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>0.0029</t>
+          <t>0.1176</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -6657,17 +6657,17 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>64.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>705.60฿</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>气门嘴</t>
+          <t>蘑菇钉补胎贴</t>
         </is>
       </c>
     </row>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>ZY202471573119#2</t>
+          <t>435289604798722</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -6693,7 +6693,7 @@
       <c r="E91" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-6</t>
+ รถ lot18462-3</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -6703,7 +6703,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -6713,12 +6713,12 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>8.70</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>0.0441</t>
+          <t>0.0029</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -6728,15 +6728,19 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>64.50฿</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>264.60฿</t>
-        </is>
-      </c>
-      <c r="N91" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>气门嘴</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -6744,7 +6748,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>ZY202471573119</t>
+          <t>ZY202471573119#2</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -6760,7 +6764,7 @@
       <c r="E92" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-5</t>
+ รถ lot18463-6</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -6780,12 +6784,12 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>11.90</t>
+          <t>8.70</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>0.0832</t>
+          <t>0.0441</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -6800,14 +6804,10 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>499.20฿</t>
-        </is>
-      </c>
-      <c r="N92" t="inlineStr">
-        <is>
-          <t>蘑菇钉补胎</t>
-        </is>
-      </c>
+          <t>264.60฿</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -6815,7 +6815,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>YT7635427281240</t>
+          <t>ZY202471573119</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -6831,7 +6831,7 @@
       <c r="E93" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18458-21</t>
+ รถ lot18463-5</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -6851,12 +6851,12 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>11.90</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>0.0117</t>
+          <t>0.0832</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -6871,12 +6871,12 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>70.20฿</t>
+          <t>499.20฿</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>气阀</t>
+          <t>蘑菇钉补胎</t>
         </is>
       </c>
     </row>
@@ -6886,7 +6886,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>79021262374216</t>
+          <t>YT7635427281240</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -6896,38 +6896,38 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>UN-INV260804-00019</t>
+          <t>UN-INV260807-00009</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18435-5-73</t>
+ รถ lot18458-21</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>12.20</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>0.0352</t>
+          <t>0.0117</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -6942,12 +6942,12 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>211.20฿</t>
+          <t>70.20฿</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>加长弯头</t>
+          <t>气阀</t>
         </is>
       </c>
     </row>
@@ -6957,7 +6957,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>113162219964#3</t>
+          <t>79021262374216</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -6973,17 +6973,17 @@
       <c r="E95" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18434-9-28</t>
+ รถ lot18435-5-73</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6993,12 +6993,12 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>18.70</t>
+          <t>12.20</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>0.0443</t>
+          <t>0.0352</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -7008,15 +7008,19 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>280.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr"/>
+          <t>211.20฿</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>加长弯头</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -7024,7 +7028,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>113162219964#2</t>
+          <t>113162219964#3</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -7040,7 +7044,7 @@
       <c r="E96" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18434-9-27</t>
+ รถ lot18434-9-28</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -7060,12 +7064,12 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>22.90</t>
+          <t>18.70</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>0.0522</t>
+          <t>0.0443</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -7075,7 +7079,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>343.50฿</t>
+          <t>280.50฿</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -7091,7 +7095,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>113162219964</t>
+          <t>113162219964#2</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -7107,7 +7111,7 @@
       <c r="E97" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18434-9-26</t>
+ รถ lot18434-9-27</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -7127,12 +7131,12 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>25.60</t>
+          <t>22.90</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>0.0574</t>
+          <t>0.0522</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -7142,7 +7146,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>384.00฿</t>
+          <t>343.50฿</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -7150,11 +7154,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N97" t="inlineStr">
-        <is>
-          <t>补胎胶片/3件</t>
-        </is>
-      </c>
+      <c r="N97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -7162,7 +7162,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>113158800045#2</t>
+          <t>113162219964</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -7178,32 +7178,32 @@
       <c r="E98" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18427-7-3</t>
+ รถ lot18434-9-26</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>26/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>26/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>26.30</t>
+          <t>25.60</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>0.0377</t>
+          <t>0.0574</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -7213,7 +7213,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>394.50฿</t>
+          <t>384.00฿</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -7221,7 +7221,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N98" t="inlineStr"/>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>补胎胶片/3件</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -7229,7 +7233,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>113158800045</t>
+          <t>113158800045#2</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -7245,7 +7249,7 @@
       <c r="E99" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18427-7-2</t>
+ รถ lot18427-7-3</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -7265,12 +7269,12 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>26.50</t>
+          <t>26.30</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>0.0379</t>
+          <t>0.0377</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -7280,7 +7284,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>397.50฿</t>
+          <t>394.50฿</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -7288,11 +7292,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N99" t="inlineStr">
-        <is>
-          <t>塑料配件/2件</t>
-        </is>
-      </c>
+      <c r="N99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -7300,7 +7300,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>YT2550516723148</t>
+          <t>113158800045</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -7316,32 +7316,32 @@
       <c r="E100" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18398-3-10</t>
+ รถ lot18427-7-2</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>22/07/2026</t>
+          <t>26/07/2026</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>23/07/2026</t>
+          <t>26/07/2026</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>26.50</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>0.0127</t>
+          <t>0.0379</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -7351,17 +7351,17 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>397.50฿</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>76.20฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>硅胶风管</t>
+          <t>塑料配件/2件</t>
         </is>
       </c>
     </row>
@@ -7371,7 +7371,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>ZY202467269952#4</t>
+          <t>YT2550516723148</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -7381,38 +7381,38 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>UN-INV260724-00013</t>
+          <t>UN-INV260804-00019</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18314-8-30</t>
+ รถ lot18398-3-10</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>11/07/2026</t>
+          <t>22/07/2026</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>12/07/2026</t>
+          <t>23/07/2026</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>15.50</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>0.0492</t>
+          <t>0.0127</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -7427,10 +7427,14 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>295.20฿</t>
-        </is>
-      </c>
-      <c r="N101" t="inlineStr"/>
+          <t>76.20฿</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>硅胶风管</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/cargo_packages_p1-5.xlsx
+++ b/cargo_packages_p1-5.xlsx
@@ -532,7 +532,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>UN-INV260918-00012</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1210,7 +1210,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>UN-INV260918-00012</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>UN-INV260918-00012</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">

--- a/cargo_packages_p1-5.xlsx
+++ b/cargo_packages_p1-5.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>435358249576981</t>
+          <t>S71749075994</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -522,17 +522,17 @@
       <c r="E2" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18815-4-6</t>
+ รถ lot18830-6-30</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -542,12 +542,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5.20</t>
+          <t>119.00</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.0044</t>
+          <t>0.2302</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -557,7 +557,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>78.00฿</t>
+          <t>1,785.00฿</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -567,7 +567,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>气门嘴</t>
+          <t>真空胎扒胎机配件/木箱</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>S71195667064</t>
+          <t>435358249576981</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -593,12 +593,12 @@
       <c r="E3" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18810-6-3</t>
+ รถ lot18815-4-6</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -613,32 +613,32 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>165.00</t>
+          <t>5.20</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.8568</t>
+          <t>0.0044</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>78.00฿</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>5,140.80฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>千斤顶，3件，客户不打木架发</t>
+          <t>气门嘴</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>113350746029#4</t>
+          <t>S71195667064</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -664,17 +664,17 @@
       <c r="E4" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18799-6-32</t>
+ รถ lot18810-6-3</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -684,17 +684,17 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>27.70</t>
+          <t>165.00</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.0800</t>
+          <t>0.8568</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -704,10 +704,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>480.00฿</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>5,140.80฿</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>千斤顶，3件，客户不打木架发</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -715,7 +719,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>113350746029#3</t>
+          <t>113350746029#4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -731,7 +735,7 @@
       <c r="E5" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18799-6-31</t>
+ รถ lot18799-6-32</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -751,12 +755,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10.90</t>
+          <t>27.70</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.0377</t>
+          <t>0.0800</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -771,7 +775,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>226.20฿</t>
+          <t>480.00฿</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -782,7 +786,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>113350746029#2</t>
+          <t>113350746029#3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -798,7 +802,7 @@
       <c r="E6" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18799-6-30</t>
+ รถ lot18799-6-31</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -818,12 +822,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>15.00</t>
+          <t>10.90</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.0101</t>
+          <t>0.0377</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -833,12 +837,12 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>225.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>226.20฿</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -849,7 +853,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>113350746029</t>
+          <t>113350746029#2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -865,7 +869,7 @@
       <c r="E7" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18799-6-29</t>
+ รถ lot18799-6-30</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -885,12 +889,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>16.50</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.0127</t>
+          <t>0.0101</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -900,7 +904,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>247.50฿</t>
+          <t>225.00฿</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -908,11 +912,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>真空胎加固修理补片</t>
-        </is>
-      </c>
+      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -920,7 +920,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>760246657062</t>
+          <t>113350746029</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -936,7 +936,7 @@
       <c r="E8" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18799-7-3</t>
+ รถ lot18799-6-29</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>16.50</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.0005</t>
+          <t>0.0127</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -971,17 +971,17 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>247.50฿</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>10.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>气门嘴，轮胎修补工具，气门芯宣传册</t>
+          <t>真空胎加固修理补片</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>113348267192#2</t>
+          <t>760246657062</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1007,17 +1007,17 @@
       <c r="E9" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18795-2-7</t>
+ รถ lot18799-7-3</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>28.10</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.0628</t>
+          <t>0.0005</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1042,15 +1042,19 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>421.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>10.00฿</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>气门嘴，轮胎修补工具，气门芯宣传册</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1058,7 +1062,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>113348267192</t>
+          <t>113348267192#2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1074,7 +1078,7 @@
       <c r="E10" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18795-2-6</t>
+ รถ lot18795-2-7</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1094,12 +1098,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>19.50</t>
+          <t>28.10</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.0505</t>
+          <t>0.0628</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1109,19 +1113,15 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>421.50฿</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>303.00฿</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>补胎胶片</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ZY202472578299</t>
+          <t>113348267192</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1139,43 +1139,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>UN-INV260918-00012</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18758-7-43</t>
+ รถ lot18795-2-6</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>47.40</t>
+          <t>19.50</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.1603</t>
+          <t>0.0505</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>961.20฿</t>
+          <t>303.00฿</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>补胎贴，3件</t>
+          <t>补胎胶片</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>773440822655698</t>
+          <t>ZY202472578299</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1216,7 +1216,7 @@
       <c r="E12" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18758-4-31</t>
+ รถ lot18758-7-43</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1236,32 +1236,32 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>47.40</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0.0022</t>
+          <t>0.1603</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>18.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>961.20฿</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>钻头</t>
+          <t>补胎贴，3件</t>
         </is>
       </c>
     </row>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>YT7642998390994</t>
+          <t>773440822655698</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1287,7 +1287,7 @@
       <c r="E13" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18769-3-57</t>
+ รถ lot18758-4-31</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1307,12 +1307,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5.80</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0.0070</t>
+          <t>0.0022</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>87.00฿</t>
+          <t>18.00฿</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>钻头</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DPK212614057101</t>
+          <t>YT7642998390994</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1352,38 +1352,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>UN-INV260916-00003</t>
+          <t>UN-INV260918-00012</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18749-4-3</t>
+ รถ lot18769-3-57</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>9.60</t>
+          <t>5.80</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.0060</t>
+          <t>0.0070</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1393,7 +1393,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>144.00฿</t>
+          <t>87.00฿</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>轮胎气门嘴</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -1413,7 +1413,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>79031204783305</t>
+          <t>DPK212614057101</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1429,7 +1429,7 @@
       <c r="E15" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18744-6-15</t>
+ รถ lot18749-4-3</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>9.60</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.0020</t>
+          <t>0.0060</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>39.00฿</t>
+          <t>144.00฿</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>轮胎气门嘴</t>
         </is>
       </c>
     </row>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>435342988112655</t>
+          <t>79031204783305</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1500,17 +1500,17 @@
       <c r="E16" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18743-3-34</t>
+ รถ lot18744-6-15</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1520,12 +1520,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>0.0014</t>
+          <t>0.0020</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1535,17 +1535,17 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>39.00฿</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>10.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>橡胶垫圈</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>435343890137834</t>
+          <t>435342988112655</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1571,7 +1571,7 @@
       <c r="E17" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18743-7-25</t>
+ รถ lot18743-3-34</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>21.40</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.0080</t>
+          <t>0.0014</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1606,17 +1606,17 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>321.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10.00฿</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>扒胎机包胶撬棍</t>
+          <t>橡胶垫圈</t>
         </is>
       </c>
     </row>
@@ -1626,7 +1626,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>YT7642670434639</t>
+          <t>435343890137834</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1642,7 +1642,7 @@
       <c r="E18" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18743-2-8</t>
+ รถ lot18743-7-25</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1662,12 +1662,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>21.40</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>0.0010</t>
+          <t>0.0080</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>12.00฿</t>
+          <t>321.00฿</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1687,7 +1687,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>片片</t>
+          <t>扒胎机包胶撬棍</t>
         </is>
       </c>
     </row>
@@ -1697,7 +1697,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>93015797092</t>
+          <t>YT7642670434639</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1707,18 +1707,18 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>UN-INV260914-00014</t>
+          <t>UN-INV260916-00003</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18735-4-40</t>
+ รถ lot18743-2-8</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1728,17 +1728,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>12/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>8.60</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>0.0148</t>
+          <t>0.0010</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1748,7 +1748,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>129.00฿</t>
+          <t>12.00฿</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>仪表</t>
+          <t>片片</t>
         </is>
       </c>
     </row>
@@ -1768,7 +1768,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>YT7642390374765</t>
+          <t>93015797092</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1778,13 +1778,13 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>UN-INV260914-00015</t>
+          <t>UN-INV260914-00014</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18735-4-20</t>
+ รถ lot18735-4-40</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>20.80</t>
+          <t>8.60</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0.0598</t>
+          <t>0.0148</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1819,17 +1819,17 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>129.00฿</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>358.80฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>打磨机</t>
+          <t>仪表</t>
         </is>
       </c>
     </row>
@@ -1839,7 +1839,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>435342255104130</t>
+          <t>YT7642390374765</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1849,13 +1849,13 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>UN-INV260914-00014</t>
+          <t>UN-INV260914-00015</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18735-43</t>
+ รถ lot18735-4-20</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1875,12 +1875,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>4.90</t>
+          <t>20.80</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.0172</t>
+          <t>0.0598</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1895,12 +1895,12 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>103.20฿</t>
+          <t>358.80฿</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>轮毂保护套</t>
+          <t>打磨机</t>
         </is>
       </c>
     </row>
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>773440312345715</t>
+          <t>435342255104130</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1926,7 +1926,7 @@
       <c r="E22" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18735-3-78</t>
+ รถ lot18735-43</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1946,12 +1946,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>4.90</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.0013</t>
+          <t>0.0172</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1961,17 +1961,17 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>19.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>103.20฿</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>轮毂保护套</t>
         </is>
       </c>
     </row>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>773440291470393</t>
+          <t>773440312345715</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1997,7 +1997,7 @@
       <c r="E23" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18735-34</t>
+ รถ lot18735-3-78</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2017,12 +2017,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.0029</t>
+          <t>0.0013</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>48.00฿</t>
+          <t>19.50฿</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2042,7 +2042,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>球阀</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>435342261175750</t>
+          <t>773440291470393</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2062,13 +2062,13 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>UN-INV260914-00015</t>
+          <t>UN-INV260914-00014</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18736-13</t>
+ รถ lot18735-34</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2078,7 +2078,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2088,12 +2088,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>13.90</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.0137</t>
+          <t>0.0029</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2103,7 +2103,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>208.50฿</t>
+          <t>48.00฿</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>球阀</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ZY202461195200</t>
+          <t>435342261175750</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2139,7 +2139,7 @@
       <c r="E25" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18728-7-13</t>
+ รถ lot18736-13</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2154,17 +2154,17 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>13/09/2026</t>
+          <t>12/09/2026</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>47.40</t>
+          <t>13.90</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.0116</t>
+          <t>0.0137</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>711.00฿</t>
+          <t>208.50฿</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>79030687835952</t>
+          <t>ZY202461195200</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2204,13 +2204,13 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>UN-INV260914-00014</t>
+          <t>UN-INV260914-00015</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18728-3-64</t>
+ รถ lot18728-7-13</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>4.30</t>
+          <t>47.40</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>0.0030</t>
+          <t>0.0116</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2245,7 +2245,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>64.50฿</t>
+          <t>711.00฿</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2255,7 +2255,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>接头配件</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -2265,7 +2265,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>LJ20722214#3</t>
+          <t>79030687835952</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2275,38 +2275,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>UN-INV260912-00011</t>
+          <t>UN-INV260914-00014</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18726-7-8</t>
+ รถ lot18728-3-64</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>13/09/2026</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>14.00</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.0171</t>
+          <t>0.0030</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>210.00฿</t>
+          <t>64.50฿</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2324,7 +2324,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>接头配件</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2332,7 +2336,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>LJ20722214#2</t>
+          <t>LJ20722214#3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2348,7 +2352,7 @@
       <c r="E28" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18726-7-7</t>
+ รถ lot18726-7-8</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2368,12 +2372,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>11.90</t>
+          <t>14.00</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.0089</t>
+          <t>0.0171</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2383,7 +2387,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>178.50฿</t>
+          <t>210.00฿</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2399,7 +2403,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>LJ20722214</t>
+          <t>LJ20722214#2</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2415,7 +2419,7 @@
       <c r="E29" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18726-7-6</t>
+ รถ lot18726-7-7</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2435,12 +2439,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>16.00</t>
+          <t>11.90</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0.0144</t>
+          <t>0.0089</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2450,7 +2454,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>240.00฿</t>
+          <t>178.50฿</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2458,11 +2462,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>电板套筒配件/3件</t>
-        </is>
-      </c>
+      <c r="N29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>YT7641966426761</t>
+          <t>LJ20722214</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2486,17 +2486,17 @@
       <c r="E30" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18714-9-23</t>
+ รถ lot18726-7-6</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>13.60</t>
+          <t>16.00</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.0422</t>
+          <t>0.0144</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2521,17 +2521,17 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>240.00฿</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>253.20฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>带表汽车轮胎打气嘴</t>
+          <t>电板套筒配件/3件</t>
         </is>
       </c>
     </row>
@@ -2541,7 +2541,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ZY202471681117#2</t>
+          <t>YT7641966426761</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2557,7 +2557,7 @@
       <c r="E31" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18714-9-8</t>
+ รถ lot18714-9-23</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2577,12 +2577,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>11.80</t>
+          <t>13.60</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.0832</t>
+          <t>0.0422</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2597,10 +2597,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>499.20฿</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
+          <t>253.20฿</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>带表汽车轮胎打气嘴</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2608,7 +2612,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ZY202471681117</t>
+          <t>ZY202471681117#2</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2624,7 +2628,7 @@
       <c r="E32" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18714-9-7</t>
+ รถ lot18714-9-8</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2644,12 +2648,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>7.70</t>
+          <t>11.80</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.0493</t>
+          <t>0.0832</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2664,14 +2668,10 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>295.80฿</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>补胎胶片/2件</t>
-        </is>
-      </c>
+          <t>499.20฿</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>302285502767#2</t>
+          <t>ZY202471681117</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2695,7 +2695,7 @@
       <c r="E33" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18714-8-10</t>
+ รถ lot18714-9-7</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>33.70</t>
+          <t>7.70</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.0145</t>
+          <t>0.0493</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2730,15 +2730,19 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>505.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
+          <t>295.80฿</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>补胎胶片/2件</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2746,7 +2750,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>302285502767</t>
+          <t>302285502767#2</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2762,7 +2766,7 @@
       <c r="E34" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18714-8-9</t>
+ รถ lot18714-8-10</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2782,12 +2786,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>23.40</t>
+          <t>33.70</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.0123</t>
+          <t>0.0145</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2797,7 +2801,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>351.00฿</t>
+          <t>505.50฿</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2805,11 +2809,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>扳手</t>
-        </is>
-      </c>
+      <c r="N34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2817,7 +2817,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>LJ20716178#2</t>
+          <t>302285502767</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2827,18 +2827,18 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>UN-INV260911-00013</t>
+          <t>UN-INV260912-00011</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18713-6-65</t>
+ รถ lot18714-8-9</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2848,17 +2848,17 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>19.50</t>
+          <t>23.40</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.0075</t>
+          <t>0.0123</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>292.50฿</t>
+          <t>351.00฿</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2876,7 +2876,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>扳手</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2884,7 +2888,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>LJ20716178</t>
+          <t>LJ20716178#2</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2900,7 +2904,7 @@
       <c r="E36" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18713-6-64</t>
+ รถ lot18713-6-65</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2920,7 +2924,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>19.60</t>
+          <t>19.50</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2935,7 +2939,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>294.00฿</t>
+          <t>292.50฿</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2943,11 +2947,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>配件</t>
-        </is>
-      </c>
+      <c r="N36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>435338972466812</t>
+          <t>LJ20716178</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2971,7 +2971,7 @@
       <c r="E37" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18710-6-35</t>
+ รถ lot18713-6-64</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>13.10</t>
+          <t>19.60</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.0624</t>
+          <t>0.0075</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -3006,17 +3006,17 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>294.00฿</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>374.40฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>修补工具</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -3026,7 +3026,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>435334324045675</t>
+          <t>435338972466812</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3036,38 +3036,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>UN-INV260908-00009</t>
+          <t>UN-INV260911-00013</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18696-14</t>
+ รถ lot18710-6-35</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>10.80</t>
+          <t>13.10</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.0088</t>
+          <t>0.0624</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -3077,17 +3077,17 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>162.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>374.40฿</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>修补工具</t>
         </is>
       </c>
     </row>
@@ -3097,7 +3097,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>YT7641276428798</t>
+          <t>435334324045675</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3113,7 +3113,7 @@
       <c r="E39" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18697-11</t>
+ รถ lot18696-14</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>9.50</t>
+          <t>10.80</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.0296</t>
+          <t>0.0088</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>162.00฿</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>177.60฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>79029430531776</t>
+          <t>YT7641276428798</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3178,18 +3178,18 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>UN-INV260907-00015</t>
+          <t>UN-INV260908-00009</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18689-26</t>
+ รถ lot18697-11</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -3199,17 +3199,17 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>9.50</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.0135</t>
+          <t>0.0296</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -3224,12 +3224,12 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>81.00฿</t>
+          <t>177.60฿</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>卡套</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>113282578128#2</t>
+          <t>79029430531776</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3255,17 +3255,17 @@
       <c r="E41" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18683-4</t>
+ รถ lot18689-26</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3275,12 +3275,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>38.00</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.1601</t>
+          <t>0.0135</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -3295,10 +3295,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>960.60฿</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
+          <t>81.00฿</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>卡套</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -3306,7 +3310,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>113282578128</t>
+          <t>113282578128#2</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3322,7 +3326,7 @@
       <c r="E42" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18683-3</t>
+ รถ lot18683-4</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -3342,12 +3346,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>27.50</t>
+          <t>38.00</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.1566</t>
+          <t>0.1601</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3362,14 +3366,10 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>939.60฿</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>压条取出器 一票两件破损件</t>
-        </is>
-      </c>
+          <t>960.60฿</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>82730128600#3</t>
+          <t>113282578128</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3393,12 +3393,12 @@
       <c r="E43" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18678-6-21</t>
+ รถ lot18683-3</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>30/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -3413,12 +3413,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>33.00</t>
+          <t>27.50</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.0122</t>
+          <t>0.1566</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3428,15 +3428,19 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>495.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
+          <t>939.60฿</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>压条取出器 一票两件破损件</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -3444,7 +3448,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>82730128600#2</t>
+          <t>82730128600#3</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3460,7 +3464,7 @@
       <c r="E44" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18678-6-20</t>
+ รถ lot18678-6-21</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -3480,12 +3484,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>27.60</t>
+          <t>33.00</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.0095</t>
+          <t>0.0122</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3495,7 +3499,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>414.00฿</t>
+          <t>495.00฿</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3511,7 +3515,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>82730128600</t>
+          <t>82730128600#2</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3527,7 +3531,7 @@
       <c r="E45" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18678-6-19</t>
+ รถ lot18678-6-20</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -3547,12 +3551,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>28.10</t>
+          <t>27.60</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.0118</t>
+          <t>0.0095</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3562,7 +3566,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>421.50฿</t>
+          <t>414.00฿</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3570,11 +3574,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>五金配件/3件</t>
-        </is>
-      </c>
+      <c r="N45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -3582,7 +3582,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>113278387839#3</t>
+          <t>82730128600</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3592,38 +3592,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>UN-INV260903-00023</t>
+          <t>UN-INV260907-00015</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18663-8-3</t>
+ รถ lot18678-6-19</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>30/08/2026</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>25.30</t>
+          <t>28.10</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>0.0404</t>
+          <t>0.0118</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3633,7 +3633,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>379.50฿</t>
+          <t>421.50฿</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3641,7 +3641,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>五金配件/3件</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -3649,7 +3653,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>113278387839#2</t>
+          <t>113278387839#3</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3665,7 +3669,7 @@
       <c r="E47" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18663-8-2</t>
+ รถ lot18663-8-3</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -3685,12 +3689,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>26.10</t>
+          <t>25.30</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>0.0304</t>
+          <t>0.0404</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3700,7 +3704,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>391.50฿</t>
+          <t>379.50฿</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3716,7 +3720,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>113278387839</t>
+          <t>113278387839#2</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3732,7 +3736,7 @@
       <c r="E48" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18663-8-1</t>
+ รถ lot18663-8-2</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -3752,12 +3756,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>9.10</t>
+          <t>26.10</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>0.0144</t>
+          <t>0.0304</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3767,7 +3771,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>136.50฿</t>
+          <t>391.50฿</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3775,11 +3779,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>配件/3件</t>
-        </is>
-      </c>
+      <c r="N48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -3787,7 +3787,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>113276098937#3</t>
+          <t>113278387839</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3797,38 +3797,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>UN-INV260901-00057</t>
+          <t>UN-INV260903-00023</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-45</t>
+ รถ lot18663-8-1</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>17.80</t>
+          <t>9.10</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>0.0302</t>
+          <t>0.0144</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>267.00฿</t>
+          <t>136.50฿</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3846,7 +3846,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr"/>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>配件/3件</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -3854,7 +3858,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>113276098937#2</t>
+          <t>113276098937#3</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3870,7 +3874,7 @@
       <c r="E50" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-44</t>
+ รถ lot18655-9-45</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3890,12 +3894,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>10.90</t>
+          <t>17.80</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>0.0313</t>
+          <t>0.0302</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3905,12 +3909,12 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>267.00฿</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>187.80฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N50" t="inlineStr"/>
@@ -3921,7 +3925,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>113276098937</t>
+          <t>113276098937#2</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3937,7 +3941,7 @@
       <c r="E51" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-43</t>
+ รถ lot18655-9-44</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -3957,12 +3961,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>33.60</t>
+          <t>10.90</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>0.0825</t>
+          <t>0.0313</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3972,19 +3976,15 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>504.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>补胎胶片+配件/3件</t>
-        </is>
-      </c>
+          <t>187.80฿</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -3992,7 +3992,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ZY202464580877#4</t>
+          <t>113276098937</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -4008,7 +4008,7 @@
       <c r="E52" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-17</t>
+ รถ lot18655-9-43</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -4028,12 +4028,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>20.10</t>
+          <t>33.60</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>0.0466</t>
+          <t>0.0825</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -4043,7 +4043,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>301.50฿</t>
+          <t>504.00฿</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -4051,7 +4051,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>补胎胶片+配件/3件</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -4059,7 +4063,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ZY202464580877#7</t>
+          <t>ZY202464580877#4</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -4075,7 +4079,7 @@
       <c r="E53" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-16</t>
+ รถ lot18655-9-17</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -4095,12 +4099,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>16.60</t>
+          <t>20.10</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>0.0430</t>
+          <t>0.0466</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -4110,12 +4114,12 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>301.50฿</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>258.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
@@ -4126,7 +4130,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ZY202464580877#2</t>
+          <t>ZY202464580877#7</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -4142,7 +4146,7 @@
       <c r="E54" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-15</t>
+ รถ lot18655-9-16</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -4162,12 +4166,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>25.10</t>
+          <t>16.60</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>0.0483</t>
+          <t>0.0430</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -4177,12 +4181,12 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>376.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>258.00฿</t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
@@ -4193,7 +4197,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ZY202464580877#8</t>
+          <t>ZY202464580877#2</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -4209,7 +4213,7 @@
       <c r="E55" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-14</t>
+ รถ lot18655-9-15</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -4229,12 +4233,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>28.90</t>
+          <t>25.10</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>0.0800</t>
+          <t>0.0483</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -4244,12 +4248,12 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>376.50฿</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>480.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N55" t="inlineStr"/>
@@ -4260,7 +4264,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ZY202464580877#6</t>
+          <t>ZY202464580877#8</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -4276,7 +4280,7 @@
       <c r="E56" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-13</t>
+ รถ lot18655-9-14</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -4296,12 +4300,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>20.90</t>
+          <t>28.90</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>0.0534</t>
+          <t>0.0800</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -4316,7 +4320,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>320.40฿</t>
+          <t>480.00฿</t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
@@ -4327,7 +4331,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ZY202464580877#5</t>
+          <t>ZY202464580877#6</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -4343,7 +4347,7 @@
       <c r="E57" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-12</t>
+ รถ lot18655-9-13</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -4363,12 +4367,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>26.20</t>
+          <t>20.90</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>0.0535</t>
+          <t>0.0534</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -4378,12 +4382,12 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>393.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>320.40฿</t>
         </is>
       </c>
       <c r="N57" t="inlineStr"/>
@@ -4394,7 +4398,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ZY202464580877</t>
+          <t>ZY202464580877#5</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -4410,7 +4414,7 @@
       <c r="E58" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-11</t>
+ รถ lot18655-9-12</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -4430,12 +4434,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>20.70</t>
+          <t>26.20</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>0.0531</t>
+          <t>0.0535</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -4445,12 +4449,12 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>393.00฿</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>318.60฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
@@ -4461,7 +4465,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ZY202464580877#9</t>
+          <t>ZY202464580877</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4477,7 +4481,7 @@
       <c r="E59" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-10</t>
+ รถ lot18655-9-11</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -4497,12 +4501,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>27.70</t>
+          <t>20.70</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>0.0800</t>
+          <t>0.0531</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4517,7 +4521,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>480.00฿</t>
+          <t>318.60฿</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
@@ -4528,7 +4532,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ZY202464580877#3</t>
+          <t>ZY202464580877#9</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4544,7 +4548,7 @@
       <c r="E60" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-9</t>
+ รถ lot18655-9-10</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -4564,12 +4568,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>27.10</t>
+          <t>27.70</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>0.0567</t>
+          <t>0.0800</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -4579,19 +4583,15 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>406.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>补胎胶片/9件</t>
-        </is>
-      </c>
+          <t>480.00฿</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -4599,7 +4599,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>S71090288685</t>
+          <t>ZY202464580877#3</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4609,38 +4609,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>UN-INV260831-00017</t>
+          <t>UN-INV260901-00057</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18634-7-3</t>
+ รถ lot18655-9-9</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>29/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>12.10</t>
+          <t>27.10</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>0.0240</t>
+          <t>0.0567</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -4650,7 +4650,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>181.50฿</t>
+          <t>406.50฿</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -4660,7 +4660,7 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>补胎胶片/9件</t>
         </is>
       </c>
     </row>
@@ -4670,7 +4670,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>YT7638092409979</t>
+          <t>S71090288685</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4680,38 +4680,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>UN-INV260822-00010</t>
+          <t>UN-INV260831-00017</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18569-7-7</t>
+ รถ lot18634-7-3</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>16/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>16/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>29/08/2026</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>15.00</t>
+          <t>12.10</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>0.0140</t>
+          <t>0.0240</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>225.00฿</t>
+          <t>181.50฿</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -4741,7 +4741,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>435308000517585</t>
+          <t>YT7638092409979</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4757,32 +4757,32 @@
       <c r="E63" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18550-6-11</t>
+ รถ lot18569-7-7</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>16/08/2026</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>16/08/2026</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>0.0032</t>
+          <t>0.0140</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -4792,7 +4792,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>54.00฿</t>
+          <t>225.00฿</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>气门嘴</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -4812,7 +4812,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>710094401487</t>
+          <t>435308000517585</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4828,17 +4828,17 @@
       <c r="E64" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18544-8-14</t>
+ รถ lot18550-6-11</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4848,32 +4848,32 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>107.10</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>0.4536</t>
+          <t>0.0032</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>54.00฿</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>2,721.60฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>空的高压充气罐/一票10件，仓库实收到9件，已确认收到的9件先发</t>
+          <t>气门嘴</t>
         </is>
       </c>
     </row>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>773435675083665</t>
+          <t>710094401487</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4893,58 +4893,58 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>UN-INV260815-00046</t>
+          <t>UN-INV260822-00010</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18526-6-17</t>
+ รถ lot18544-8-14</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>13.10</t>
+          <t>107.10</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>0.0214</t>
+          <t>0.4536</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>196.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2,721.60฿</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>补胎工具</t>
+          <t>空的高压充气罐/一票10件，仓库实收到9件，已确认收到的9件先发</t>
         </is>
       </c>
     </row>
@@ -4954,7 +4954,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>YT7637032206975</t>
+          <t>773435675083665</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4964,38 +4964,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>UN-INV260819-00010</t>
+          <t>UN-INV260815-00046</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>มอก.
- รถ lot18523-6-30</t>
+          <t>ธรรมดา
+ รถ lot18526-6-17</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>16/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>9.60</t>
+          <t>13.10</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>0.0316</t>
+          <t>0.0214</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -5005,17 +5005,17 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>196.50฿</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>214.88฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>气动模具研磨机+配件</t>
+          <t>补胎工具</t>
         </is>
       </c>
     </row>
@@ -5025,7 +5025,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>ZY202466648481#5</t>
+          <t>YT7637032206975</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -5035,13 +5035,13 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>UN-INV260815-00046</t>
+          <t>UN-INV260819-00010</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>ธรรมดา
- รถ lot18519-6-17</t>
+          <t>มอก.
+ รถ lot18523-6-30</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -5056,17 +5056,17 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>15/08/2026</t>
+          <t>16/08/2026</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>16.10</t>
+          <t>9.60</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>0.0493</t>
+          <t>0.0316</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -5081,10 +5081,14 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>295.80฿</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
+          <t>214.88฿</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>气动模具研磨机+配件</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -5092,7 +5096,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>ZY202466648481#4</t>
+          <t>ZY202466648481#5</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -5108,7 +5112,7 @@
       <c r="E68" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18519-6-16</t>
+ รถ lot18519-6-17</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -5128,12 +5132,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>20.50</t>
+          <t>16.10</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>0.0656</t>
+          <t>0.0493</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -5148,7 +5152,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>393.60฿</t>
+          <t>295.80฿</t>
         </is>
       </c>
       <c r="N68" t="inlineStr"/>
@@ -5159,7 +5163,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>ZY202466648481#3</t>
+          <t>ZY202466648481#4</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -5175,7 +5179,7 @@
       <c r="E69" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18519-6-15</t>
+ รถ lot18519-6-16</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -5195,12 +5199,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>15.70</t>
+          <t>20.50</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>0.0508</t>
+          <t>0.0656</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -5215,7 +5219,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>304.80฿</t>
+          <t>393.60฿</t>
         </is>
       </c>
       <c r="N69" t="inlineStr"/>
@@ -5226,7 +5230,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>ZY202466648481#2</t>
+          <t>ZY202466648481#3</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -5242,7 +5246,7 @@
       <c r="E70" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18519-6-14</t>
+ รถ lot18519-6-15</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -5262,12 +5266,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>20.20</t>
+          <t>15.70</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>0.0660</t>
+          <t>0.0508</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -5282,7 +5286,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>396.00฿</t>
+          <t>304.80฿</t>
         </is>
       </c>
       <c r="N70" t="inlineStr"/>
@@ -5293,7 +5297,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>ZY202466648481</t>
+          <t>ZY202466648481#2</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -5309,7 +5313,7 @@
       <c r="E71" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18519-6-13</t>
+ รถ lot18519-6-14</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -5329,12 +5333,12 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>15.80</t>
+          <t>20.20</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>0.0522</t>
+          <t>0.0660</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -5349,14 +5353,10 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>313.20฿</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr">
-        <is>
-          <t>补胎胶条/5件</t>
-        </is>
-      </c>
+          <t>396.00฿</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -5364,7 +5364,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>113204676267#2</t>
+          <t>ZY202466648481</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -5380,32 +5380,32 @@
       <c r="E72" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18518-5-3</t>
+ รถ lot18519-6-13</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>15/08/2026</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>24.60</t>
+          <t>15.80</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>0.0608</t>
+          <t>0.0522</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -5415,15 +5415,19 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>369.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr"/>
+          <t>313.20฿</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>补胎胶条/5件</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -5431,7 +5435,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>113204676267</t>
+          <t>113204676267#2</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -5447,7 +5451,7 @@
       <c r="E73" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18518-5-2</t>
+ รถ lot18518-5-3</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -5467,12 +5471,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>25.00</t>
+          <t>24.60</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>0.0566</t>
+          <t>0.0608</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -5482,7 +5486,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>375.00฿</t>
+          <t>369.00฿</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -5490,11 +5494,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t>真空胎冷补胶片</t>
-        </is>
-      </c>
+      <c r="N73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>910061892464#2</t>
+          <t>113204676267</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -5518,32 +5518,32 @@
       <c r="E74" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18505-5-23</t>
+ รถ lot18518-5-2</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>30.40</t>
+          <t>25.00</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>0.0523</t>
+          <t>0.0566</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -5553,7 +5553,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>456.00฿</t>
+          <t>375.00฿</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -5561,7 +5561,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N74" t="inlineStr"/>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>真空胎冷补胶片</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -5569,7 +5573,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>910061892464</t>
+          <t>910061892464#2</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -5585,7 +5589,7 @@
       <c r="E75" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18505-5-22</t>
+ รถ lot18505-5-23</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -5605,12 +5609,12 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>15.90</t>
+          <t>30.40</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>0.0353</t>
+          <t>0.0523</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -5620,7 +5624,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>238.50฿</t>
+          <t>456.00฿</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -5628,11 +5632,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N75" t="inlineStr">
-        <is>
-          <t>记号蜡笔</t>
-        </is>
-      </c>
+      <c r="N75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -5640,7 +5640,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>773434709817985</t>
+          <t>910061892464</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5650,38 +5650,38 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>UN-INV260819-00010</t>
+          <t>UN-INV260815-00046</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18535-8</t>
+ รถ lot18505-5-22</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>16/08/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>15.90</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>0.0184</t>
+          <t>0.0353</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -5691,17 +5691,17 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>238.50฿</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>110.40฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>锅具 二次包装货物变形</t>
+          <t>记号蜡笔</t>
         </is>
       </c>
     </row>
@@ -5711,7 +5711,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>435295775627304</t>
+          <t>773434709817985</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -5721,38 +5721,38 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>UN-INV260811-00012</t>
+          <t>UN-INV260819-00010</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18492-2</t>
+ รถ lot18535-8</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>16/08/2026</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>5.30</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>0.0090</t>
+          <t>0.0184</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -5762,17 +5762,17 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>79.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>110.40฿</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>配件 破损件</t>
+          <t>锅具 二次包装货物变形</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>YT7636332367470</t>
+          <t>435295775627304</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -5798,7 +5798,7 @@
       <c r="E78" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18487-2-27</t>
+ รถ lot18492-2</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>5.30</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>0.0004</t>
+          <t>0.0090</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>79.50฿</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>10.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>立牌</t>
+          <t>配件 破损件</t>
         </is>
       </c>
     </row>
@@ -5853,7 +5853,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>S35386280517#2</t>
+          <t>YT7636332367470</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -5869,32 +5869,32 @@
       <c r="E79" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18475-24</t>
+ รถ lot18487-2-27</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>8.80</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>0.0045</t>
+          <t>0.0004</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -5904,15 +5904,19 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>132.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr"/>
+          <t>10.00฿</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>立牌</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -5920,7 +5924,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>S35386280517</t>
+          <t>S35386280517#2</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -5936,7 +5940,7 @@
       <c r="E80" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18475-23</t>
+ รถ lot18475-24</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -5956,22 +5960,22 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>103.50</t>
+          <t>8.80</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>0.2236</t>
+          <t>0.0045</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>1,552.50฿</t>
+          <t>132.00฿</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -5979,11 +5983,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N80" t="inlineStr">
-        <is>
-          <t>气门嘴 顺心捷达，一票16件</t>
-        </is>
-      </c>
+      <c r="N80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>YT7635787693833</t>
+          <t>S35386280517</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -6007,7 +6007,7 @@
       <c r="E81" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18473-6-41</t>
+ รถ lot18475-23</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -6022,37 +6022,37 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>13.80</t>
+          <t>103.50</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>0.0432</t>
+          <t>0.2236</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1,552.50฿</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>259.20฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>气压表/面单没有代码</t>
+          <t>气门嘴 顺心捷达，一票16件</t>
         </is>
       </c>
     </row>
@@ -6062,7 +6062,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>ZY202465806614</t>
+          <t>YT7635787693833</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -6072,38 +6072,38 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>UN-INV260807-00009</t>
+          <t>UN-INV260811-00012</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>มอก.
- รถ lot18466-5-51</t>
+          <t>ธรรมดา
+ รถ lot18473-6-41</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>11.30</t>
+          <t>13.80</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>0.0655</t>
+          <t>0.0432</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -6118,12 +6118,12 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>445.40฿</t>
+          <t>259.20฿</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>电子数显胎压枪</t>
+          <t>气压表/面单没有代码</t>
         </is>
       </c>
     </row>
@@ -6133,7 +6133,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>113177184579#7</t>
+          <t>ZY202465806614</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -6148,18 +6148,18 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>ธรรมดา
- รถ lot18463-17</t>
+          <t>มอก.
+ รถ lot18466-5-51</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -6169,12 +6169,12 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>9.70</t>
+          <t>11.30</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>0.0305</t>
+          <t>0.0655</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -6189,10 +6189,14 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>183.00฿</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr"/>
+          <t>445.40฿</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>电子数显胎压枪</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -6200,7 +6204,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>113177184579#5</t>
+          <t>113177184579#7</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -6216,7 +6220,7 @@
       <c r="E84" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-16</t>
+ รถ lot18463-17</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -6236,12 +6240,12 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>15.00</t>
+          <t>9.70</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>0.0137</t>
+          <t>0.0305</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -6251,12 +6255,12 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>225.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>183.00฿</t>
         </is>
       </c>
       <c r="N84" t="inlineStr"/>
@@ -6267,7 +6271,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>113177184579#4</t>
+          <t>113177184579#5</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -6283,7 +6287,7 @@
       <c r="E85" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-15</t>
+ รถ lot18463-16</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -6303,12 +6307,12 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>7.30</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>0.0235</t>
+          <t>0.0137</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -6318,12 +6322,12 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>225.00฿</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>141.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N85" t="inlineStr"/>
@@ -6334,7 +6338,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>113177184579#3</t>
+          <t>113177184579#4</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -6350,7 +6354,7 @@
       <c r="E86" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-14</t>
+ รถ lot18463-15</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -6370,12 +6374,12 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>11.90</t>
+          <t>7.30</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>0.0302</t>
+          <t>0.0235</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -6390,7 +6394,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>181.20฿</t>
+          <t>141.00฿</t>
         </is>
       </c>
       <c r="N86" t="inlineStr"/>
@@ -6401,7 +6405,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>113177184579#6</t>
+          <t>113177184579#3</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -6417,7 +6421,7 @@
       <c r="E87" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-13</t>
+ รถ lot18463-14</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -6437,12 +6441,12 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>26.10</t>
+          <t>11.90</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>0.0673</t>
+          <t>0.0302</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -6457,7 +6461,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>403.80฿</t>
+          <t>181.20฿</t>
         </is>
       </c>
       <c r="N87" t="inlineStr"/>
@@ -6468,7 +6472,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>435289604798626</t>
+          <t>113177184579#6</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -6484,7 +6488,7 @@
       <c r="E88" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18462-6-6</t>
+ รถ lot18463-13</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -6494,7 +6498,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -6504,12 +6508,12 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>9.60</t>
+          <t>26.10</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>0.0090</t>
+          <t>0.0673</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -6519,19 +6523,15 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>144.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr">
-        <is>
-          <t>螺丝配件</t>
-        </is>
-      </c>
+          <t>403.80฿</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -6539,7 +6539,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>113177184579#2</t>
+          <t>435289604798626</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -6555,7 +6555,7 @@
       <c r="E89" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-12</t>
+ รถ lot18462-6-6</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -6565,7 +6565,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -6575,12 +6575,12 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>5.30</t>
+          <t>9.60</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>0.0635</t>
+          <t>0.0090</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -6590,15 +6590,19 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>144.00฿</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>381.00฿</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>螺丝配件</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -6606,7 +6610,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>113177184579</t>
+          <t>113177184579#2</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -6622,7 +6626,7 @@
       <c r="E90" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-11</t>
+ รถ lot18463-12</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -6642,12 +6646,12 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>13.30</t>
+          <t>5.30</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>0.1176</t>
+          <t>0.0635</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -6662,14 +6666,10 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>705.60฿</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr">
-        <is>
-          <t>蘑菇钉补胎贴</t>
-        </is>
-      </c>
+          <t>381.00฿</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -6677,7 +6677,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>435289604798722</t>
+          <t>113177184579</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -6693,7 +6693,7 @@
       <c r="E91" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18462-3</t>
+ รถ lot18463-11</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -6703,7 +6703,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -6713,12 +6713,12 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>4.30</t>
+          <t>13.30</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>0.0029</t>
+          <t>0.1176</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -6728,17 +6728,17 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>64.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>705.60฿</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>气门嘴</t>
+          <t>蘑菇钉补胎贴</t>
         </is>
       </c>
     </row>
@@ -6748,7 +6748,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>ZY202471573119#2</t>
+          <t>435289604798722</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -6764,7 +6764,7 @@
       <c r="E92" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-6</t>
+ รถ lot18462-3</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -6774,7 +6774,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6784,12 +6784,12 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>8.70</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>0.0441</t>
+          <t>0.0029</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -6799,15 +6799,19 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>64.50฿</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>264.60฿</t>
-        </is>
-      </c>
-      <c r="N92" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>气门嘴</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -6815,7 +6819,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>ZY202471573119</t>
+          <t>ZY202471573119#2</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -6831,7 +6835,7 @@
       <c r="E93" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-5</t>
+ รถ lot18463-6</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -6851,12 +6855,12 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>11.90</t>
+          <t>8.70</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>0.0832</t>
+          <t>0.0441</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -6871,14 +6875,10 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>499.20฿</t>
-        </is>
-      </c>
-      <c r="N93" t="inlineStr">
-        <is>
-          <t>蘑菇钉补胎</t>
-        </is>
-      </c>
+          <t>264.60฿</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -6886,7 +6886,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>YT7635427281240</t>
+          <t>ZY202471573119</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -6902,7 +6902,7 @@
       <c r="E94" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18458-21</t>
+ รถ lot18463-5</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>11.90</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>0.0117</t>
+          <t>0.0832</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -6942,12 +6942,12 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>70.20฿</t>
+          <t>499.20฿</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>气阀</t>
+          <t>蘑菇钉补胎</t>
         </is>
       </c>
     </row>
@@ -6957,7 +6957,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>79021262374216</t>
+          <t>YT7635427281240</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -6967,38 +6967,38 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>UN-INV260804-00019</t>
+          <t>UN-INV260807-00009</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18435-5-73</t>
+ รถ lot18458-21</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>12.20</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>0.0352</t>
+          <t>0.0117</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -7013,12 +7013,12 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>211.20฿</t>
+          <t>70.20฿</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>加长弯头</t>
+          <t>气阀</t>
         </is>
       </c>
     </row>
@@ -7028,7 +7028,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>113162219964#3</t>
+          <t>79021262374216</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -7044,17 +7044,17 @@
       <c r="E96" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18434-9-28</t>
+ รถ lot18435-5-73</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -7064,12 +7064,12 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>18.70</t>
+          <t>12.20</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>0.0443</t>
+          <t>0.0352</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -7079,15 +7079,19 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>280.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr"/>
+          <t>211.20฿</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>加长弯头</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -7095,7 +7099,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>113162219964#2</t>
+          <t>113162219964#3</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -7111,7 +7115,7 @@
       <c r="E97" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18434-9-27</t>
+ รถ lot18434-9-28</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -7131,12 +7135,12 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>22.90</t>
+          <t>18.70</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>0.0522</t>
+          <t>0.0443</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -7146,7 +7150,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>343.50฿</t>
+          <t>280.50฿</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -7162,7 +7166,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>113162219964</t>
+          <t>113162219964#2</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -7178,7 +7182,7 @@
       <c r="E98" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18434-9-26</t>
+ รถ lot18434-9-27</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -7198,12 +7202,12 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>25.60</t>
+          <t>22.90</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>0.0574</t>
+          <t>0.0522</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -7213,7 +7217,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>384.00฿</t>
+          <t>343.50฿</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -7221,11 +7225,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N98" t="inlineStr">
-        <is>
-          <t>补胎胶片/3件</t>
-        </is>
-      </c>
+      <c r="N98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -7233,7 +7233,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>113158800045#2</t>
+          <t>113162219964</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -7249,32 +7249,32 @@
       <c r="E99" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18427-7-3</t>
+ รถ lot18434-9-26</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>26/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>26/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>26.30</t>
+          <t>25.60</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>0.0377</t>
+          <t>0.0574</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -7284,7 +7284,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>394.50฿</t>
+          <t>384.00฿</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -7292,7 +7292,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N99" t="inlineStr"/>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>补胎胶片/3件</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -7300,7 +7304,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>113158800045</t>
+          <t>113158800045#2</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -7316,7 +7320,7 @@
       <c r="E100" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18427-7-2</t>
+ รถ lot18427-7-3</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -7336,12 +7340,12 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>26.50</t>
+          <t>26.30</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>0.0379</t>
+          <t>0.0377</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -7351,7 +7355,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>397.50฿</t>
+          <t>394.50฿</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -7359,11 +7363,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N100" t="inlineStr">
-        <is>
-          <t>塑料配件/2件</t>
-        </is>
-      </c>
+      <c r="N100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -7371,7 +7371,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>YT2550516723148</t>
+          <t>113158800045</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -7387,32 +7387,32 @@
       <c r="E101" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18398-3-10</t>
+ รถ lot18427-7-2</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>22/07/2026</t>
+          <t>26/07/2026</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>23/07/2026</t>
+          <t>26/07/2026</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>26.50</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>0.0127</t>
+          <t>0.0379</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -7422,17 +7422,17 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>397.50฿</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>76.20฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>硅胶风管</t>
+          <t>塑料配件/2件</t>
         </is>
       </c>
     </row>

--- a/cargo_packages_p1-5.xlsx
+++ b/cargo_packages_p1-5.xlsx
@@ -1093,7 +1093,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">

--- a/cargo_packages_p1-5.xlsx
+++ b/cargo_packages_p1-5.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>S71749075994</t>
+          <t>ZY202462495078</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -522,17 +522,17 @@
       <c r="E2" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18830-6-30</t>
+ รถ lot18844-9-4</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -542,12 +542,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>119.00</t>
+          <t>14.30</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.2302</t>
+          <t>0.0624</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -557,17 +557,17 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>1,785.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>374.40฿</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>真空胎扒胎机配件/木箱</t>
+          <t>胎压表</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>435358249576981</t>
+          <t>S71749075994</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -593,17 +593,17 @@
       <c r="E3" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18815-4-6</t>
+ รถ lot18830-6-30</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -613,12 +613,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5.20</t>
+          <t>119.00</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.0044</t>
+          <t>0.2302</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -628,7 +628,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>78.00฿</t>
+          <t>1,785.00฿</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>气门嘴</t>
+          <t>真空胎扒胎机配件/木箱</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>S71195667064</t>
+          <t>435358249576981</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -664,12 +664,12 @@
       <c r="E4" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18810-6-3</t>
+ รถ lot18815-4-6</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -684,32 +684,32 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>165.00</t>
+          <t>5.20</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.8568</t>
+          <t>0.0044</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>78.00฿</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>5,140.80฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>千斤顶，3件，客户不打木架发</t>
+          <t>气门嘴</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>113350746029#4</t>
+          <t>S71195667064</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,17 +735,17 @@
       <c r="E5" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18799-6-32</t>
+ รถ lot18810-6-3</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -755,17 +755,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>27.70</t>
+          <t>165.00</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.0800</t>
+          <t>0.8568</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -775,10 +775,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>480.00฿</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>5,140.80฿</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>千斤顶，3件，客户不打木架发</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -786,7 +790,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>113350746029#3</t>
+          <t>113350746029#4</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -802,7 +806,7 @@
       <c r="E6" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18799-6-31</t>
+ รถ lot18799-6-32</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -822,12 +826,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>10.90</t>
+          <t>27.70</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.0377</t>
+          <t>0.0800</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -842,7 +846,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>226.20฿</t>
+          <t>480.00฿</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -853,7 +857,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>113350746029#2</t>
+          <t>113350746029#3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -869,7 +873,7 @@
       <c r="E7" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18799-6-30</t>
+ รถ lot18799-6-31</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -889,12 +893,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>15.00</t>
+          <t>10.90</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.0101</t>
+          <t>0.0377</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -904,12 +908,12 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>225.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>226.20฿</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -920,7 +924,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>113350746029</t>
+          <t>113350746029#2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -936,7 +940,7 @@
       <c r="E8" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18799-6-29</t>
+ รถ lot18799-6-30</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -956,12 +960,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>16.50</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.0127</t>
+          <t>0.0101</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -971,7 +975,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>247.50฿</t>
+          <t>225.00฿</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -979,11 +983,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>真空胎加固修理补片</t>
-        </is>
-      </c>
+      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -991,7 +991,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>760246657062</t>
+          <t>113350746029</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1007,7 +1007,7 @@
       <c r="E9" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18799-7-3</t>
+ รถ lot18799-6-29</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>16.50</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.0005</t>
+          <t>0.0127</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1042,17 +1042,17 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>247.50฿</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>10.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>气门嘴，轮胎修补工具，气门芯宣传册</t>
+          <t>真空胎加固修理补片</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>113348267192#2</t>
+          <t>760246657062</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1078,32 +1078,32 @@
       <c r="E10" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18795-2-7</t>
+ รถ lot18799-7-3</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>28.10</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.0628</t>
+          <t>0.0005</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1113,15 +1113,19 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>421.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+          <t>10.00฿</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>气门嘴，轮胎修补工具，气门芯宣传册</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1129,7 +1133,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>113348267192</t>
+          <t>113348267192#2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1139,13 +1143,13 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>UN-INV260921-00019</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18795-2-6</t>
+ รถ lot18795-2-7</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1165,12 +1169,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>19.50</t>
+          <t>28.10</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.0505</t>
+          <t>0.0628</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1180,19 +1184,15 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>421.50฿</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>303.00฿</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>补胎胶片</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ZY202472578299</t>
+          <t>113348267192</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1210,43 +1210,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>UN-INV260918-00012</t>
+          <t>UN-INV260921-00019</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18758-7-43</t>
+ รถ lot18795-2-6</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>47.40</t>
+          <t>19.50</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0.1603</t>
+          <t>0.0505</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>961.20฿</t>
+          <t>303.00฿</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>补胎贴，3件</t>
+          <t>补胎胶片</t>
         </is>
       </c>
     </row>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>773440822655698</t>
+          <t>ZY202472578299</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1287,7 +1287,7 @@
       <c r="E13" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18758-4-31</t>
+ รถ lot18758-7-43</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>47.40</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0.0022</t>
+          <t>0.1603</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>18.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>961.20฿</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>钻头</t>
+          <t>补胎贴，3件</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>YT7642998390994</t>
+          <t>773440822655698</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1358,7 +1358,7 @@
       <c r="E14" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18769-3-57</t>
+ รถ lot18758-4-31</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1378,12 +1378,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>5.80</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.0070</t>
+          <t>0.0022</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1393,7 +1393,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>87.00฿</t>
+          <t>18.00฿</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>钻头</t>
         </is>
       </c>
     </row>
@@ -1413,7 +1413,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DPK212614057101</t>
+          <t>YT7642998390994</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1423,38 +1423,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>UN-INV260916-00003</t>
+          <t>UN-INV260918-00012</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18749-4-3</t>
+ รถ lot18769-3-57</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>9.60</t>
+          <t>5.80</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.0060</t>
+          <t>0.0070</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>144.00฿</t>
+          <t>87.00฿</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>轮胎气门嘴</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>79031204783305</t>
+          <t>DPK212614057101</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1500,7 +1500,7 @@
       <c r="E16" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18744-6-15</t>
+ รถ lot18749-4-3</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1520,12 +1520,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>9.60</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>0.0020</t>
+          <t>0.0060</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>39.00฿</t>
+          <t>144.00฿</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>轮胎气门嘴</t>
         </is>
       </c>
     </row>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>435342988112655</t>
+          <t>79031204783305</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1571,17 +1571,17 @@
       <c r="E17" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18743-3-34</t>
+ รถ lot18744-6-15</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.0014</t>
+          <t>0.0020</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1606,17 +1606,17 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>39.00฿</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>10.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>橡胶垫圈</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -1626,7 +1626,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>435343890137834</t>
+          <t>435342988112655</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1642,7 +1642,7 @@
       <c r="E18" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18743-7-25</t>
+ รถ lot18743-3-34</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1662,12 +1662,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>21.40</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>0.0080</t>
+          <t>0.0014</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1677,17 +1677,17 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>321.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10.00฿</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>扒胎机包胶撬棍</t>
+          <t>橡胶垫圈</t>
         </is>
       </c>
     </row>
@@ -1697,7 +1697,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>YT7642670434639</t>
+          <t>435343890137834</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1713,7 +1713,7 @@
       <c r="E19" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18743-2-8</t>
+ รถ lot18743-7-25</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1733,12 +1733,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>21.40</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>0.0010</t>
+          <t>0.0080</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1748,7 +1748,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>12.00฿</t>
+          <t>321.00฿</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>片片</t>
+          <t>扒胎机包胶撬棍</t>
         </is>
       </c>
     </row>
@@ -1768,7 +1768,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>93015797092</t>
+          <t>YT7642670434639</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1778,18 +1778,18 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>UN-INV260914-00014</t>
+          <t>UN-INV260916-00003</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18735-4-40</t>
+ รถ lot18743-2-8</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1799,17 +1799,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>12/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>8.60</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0.0148</t>
+          <t>0.0010</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1819,7 +1819,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>129.00฿</t>
+          <t>12.00฿</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1829,7 +1829,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>仪表</t>
+          <t>片片</t>
         </is>
       </c>
     </row>
@@ -1839,7 +1839,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>YT7642390374765</t>
+          <t>93015797092</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1849,13 +1849,13 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>UN-INV260914-00015</t>
+          <t>UN-INV260914-00014</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18735-4-20</t>
+ รถ lot18735-4-40</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1875,12 +1875,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>20.80</t>
+          <t>8.60</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.0598</t>
+          <t>0.0148</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1890,17 +1890,17 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>129.00฿</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>358.80฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>打磨机</t>
+          <t>仪表</t>
         </is>
       </c>
     </row>
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>435342255104130</t>
+          <t>YT7642390374765</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1920,13 +1920,13 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>UN-INV260914-00014</t>
+          <t>UN-INV260914-00015</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18735-43</t>
+ รถ lot18735-4-20</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1946,12 +1946,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>4.90</t>
+          <t>20.80</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.0172</t>
+          <t>0.0598</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1966,12 +1966,12 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>103.20฿</t>
+          <t>358.80฿</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>轮毂保护套</t>
+          <t>打磨机</t>
         </is>
       </c>
     </row>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>773440312345715</t>
+          <t>435342255104130</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1997,7 +1997,7 @@
       <c r="E23" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18735-3-78</t>
+ รถ lot18735-43</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2017,12 +2017,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>4.90</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.0013</t>
+          <t>0.0172</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2032,17 +2032,17 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>19.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>103.20฿</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>轮毂保护套</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>773440291470393</t>
+          <t>773440312345715</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2068,7 +2068,7 @@
       <c r="E24" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18735-34</t>
+ รถ lot18735-3-78</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2088,12 +2088,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.0029</t>
+          <t>0.0013</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2103,7 +2103,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>48.00฿</t>
+          <t>19.50฿</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>球阀</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>435342261175750</t>
+          <t>773440291470393</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2133,13 +2133,13 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>UN-INV260914-00015</t>
+          <t>UN-INV260914-00014</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18736-13</t>
+ รถ lot18735-34</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2159,12 +2159,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>13.90</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.0137</t>
+          <t>0.0029</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>208.50฿</t>
+          <t>48.00฿</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>球阀</t>
         </is>
       </c>
     </row>
@@ -2194,7 +2194,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ZY202461195200</t>
+          <t>435342261175750</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2210,7 +2210,7 @@
       <c r="E26" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18728-7-13</t>
+ รถ lot18736-13</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2225,17 +2225,17 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>13/09/2026</t>
+          <t>12/09/2026</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>47.40</t>
+          <t>13.90</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>0.0116</t>
+          <t>0.0137</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2245,7 +2245,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>711.00฿</t>
+          <t>208.50฿</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>79030687835952</t>
+          <t>ZY202461195200</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2275,13 +2275,13 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>UN-INV260914-00014</t>
+          <t>UN-INV260914-00015</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18728-3-64</t>
+ รถ lot18728-7-13</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>4.30</t>
+          <t>47.40</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.0030</t>
+          <t>0.0116</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>64.50฿</t>
+          <t>711.00฿</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2326,7 +2326,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>接头配件</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>LJ20722214#3</t>
+          <t>79030687835952</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2346,38 +2346,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>UN-INV260912-00011</t>
+          <t>UN-INV260914-00014</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18726-7-8</t>
+ รถ lot18728-3-64</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>13/09/2026</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>14.00</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.0171</t>
+          <t>0.0030</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2387,7 +2387,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>210.00฿</t>
+          <t>64.50฿</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2395,7 +2395,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>接头配件</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2403,7 +2407,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>LJ20722214#2</t>
+          <t>LJ20722214#3</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2419,7 +2423,7 @@
       <c r="E29" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18726-7-7</t>
+ รถ lot18726-7-8</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2439,12 +2443,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>11.90</t>
+          <t>14.00</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0.0089</t>
+          <t>0.0171</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2454,7 +2458,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>178.50฿</t>
+          <t>210.00฿</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2470,7 +2474,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>LJ20722214</t>
+          <t>LJ20722214#2</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2486,7 +2490,7 @@
       <c r="E30" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18726-7-6</t>
+ รถ lot18726-7-7</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2506,12 +2510,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>16.00</t>
+          <t>11.90</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.0144</t>
+          <t>0.0089</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2521,7 +2525,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>240.00฿</t>
+          <t>178.50฿</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2529,11 +2533,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>电板套筒配件/3件</t>
-        </is>
-      </c>
+      <c r="N30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2541,7 +2541,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>YT7641966426761</t>
+          <t>LJ20722214</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2557,17 +2557,17 @@
       <c r="E31" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18714-9-23</t>
+ รถ lot18726-7-6</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2577,12 +2577,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>13.60</t>
+          <t>16.00</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.0422</t>
+          <t>0.0144</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2592,17 +2592,17 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>240.00฿</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>253.20฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>带表汽车轮胎打气嘴</t>
+          <t>电板套筒配件/3件</t>
         </is>
       </c>
     </row>
@@ -2612,7 +2612,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ZY202471681117#2</t>
+          <t>YT7641966426761</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2628,7 +2628,7 @@
       <c r="E32" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18714-9-8</t>
+ รถ lot18714-9-23</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2648,12 +2648,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>11.80</t>
+          <t>13.60</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.0832</t>
+          <t>0.0422</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2668,10 +2668,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>499.20฿</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
+          <t>253.20฿</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>带表汽车轮胎打气嘴</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2679,7 +2683,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ZY202471681117</t>
+          <t>ZY202471681117#2</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2695,7 +2699,7 @@
       <c r="E33" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18714-9-7</t>
+ รถ lot18714-9-8</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2715,12 +2719,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>7.70</t>
+          <t>11.80</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.0493</t>
+          <t>0.0832</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2735,14 +2739,10 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>295.80฿</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>补胎胶片/2件</t>
-        </is>
-      </c>
+          <t>499.20฿</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>302285502767#2</t>
+          <t>ZY202471681117</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2766,7 +2766,7 @@
       <c r="E34" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18714-8-10</t>
+ รถ lot18714-9-7</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2786,12 +2786,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>33.70</t>
+          <t>7.70</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.0145</t>
+          <t>0.0493</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2801,15 +2801,19 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>505.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
+          <t>295.80฿</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>补胎胶片/2件</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2817,7 +2821,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>302285502767</t>
+          <t>302285502767#2</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2833,7 +2837,7 @@
       <c r="E35" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18714-8-9</t>
+ รถ lot18714-8-10</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2853,12 +2857,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>23.40</t>
+          <t>33.70</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.0123</t>
+          <t>0.0145</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2868,7 +2872,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>351.00฿</t>
+          <t>505.50฿</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2876,11 +2880,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>扳手</t>
-        </is>
-      </c>
+      <c r="N35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2888,7 +2888,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>LJ20716178#2</t>
+          <t>302285502767</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2898,18 +2898,18 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>UN-INV260911-00013</t>
+          <t>UN-INV260912-00011</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18713-6-65</t>
+ รถ lot18714-8-9</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>19.50</t>
+          <t>23.40</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.0075</t>
+          <t>0.0123</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2939,7 +2939,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>292.50฿</t>
+          <t>351.00฿</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2947,7 +2947,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>扳手</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2955,7 +2959,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>LJ20716178</t>
+          <t>LJ20716178#2</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2971,7 +2975,7 @@
       <c r="E37" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18713-6-64</t>
+ รถ lot18713-6-65</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2991,7 +2995,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>19.60</t>
+          <t>19.50</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -3006,7 +3010,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>294.00฿</t>
+          <t>292.50฿</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3014,11 +3018,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>配件</t>
-        </is>
-      </c>
+      <c r="N37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -3026,7 +3026,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>435338972466812</t>
+          <t>LJ20716178</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3042,7 +3042,7 @@
       <c r="E38" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18710-6-35</t>
+ รถ lot18713-6-64</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -3052,7 +3052,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3062,12 +3062,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>13.10</t>
+          <t>19.60</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.0624</t>
+          <t>0.0075</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -3077,17 +3077,17 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>294.00฿</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>374.40฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>修补工具</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -3097,7 +3097,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>435334324045675</t>
+          <t>435338972466812</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3107,38 +3107,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>UN-INV260908-00009</t>
+          <t>UN-INV260911-00013</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18696-14</t>
+ รถ lot18710-6-35</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>10.80</t>
+          <t>13.10</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.0088</t>
+          <t>0.0624</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -3148,17 +3148,17 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>162.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>374.40฿</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>修补工具</t>
         </is>
       </c>
     </row>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>YT7641276428798</t>
+          <t>435334324045675</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3184,7 +3184,7 @@
       <c r="E40" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18697-11</t>
+ รถ lot18696-14</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>9.50</t>
+          <t>10.80</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.0296</t>
+          <t>0.0088</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>162.00฿</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>177.60฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3239,7 +3239,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>79029430531776</t>
+          <t>YT7641276428798</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3249,18 +3249,18 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>UN-INV260907-00015</t>
+          <t>UN-INV260908-00009</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18689-26</t>
+ รถ lot18697-11</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -3270,17 +3270,17 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>9.50</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.0135</t>
+          <t>0.0296</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>81.00฿</t>
+          <t>177.60฿</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>卡套</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>113282578128#2</t>
+          <t>79029430531776</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3326,17 +3326,17 @@
       <c r="E42" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18683-4</t>
+ รถ lot18689-26</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3346,12 +3346,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>38.00</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.1601</t>
+          <t>0.0135</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3366,10 +3366,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>960.60฿</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
+          <t>81.00฿</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>卡套</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -3377,7 +3381,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>113282578128</t>
+          <t>113282578128#2</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3393,7 +3397,7 @@
       <c r="E43" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18683-3</t>
+ รถ lot18683-4</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -3413,12 +3417,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>27.50</t>
+          <t>38.00</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.1566</t>
+          <t>0.1601</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3433,14 +3437,10 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>939.60฿</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>压条取出器 一票两件破损件</t>
-        </is>
-      </c>
+          <t>960.60฿</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -3448,7 +3448,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>82730128600#3</t>
+          <t>113282578128</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3464,12 +3464,12 @@
       <c r="E44" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18678-6-21</t>
+ รถ lot18683-3</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>30/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>33.00</t>
+          <t>27.50</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.0122</t>
+          <t>0.1566</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3499,15 +3499,19 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>495.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
+          <t>939.60฿</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>压条取出器 一票两件破损件</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -3515,7 +3519,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>82730128600#2</t>
+          <t>82730128600#3</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3531,7 +3535,7 @@
       <c r="E45" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18678-6-20</t>
+ รถ lot18678-6-21</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -3551,12 +3555,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>27.60</t>
+          <t>33.00</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.0095</t>
+          <t>0.0122</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3566,7 +3570,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>414.00฿</t>
+          <t>495.00฿</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3582,7 +3586,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>82730128600</t>
+          <t>82730128600#2</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3598,7 +3602,7 @@
       <c r="E46" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18678-6-19</t>
+ รถ lot18678-6-20</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -3618,12 +3622,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>28.10</t>
+          <t>27.60</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>0.0118</t>
+          <t>0.0095</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3633,7 +3637,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>421.50฿</t>
+          <t>414.00฿</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3641,11 +3645,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>五金配件/3件</t>
-        </is>
-      </c>
+      <c r="N46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -3653,7 +3653,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>113278387839#3</t>
+          <t>82730128600</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3663,38 +3663,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>UN-INV260903-00023</t>
+          <t>UN-INV260907-00015</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18663-8-3</t>
+ รถ lot18678-6-19</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>30/08/2026</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>25.30</t>
+          <t>28.10</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>0.0404</t>
+          <t>0.0118</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>379.50฿</t>
+          <t>421.50฿</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3712,7 +3712,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>五金配件/3件</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -3720,7 +3724,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>113278387839#2</t>
+          <t>113278387839#3</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3736,7 +3740,7 @@
       <c r="E48" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18663-8-2</t>
+ รถ lot18663-8-3</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -3756,12 +3760,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>26.10</t>
+          <t>25.30</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>0.0304</t>
+          <t>0.0404</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3771,7 +3775,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>391.50฿</t>
+          <t>379.50฿</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3787,7 +3791,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>113278387839</t>
+          <t>113278387839#2</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3803,7 +3807,7 @@
       <c r="E49" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18663-8-1</t>
+ รถ lot18663-8-2</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3823,12 +3827,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>9.10</t>
+          <t>26.10</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>0.0144</t>
+          <t>0.0304</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3838,7 +3842,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>136.50฿</t>
+          <t>391.50฿</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3846,11 +3850,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>配件/3件</t>
-        </is>
-      </c>
+      <c r="N49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>113276098937#3</t>
+          <t>113278387839</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3868,38 +3868,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>UN-INV260901-00057</t>
+          <t>UN-INV260903-00023</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-45</t>
+ รถ lot18663-8-1</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>17.80</t>
+          <t>9.10</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>0.0302</t>
+          <t>0.0144</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3909,7 +3909,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>267.00฿</t>
+          <t>136.50฿</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -3917,7 +3917,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>配件/3件</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -3925,7 +3929,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>113276098937#2</t>
+          <t>113276098937#3</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3941,7 +3945,7 @@
       <c r="E51" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-44</t>
+ รถ lot18655-9-45</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -3961,12 +3965,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>10.90</t>
+          <t>17.80</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>0.0313</t>
+          <t>0.0302</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3976,12 +3980,12 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>267.00฿</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>187.80฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N51" t="inlineStr"/>
@@ -3992,7 +3996,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>113276098937</t>
+          <t>113276098937#2</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -4008,7 +4012,7 @@
       <c r="E52" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-43</t>
+ รถ lot18655-9-44</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -4028,12 +4032,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>33.60</t>
+          <t>10.90</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>0.0825</t>
+          <t>0.0313</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -4043,19 +4047,15 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>504.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>补胎胶片+配件/3件</t>
-        </is>
-      </c>
+          <t>187.80฿</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -4063,7 +4063,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ZY202464580877#4</t>
+          <t>113276098937</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -4079,7 +4079,7 @@
       <c r="E53" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-17</t>
+ รถ lot18655-9-43</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -4099,12 +4099,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>20.10</t>
+          <t>33.60</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>0.0466</t>
+          <t>0.0825</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -4114,7 +4114,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>301.50฿</t>
+          <t>504.00฿</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -4122,7 +4122,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr"/>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>补胎胶片+配件/3件</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -4130,7 +4134,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ZY202464580877#7</t>
+          <t>ZY202464580877#4</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -4146,7 +4150,7 @@
       <c r="E54" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-16</t>
+ รถ lot18655-9-17</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -4166,12 +4170,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>16.60</t>
+          <t>20.10</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>0.0430</t>
+          <t>0.0466</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -4181,12 +4185,12 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>301.50฿</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>258.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
@@ -4197,7 +4201,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ZY202464580877#2</t>
+          <t>ZY202464580877#7</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -4213,7 +4217,7 @@
       <c r="E55" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-15</t>
+ รถ lot18655-9-16</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -4233,12 +4237,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>25.10</t>
+          <t>16.60</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>0.0483</t>
+          <t>0.0430</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -4248,12 +4252,12 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>376.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>258.00฿</t>
         </is>
       </c>
       <c r="N55" t="inlineStr"/>
@@ -4264,7 +4268,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ZY202464580877#8</t>
+          <t>ZY202464580877#2</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -4280,7 +4284,7 @@
       <c r="E56" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-14</t>
+ รถ lot18655-9-15</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -4300,12 +4304,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>28.90</t>
+          <t>25.10</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>0.0800</t>
+          <t>0.0483</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -4315,12 +4319,12 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>376.50฿</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>480.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
@@ -4331,7 +4335,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ZY202464580877#6</t>
+          <t>ZY202464580877#8</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -4347,7 +4351,7 @@
       <c r="E57" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-13</t>
+ รถ lot18655-9-14</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -4367,12 +4371,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>20.90</t>
+          <t>28.90</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>0.0534</t>
+          <t>0.0800</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -4387,7 +4391,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>320.40฿</t>
+          <t>480.00฿</t>
         </is>
       </c>
       <c r="N57" t="inlineStr"/>
@@ -4398,7 +4402,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ZY202464580877#5</t>
+          <t>ZY202464580877#6</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -4414,7 +4418,7 @@
       <c r="E58" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-12</t>
+ รถ lot18655-9-13</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -4434,12 +4438,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>26.20</t>
+          <t>20.90</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>0.0535</t>
+          <t>0.0534</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -4449,12 +4453,12 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>393.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>320.40฿</t>
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
@@ -4465,7 +4469,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ZY202464580877</t>
+          <t>ZY202464580877#5</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4481,7 +4485,7 @@
       <c r="E59" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-11</t>
+ รถ lot18655-9-12</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -4501,12 +4505,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>20.70</t>
+          <t>26.20</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>0.0531</t>
+          <t>0.0535</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4516,12 +4520,12 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>393.00฿</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>318.60฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
@@ -4532,7 +4536,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ZY202464580877#9</t>
+          <t>ZY202464580877</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4548,7 +4552,7 @@
       <c r="E60" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-10</t>
+ รถ lot18655-9-11</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -4568,12 +4572,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>27.70</t>
+          <t>20.70</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>0.0800</t>
+          <t>0.0531</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -4588,7 +4592,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>480.00฿</t>
+          <t>318.60฿</t>
         </is>
       </c>
       <c r="N60" t="inlineStr"/>
@@ -4599,7 +4603,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>ZY202464580877#3</t>
+          <t>ZY202464580877#9</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4615,7 +4619,7 @@
       <c r="E61" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-9</t>
+ รถ lot18655-9-10</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -4635,12 +4639,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>27.10</t>
+          <t>27.70</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>0.0567</t>
+          <t>0.0800</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -4650,19 +4654,15 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>406.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>补胎胶片/9件</t>
-        </is>
-      </c>
+          <t>480.00฿</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>S71090288685</t>
+          <t>ZY202464580877#3</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4680,38 +4680,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>UN-INV260831-00017</t>
+          <t>UN-INV260901-00057</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18634-7-3</t>
+ รถ lot18655-9-9</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>29/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>12.10</t>
+          <t>27.10</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>0.0240</t>
+          <t>0.0567</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>181.50฿</t>
+          <t>406.50฿</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>补胎胶片/9件</t>
         </is>
       </c>
     </row>
@@ -4741,7 +4741,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>YT7638092409979</t>
+          <t>S71090288685</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4751,38 +4751,38 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>UN-INV260822-00010</t>
+          <t>UN-INV260831-00017</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18569-7-7</t>
+ รถ lot18634-7-3</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>16/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>16/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>29/08/2026</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>15.00</t>
+          <t>12.10</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>0.0140</t>
+          <t>0.0240</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -4792,7 +4792,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>225.00฿</t>
+          <t>181.50฿</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -4812,7 +4812,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>435308000517585</t>
+          <t>YT7638092409979</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4828,32 +4828,32 @@
       <c r="E64" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18550-6-11</t>
+ รถ lot18569-7-7</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>16/08/2026</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>16/08/2026</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>0.0032</t>
+          <t>0.0140</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -4863,7 +4863,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>54.00฿</t>
+          <t>225.00฿</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>气门嘴</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>710094401487</t>
+          <t>435308000517585</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4899,17 +4899,17 @@
       <c r="E65" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18544-8-14</t>
+ รถ lot18550-6-11</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4919,32 +4919,32 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>107.10</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>0.4536</t>
+          <t>0.0032</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>54.00฿</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>2,721.60฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>空的高压充气罐/一票10件，仓库实收到9件，已确认收到的9件先发</t>
+          <t>气门嘴</t>
         </is>
       </c>
     </row>
@@ -4954,7 +4954,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>773435675083665</t>
+          <t>710094401487</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4964,58 +4964,58 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>UN-INV260815-00046</t>
+          <t>UN-INV260822-00010</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18526-6-17</t>
+ รถ lot18544-8-14</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>13.10</t>
+          <t>107.10</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>0.0214</t>
+          <t>0.4536</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>196.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2,721.60฿</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>补胎工具</t>
+          <t>空的高压充气罐/一票10件，仓库实收到9件，已确认收到的9件先发</t>
         </is>
       </c>
     </row>
@@ -5025,7 +5025,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>YT7637032206975</t>
+          <t>773435675083665</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -5035,38 +5035,38 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>UN-INV260819-00010</t>
+          <t>UN-INV260815-00046</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>มอก.
- รถ lot18523-6-30</t>
+          <t>ธรรมดา
+ รถ lot18526-6-17</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>16/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>9.60</t>
+          <t>13.10</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>0.0316</t>
+          <t>0.0214</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -5076,17 +5076,17 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>196.50฿</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>214.88฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>气动模具研磨机+配件</t>
+          <t>补胎工具</t>
         </is>
       </c>
     </row>
@@ -5096,7 +5096,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>ZY202466648481#5</t>
+          <t>YT7637032206975</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -5106,13 +5106,13 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>UN-INV260815-00046</t>
+          <t>UN-INV260819-00010</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>ธรรมดา
- รถ lot18519-6-17</t>
+          <t>มอก.
+ รถ lot18523-6-30</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -5127,17 +5127,17 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>15/08/2026</t>
+          <t>16/08/2026</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>16.10</t>
+          <t>9.60</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>0.0493</t>
+          <t>0.0316</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -5152,10 +5152,14 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>295.80฿</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
+          <t>214.88฿</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>气动模具研磨机+配件</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -5163,7 +5167,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>ZY202466648481#4</t>
+          <t>ZY202466648481#5</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -5179,7 +5183,7 @@
       <c r="E69" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18519-6-16</t>
+ รถ lot18519-6-17</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -5199,12 +5203,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>20.50</t>
+          <t>16.10</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>0.0656</t>
+          <t>0.0493</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -5219,7 +5223,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>393.60฿</t>
+          <t>295.80฿</t>
         </is>
       </c>
       <c r="N69" t="inlineStr"/>
@@ -5230,7 +5234,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>ZY202466648481#3</t>
+          <t>ZY202466648481#4</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -5246,7 +5250,7 @@
       <c r="E70" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18519-6-15</t>
+ รถ lot18519-6-16</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -5266,12 +5270,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>15.70</t>
+          <t>20.50</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>0.0508</t>
+          <t>0.0656</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -5286,7 +5290,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>304.80฿</t>
+          <t>393.60฿</t>
         </is>
       </c>
       <c r="N70" t="inlineStr"/>
@@ -5297,7 +5301,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>ZY202466648481#2</t>
+          <t>ZY202466648481#3</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -5313,7 +5317,7 @@
       <c r="E71" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18519-6-14</t>
+ รถ lot18519-6-15</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -5333,12 +5337,12 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>20.20</t>
+          <t>15.70</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>0.0660</t>
+          <t>0.0508</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -5353,7 +5357,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>396.00฿</t>
+          <t>304.80฿</t>
         </is>
       </c>
       <c r="N71" t="inlineStr"/>
@@ -5364,7 +5368,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>ZY202466648481</t>
+          <t>ZY202466648481#2</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -5380,7 +5384,7 @@
       <c r="E72" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18519-6-13</t>
+ รถ lot18519-6-14</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -5400,12 +5404,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>15.80</t>
+          <t>20.20</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>0.0522</t>
+          <t>0.0660</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -5420,14 +5424,10 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>313.20฿</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr">
-        <is>
-          <t>补胎胶条/5件</t>
-        </is>
-      </c>
+          <t>396.00฿</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -5435,7 +5435,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>113204676267#2</t>
+          <t>ZY202466648481</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -5451,32 +5451,32 @@
       <c r="E73" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18518-5-3</t>
+ รถ lot18519-6-13</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>15/08/2026</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>24.60</t>
+          <t>15.80</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>0.0608</t>
+          <t>0.0522</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -5486,15 +5486,19 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>369.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr"/>
+          <t>313.20฿</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>补胎胶条/5件</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -5502,7 +5506,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>113204676267</t>
+          <t>113204676267#2</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -5518,7 +5522,7 @@
       <c r="E74" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18518-5-2</t>
+ รถ lot18518-5-3</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -5538,12 +5542,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>25.00</t>
+          <t>24.60</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>0.0566</t>
+          <t>0.0608</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -5553,7 +5557,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>375.00฿</t>
+          <t>369.00฿</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -5561,11 +5565,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N74" t="inlineStr">
-        <is>
-          <t>真空胎冷补胶片</t>
-        </is>
-      </c>
+      <c r="N74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -5573,7 +5573,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>910061892464#2</t>
+          <t>113204676267</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -5589,32 +5589,32 @@
       <c r="E75" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18505-5-23</t>
+ รถ lot18518-5-2</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>30.40</t>
+          <t>25.00</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>0.0523</t>
+          <t>0.0566</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -5624,7 +5624,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>456.00฿</t>
+          <t>375.00฿</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -5632,7 +5632,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N75" t="inlineStr"/>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>真空胎冷补胶片</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -5640,7 +5644,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>910061892464</t>
+          <t>910061892464#2</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5656,7 +5660,7 @@
       <c r="E76" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18505-5-22</t>
+ รถ lot18505-5-23</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -5676,12 +5680,12 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>15.90</t>
+          <t>30.40</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>0.0353</t>
+          <t>0.0523</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -5691,7 +5695,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>238.50฿</t>
+          <t>456.00฿</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -5699,11 +5703,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N76" t="inlineStr">
-        <is>
-          <t>记号蜡笔</t>
-        </is>
-      </c>
+      <c r="N76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>773434709817985</t>
+          <t>910061892464</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -5721,38 +5721,38 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>UN-INV260819-00010</t>
+          <t>UN-INV260815-00046</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18535-8</t>
+ รถ lot18505-5-22</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>16/08/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>15.90</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>0.0184</t>
+          <t>0.0353</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -5762,17 +5762,17 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>238.50฿</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>110.40฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>锅具 二次包装货物变形</t>
+          <t>记号蜡笔</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>435295775627304</t>
+          <t>773434709817985</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -5792,38 +5792,38 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>UN-INV260811-00012</t>
+          <t>UN-INV260819-00010</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18492-2</t>
+ รถ lot18535-8</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>16/08/2026</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>5.30</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>0.0090</t>
+          <t>0.0184</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>79.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>110.40฿</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>配件 破损件</t>
+          <t>锅具 二次包装货物变形</t>
         </is>
       </c>
     </row>
@@ -5853,7 +5853,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>YT7636332367470</t>
+          <t>435295775627304</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -5869,7 +5869,7 @@
       <c r="E79" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18487-2-27</t>
+ รถ lot18492-2</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -5889,12 +5889,12 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>5.30</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>0.0004</t>
+          <t>0.0090</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -5904,17 +5904,17 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>79.50฿</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>10.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>立牌</t>
+          <t>配件 破损件</t>
         </is>
       </c>
     </row>
@@ -5924,7 +5924,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>S35386280517#2</t>
+          <t>YT7636332367470</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -5940,32 +5940,32 @@
       <c r="E80" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18475-24</t>
+ รถ lot18487-2-27</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>8.80</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>0.0045</t>
+          <t>0.0004</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -5975,15 +5975,19 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>132.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr"/>
+          <t>10.00฿</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>立牌</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -5991,7 +5995,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>S35386280517</t>
+          <t>S35386280517#2</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -6007,7 +6011,7 @@
       <c r="E81" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18475-23</t>
+ รถ lot18475-24</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -6027,22 +6031,22 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>103.50</t>
+          <t>8.80</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>0.2236</t>
+          <t>0.0045</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>1,552.50฿</t>
+          <t>132.00฿</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -6050,11 +6054,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N81" t="inlineStr">
-        <is>
-          <t>气门嘴 顺心捷达，一票16件</t>
-        </is>
-      </c>
+      <c r="N81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -6062,7 +6062,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>YT7635787693833</t>
+          <t>S35386280517</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -6078,7 +6078,7 @@
       <c r="E82" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18473-6-41</t>
+ รถ lot18475-23</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -6093,37 +6093,37 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>13.80</t>
+          <t>103.50</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>0.0432</t>
+          <t>0.2236</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1,552.50฿</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>259.20฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>气压表/面单没有代码</t>
+          <t>气门嘴 顺心捷达，一票16件</t>
         </is>
       </c>
     </row>
@@ -6133,7 +6133,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>ZY202465806614</t>
+          <t>YT7635787693833</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -6143,38 +6143,38 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>UN-INV260807-00009</t>
+          <t>UN-INV260811-00012</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>มอก.
- รถ lot18466-5-51</t>
+          <t>ธรรมดา
+ รถ lot18473-6-41</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>11.30</t>
+          <t>13.80</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>0.0655</t>
+          <t>0.0432</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -6189,12 +6189,12 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>445.40฿</t>
+          <t>259.20฿</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>电子数显胎压枪</t>
+          <t>气压表/面单没有代码</t>
         </is>
       </c>
     </row>
@@ -6204,7 +6204,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>113177184579#7</t>
+          <t>ZY202465806614</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -6219,18 +6219,18 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>ธรรมดา
- รถ lot18463-17</t>
+          <t>มอก.
+ รถ lot18466-5-51</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>9.70</t>
+          <t>11.30</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>0.0305</t>
+          <t>0.0655</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -6260,10 +6260,14 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>183.00฿</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr"/>
+          <t>445.40฿</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>电子数显胎压枪</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -6271,7 +6275,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>113177184579#5</t>
+          <t>113177184579#7</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -6287,7 +6291,7 @@
       <c r="E85" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-16</t>
+ รถ lot18463-17</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -6307,12 +6311,12 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>15.00</t>
+          <t>9.70</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>0.0137</t>
+          <t>0.0305</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -6322,12 +6326,12 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>225.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>183.00฿</t>
         </is>
       </c>
       <c r="N85" t="inlineStr"/>
@@ -6338,7 +6342,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>113177184579#4</t>
+          <t>113177184579#5</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -6354,7 +6358,7 @@
       <c r="E86" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-15</t>
+ รถ lot18463-16</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -6374,12 +6378,12 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>7.30</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>0.0235</t>
+          <t>0.0137</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -6389,12 +6393,12 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>225.00฿</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>141.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N86" t="inlineStr"/>
@@ -6405,7 +6409,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>113177184579#3</t>
+          <t>113177184579#4</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -6421,7 +6425,7 @@
       <c r="E87" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-14</t>
+ รถ lot18463-15</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -6441,12 +6445,12 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>11.90</t>
+          <t>7.30</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>0.0302</t>
+          <t>0.0235</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -6461,7 +6465,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>181.20฿</t>
+          <t>141.00฿</t>
         </is>
       </c>
       <c r="N87" t="inlineStr"/>
@@ -6472,7 +6476,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>113177184579#6</t>
+          <t>113177184579#3</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -6488,7 +6492,7 @@
       <c r="E88" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-13</t>
+ รถ lot18463-14</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -6508,12 +6512,12 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>26.10</t>
+          <t>11.90</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>0.0673</t>
+          <t>0.0302</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -6528,7 +6532,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>403.80฿</t>
+          <t>181.20฿</t>
         </is>
       </c>
       <c r="N88" t="inlineStr"/>
@@ -6539,7 +6543,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>435289604798626</t>
+          <t>113177184579#6</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -6555,7 +6559,7 @@
       <c r="E89" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18462-6-6</t>
+ รถ lot18463-13</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -6565,7 +6569,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -6575,12 +6579,12 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>9.60</t>
+          <t>26.10</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>0.0090</t>
+          <t>0.0673</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -6590,19 +6594,15 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>144.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr">
-        <is>
-          <t>螺丝配件</t>
-        </is>
-      </c>
+          <t>403.80฿</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -6610,7 +6610,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>113177184579#2</t>
+          <t>435289604798626</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -6626,7 +6626,7 @@
       <c r="E90" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-12</t>
+ รถ lot18462-6-6</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -6636,7 +6636,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -6646,12 +6646,12 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>5.30</t>
+          <t>9.60</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>0.0635</t>
+          <t>0.0090</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -6661,15 +6661,19 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>144.00฿</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>381.00฿</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>螺丝配件</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -6677,7 +6681,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>113177184579</t>
+          <t>113177184579#2</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -6693,7 +6697,7 @@
       <c r="E91" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-11</t>
+ รถ lot18463-12</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -6713,12 +6717,12 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>13.30</t>
+          <t>5.30</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>0.1176</t>
+          <t>0.0635</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -6733,14 +6737,10 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>705.60฿</t>
-        </is>
-      </c>
-      <c r="N91" t="inlineStr">
-        <is>
-          <t>蘑菇钉补胎贴</t>
-        </is>
-      </c>
+          <t>381.00฿</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -6748,7 +6748,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>435289604798722</t>
+          <t>113177184579</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -6764,7 +6764,7 @@
       <c r="E92" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18462-3</t>
+ รถ lot18463-11</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -6774,7 +6774,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6784,12 +6784,12 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>4.30</t>
+          <t>13.30</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>0.0029</t>
+          <t>0.1176</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -6799,17 +6799,17 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>64.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>705.60฿</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>气门嘴</t>
+          <t>蘑菇钉补胎贴</t>
         </is>
       </c>
     </row>
@@ -6819,7 +6819,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>ZY202471573119#2</t>
+          <t>435289604798722</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -6835,7 +6835,7 @@
       <c r="E93" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-6</t>
+ รถ lot18462-3</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6855,12 +6855,12 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>8.70</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>0.0441</t>
+          <t>0.0029</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -6870,15 +6870,19 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>64.50฿</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>264.60฿</t>
-        </is>
-      </c>
-      <c r="N93" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>气门嘴</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -6886,7 +6890,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>ZY202471573119</t>
+          <t>ZY202471573119#2</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -6902,7 +6906,7 @@
       <c r="E94" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-5</t>
+ รถ lot18463-6</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -6922,12 +6926,12 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>11.90</t>
+          <t>8.70</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>0.0832</t>
+          <t>0.0441</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -6942,14 +6946,10 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>499.20฿</t>
-        </is>
-      </c>
-      <c r="N94" t="inlineStr">
-        <is>
-          <t>蘑菇钉补胎</t>
-        </is>
-      </c>
+          <t>264.60฿</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -6957,7 +6957,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>YT7635427281240</t>
+          <t>ZY202471573119</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -6973,7 +6973,7 @@
       <c r="E95" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18458-21</t>
+ รถ lot18463-5</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -6993,12 +6993,12 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>11.90</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>0.0117</t>
+          <t>0.0832</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -7013,12 +7013,12 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>70.20฿</t>
+          <t>499.20฿</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>气阀</t>
+          <t>蘑菇钉补胎</t>
         </is>
       </c>
     </row>
@@ -7028,7 +7028,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>79021262374216</t>
+          <t>YT7635427281240</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -7038,38 +7038,38 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>UN-INV260804-00019</t>
+          <t>UN-INV260807-00009</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18435-5-73</t>
+ รถ lot18458-21</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>12.20</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>0.0352</t>
+          <t>0.0117</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>211.20฿</t>
+          <t>70.20฿</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>加长弯头</t>
+          <t>气阀</t>
         </is>
       </c>
     </row>
@@ -7099,7 +7099,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>113162219964#3</t>
+          <t>79021262374216</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -7115,17 +7115,17 @@
       <c r="E97" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18434-9-28</t>
+ รถ lot18435-5-73</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -7135,12 +7135,12 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>18.70</t>
+          <t>12.20</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>0.0443</t>
+          <t>0.0352</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -7150,15 +7150,19 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>280.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr"/>
+          <t>211.20฿</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>加长弯头</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -7166,7 +7170,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>113162219964#2</t>
+          <t>113162219964#3</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -7182,7 +7186,7 @@
       <c r="E98" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18434-9-27</t>
+ รถ lot18434-9-28</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -7202,12 +7206,12 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>22.90</t>
+          <t>18.70</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>0.0522</t>
+          <t>0.0443</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -7217,7 +7221,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>343.50฿</t>
+          <t>280.50฿</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -7233,7 +7237,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>113162219964</t>
+          <t>113162219964#2</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -7249,7 +7253,7 @@
       <c r="E99" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18434-9-26</t>
+ รถ lot18434-9-27</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -7269,12 +7273,12 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>25.60</t>
+          <t>22.90</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>0.0574</t>
+          <t>0.0522</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -7284,7 +7288,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>384.00฿</t>
+          <t>343.50฿</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -7292,11 +7296,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N99" t="inlineStr">
-        <is>
-          <t>补胎胶片/3件</t>
-        </is>
-      </c>
+      <c r="N99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -7304,7 +7304,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>113158800045#2</t>
+          <t>113162219964</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -7320,32 +7320,32 @@
       <c r="E100" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18427-7-3</t>
+ รถ lot18434-9-26</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>26/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>26/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>26.30</t>
+          <t>25.60</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>0.0377</t>
+          <t>0.0574</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -7355,7 +7355,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>394.50฿</t>
+          <t>384.00฿</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -7363,7 +7363,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N100" t="inlineStr"/>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>补胎胶片/3件</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -7371,7 +7375,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>113158800045</t>
+          <t>113158800045#2</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -7387,7 +7391,7 @@
       <c r="E101" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18427-7-2</t>
+ รถ lot18427-7-3</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -7407,12 +7411,12 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>26.50</t>
+          <t>26.30</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>0.0379</t>
+          <t>0.0377</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -7422,7 +7426,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>397.50฿</t>
+          <t>394.50฿</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -7430,11 +7434,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N101" t="inlineStr">
-        <is>
-          <t>塑料配件/2件</t>
-        </is>
-      </c>
+      <c r="N101" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/cargo_packages_p1-5.xlsx
+++ b/cargo_packages_p1-5.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N101"/>
+  <dimension ref="A1:N81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -532,7 +532,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -821,7 +821,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4666,11 +4666,11 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>ZY202464580877#3</t>
+          <t>S35386280517</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4680,48 +4680,48 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>UN-INV260901-00057</t>
+          <t>UN-INV260811-00012</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-9</t>
+ รถ lot18475-23</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>27.10</t>
+          <t>103.50</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>0.0567</t>
+          <t>0.2236</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>406.50฿</t>
+          <t>1,552.50฿</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -4731,17 +4731,17 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>补胎胶片/9件</t>
+          <t>气门嘴 顺心捷达，一票16件</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>S71090288685</t>
+          <t>YT7635787693833</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4751,38 +4751,38 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>UN-INV260831-00017</t>
+          <t>UN-INV260811-00012</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18634-7-3</t>
+ รถ lot18473-6-41</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>29/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>12.10</t>
+          <t>13.80</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>0.0240</t>
+          <t>0.0432</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -4792,27 +4792,27 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>181.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>259.20฿</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>气压表/面单没有代码</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>YT7638092409979</t>
+          <t>ZY202465806614</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4822,38 +4822,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>UN-INV260822-00010</t>
+          <t>UN-INV260807-00009</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>ธรรมดา
- รถ lot18569-7-7</t>
+          <t>มอก.
+ รถ lot18466-5-51</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>16/08/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>16/08/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>15.00</t>
+          <t>11.30</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>0.0140</t>
+          <t>0.0655</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -4863,27 +4863,27 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>225.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>445.40฿</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>电子数显胎压枪</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>435308000517585</t>
+          <t>113177184579#7</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4893,38 +4893,38 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>UN-INV260822-00010</t>
+          <t>UN-INV260807-00009</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18550-6-11</t>
+ รถ lot18463-17</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>9.70</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>0.0032</t>
+          <t>0.0305</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -4934,27 +4934,23 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>54.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr">
-        <is>
-          <t>气门嘴</t>
-        </is>
-      </c>
+          <t>183.00฿</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>710094401487</t>
+          <t>113177184579#5</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4964,68 +4960,64 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>UN-INV260822-00010</t>
+          <t>UN-INV260807-00009</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18544-8-14</t>
+ รถ lot18463-16</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>107.10</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>0.4536</t>
+          <t>0.0137</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>225.00฿</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>2,721.60฿</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr">
-        <is>
-          <t>空的高压充气罐/一票10件，仓库实收到9件，已确认收到的9件先发</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>773435675083665</t>
+          <t>113177184579#4</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -5035,38 +5027,38 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>UN-INV260815-00046</t>
+          <t>UN-INV260807-00009</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18526-6-17</t>
+ รถ lot18463-15</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>13.10</t>
+          <t>7.30</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>0.0214</t>
+          <t>0.0235</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -5076,27 +5068,23 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>196.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr">
-        <is>
-          <t>补胎工具</t>
-        </is>
-      </c>
+          <t>141.00฿</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>YT7637032206975</t>
+          <t>113177184579#3</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -5106,38 +5094,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>UN-INV260819-00010</t>
+          <t>UN-INV260807-00009</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>มอก.
- รถ lot18523-6-30</t>
+          <t>ธรรมดา
+ รถ lot18463-14</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>16/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>9.60</t>
+          <t>11.90</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>0.0316</t>
+          <t>0.0302</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -5152,22 +5140,18 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>214.88฿</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>气动模具研磨机+配件</t>
-        </is>
-      </c>
+          <t>181.20฿</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>ZY202466648481#5</t>
+          <t>113177184579#6</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -5177,38 +5161,38 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>UN-INV260815-00046</t>
+          <t>UN-INV260807-00009</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18519-6-17</t>
+ รถ lot18463-13</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>15/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>16.10</t>
+          <t>26.10</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>0.0493</t>
+          <t>0.0673</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -5223,18 +5207,18 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>295.80฿</t>
+          <t>403.80฿</t>
         </is>
       </c>
       <c r="N69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>ZY202466648481#4</t>
+          <t>435289604798626</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -5244,38 +5228,38 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>UN-INV260815-00046</t>
+          <t>UN-INV260807-00009</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18519-6-16</t>
+ รถ lot18462-6-6</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>15/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>20.50</t>
+          <t>9.60</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>0.0656</t>
+          <t>0.0090</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -5285,23 +5269,27 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>144.00฿</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>393.60฿</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>螺丝配件</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>ZY202466648481#3</t>
+          <t>113177184579#2</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -5311,38 +5299,38 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>UN-INV260815-00046</t>
+          <t>UN-INV260807-00009</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18519-6-15</t>
+ รถ lot18463-12</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>15/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>15.70</t>
+          <t>5.30</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>0.0508</t>
+          <t>0.0635</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -5357,18 +5345,18 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>304.80฿</t>
+          <t>381.00฿</t>
         </is>
       </c>
       <c r="N71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>ZY202466648481#2</t>
+          <t>113177184579</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -5378,38 +5366,38 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>UN-INV260815-00046</t>
+          <t>UN-INV260807-00009</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18519-6-14</t>
+ รถ lot18463-11</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>15/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>20.20</t>
+          <t>13.30</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>0.0660</t>
+          <t>0.1176</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -5424,18 +5412,22 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>396.00฿</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr"/>
+          <t>705.60฿</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>蘑菇钉补胎贴</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>ZY202466648481</t>
+          <t>435289604798722</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -5445,38 +5437,38 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>UN-INV260815-00046</t>
+          <t>UN-INV260807-00009</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18519-6-13</t>
+ รถ lot18462-3</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>15/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>15.80</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>0.0522</t>
+          <t>0.0029</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -5486,27 +5478,27 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>64.50฿</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>313.20฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>补胎胶条/5件</t>
+          <t>气门嘴</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>113204676267#2</t>
+          <t>ZY202471573119#2</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -5516,38 +5508,38 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>UN-INV260815-00046</t>
+          <t>UN-INV260807-00009</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18518-5-3</t>
+ รถ lot18463-6</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>24.60</t>
+          <t>8.70</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>0.0608</t>
+          <t>0.0441</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -5557,23 +5549,23 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>369.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>264.60฿</t>
         </is>
       </c>
       <c r="N74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>113204676267</t>
+          <t>ZY202471573119</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -5583,38 +5575,38 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>UN-INV260815-00046</t>
+          <t>UN-INV260807-00009</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18518-5-2</t>
+ รถ lot18463-5</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>25.00</t>
+          <t>11.90</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>0.0566</t>
+          <t>0.0832</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -5624,27 +5616,27 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>375.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>499.20฿</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>真空胎冷补胶片</t>
+          <t>蘑菇钉补胎</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>910061892464#2</t>
+          <t>YT7635427281240</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5654,38 +5646,38 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>UN-INV260815-00046</t>
+          <t>UN-INV260807-00009</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18505-5-23</t>
+ รถ lot18458-21</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>30.40</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>0.0523</t>
+          <t>0.0117</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -5695,23 +5687,27 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>456.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr"/>
+          <t>70.20฿</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>气阀</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>910061892464</t>
+          <t>79021262374216</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -5721,38 +5717,38 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>UN-INV260815-00046</t>
+          <t>UN-INV260804-00019</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18505-5-22</t>
+ รถ lot18435-5-73</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>15.90</t>
+          <t>12.20</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>0.0353</t>
+          <t>0.0352</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -5762,27 +5758,27 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>238.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>211.20฿</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>记号蜡笔</t>
+          <t>加长弯头</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>773434709817985</t>
+          <t>113162219964#3</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -5792,38 +5788,38 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>UN-INV260819-00010</t>
+          <t>UN-INV260804-00019</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18535-8</t>
+ รถ lot18434-9-28</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>16/08/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>18.70</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>0.0184</t>
+          <t>0.0443</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -5833,27 +5829,23 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>280.50฿</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>110.40฿</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr">
-        <is>
-          <t>锅具 二次包装货物变形</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>435295775627304</t>
+          <t>113162219964#2</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -5863,38 +5855,38 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>UN-INV260811-00012</t>
+          <t>UN-INV260804-00019</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18492-2</t>
+ รถ lot18434-9-27</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>5.30</t>
+          <t>22.90</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>0.0090</t>
+          <t>0.0522</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -5904,7 +5896,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>79.50฿</t>
+          <t>343.50฿</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -5912,19 +5904,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N79" t="inlineStr">
-        <is>
-          <t>配件 破损件</t>
-        </is>
-      </c>
+      <c r="N79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>YT7636332367470</t>
+          <t>113162219964</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -5934,38 +5922,38 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>UN-INV260811-00012</t>
+          <t>UN-INV260804-00019</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18487-2-27</t>
+ รถ lot18434-9-26</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>25.60</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>0.0004</t>
+          <t>0.0574</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -5975,27 +5963,27 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>384.00฿</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>10.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>立牌</t>
+          <t>补胎胶片/3件</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>S35386280517#2</t>
+          <t>113158800045#2</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -6005,38 +5993,38 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>UN-INV260811-00012</t>
+          <t>UN-INV260804-00019</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18475-24</t>
+ รถ lot18427-7-3</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>26/07/2026</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>26/07/2026</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>8.80</t>
+          <t>26.30</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>0.0045</t>
+          <t>0.0377</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -6046,7 +6034,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>132.00฿</t>
+          <t>394.50฿</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -6055,1386 +6043,6 @@
         </is>
       </c>
       <c r="N81" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" t="n">
-        <v>5</v>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>S35386280517</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>UN-INV260811-00012</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>ธรรมดา
- รถ lot18475-23</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>02/08/2026</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>02/08/2026</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>08/08/2026</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>103.50</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>0.2236</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>1,552.50฿</t>
-        </is>
-      </c>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr">
-        <is>
-          <t>气门嘴 顺心捷达，一票16件</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="n">
-        <v>5</v>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>YT7635787693833</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>UN-INV260811-00012</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>ธรรมดา
- รถ lot18473-6-41</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>02/08/2026</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>02/08/2026</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>07/08/2026</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>13.80</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>0.0432</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>259.20฿</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr">
-        <is>
-          <t>气压表/面单没有代码</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="n">
-        <v>5</v>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>ZY202465806614</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>UN-INV260807-00009</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>มอก.
- รถ lot18466-5-51</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>01/08/2026</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>01/08/2026</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>06/08/2026</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>11.30</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>0.0655</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L84" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>445.40฿</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr">
-        <is>
-          <t>电子数显胎压枪</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="n">
-        <v>5</v>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>113177184579#7</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>UN-INV260807-00009</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>ธรรมดา
- รถ lot18463-17</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>31/07/2026</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>31/07/2026</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>06/08/2026</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>9.70</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>0.0305</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>183.00฿</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" t="n">
-        <v>5</v>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>113177184579#5</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>UN-INV260807-00009</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>ธรรมดา
- รถ lot18463-16</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>31/07/2026</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>31/07/2026</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>06/08/2026</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>15.00</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>0.0137</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L86" t="inlineStr">
-        <is>
-          <t>225.00฿</t>
-        </is>
-      </c>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" t="n">
-        <v>5</v>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>113177184579#4</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>UN-INV260807-00009</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>ธรรมดา
- รถ lot18463-15</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>31/07/2026</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>31/07/2026</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>06/08/2026</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>7.30</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>0.0235</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>141.00฿</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" t="n">
-        <v>5</v>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>113177184579#3</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>UN-INV260807-00009</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>ธรรมดา
- รถ lot18463-14</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>31/07/2026</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>31/07/2026</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>06/08/2026</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>11.90</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>0.0302</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>181.20฿</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" t="n">
-        <v>5</v>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>113177184579#6</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>UN-INV260807-00009</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>ธรรมดา
- รถ lot18463-13</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>31/07/2026</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>31/07/2026</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>06/08/2026</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>26.10</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>0.0673</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>403.80฿</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" t="n">
-        <v>5</v>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>435289604798626</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>UN-INV260807-00009</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>ธรรมดา
- รถ lot18462-6-6</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>31/07/2026</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>01/08/2026</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>06/08/2026</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>9.60</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>0.0090</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L90" t="inlineStr">
-        <is>
-          <t>144.00฿</t>
-        </is>
-      </c>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr">
-        <is>
-          <t>螺丝配件</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="n">
-        <v>5</v>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>113177184579#2</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>UN-INV260807-00009</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>ธรรมดา
- รถ lot18463-12</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>31/07/2026</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>31/07/2026</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>06/08/2026</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>5.30</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>0.0635</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L91" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>381.00฿</t>
-        </is>
-      </c>
-      <c r="N91" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" t="n">
-        <v>5</v>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>113177184579</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>UN-INV260807-00009</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>ธรรมดา
- รถ lot18463-11</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>31/07/2026</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>31/07/2026</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>06/08/2026</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>13.30</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>0.1176</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L92" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>705.60฿</t>
-        </is>
-      </c>
-      <c r="N92" t="inlineStr">
-        <is>
-          <t>蘑菇钉补胎贴</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="n">
-        <v>5</v>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>435289604798722</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>UN-INV260807-00009</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>ธรรมดา
- รถ lot18462-3</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>31/07/2026</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>01/08/2026</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>06/08/2026</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>4.30</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>0.0029</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L93" t="inlineStr">
-        <is>
-          <t>64.50฿</t>
-        </is>
-      </c>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N93" t="inlineStr">
-        <is>
-          <t>气门嘴</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="n">
-        <v>5</v>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>ZY202471573119#2</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>UN-INV260807-00009</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>ธรรมดา
- รถ lot18463-6</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>31/07/2026</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>31/07/2026</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>06/08/2026</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>8.70</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>0.0441</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L94" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>264.60฿</t>
-        </is>
-      </c>
-      <c r="N94" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" t="n">
-        <v>5</v>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>ZY202471573119</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>UN-INV260807-00009</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>ธรรมดา
- รถ lot18463-5</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>31/07/2026</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>31/07/2026</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>06/08/2026</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>11.90</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>0.0832</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L95" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>499.20฿</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr">
-        <is>
-          <t>蘑菇钉补胎</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="n">
-        <v>5</v>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>YT7635427281240</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>UN-INV260807-00009</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>ธรรมดา
- รถ lot18458-21</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>31/07/2026</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>31/07/2026</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>06/08/2026</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>0.0117</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L96" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>70.20฿</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr">
-        <is>
-          <t>气阀</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="n">
-        <v>5</v>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>79021262374216</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>UN-INV260804-00019</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>ธรรมดา
- รถ lot18435-5-73</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>28/07/2026</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>28/07/2026</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>02/08/2026</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>12.20</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>0.0352</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L97" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>211.20฿</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr">
-        <is>
-          <t>加长弯头</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="n">
-        <v>5</v>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>113162219964#3</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>UN-INV260804-00019</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>ธรรมดา
- รถ lot18434-9-28</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>27/07/2026</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>27/07/2026</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>02/08/2026</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>18.70</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>0.0443</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L98" t="inlineStr">
-        <is>
-          <t>280.50฿</t>
-        </is>
-      </c>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" t="n">
-        <v>5</v>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>113162219964#2</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>UN-INV260804-00019</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>ธรรมดา
- รถ lot18434-9-27</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>27/07/2026</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>27/07/2026</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>02/08/2026</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>22.90</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>0.0522</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L99" t="inlineStr">
-        <is>
-          <t>343.50฿</t>
-        </is>
-      </c>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" t="n">
-        <v>5</v>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>113162219964</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>UN-INV260804-00019</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>ธรรมดา
- รถ lot18434-9-26</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>27/07/2026</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>27/07/2026</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>02/08/2026</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>25.60</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>0.0574</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L100" t="inlineStr">
-        <is>
-          <t>384.00฿</t>
-        </is>
-      </c>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N100" t="inlineStr">
-        <is>
-          <t>补胎胶片/3件</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="n">
-        <v>5</v>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>113158800045#2</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>UN-INV260804-00019</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>ธรรมดา
- รถ lot18427-7-3</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>26/07/2026</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>26/07/2026</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>31/07/2026</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>26.30</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>0.0377</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L101" t="inlineStr">
-        <is>
-          <t>394.50฿</t>
-        </is>
-      </c>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N101" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/cargo_packages_p1-5.xlsx
+++ b/cargo_packages_p1-5.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N81"/>
+  <dimension ref="A1:N101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4666,11 +4666,11 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>S35386280517</t>
+          <t>ZY202464580877#3</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4680,48 +4680,48 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>UN-INV260811-00012</t>
+          <t>UN-INV260901-00057</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18475-23</t>
+ รถ lot18655-9-9</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>103.50</t>
+          <t>27.10</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>0.2236</t>
+          <t>0.0567</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>1,552.50฿</t>
+          <t>406.50฿</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -4731,17 +4731,17 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>气门嘴 顺心捷达，一票16件</t>
+          <t>补胎胶片/9件</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>YT7635787693833</t>
+          <t>S71090288685</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4751,38 +4751,38 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>UN-INV260811-00012</t>
+          <t>UN-INV260831-00017</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18473-6-41</t>
+ รถ lot18634-7-3</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>29/08/2026</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>13.80</t>
+          <t>12.10</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>0.0432</t>
+          <t>0.0240</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -4792,1257 +4792,2649 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>181.50฿</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>259.20฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>气压表/面单没有代码</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
+        <v>4</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>YT7638092409979</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>UN-INV260822-00010</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>ธรรมดา
+ รถ lot18569-7-7</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>16/08/2026</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>16/08/2026</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>15.00</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>0.0140</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>225.00฿</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>配件</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>4</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>435308000517585</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>UN-INV260822-00010</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>ธรรมดา
+ รถ lot18550-6-11</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>0.0032</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>54.00฿</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>气门嘴</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>4</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>710094401487</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>UN-INV260822-00010</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>ธรรมดา
+ รถ lot18544-8-14</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>13/08/2026</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>13/08/2026</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>107.10</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>0.4536</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>2,721.60฿</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>空的高压充气罐/一票10件，仓库实收到9件，已确认收到的9件先发</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>4</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>773435675083665</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>UN-INV260815-00046</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>ธรรมดา
+ รถ lot18526-6-17</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>13.10</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>0.0214</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>196.50฿</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>补胎工具</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>4</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>YT7637032206975</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>UN-INV260819-00010</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>มอก.
+ รถ lot18523-6-30</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>09/08/2026</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>09/08/2026</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>16/08/2026</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>9.60</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>0.0316</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>214.88฿</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>气动模具研磨机+配件</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>4</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>ZY202466648481#5</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>UN-INV260815-00046</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>ธรรมดา
+ รถ lot18519-6-17</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>09/08/2026</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>09/08/2026</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>15/08/2026</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>16.10</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>0.0493</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>295.80฿</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>4</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>ZY202466648481#4</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>UN-INV260815-00046</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>ธรรมดา
+ รถ lot18519-6-16</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>09/08/2026</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>09/08/2026</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>15/08/2026</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>20.50</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>0.0656</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>393.60฿</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>4</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>ZY202466648481#3</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>UN-INV260815-00046</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>ธรรมดา
+ รถ lot18519-6-15</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>09/08/2026</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>09/08/2026</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>15/08/2026</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>15.70</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>0.0508</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>304.80฿</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>4</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>ZY202466648481#2</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>UN-INV260815-00046</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>ธรรมดา
+ รถ lot18519-6-14</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>09/08/2026</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>09/08/2026</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>15/08/2026</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>20.20</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>0.0660</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>396.00฿</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>4</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>ZY202466648481</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>UN-INV260815-00046</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>ธรรมดา
+ รถ lot18519-6-13</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>09/08/2026</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>09/08/2026</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>15/08/2026</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>15.80</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>0.0522</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>313.20฿</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>补胎胶条/5件</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>4</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>113204676267#2</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>UN-INV260815-00046</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>ธรรมดา
+ รถ lot18518-5-3</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>08/08/2026</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>08/08/2026</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>13/08/2026</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>24.60</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>0.0608</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>369.00฿</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>4</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>113204676267</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>UN-INV260815-00046</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>ธรรมดา
+ รถ lot18518-5-2</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>08/08/2026</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>08/08/2026</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>13/08/2026</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>25.00</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>0.0566</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>375.00฿</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>真空胎冷补胶片</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>4</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>910061892464#2</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>UN-INV260815-00046</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>ธรรมดา
+ รถ lot18505-5-23</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>07/08/2026</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>07/08/2026</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>12/08/2026</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>30.40</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>0.0523</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>456.00฿</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>4</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>910061892464</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>UN-INV260815-00046</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>ธรรมดา
+ รถ lot18505-5-22</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>07/08/2026</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>07/08/2026</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>12/08/2026</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>15.90</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>0.0353</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>238.50฿</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>记号蜡笔</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>4</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>773434709817985</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>UN-INV260819-00010</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>ธรรมดา
+ รถ lot18535-8</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>16/08/2026</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>0.0184</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>110.40฿</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>锅具 二次包装货物变形</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>4</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>435295775627304</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>UN-INV260811-00012</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>ธรรมดา
+ รถ lot18492-2</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>05/08/2026</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>09/08/2026</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>5.30</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>0.0090</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>79.50฿</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>配件 破损件</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>4</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>YT7636332367470</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>UN-INV260811-00012</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>ธรรมดา
+ รถ lot18487-2-27</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>05/08/2026</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>09/08/2026</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>0.10</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>0.0004</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>10.00฿</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>立牌</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>4</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>S35386280517#2</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>UN-INV260811-00012</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>ธรรมดา
+ รถ lot18475-24</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>02/08/2026</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>02/08/2026</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>08/08/2026</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>8.80</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>0.0045</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>132.00฿</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
         <v>5</v>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>S35386280517</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>UN-INV260811-00012</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>ธรรมดา
+ รถ lot18475-23</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>02/08/2026</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>02/08/2026</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>08/08/2026</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>103.50</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>0.2236</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>1,552.50฿</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>气门嘴 顺心捷达，一票16件</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>5</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>YT7635787693833</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>UN-INV260811-00012</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>ธรรมดา
+ รถ lot18473-6-41</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>02/08/2026</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>02/08/2026</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>07/08/2026</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>13.80</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>0.0432</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>259.20฿</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>气压表/面单没有代码</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>5</v>
+      </c>
+      <c r="B84" t="inlineStr">
         <is>
           <t>ZY202465806614</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
         <is>
           <t>UN-INV260807-00009</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="E84" t="inlineStr">
         <is>
           <t>มอก.
  รถ lot18466-5-51</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="F84" t="inlineStr">
         <is>
           <t>01/08/2026</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="G84" t="inlineStr">
         <is>
           <t>01/08/2026</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="H84" t="inlineStr">
         <is>
           <t>06/08/2026</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
+      <c r="I84" t="inlineStr">
         <is>
           <t>11.30</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
+      <c r="J84" t="inlineStr">
         <is>
           <t>0.0655</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M64" t="inlineStr">
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
         <is>
           <t>445.40฿</t>
         </is>
       </c>
-      <c r="N64" t="inlineStr">
+      <c r="N84" t="inlineStr">
         <is>
           <t>电子数显胎压枪</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" t="n">
+    <row r="85">
+      <c r="A85" t="n">
         <v>5</v>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B85" t="inlineStr">
         <is>
           <t>113177184579#7</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
         <is>
           <t>UN-INV260807-00009</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="E85" t="inlineStr">
         <is>
           <t>ธรรมดา
  รถ lot18463-17</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="F85" t="inlineStr">
         <is>
           <t>31/07/2026</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="G85" t="inlineStr">
         <is>
           <t>31/07/2026</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="H85" t="inlineStr">
         <is>
           <t>06/08/2026</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
+      <c r="I85" t="inlineStr">
         <is>
           <t>9.70</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr">
+      <c r="J85" t="inlineStr">
         <is>
           <t>0.0305</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M65" t="inlineStr">
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
         <is>
           <t>183.00฿</t>
         </is>
       </c>
-      <c r="N65" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" t="n">
+      <c r="N85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
         <v>5</v>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B86" t="inlineStr">
         <is>
           <t>113177184579#5</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
         <is>
           <t>UN-INV260807-00009</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="E86" t="inlineStr">
         <is>
           <t>ธรรมดา
  รถ lot18463-16</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="F86" t="inlineStr">
         <is>
           <t>31/07/2026</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="G86" t="inlineStr">
         <is>
           <t>31/07/2026</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="H86" t="inlineStr">
         <is>
           <t>06/08/2026</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
+      <c r="I86" t="inlineStr">
         <is>
           <t>15.00</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr">
+      <c r="J86" t="inlineStr">
         <is>
           <t>0.0137</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr">
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
         <is>
           <t>225.00฿</t>
         </is>
       </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" t="n">
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
         <v>5</v>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B87" t="inlineStr">
         <is>
           <t>113177184579#4</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
         <is>
           <t>UN-INV260807-00009</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="E87" t="inlineStr">
         <is>
           <t>ธรรมดา
  รถ lot18463-15</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="F87" t="inlineStr">
         <is>
           <t>31/07/2026</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="G87" t="inlineStr">
         <is>
           <t>31/07/2026</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
+      <c r="H87" t="inlineStr">
         <is>
           <t>06/08/2026</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
+      <c r="I87" t="inlineStr">
         <is>
           <t>7.30</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr">
+      <c r="J87" t="inlineStr">
         <is>
           <t>0.0235</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M67" t="inlineStr">
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
         <is>
           <t>141.00฿</t>
         </is>
       </c>
-      <c r="N67" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" t="n">
+      <c r="N87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
         <v>5</v>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B88" t="inlineStr">
         <is>
           <t>113177184579#3</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
         <is>
           <t>UN-INV260807-00009</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="E88" t="inlineStr">
         <is>
           <t>ธรรมดา
  รถ lot18463-14</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="F88" t="inlineStr">
         <is>
           <t>31/07/2026</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="G88" t="inlineStr">
         <is>
           <t>31/07/2026</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
+      <c r="H88" t="inlineStr">
         <is>
           <t>06/08/2026</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
+      <c r="I88" t="inlineStr">
         <is>
           <t>11.90</t>
         </is>
       </c>
-      <c r="J68" t="inlineStr">
+      <c r="J88" t="inlineStr">
         <is>
           <t>0.0302</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr">
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
         <is>
           <t>181.20฿</t>
         </is>
       </c>
-      <c r="N68" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" t="n">
+      <c r="N88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
         <v>5</v>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="B89" t="inlineStr">
         <is>
           <t>113177184579#6</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
         <is>
           <t>UN-INV260807-00009</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="E89" t="inlineStr">
         <is>
           <t>ธรรมดา
  รถ lot18463-13</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
+      <c r="F89" t="inlineStr">
         <is>
           <t>31/07/2026</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="G89" t="inlineStr">
         <is>
           <t>31/07/2026</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
+      <c r="H89" t="inlineStr">
         <is>
           <t>06/08/2026</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
+      <c r="I89" t="inlineStr">
         <is>
           <t>26.10</t>
         </is>
       </c>
-      <c r="J69" t="inlineStr">
+      <c r="J89" t="inlineStr">
         <is>
           <t>0.0673</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M69" t="inlineStr">
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
         <is>
           <t>403.80฿</t>
         </is>
       </c>
-      <c r="N69" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
+      <c r="N89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
         <v>5</v>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="B90" t="inlineStr">
         <is>
           <t>435289604798626</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
         <is>
           <t>UN-INV260807-00009</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="E90" t="inlineStr">
         <is>
           <t>ธรรมดา
  รถ lot18462-6-6</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
+      <c r="F90" t="inlineStr">
         <is>
           <t>31/07/2026</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="G90" t="inlineStr">
         <is>
           <t>01/08/2026</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
+      <c r="H90" t="inlineStr">
         <is>
           <t>06/08/2026</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
+      <c r="I90" t="inlineStr">
         <is>
           <t>9.60</t>
         </is>
       </c>
-      <c r="J70" t="inlineStr">
+      <c r="J90" t="inlineStr">
         <is>
           <t>0.0090</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr">
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
         <is>
           <t>144.00฿</t>
         </is>
       </c>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr">
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
         <is>
           <t>螺丝配件</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" t="n">
+    <row r="91">
+      <c r="A91" t="n">
         <v>5</v>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="B91" t="inlineStr">
         <is>
           <t>113177184579#2</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
         <is>
           <t>UN-INV260807-00009</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="E91" t="inlineStr">
         <is>
           <t>ธรรมดา
  รถ lot18463-12</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
+      <c r="F91" t="inlineStr">
         <is>
           <t>31/07/2026</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
+      <c r="G91" t="inlineStr">
         <is>
           <t>31/07/2026</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
+      <c r="H91" t="inlineStr">
         <is>
           <t>06/08/2026</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr">
+      <c r="I91" t="inlineStr">
         <is>
           <t>5.30</t>
         </is>
       </c>
-      <c r="J71" t="inlineStr">
+      <c r="J91" t="inlineStr">
         <is>
           <t>0.0635</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M71" t="inlineStr">
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
         <is>
           <t>381.00฿</t>
         </is>
       </c>
-      <c r="N71" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" t="n">
+      <c r="N91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
         <v>5</v>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="B92" t="inlineStr">
         <is>
           <t>113177184579</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
         <is>
           <t>UN-INV260807-00009</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
+      <c r="E92" t="inlineStr">
         <is>
           <t>ธรรมดา
  รถ lot18463-11</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
+      <c r="F92" t="inlineStr">
         <is>
           <t>31/07/2026</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
+      <c r="G92" t="inlineStr">
         <is>
           <t>31/07/2026</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
+      <c r="H92" t="inlineStr">
         <is>
           <t>06/08/2026</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
+      <c r="I92" t="inlineStr">
         <is>
           <t>13.30</t>
         </is>
       </c>
-      <c r="J72" t="inlineStr">
+      <c r="J92" t="inlineStr">
         <is>
           <t>0.1176</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M72" t="inlineStr">
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
         <is>
           <t>705.60฿</t>
         </is>
       </c>
-      <c r="N72" t="inlineStr">
+      <c r="N92" t="inlineStr">
         <is>
           <t>蘑菇钉补胎贴</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" t="n">
+    <row r="93">
+      <c r="A93" t="n">
         <v>5</v>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="B93" t="inlineStr">
         <is>
           <t>435289604798722</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
         <is>
           <t>UN-INV260807-00009</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
+      <c r="E93" t="inlineStr">
         <is>
           <t>ธรรมดา
  รถ lot18462-3</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
+      <c r="F93" t="inlineStr">
         <is>
           <t>31/07/2026</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
+      <c r="G93" t="inlineStr">
         <is>
           <t>01/08/2026</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
+      <c r="H93" t="inlineStr">
         <is>
           <t>06/08/2026</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
+      <c r="I93" t="inlineStr">
         <is>
           <t>4.30</t>
         </is>
       </c>
-      <c r="J73" t="inlineStr">
+      <c r="J93" t="inlineStr">
         <is>
           <t>0.0029</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L73" t="inlineStr">
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
         <is>
           <t>64.50฿</t>
         </is>
       </c>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr">
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
         <is>
           <t>气门嘴</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" t="n">
+    <row r="94">
+      <c r="A94" t="n">
         <v>5</v>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="B94" t="inlineStr">
         <is>
           <t>ZY202471573119#2</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
         <is>
           <t>UN-INV260807-00009</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="E94" t="inlineStr">
         <is>
           <t>ธรรมดา
  รถ lot18463-6</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
+      <c r="F94" t="inlineStr">
         <is>
           <t>31/07/2026</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
+      <c r="G94" t="inlineStr">
         <is>
           <t>31/07/2026</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
+      <c r="H94" t="inlineStr">
         <is>
           <t>06/08/2026</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
+      <c r="I94" t="inlineStr">
         <is>
           <t>8.70</t>
         </is>
       </c>
-      <c r="J74" t="inlineStr">
+      <c r="J94" t="inlineStr">
         <is>
           <t>0.0441</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M74" t="inlineStr">
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
         <is>
           <t>264.60฿</t>
         </is>
       </c>
-      <c r="N74" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" t="n">
+      <c r="N94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
         <v>5</v>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B95" t="inlineStr">
         <is>
           <t>ZY202471573119</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
         <is>
           <t>UN-INV260807-00009</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="E95" t="inlineStr">
         <is>
           <t>ธรรมดา
  รถ lot18463-5</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
+      <c r="F95" t="inlineStr">
         <is>
           <t>31/07/2026</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="G95" t="inlineStr">
         <is>
           <t>31/07/2026</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
+      <c r="H95" t="inlineStr">
         <is>
           <t>06/08/2026</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
+      <c r="I95" t="inlineStr">
         <is>
           <t>11.90</t>
         </is>
       </c>
-      <c r="J75" t="inlineStr">
+      <c r="J95" t="inlineStr">
         <is>
           <t>0.0832</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M75" t="inlineStr">
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
         <is>
           <t>499.20฿</t>
         </is>
       </c>
-      <c r="N75" t="inlineStr">
+      <c r="N95" t="inlineStr">
         <is>
           <t>蘑菇钉补胎</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" t="n">
+    <row r="96">
+      <c r="A96" t="n">
         <v>5</v>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B96" t="inlineStr">
         <is>
           <t>YT7635427281240</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
         <is>
           <t>UN-INV260807-00009</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="E96" t="inlineStr">
         <is>
           <t>ธรรมดา
  รถ lot18458-21</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
+      <c r="F96" t="inlineStr">
         <is>
           <t>31/07/2026</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="G96" t="inlineStr">
         <is>
           <t>31/07/2026</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
+      <c r="H96" t="inlineStr">
         <is>
           <t>06/08/2026</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
+      <c r="I96" t="inlineStr">
         <is>
           <t>1.90</t>
         </is>
       </c>
-      <c r="J76" t="inlineStr">
+      <c r="J96" t="inlineStr">
         <is>
           <t>0.0117</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M76" t="inlineStr">
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
         <is>
           <t>70.20฿</t>
         </is>
       </c>
-      <c r="N76" t="inlineStr">
+      <c r="N96" t="inlineStr">
         <is>
           <t>气阀</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" t="n">
+    <row r="97">
+      <c r="A97" t="n">
         <v>5</v>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B97" t="inlineStr">
         <is>
           <t>79021262374216</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
         <is>
           <t>UN-INV260804-00019</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="E97" t="inlineStr">
         <is>
           <t>ธรรมดา
  รถ lot18435-5-73</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
+      <c r="F97" t="inlineStr">
         <is>
           <t>28/07/2026</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="G97" t="inlineStr">
         <is>
           <t>28/07/2026</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
+      <c r="H97" t="inlineStr">
         <is>
           <t>02/08/2026</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr">
+      <c r="I97" t="inlineStr">
         <is>
           <t>12.20</t>
         </is>
       </c>
-      <c r="J77" t="inlineStr">
+      <c r="J97" t="inlineStr">
         <is>
           <t>0.0352</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M77" t="inlineStr">
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
         <is>
           <t>211.20฿</t>
         </is>
       </c>
-      <c r="N77" t="inlineStr">
+      <c r="N97" t="inlineStr">
         <is>
           <t>加长弯头</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" t="n">
+    <row r="98">
+      <c r="A98" t="n">
         <v>5</v>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="B98" t="inlineStr">
         <is>
           <t>113162219964#3</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
         <is>
           <t>UN-INV260804-00019</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
+      <c r="E98" t="inlineStr">
         <is>
           <t>ธรรมดา
  รถ lot18434-9-28</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
+      <c r="F98" t="inlineStr">
         <is>
           <t>27/07/2026</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
+      <c r="G98" t="inlineStr">
         <is>
           <t>27/07/2026</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
+      <c r="H98" t="inlineStr">
         <is>
           <t>02/08/2026</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
+      <c r="I98" t="inlineStr">
         <is>
           <t>18.70</t>
         </is>
       </c>
-      <c r="J78" t="inlineStr">
+      <c r="J98" t="inlineStr">
         <is>
           <t>0.0443</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L78" t="inlineStr">
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
         <is>
           <t>280.50฿</t>
         </is>
       </c>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" t="n">
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
         <v>5</v>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="B99" t="inlineStr">
         <is>
           <t>113162219964#2</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
         <is>
           <t>UN-INV260804-00019</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="E99" t="inlineStr">
         <is>
           <t>ธรรมดา
  รถ lot18434-9-27</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
+      <c r="F99" t="inlineStr">
         <is>
           <t>27/07/2026</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
+      <c r="G99" t="inlineStr">
         <is>
           <t>27/07/2026</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
+      <c r="H99" t="inlineStr">
         <is>
           <t>02/08/2026</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr">
+      <c r="I99" t="inlineStr">
         <is>
           <t>22.90</t>
         </is>
       </c>
-      <c r="J79" t="inlineStr">
+      <c r="J99" t="inlineStr">
         <is>
           <t>0.0522</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L79" t="inlineStr">
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
         <is>
           <t>343.50฿</t>
         </is>
       </c>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" t="n">
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
         <v>5</v>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="B100" t="inlineStr">
         <is>
           <t>113162219964</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
         <is>
           <t>UN-INV260804-00019</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
+      <c r="E100" t="inlineStr">
         <is>
           <t>ธรรมดา
  รถ lot18434-9-26</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
+      <c r="F100" t="inlineStr">
         <is>
           <t>27/07/2026</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
+      <c r="G100" t="inlineStr">
         <is>
           <t>27/07/2026</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
+      <c r="H100" t="inlineStr">
         <is>
           <t>02/08/2026</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
+      <c r="I100" t="inlineStr">
         <is>
           <t>25.60</t>
         </is>
       </c>
-      <c r="J80" t="inlineStr">
+      <c r="J100" t="inlineStr">
         <is>
           <t>0.0574</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L80" t="inlineStr">
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
         <is>
           <t>384.00฿</t>
         </is>
       </c>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr">
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
         <is>
           <t>补胎胶片/3件</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" t="n">
+    <row r="101">
+      <c r="A101" t="n">
         <v>5</v>
       </c>
-      <c r="B81" t="inlineStr">
+      <c r="B101" t="inlineStr">
         <is>
           <t>113158800045#2</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
         <is>
           <t>UN-INV260804-00019</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
+      <c r="E101" t="inlineStr">
         <is>
           <t>ธรรมดา
  รถ lot18427-7-3</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
+      <c r="F101" t="inlineStr">
         <is>
           <t>26/07/2026</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
+      <c r="G101" t="inlineStr">
         <is>
           <t>26/07/2026</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
+      <c r="H101" t="inlineStr">
         <is>
           <t>31/07/2026</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
+      <c r="I101" t="inlineStr">
         <is>
           <t>26.30</t>
         </is>
       </c>
-      <c r="J81" t="inlineStr">
+      <c r="J101" t="inlineStr">
         <is>
           <t>0.0377</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L81" t="inlineStr">
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
         <is>
           <t>394.50฿</t>
         </is>
       </c>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/cargo_packages_p1-5.xlsx
+++ b/cargo_packages_p1-5.xlsx
@@ -608,7 +608,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">

--- a/cargo_packages_p1-5.xlsx
+++ b/cargo_packages_p1-5.xlsx
@@ -587,7 +587,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>UN-INV260924-00056</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -658,7 +658,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>UN-INV260924-00056</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -729,7 +729,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>UN-INV260924-00056</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -800,7 +800,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>UN-INV260924-00056</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>UN-INV260924-00056</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>UN-INV260924-00056</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>UN-INV260924-00056</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>UN-INV260924-00056</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">

--- a/cargo_packages_p1-5.xlsx
+++ b/cargo_packages_p1-5.xlsx
@@ -537,7 +537,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">

--- a/cargo_packages_p1-5.xlsx
+++ b/cargo_packages_p1-5.xlsx
@@ -516,7 +516,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>UN-INV260926-00006</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">

--- a/cargo_packages_p1-5.xlsx
+++ b/cargo_packages_p1-5.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ZY202462495078</t>
+          <t>YT7646197126750</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -516,38 +516,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>UN-INV260926-00006</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18844-9-4</t>
+ รถ lot18887-50</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>26/09/2026</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>26/09/2026</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>14.30</t>
+          <t>8.30</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.0624</t>
+          <t>0.0127</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -557,17 +557,17 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>124.50฿</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>374.40฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>胎压表</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>S71749075994</t>
+          <t>ZY202462495078</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -587,38 +587,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>UN-INV260924-00056</t>
+          <t>UN-INV260926-00006</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18830-6-30</t>
+ รถ lot18844-9-4</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>119.00</t>
+          <t>14.30</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.2302</t>
+          <t>0.0624</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -628,17 +628,17 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>1,785.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>374.40฿</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>真空胎扒胎机配件/木箱</t>
+          <t>胎压表</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>435358249576981</t>
+          <t>S71749075994</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -664,17 +664,17 @@
       <c r="E4" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18815-4-6</t>
+ รถ lot18830-6-30</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -684,12 +684,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5.20</t>
+          <t>119.00</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.0044</t>
+          <t>0.2302</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>78.00฿</t>
+          <t>1,785.00฿</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>气门嘴</t>
+          <t>真空胎扒胎机配件/木箱</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>S71195667064</t>
+          <t>435358249576981</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,12 +735,12 @@
       <c r="E5" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18810-6-3</t>
+ รถ lot18815-4-6</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -750,37 +750,37 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>165.00</t>
+          <t>5.20</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.8568</t>
+          <t>0.0044</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>78.00฿</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>5,140.80฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>千斤顶，3件，客户不打木架发</t>
+          <t>气门嘴</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>113350746029#4</t>
+          <t>S71195667064</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -806,17 +806,17 @@
       <c r="E6" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18799-6-32</t>
+ รถ lot18810-6-3</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -826,17 +826,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>27.70</t>
+          <t>165.00</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.0800</t>
+          <t>0.8568</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -846,10 +846,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>480.00฿</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>5,140.80฿</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>千斤顶，3件，客户不打木架发</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -857,7 +861,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>113350746029#3</t>
+          <t>113350746029#4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -873,7 +877,7 @@
       <c r="E7" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18799-6-31</t>
+ รถ lot18799-6-32</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -893,12 +897,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>10.90</t>
+          <t>27.70</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.0377</t>
+          <t>0.0800</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -913,7 +917,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>226.20฿</t>
+          <t>480.00฿</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -924,7 +928,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>113350746029#2</t>
+          <t>113350746029#3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -940,7 +944,7 @@
       <c r="E8" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18799-6-30</t>
+ รถ lot18799-6-31</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -960,12 +964,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>15.00</t>
+          <t>10.90</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.0101</t>
+          <t>0.0377</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -975,12 +979,12 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>225.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>226.20฿</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -991,7 +995,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>113350746029</t>
+          <t>113350746029#2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1007,7 +1011,7 @@
       <c r="E9" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18799-6-29</t>
+ รถ lot18799-6-30</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1027,12 +1031,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>16.50</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.0127</t>
+          <t>0.0101</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1042,7 +1046,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>247.50฿</t>
+          <t>225.00฿</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1050,11 +1054,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>真空胎加固修理补片</t>
-        </is>
-      </c>
+      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>760246657062</t>
+          <t>113350746029</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1078,7 +1078,7 @@
       <c r="E10" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18799-7-3</t>
+ รถ lot18799-6-29</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>16.50</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.0005</t>
+          <t>0.0127</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1113,17 +1113,17 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>247.50฿</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>10.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>气门嘴，轮胎修补工具，气门芯宣传册</t>
+          <t>真空胎加固修理补片</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1133,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>113348267192#2</t>
+          <t>760246657062</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1143,38 +1143,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>UN-INV260921-00019</t>
+          <t>UN-INV260924-00056</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18795-2-7</t>
+ รถ lot18799-7-3</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>28.10</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.0628</t>
+          <t>0.0005</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1184,15 +1184,19 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>421.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+          <t>10.00฿</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>气门嘴，轮胎修补工具，气门芯宣传册</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1200,7 +1204,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>113348267192</t>
+          <t>113348267192#2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1216,7 +1220,7 @@
       <c r="E12" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18795-2-6</t>
+ รถ lot18795-2-7</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1236,12 +1240,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>19.50</t>
+          <t>28.10</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0.0505</t>
+          <t>0.0628</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1251,19 +1255,15 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>421.50฿</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>303.00฿</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>补胎胶片</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ZY202472578299</t>
+          <t>113348267192</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1281,43 +1281,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>UN-INV260918-00012</t>
+          <t>UN-INV260921-00019</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18758-7-43</t>
+ รถ lot18795-2-6</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>47.40</t>
+          <t>19.50</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0.1603</t>
+          <t>0.0505</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1327,12 +1327,12 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>961.20฿</t>
+          <t>303.00฿</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>补胎贴，3件</t>
+          <t>补胎胶片</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>773440822655698</t>
+          <t>ZY202472578299</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1358,7 +1358,7 @@
       <c r="E14" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18758-4-31</t>
+ รถ lot18758-7-43</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1378,32 +1378,32 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>47.40</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.0022</t>
+          <t>0.1603</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>18.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>961.20฿</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>钻头</t>
+          <t>补胎贴，3件</t>
         </is>
       </c>
     </row>
@@ -1413,7 +1413,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>YT7642998390994</t>
+          <t>773440822655698</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1429,7 +1429,7 @@
       <c r="E15" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18769-3-57</t>
+ รถ lot18758-4-31</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>5.80</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.0070</t>
+          <t>0.0022</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>87.00฿</t>
+          <t>18.00฿</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>钻头</t>
         </is>
       </c>
     </row>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>DPK212614057101</t>
+          <t>YT7642998390994</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1494,38 +1494,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>UN-INV260916-00003</t>
+          <t>UN-INV260918-00012</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18749-4-3</t>
+ รถ lot18769-3-57</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>9.60</t>
+          <t>5.80</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>0.0060</t>
+          <t>0.0070</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>144.00฿</t>
+          <t>87.00฿</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>轮胎气门嘴</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>79031204783305</t>
+          <t>DPK212614057101</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1571,7 +1571,7 @@
       <c r="E17" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18744-6-15</t>
+ รถ lot18749-4-3</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>9.60</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.0020</t>
+          <t>0.0060</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>39.00฿</t>
+          <t>144.00฿</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>轮胎气门嘴</t>
         </is>
       </c>
     </row>
@@ -1626,7 +1626,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>435342988112655</t>
+          <t>79031204783305</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1642,17 +1642,17 @@
       <c r="E18" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18743-3-34</t>
+ รถ lot18744-6-15</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1662,12 +1662,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>0.0014</t>
+          <t>0.0020</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1677,17 +1677,17 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>39.00฿</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>10.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>橡胶垫圈</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -1697,7 +1697,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>435343890137834</t>
+          <t>435342988112655</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1713,7 +1713,7 @@
       <c r="E19" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18743-7-25</t>
+ รถ lot18743-3-34</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1733,12 +1733,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>21.40</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>0.0080</t>
+          <t>0.0014</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1748,17 +1748,17 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>321.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10.00฿</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>扒胎机包胶撬棍</t>
+          <t>橡胶垫圈</t>
         </is>
       </c>
     </row>
@@ -1768,7 +1768,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>YT7642670434639</t>
+          <t>435343890137834</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1784,7 +1784,7 @@
       <c r="E20" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18743-2-8</t>
+ รถ lot18743-7-25</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>21.40</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0.0010</t>
+          <t>0.0080</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1819,7 +1819,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>12.00฿</t>
+          <t>321.00฿</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1829,7 +1829,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>片片</t>
+          <t>扒胎机包胶撬棍</t>
         </is>
       </c>
     </row>
@@ -1839,7 +1839,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>93015797092</t>
+          <t>YT7642670434639</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1849,18 +1849,18 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>UN-INV260914-00014</t>
+          <t>UN-INV260916-00003</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18735-4-40</t>
+ รถ lot18743-2-8</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1870,17 +1870,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>12/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>8.60</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.0148</t>
+          <t>0.0010</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>129.00฿</t>
+          <t>12.00฿</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>仪表</t>
+          <t>片片</t>
         </is>
       </c>
     </row>
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>YT7642390374765</t>
+          <t>93015797092</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1920,13 +1920,13 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>UN-INV260914-00015</t>
+          <t>UN-INV260914-00014</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18735-4-20</t>
+ รถ lot18735-4-40</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1946,12 +1946,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>20.80</t>
+          <t>8.60</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.0598</t>
+          <t>0.0148</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1961,17 +1961,17 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>129.00฿</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>358.80฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>打磨机</t>
+          <t>仪表</t>
         </is>
       </c>
     </row>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>435342255104130</t>
+          <t>YT7642390374765</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1991,13 +1991,13 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>UN-INV260914-00014</t>
+          <t>UN-INV260914-00015</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18735-43</t>
+ รถ lot18735-4-20</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2017,12 +2017,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>4.90</t>
+          <t>20.80</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.0172</t>
+          <t>0.0598</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2037,12 +2037,12 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>103.20฿</t>
+          <t>358.80฿</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>轮毂保护套</t>
+          <t>打磨机</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>773440312345715</t>
+          <t>435342255104130</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2068,7 +2068,7 @@
       <c r="E24" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18735-3-78</t>
+ รถ lot18735-43</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2088,12 +2088,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>4.90</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.0013</t>
+          <t>0.0172</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2103,17 +2103,17 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>19.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>103.20฿</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>轮毂保护套</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>773440291470393</t>
+          <t>773440312345715</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2139,7 +2139,7 @@
       <c r="E25" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18735-34</t>
+ รถ lot18735-3-78</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2159,12 +2159,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.0029</t>
+          <t>0.0013</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>48.00฿</t>
+          <t>19.50฿</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>球阀</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -2194,7 +2194,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>435342261175750</t>
+          <t>773440291470393</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2204,13 +2204,13 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>UN-INV260914-00015</t>
+          <t>UN-INV260914-00014</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18736-13</t>
+ รถ lot18735-34</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2220,7 +2220,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>13.90</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>0.0137</t>
+          <t>0.0029</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2245,7 +2245,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>208.50฿</t>
+          <t>48.00฿</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2255,7 +2255,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>球阀</t>
         </is>
       </c>
     </row>
@@ -2265,7 +2265,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ZY202461195200</t>
+          <t>435342261175750</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2281,7 +2281,7 @@
       <c r="E27" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18728-7-13</t>
+ รถ lot18736-13</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2296,17 +2296,17 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>13/09/2026</t>
+          <t>12/09/2026</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>47.40</t>
+          <t>13.90</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.0116</t>
+          <t>0.0137</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>711.00฿</t>
+          <t>208.50฿</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2336,7 +2336,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>79030687835952</t>
+          <t>ZY202461195200</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2346,13 +2346,13 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>UN-INV260914-00014</t>
+          <t>UN-INV260914-00015</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18728-3-64</t>
+ รถ lot18728-7-13</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>4.30</t>
+          <t>47.40</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.0030</t>
+          <t>0.0116</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2387,7 +2387,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>64.50฿</t>
+          <t>711.00฿</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2397,7 +2397,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>接头配件</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -2407,7 +2407,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>LJ20722214#3</t>
+          <t>79030687835952</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2417,38 +2417,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>UN-INV260912-00011</t>
+          <t>UN-INV260914-00014</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18726-7-8</t>
+ รถ lot18728-3-64</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>13/09/2026</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>14.00</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0.0171</t>
+          <t>0.0030</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2458,7 +2458,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>210.00฿</t>
+          <t>64.50฿</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2466,7 +2466,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>接头配件</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2474,7 +2478,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>LJ20722214#2</t>
+          <t>LJ20722214#3</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2490,7 +2494,7 @@
       <c r="E30" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18726-7-7</t>
+ รถ lot18726-7-8</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2510,12 +2514,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>11.90</t>
+          <t>14.00</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.0089</t>
+          <t>0.0171</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2525,7 +2529,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>178.50฿</t>
+          <t>210.00฿</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2541,7 +2545,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>LJ20722214</t>
+          <t>LJ20722214#2</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2557,7 +2561,7 @@
       <c r="E31" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18726-7-6</t>
+ รถ lot18726-7-7</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2577,12 +2581,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>16.00</t>
+          <t>11.90</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.0144</t>
+          <t>0.0089</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2592,7 +2596,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>240.00฿</t>
+          <t>178.50฿</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2600,11 +2604,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>电板套筒配件/3件</t>
-        </is>
-      </c>
+      <c r="N31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>YT7641966426761</t>
+          <t>LJ20722214</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2628,17 +2628,17 @@
       <c r="E32" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18714-9-23</t>
+ รถ lot18726-7-6</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2648,12 +2648,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>13.60</t>
+          <t>16.00</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.0422</t>
+          <t>0.0144</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2663,17 +2663,17 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>240.00฿</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>253.20฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>带表汽车轮胎打气嘴</t>
+          <t>电板套筒配件/3件</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ZY202471681117#2</t>
+          <t>YT7641966426761</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2699,7 +2699,7 @@
       <c r="E33" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18714-9-8</t>
+ รถ lot18714-9-23</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>11.80</t>
+          <t>13.60</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.0832</t>
+          <t>0.0422</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2739,10 +2739,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>499.20฿</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
+          <t>253.20฿</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>带表汽车轮胎打气嘴</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2750,7 +2754,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ZY202471681117</t>
+          <t>ZY202471681117#2</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2766,7 +2770,7 @@
       <c r="E34" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18714-9-7</t>
+ รถ lot18714-9-8</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2786,12 +2790,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>7.70</t>
+          <t>11.80</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.0493</t>
+          <t>0.0832</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2806,14 +2810,10 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>295.80฿</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>补胎胶片/2件</t>
-        </is>
-      </c>
+          <t>499.20฿</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2821,7 +2821,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>302285502767#2</t>
+          <t>ZY202471681117</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2837,7 +2837,7 @@
       <c r="E35" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18714-8-10</t>
+ รถ lot18714-9-7</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>33.70</t>
+          <t>7.70</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.0145</t>
+          <t>0.0493</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2872,15 +2872,19 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>505.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
+          <t>295.80฿</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>补胎胶片/2件</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2888,7 +2892,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>302285502767</t>
+          <t>302285502767#2</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2904,7 +2908,7 @@
       <c r="E36" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18714-8-9</t>
+ รถ lot18714-8-10</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2924,12 +2928,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>23.40</t>
+          <t>33.70</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.0123</t>
+          <t>0.0145</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2939,7 +2943,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>351.00฿</t>
+          <t>505.50฿</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2947,11 +2951,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>扳手</t>
-        </is>
-      </c>
+      <c r="N36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>LJ20716178#2</t>
+          <t>302285502767</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2969,18 +2969,18 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>UN-INV260911-00013</t>
+          <t>UN-INV260912-00011</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18713-6-65</t>
+ รถ lot18714-8-9</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2990,17 +2990,17 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>19.50</t>
+          <t>23.40</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.0075</t>
+          <t>0.0123</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -3010,7 +3010,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>292.50฿</t>
+          <t>351.00฿</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3018,7 +3018,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>扳手</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -3026,7 +3030,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>LJ20716178</t>
+          <t>LJ20716178#2</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3042,7 +3046,7 @@
       <c r="E38" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18713-6-64</t>
+ รถ lot18713-6-65</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -3062,7 +3066,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>19.60</t>
+          <t>19.50</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -3077,7 +3081,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>294.00฿</t>
+          <t>292.50฿</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3085,11 +3089,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>配件</t>
-        </is>
-      </c>
+      <c r="N38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>435338972466812</t>
+          <t>LJ20716178</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3113,7 +3113,7 @@
       <c r="E39" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18710-6-35</t>
+ รถ lot18713-6-64</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -3123,7 +3123,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>13.10</t>
+          <t>19.60</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.0624</t>
+          <t>0.0075</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -3148,17 +3148,17 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>294.00฿</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>374.40฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>修补工具</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>435334324045675</t>
+          <t>435338972466812</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3178,38 +3178,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>UN-INV260908-00009</t>
+          <t>UN-INV260911-00013</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18696-14</t>
+ รถ lot18710-6-35</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>10.80</t>
+          <t>13.10</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.0088</t>
+          <t>0.0624</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -3219,17 +3219,17 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>162.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>374.40฿</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>修补工具</t>
         </is>
       </c>
     </row>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>YT7641276428798</t>
+          <t>435334324045675</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3255,7 +3255,7 @@
       <c r="E41" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18697-11</t>
+ รถ lot18696-14</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -3275,12 +3275,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>9.50</t>
+          <t>10.80</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.0296</t>
+          <t>0.0088</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -3290,12 +3290,12 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>162.00฿</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>177.60฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3310,7 +3310,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>79029430531776</t>
+          <t>YT7641276428798</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3320,18 +3320,18 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>UN-INV260907-00015</t>
+          <t>UN-INV260908-00009</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18689-26</t>
+ รถ lot18697-11</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -3341,17 +3341,17 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>9.50</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.0135</t>
+          <t>0.0296</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3366,12 +3366,12 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>81.00฿</t>
+          <t>177.60฿</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>卡套</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -3381,7 +3381,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>113282578128#2</t>
+          <t>79029430531776</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3397,17 +3397,17 @@
       <c r="E43" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18683-4</t>
+ รถ lot18689-26</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>38.00</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.1601</t>
+          <t>0.0135</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3437,10 +3437,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>960.60฿</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
+          <t>81.00฿</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>卡套</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -3448,7 +3452,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>113282578128</t>
+          <t>113282578128#2</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3464,7 +3468,7 @@
       <c r="E44" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18683-3</t>
+ รถ lot18683-4</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -3484,12 +3488,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>27.50</t>
+          <t>38.00</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.1566</t>
+          <t>0.1601</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3504,14 +3508,10 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>939.60฿</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>压条取出器 一票两件破损件</t>
-        </is>
-      </c>
+          <t>960.60฿</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -3519,7 +3519,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>82730128600#3</t>
+          <t>113282578128</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3535,12 +3535,12 @@
       <c r="E45" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18678-6-21</t>
+ รถ lot18683-3</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>30/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>33.00</t>
+          <t>27.50</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.0122</t>
+          <t>0.1566</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3570,15 +3570,19 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>495.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
+          <t>939.60฿</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>压条取出器 一票两件破损件</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -3586,7 +3590,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>82730128600#2</t>
+          <t>82730128600#3</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3602,7 +3606,7 @@
       <c r="E46" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18678-6-20</t>
+ รถ lot18678-6-21</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -3622,12 +3626,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>27.60</t>
+          <t>33.00</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>0.0095</t>
+          <t>0.0122</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3637,7 +3641,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>414.00฿</t>
+          <t>495.00฿</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3653,7 +3657,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>82730128600</t>
+          <t>82730128600#2</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3669,7 +3673,7 @@
       <c r="E47" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18678-6-19</t>
+ รถ lot18678-6-20</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -3689,12 +3693,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>28.10</t>
+          <t>27.60</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>0.0118</t>
+          <t>0.0095</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3704,7 +3708,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>421.50฿</t>
+          <t>414.00฿</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3712,11 +3716,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>五金配件/3件</t>
-        </is>
-      </c>
+      <c r="N47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>113278387839#3</t>
+          <t>82730128600</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3734,38 +3734,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>UN-INV260903-00023</t>
+          <t>UN-INV260907-00015</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18663-8-3</t>
+ รถ lot18678-6-19</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>30/08/2026</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>25.30</t>
+          <t>28.10</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>0.0404</t>
+          <t>0.0118</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3775,7 +3775,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>379.50฿</t>
+          <t>421.50฿</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3783,7 +3783,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>五金配件/3件</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -3791,7 +3795,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>113278387839#2</t>
+          <t>113278387839#3</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3807,7 +3811,7 @@
       <c r="E49" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18663-8-2</t>
+ รถ lot18663-8-3</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3827,12 +3831,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>26.10</t>
+          <t>25.30</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>0.0304</t>
+          <t>0.0404</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3842,7 +3846,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>391.50฿</t>
+          <t>379.50฿</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3858,7 +3862,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>113278387839</t>
+          <t>113278387839#2</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3874,7 +3878,7 @@
       <c r="E50" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18663-8-1</t>
+ รถ lot18663-8-2</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3894,12 +3898,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>9.10</t>
+          <t>26.10</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>0.0144</t>
+          <t>0.0304</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3909,7 +3913,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>136.50฿</t>
+          <t>391.50฿</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -3917,11 +3921,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>配件/3件</t>
-        </is>
-      </c>
+      <c r="N50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -3929,7 +3929,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>113276098937#3</t>
+          <t>113278387839</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3939,38 +3939,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>UN-INV260901-00057</t>
+          <t>UN-INV260903-00023</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-45</t>
+ รถ lot18663-8-1</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>17.80</t>
+          <t>9.10</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>0.0302</t>
+          <t>0.0144</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3980,7 +3980,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>267.00฿</t>
+          <t>136.50฿</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -3988,7 +3988,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr"/>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>配件/3件</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -3996,7 +4000,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>113276098937#2</t>
+          <t>113276098937#3</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -4012,7 +4016,7 @@
       <c r="E52" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-44</t>
+ รถ lot18655-9-45</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -4032,12 +4036,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>10.90</t>
+          <t>17.80</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>0.0313</t>
+          <t>0.0302</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -4047,12 +4051,12 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>267.00฿</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>187.80฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
@@ -4063,7 +4067,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>113276098937</t>
+          <t>113276098937#2</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -4079,7 +4083,7 @@
       <c r="E53" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-43</t>
+ รถ lot18655-9-44</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -4099,12 +4103,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>33.60</t>
+          <t>10.90</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>0.0825</t>
+          <t>0.0313</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -4114,19 +4118,15 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>504.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>补胎胶片+配件/3件</t>
-        </is>
-      </c>
+          <t>187.80฿</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -4134,7 +4134,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ZY202464580877#4</t>
+          <t>113276098937</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -4150,7 +4150,7 @@
       <c r="E54" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-17</t>
+ รถ lot18655-9-43</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -4170,12 +4170,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>20.10</t>
+          <t>33.60</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>0.0466</t>
+          <t>0.0825</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -4185,7 +4185,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>301.50฿</t>
+          <t>504.00฿</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -4193,7 +4193,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>补胎胶片+配件/3件</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -4201,7 +4205,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ZY202464580877#7</t>
+          <t>ZY202464580877#4</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -4217,7 +4221,7 @@
       <c r="E55" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-16</t>
+ รถ lot18655-9-17</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -4237,12 +4241,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>16.60</t>
+          <t>20.10</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>0.0430</t>
+          <t>0.0466</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -4252,12 +4256,12 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>301.50฿</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>258.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N55" t="inlineStr"/>
@@ -4268,7 +4272,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ZY202464580877#2</t>
+          <t>ZY202464580877#7</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -4284,7 +4288,7 @@
       <c r="E56" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-15</t>
+ รถ lot18655-9-16</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -4304,12 +4308,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>25.10</t>
+          <t>16.60</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>0.0483</t>
+          <t>0.0430</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -4319,12 +4323,12 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>376.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>258.00฿</t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
@@ -4335,7 +4339,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ZY202464580877#8</t>
+          <t>ZY202464580877#2</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -4351,7 +4355,7 @@
       <c r="E57" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-14</t>
+ รถ lot18655-9-15</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -4371,12 +4375,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>28.90</t>
+          <t>25.10</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>0.0800</t>
+          <t>0.0483</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -4386,12 +4390,12 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>376.50฿</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>480.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N57" t="inlineStr"/>
@@ -4402,7 +4406,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ZY202464580877#6</t>
+          <t>ZY202464580877#8</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -4418,7 +4422,7 @@
       <c r="E58" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-13</t>
+ รถ lot18655-9-14</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -4438,12 +4442,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>20.90</t>
+          <t>28.90</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>0.0534</t>
+          <t>0.0800</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -4458,7 +4462,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>320.40฿</t>
+          <t>480.00฿</t>
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
@@ -4469,7 +4473,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ZY202464580877#5</t>
+          <t>ZY202464580877#6</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4485,7 +4489,7 @@
       <c r="E59" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-12</t>
+ รถ lot18655-9-13</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -4505,12 +4509,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>26.20</t>
+          <t>20.90</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>0.0535</t>
+          <t>0.0534</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4520,12 +4524,12 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>393.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>320.40฿</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
@@ -4536,7 +4540,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ZY202464580877</t>
+          <t>ZY202464580877#5</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4552,7 +4556,7 @@
       <c r="E60" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-11</t>
+ รถ lot18655-9-12</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -4572,12 +4576,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>20.70</t>
+          <t>26.20</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>0.0531</t>
+          <t>0.0535</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -4587,12 +4591,12 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>393.00฿</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>318.60฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N60" t="inlineStr"/>
@@ -4603,7 +4607,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>ZY202464580877#9</t>
+          <t>ZY202464580877</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4619,7 +4623,7 @@
       <c r="E61" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-10</t>
+ รถ lot18655-9-11</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -4639,12 +4643,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>27.70</t>
+          <t>20.70</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>0.0800</t>
+          <t>0.0531</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -4659,7 +4663,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>480.00฿</t>
+          <t>318.60฿</t>
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
@@ -4670,7 +4674,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>ZY202464580877#3</t>
+          <t>ZY202464580877#9</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4686,7 +4690,7 @@
       <c r="E62" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-9</t>
+ รถ lot18655-9-10</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -4706,12 +4710,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>27.10</t>
+          <t>27.70</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>0.0567</t>
+          <t>0.0800</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -4721,19 +4725,15 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>406.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>补胎胶片/9件</t>
-        </is>
-      </c>
+          <t>480.00฿</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -4741,7 +4741,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>S71090288685</t>
+          <t>ZY202464580877#3</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4751,38 +4751,38 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>UN-INV260831-00017</t>
+          <t>UN-INV260901-00057</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18634-7-3</t>
+ รถ lot18655-9-9</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>29/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>12.10</t>
+          <t>27.10</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>0.0240</t>
+          <t>0.0567</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -4792,7 +4792,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>181.50฿</t>
+          <t>406.50฿</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>补胎胶片/9件</t>
         </is>
       </c>
     </row>
@@ -4812,7 +4812,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>YT7638092409979</t>
+          <t>S71090288685</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4822,38 +4822,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>UN-INV260822-00010</t>
+          <t>UN-INV260831-00017</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18569-7-7</t>
+ รถ lot18634-7-3</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>16/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>16/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>29/08/2026</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>15.00</t>
+          <t>12.10</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>0.0140</t>
+          <t>0.0240</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -4863,7 +4863,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>225.00฿</t>
+          <t>181.50฿</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -4883,7 +4883,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>435308000517585</t>
+          <t>YT7638092409979</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4899,32 +4899,32 @@
       <c r="E65" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18550-6-11</t>
+ รถ lot18569-7-7</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>16/08/2026</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>16/08/2026</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>0.0032</t>
+          <t>0.0140</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -4934,7 +4934,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>54.00฿</t>
+          <t>225.00฿</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -4944,7 +4944,7 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>气门嘴</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -4954,7 +4954,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>710094401487</t>
+          <t>435308000517585</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4970,17 +4970,17 @@
       <c r="E66" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18544-8-14</t>
+ รถ lot18550-6-11</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4990,32 +4990,32 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>107.10</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>0.4536</t>
+          <t>0.0032</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>54.00฿</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>2,721.60฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>空的高压充气罐/一票10件，仓库实收到9件，已确认收到的9件先发</t>
+          <t>气门嘴</t>
         </is>
       </c>
     </row>
@@ -5025,7 +5025,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>773435675083665</t>
+          <t>710094401487</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -5035,58 +5035,58 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>UN-INV260815-00046</t>
+          <t>UN-INV260822-00010</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18526-6-17</t>
+ รถ lot18544-8-14</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>13.10</t>
+          <t>107.10</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>0.0214</t>
+          <t>0.4536</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>196.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2,721.60฿</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>补胎工具</t>
+          <t>空的高压充气罐/一票10件，仓库实收到9件，已确认收到的9件先发</t>
         </is>
       </c>
     </row>
@@ -5096,7 +5096,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>YT7637032206975</t>
+          <t>773435675083665</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -5106,38 +5106,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>UN-INV260819-00010</t>
+          <t>UN-INV260815-00046</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>มอก.
- รถ lot18523-6-30</t>
+          <t>ธรรมดา
+ รถ lot18526-6-17</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>16/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>9.60</t>
+          <t>13.10</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>0.0316</t>
+          <t>0.0214</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -5147,17 +5147,17 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>196.50฿</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>214.88฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>气动模具研磨机+配件</t>
+          <t>补胎工具</t>
         </is>
       </c>
     </row>
@@ -5167,7 +5167,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>ZY202466648481#5</t>
+          <t>YT7637032206975</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -5177,13 +5177,13 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>UN-INV260815-00046</t>
+          <t>UN-INV260819-00010</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>ธรรมดา
- รถ lot18519-6-17</t>
+          <t>มอก.
+ รถ lot18523-6-30</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -5198,17 +5198,17 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>15/08/2026</t>
+          <t>16/08/2026</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>16.10</t>
+          <t>9.60</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>0.0493</t>
+          <t>0.0316</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -5223,10 +5223,14 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>295.80฿</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
+          <t>214.88฿</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>气动模具研磨机+配件</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -5234,7 +5238,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>ZY202466648481#4</t>
+          <t>ZY202466648481#5</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -5250,7 +5254,7 @@
       <c r="E70" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18519-6-16</t>
+ รถ lot18519-6-17</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -5270,12 +5274,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>20.50</t>
+          <t>16.10</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>0.0656</t>
+          <t>0.0493</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -5290,7 +5294,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>393.60฿</t>
+          <t>295.80฿</t>
         </is>
       </c>
       <c r="N70" t="inlineStr"/>
@@ -5301,7 +5305,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>ZY202466648481#3</t>
+          <t>ZY202466648481#4</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -5317,7 +5321,7 @@
       <c r="E71" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18519-6-15</t>
+ รถ lot18519-6-16</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -5337,12 +5341,12 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>15.70</t>
+          <t>20.50</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>0.0508</t>
+          <t>0.0656</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -5357,7 +5361,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>304.80฿</t>
+          <t>393.60฿</t>
         </is>
       </c>
       <c r="N71" t="inlineStr"/>
@@ -5368,7 +5372,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>ZY202466648481#2</t>
+          <t>ZY202466648481#3</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -5384,7 +5388,7 @@
       <c r="E72" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18519-6-14</t>
+ รถ lot18519-6-15</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -5404,12 +5408,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>20.20</t>
+          <t>15.70</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>0.0660</t>
+          <t>0.0508</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -5424,7 +5428,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>396.00฿</t>
+          <t>304.80฿</t>
         </is>
       </c>
       <c r="N72" t="inlineStr"/>
@@ -5435,7 +5439,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>ZY202466648481</t>
+          <t>ZY202466648481#2</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -5451,7 +5455,7 @@
       <c r="E73" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18519-6-13</t>
+ รถ lot18519-6-14</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -5471,12 +5475,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>15.80</t>
+          <t>20.20</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>0.0522</t>
+          <t>0.0660</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -5491,14 +5495,10 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>313.20฿</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t>补胎胶条/5件</t>
-        </is>
-      </c>
+          <t>396.00฿</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -5506,7 +5506,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>113204676267#2</t>
+          <t>ZY202466648481</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -5522,32 +5522,32 @@
       <c r="E74" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18518-5-3</t>
+ รถ lot18519-6-13</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>15/08/2026</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>24.60</t>
+          <t>15.80</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>0.0608</t>
+          <t>0.0522</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -5557,15 +5557,19 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>369.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr"/>
+          <t>313.20฿</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>补胎胶条/5件</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -5573,7 +5577,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>113204676267</t>
+          <t>113204676267#2</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -5589,7 +5593,7 @@
       <c r="E75" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18518-5-2</t>
+ รถ lot18518-5-3</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -5609,12 +5613,12 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>25.00</t>
+          <t>24.60</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>0.0566</t>
+          <t>0.0608</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -5624,7 +5628,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>375.00฿</t>
+          <t>369.00฿</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -5632,11 +5636,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N75" t="inlineStr">
-        <is>
-          <t>真空胎冷补胶片</t>
-        </is>
-      </c>
+      <c r="N75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -5644,7 +5644,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>910061892464#2</t>
+          <t>113204676267</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5660,32 +5660,32 @@
       <c r="E76" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18505-5-23</t>
+ รถ lot18518-5-2</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>30.40</t>
+          <t>25.00</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>0.0523</t>
+          <t>0.0566</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -5695,7 +5695,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>456.00฿</t>
+          <t>375.00฿</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -5703,7 +5703,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N76" t="inlineStr"/>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>真空胎冷补胶片</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -5711,7 +5715,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>910061892464</t>
+          <t>910061892464#2</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -5727,7 +5731,7 @@
       <c r="E77" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18505-5-22</t>
+ รถ lot18505-5-23</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -5747,12 +5751,12 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>15.90</t>
+          <t>30.40</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>0.0353</t>
+          <t>0.0523</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -5762,7 +5766,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>238.50฿</t>
+          <t>456.00฿</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -5770,11 +5774,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N77" t="inlineStr">
-        <is>
-          <t>记号蜡笔</t>
-        </is>
-      </c>
+      <c r="N77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -5782,7 +5782,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>773434709817985</t>
+          <t>910061892464</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -5792,38 +5792,38 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>UN-INV260819-00010</t>
+          <t>UN-INV260815-00046</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18535-8</t>
+ รถ lot18505-5-22</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>16/08/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>15.90</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>0.0184</t>
+          <t>0.0353</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>238.50฿</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>110.40฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>锅具 二次包装货物变形</t>
+          <t>记号蜡笔</t>
         </is>
       </c>
     </row>
@@ -5853,7 +5853,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>435295775627304</t>
+          <t>773434709817985</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -5863,38 +5863,38 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>UN-INV260811-00012</t>
+          <t>UN-INV260819-00010</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18492-2</t>
+ รถ lot18535-8</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>16/08/2026</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>5.30</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>0.0090</t>
+          <t>0.0184</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -5904,17 +5904,17 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>79.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>110.40฿</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>配件 破损件</t>
+          <t>锅具 二次包装货物变形</t>
         </is>
       </c>
     </row>
@@ -5924,7 +5924,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>YT7636332367470</t>
+          <t>435295775627304</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -5940,7 +5940,7 @@
       <c r="E80" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18487-2-27</t>
+ รถ lot18492-2</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -5960,12 +5960,12 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>5.30</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>0.0004</t>
+          <t>0.0090</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -5975,17 +5975,17 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>79.50฿</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>10.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>立牌</t>
+          <t>配件 破损件</t>
         </is>
       </c>
     </row>
@@ -5995,7 +5995,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>S35386280517#2</t>
+          <t>YT7636332367470</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -6011,32 +6011,32 @@
       <c r="E81" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18475-24</t>
+ รถ lot18487-2-27</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>8.80</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>0.0045</t>
+          <t>0.0004</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -6046,15 +6046,19 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>132.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr"/>
+          <t>10.00฿</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>立牌</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -6062,7 +6066,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>S35386280517</t>
+          <t>S35386280517#2</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -6078,7 +6082,7 @@
       <c r="E82" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18475-23</t>
+ รถ lot18475-24</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -6098,22 +6102,22 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>103.50</t>
+          <t>8.80</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>0.2236</t>
+          <t>0.0045</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>1,552.50฿</t>
+          <t>132.00฿</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -6121,11 +6125,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N82" t="inlineStr">
-        <is>
-          <t>气门嘴 顺心捷达，一票16件</t>
-        </is>
-      </c>
+      <c r="N82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>YT7635787693833</t>
+          <t>S35386280517</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -6149,7 +6149,7 @@
       <c r="E83" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18473-6-41</t>
+ รถ lot18475-23</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -6164,37 +6164,37 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>13.80</t>
+          <t>103.50</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>0.0432</t>
+          <t>0.2236</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1,552.50฿</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>259.20฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>气压表/面单没有代码</t>
+          <t>气门嘴 顺心捷达，一票16件</t>
         </is>
       </c>
     </row>
@@ -6204,7 +6204,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>ZY202465806614</t>
+          <t>YT7635787693833</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -6214,38 +6214,38 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>UN-INV260807-00009</t>
+          <t>UN-INV260811-00012</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>มอก.
- รถ lot18466-5-51</t>
+          <t>ธรรมดา
+ รถ lot18473-6-41</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>11.30</t>
+          <t>13.80</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>0.0655</t>
+          <t>0.0432</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>445.40฿</t>
+          <t>259.20฿</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>电子数显胎压枪</t>
+          <t>气压表/面单没有代码</t>
         </is>
       </c>
     </row>
@@ -6275,7 +6275,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>113177184579#7</t>
+          <t>ZY202465806614</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -6290,18 +6290,18 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>ธรรมดา
- รถ lot18463-17</t>
+          <t>มอก.
+ รถ lot18466-5-51</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>9.70</t>
+          <t>11.30</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>0.0305</t>
+          <t>0.0655</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -6331,10 +6331,14 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>183.00฿</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr"/>
+          <t>445.40฿</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>电子数显胎压枪</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -6342,7 +6346,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>113177184579#5</t>
+          <t>113177184579#7</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -6358,7 +6362,7 @@
       <c r="E86" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-16</t>
+ รถ lot18463-17</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -6378,12 +6382,12 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>15.00</t>
+          <t>9.70</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>0.0137</t>
+          <t>0.0305</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -6393,12 +6397,12 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>225.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>183.00฿</t>
         </is>
       </c>
       <c r="N86" t="inlineStr"/>
@@ -6409,7 +6413,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>113177184579#4</t>
+          <t>113177184579#5</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -6425,7 +6429,7 @@
       <c r="E87" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-15</t>
+ รถ lot18463-16</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -6445,12 +6449,12 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>7.30</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>0.0235</t>
+          <t>0.0137</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -6460,12 +6464,12 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>225.00฿</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>141.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N87" t="inlineStr"/>
@@ -6476,7 +6480,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>113177184579#3</t>
+          <t>113177184579#4</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -6492,7 +6496,7 @@
       <c r="E88" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-14</t>
+ รถ lot18463-15</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -6512,12 +6516,12 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>11.90</t>
+          <t>7.30</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>0.0302</t>
+          <t>0.0235</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -6532,7 +6536,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>181.20฿</t>
+          <t>141.00฿</t>
         </is>
       </c>
       <c r="N88" t="inlineStr"/>
@@ -6543,7 +6547,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>113177184579#6</t>
+          <t>113177184579#3</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -6559,7 +6563,7 @@
       <c r="E89" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-13</t>
+ รถ lot18463-14</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -6579,12 +6583,12 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>26.10</t>
+          <t>11.90</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>0.0673</t>
+          <t>0.0302</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -6599,7 +6603,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>403.80฿</t>
+          <t>181.20฿</t>
         </is>
       </c>
       <c r="N89" t="inlineStr"/>
@@ -6610,7 +6614,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>435289604798626</t>
+          <t>113177184579#6</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -6626,7 +6630,7 @@
       <c r="E90" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18462-6-6</t>
+ รถ lot18463-13</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -6636,7 +6640,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -6646,12 +6650,12 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>9.60</t>
+          <t>26.10</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>0.0090</t>
+          <t>0.0673</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -6661,19 +6665,15 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>144.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr">
-        <is>
-          <t>螺丝配件</t>
-        </is>
-      </c>
+          <t>403.80฿</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -6681,7 +6681,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>113177184579#2</t>
+          <t>435289604798626</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -6697,7 +6697,7 @@
       <c r="E91" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-12</t>
+ รถ lot18462-6-6</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -6707,7 +6707,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>5.30</t>
+          <t>9.60</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>0.0635</t>
+          <t>0.0090</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -6732,15 +6732,19 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>144.00฿</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>381.00฿</t>
-        </is>
-      </c>
-      <c r="N91" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>螺丝配件</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -6748,7 +6752,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>113177184579</t>
+          <t>113177184579#2</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -6764,7 +6768,7 @@
       <c r="E92" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-11</t>
+ รถ lot18463-12</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -6784,12 +6788,12 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>13.30</t>
+          <t>5.30</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>0.1176</t>
+          <t>0.0635</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -6804,14 +6808,10 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>705.60฿</t>
-        </is>
-      </c>
-      <c r="N92" t="inlineStr">
-        <is>
-          <t>蘑菇钉补胎贴</t>
-        </is>
-      </c>
+          <t>381.00฿</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>435289604798722</t>
+          <t>113177184579</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -6835,7 +6835,7 @@
       <c r="E93" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18462-3</t>
+ รถ lot18463-11</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6855,12 +6855,12 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>4.30</t>
+          <t>13.30</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>0.0029</t>
+          <t>0.1176</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -6870,17 +6870,17 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>64.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>705.60฿</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>气门嘴</t>
+          <t>蘑菇钉补胎贴</t>
         </is>
       </c>
     </row>
@@ -6890,7 +6890,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>ZY202471573119#2</t>
+          <t>435289604798722</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -6906,7 +6906,7 @@
       <c r="E94" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-6</t>
+ รถ lot18462-3</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -6916,7 +6916,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6926,12 +6926,12 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>8.70</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>0.0441</t>
+          <t>0.0029</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -6941,15 +6941,19 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>64.50฿</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>264.60฿</t>
-        </is>
-      </c>
-      <c r="N94" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>气门嘴</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -6957,7 +6961,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>ZY202471573119</t>
+          <t>ZY202471573119#2</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -6973,7 +6977,7 @@
       <c r="E95" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-5</t>
+ รถ lot18463-6</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -6993,12 +6997,12 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>11.90</t>
+          <t>8.70</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>0.0832</t>
+          <t>0.0441</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -7013,14 +7017,10 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>499.20฿</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr">
-        <is>
-          <t>蘑菇钉补胎</t>
-        </is>
-      </c>
+          <t>264.60฿</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -7028,7 +7028,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>YT7635427281240</t>
+          <t>ZY202471573119</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -7044,7 +7044,7 @@
       <c r="E96" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18458-21</t>
+ รถ lot18463-5</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -7064,12 +7064,12 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>11.90</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>0.0117</t>
+          <t>0.0832</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>70.20฿</t>
+          <t>499.20฿</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>气阀</t>
+          <t>蘑菇钉补胎</t>
         </is>
       </c>
     </row>
@@ -7099,7 +7099,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>79021262374216</t>
+          <t>YT7635427281240</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -7109,38 +7109,38 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>UN-INV260804-00019</t>
+          <t>UN-INV260807-00009</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18435-5-73</t>
+ รถ lot18458-21</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>12.20</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>0.0352</t>
+          <t>0.0117</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -7155,12 +7155,12 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>211.20฿</t>
+          <t>70.20฿</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>加长弯头</t>
+          <t>气阀</t>
         </is>
       </c>
     </row>
@@ -7170,7 +7170,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>113162219964#3</t>
+          <t>79021262374216</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -7186,17 +7186,17 @@
       <c r="E98" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18434-9-28</t>
+ รถ lot18435-5-73</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -7206,12 +7206,12 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>18.70</t>
+          <t>12.20</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>0.0443</t>
+          <t>0.0352</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -7221,15 +7221,19 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>280.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr"/>
+          <t>211.20฿</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>加长弯头</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -7237,7 +7241,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>113162219964#2</t>
+          <t>113162219964#3</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -7253,7 +7257,7 @@
       <c r="E99" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18434-9-27</t>
+ รถ lot18434-9-28</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -7273,12 +7277,12 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>22.90</t>
+          <t>18.70</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>0.0522</t>
+          <t>0.0443</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -7288,7 +7292,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>343.50฿</t>
+          <t>280.50฿</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -7304,7 +7308,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>113162219964</t>
+          <t>113162219964#2</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -7320,7 +7324,7 @@
       <c r="E100" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18434-9-26</t>
+ รถ lot18434-9-27</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -7340,12 +7344,12 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>25.60</t>
+          <t>22.90</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>0.0574</t>
+          <t>0.0522</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -7355,7 +7359,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>384.00฿</t>
+          <t>343.50฿</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -7363,11 +7367,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N100" t="inlineStr">
-        <is>
-          <t>补胎胶片/3件</t>
-        </is>
-      </c>
+      <c r="N100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -7375,7 +7375,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>113158800045#2</t>
+          <t>113162219964</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -7391,32 +7391,32 @@
       <c r="E101" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18427-7-3</t>
+ รถ lot18434-9-26</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>26/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>26/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>26.30</t>
+          <t>25.60</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>0.0377</t>
+          <t>0.0574</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -7426,7 +7426,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>394.50฿</t>
+          <t>384.00฿</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -7434,7 +7434,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N101" t="inlineStr"/>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>补胎胶片/3件</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/cargo_packages_p1-5.xlsx
+++ b/cargo_packages_p1-5.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>YT7646197126750</t>
+          <t>S35386291018</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -522,17 +522,17 @@
       <c r="E2" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18887-50</t>
+ รถ lot18901-6-32</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>26/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>26/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -542,22 +542,22 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>8.30</t>
+          <t>82.80</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.0127</t>
+          <t>0.1641</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>124.50฿</t>
+          <t>1,242.00฿</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -567,7 +567,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>配件，12件</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ZY202462495078</t>
+          <t>113405301091#3</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -587,38 +587,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>UN-INV260926-00006</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18844-9-4</t>
+ รถ lot18901-7-3</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>14.30</t>
+          <t>13.10</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.0624</t>
+          <t>0.0347</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -633,14 +633,10 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>374.40฿</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>胎压表</t>
-        </is>
-      </c>
+          <t>208.20฿</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -648,7 +644,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>S71749075994</t>
+          <t>113405301091#2</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -658,38 +654,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>UN-INV260924-00056</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18830-6-30</t>
+ รถ lot18901-7-2</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>119.00</t>
+          <t>16.10</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.2302</t>
+          <t>0.0397</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -699,7 +695,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>1,785.00฿</t>
+          <t>241.50฿</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -707,11 +703,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>真空胎扒胎机配件/木箱</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -719,7 +711,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>435358249576981</t>
+          <t>113405301091</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -729,38 +721,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>UN-INV260924-00056</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18815-4-6</t>
+ รถ lot18901-7-1</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5.20</t>
+          <t>33.60</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.0044</t>
+          <t>0.0832</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -770,7 +762,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>78.00฿</t>
+          <t>504.00฿</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -780,7 +772,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>气门嘴</t>
+          <t>补胎胶片/3件</t>
         </is>
       </c>
     </row>
@@ -790,7 +782,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>S71195667064</t>
+          <t>YT7646197126750</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -800,58 +792,58 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>UN-INV260924-00056</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18810-6-3</t>
+ รถ lot18887-50</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>26/09/2026</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>26/09/2026</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>165.00</t>
+          <t>8.30</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.8568</t>
+          <t>0.0127</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>124.50฿</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>5,140.80฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>千斤顶，3件，客户不打木架发</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -861,7 +853,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>113350746029#4</t>
+          <t>ZY202462495078</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -871,38 +863,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>UN-INV260924-00056</t>
+          <t>UN-INV260926-00006</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18799-6-32</t>
+ รถ lot18844-9-4</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>27.70</t>
+          <t>14.30</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.0800</t>
+          <t>0.0624</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -917,10 +909,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>480.00฿</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>374.40฿</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>胎压表</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -928,7 +924,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>113350746029#3</t>
+          <t>S71749075994</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -944,32 +940,32 @@
       <c r="E8" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18799-6-31</t>
+ รถ lot18830-6-30</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>10.90</t>
+          <t>119.00</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.0377</t>
+          <t>0.2302</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -979,15 +975,19 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1,785.00฿</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>226.20฿</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>真空胎扒胎机配件/木箱</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -995,7 +995,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>113350746029#2</t>
+          <t>435358249576981</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1011,32 +1011,32 @@
       <c r="E9" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18799-6-30</t>
+ รถ lot18815-4-6</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>15.00</t>
+          <t>5.20</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.0101</t>
+          <t>0.0044</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>225.00฿</t>
+          <t>78.00฿</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1054,7 +1054,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>气门嘴</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1062,7 +1066,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>113350746029</t>
+          <t>S71195667064</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1078,17 +1082,17 @@
       <c r="E10" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18799-6-29</t>
+ รถ lot18810-6-3</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1098,32 +1102,32 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>16.50</t>
+          <t>165.00</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.0127</t>
+          <t>0.8568</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>247.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>5,140.80฿</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>真空胎加固修理补片</t>
+          <t>千斤顶，3件，客户不打木架发</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1137,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>760246657062</t>
+          <t>113350746029#4</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1149,7 +1153,7 @@
       <c r="E11" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18799-7-3</t>
+ รถ lot18799-6-32</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1169,12 +1173,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>27.70</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.0005</t>
+          <t>0.0800</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1189,14 +1193,10 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>10.00฿</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>气门嘴，轮胎修补工具，气门芯宣传册</t>
-        </is>
-      </c>
+          <t>480.00฿</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>113348267192#2</t>
+          <t>113350746029#3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1214,38 +1214,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>UN-INV260921-00019</t>
+          <t>UN-INV260924-00056</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18795-2-7</t>
+ รถ lot18799-6-31</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>28.10</t>
+          <t>10.90</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0.0628</t>
+          <t>0.0377</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>421.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>226.20฿</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>113348267192</t>
+          <t>113350746029#2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1281,38 +1281,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>UN-INV260921-00019</t>
+          <t>UN-INV260924-00056</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18795-2-6</t>
+ รถ lot18799-6-30</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>19.50</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0.0505</t>
+          <t>0.0101</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1322,19 +1322,15 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>225.00฿</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>303.00฿</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>补胎胶片</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1342,7 +1338,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ZY202472578299</t>
+          <t>113350746029</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1352,58 +1348,58 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>UN-INV260918-00012</t>
+          <t>UN-INV260924-00056</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18758-7-43</t>
+ รถ lot18799-6-29</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>47.40</t>
+          <t>16.50</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.1603</t>
+          <t>0.0127</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>247.50฿</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>961.20฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>补胎贴，3件</t>
+          <t>真空胎加固修理补片</t>
         </is>
       </c>
     </row>
@@ -1413,7 +1409,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>773440822655698</t>
+          <t>760246657062</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1423,38 +1419,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>UN-INV260918-00012</t>
+          <t>UN-INV260924-00056</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18758-4-31</t>
+ รถ lot18799-7-3</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.0022</t>
+          <t>0.0005</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1464,17 +1460,17 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>18.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10.00฿</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>钻头</t>
+          <t>气门嘴，轮胎修补工具，气门芯宣传册</t>
         </is>
       </c>
     </row>
@@ -1484,7 +1480,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>YT7642998390994</t>
+          <t>113348267192#2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1494,38 +1490,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>UN-INV260918-00012</t>
+          <t>UN-INV260921-00019</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18769-3-57</t>
+ รถ lot18795-2-7</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>5.80</t>
+          <t>28.10</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>0.0070</t>
+          <t>0.0628</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1535,7 +1531,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>87.00฿</t>
+          <t>421.50฿</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1543,11 +1539,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>配件</t>
-        </is>
-      </c>
+      <c r="N16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1555,7 +1547,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DPK212614057101</t>
+          <t>113348267192</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1565,38 +1557,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>UN-INV260916-00003</t>
+          <t>UN-INV260921-00019</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18749-4-3</t>
+ รถ lot18795-2-6</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>9.60</t>
+          <t>19.50</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.0060</t>
+          <t>0.0505</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1606,17 +1598,17 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>144.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>303.00฿</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>轮胎气门嘴</t>
+          <t>补胎胶片</t>
         </is>
       </c>
     </row>
@@ -1626,7 +1618,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>79031204783305</t>
+          <t>ZY202472578299</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1636,58 +1628,58 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>UN-INV260916-00003</t>
+          <t>UN-INV260918-00012</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18744-6-15</t>
+ รถ lot18758-7-43</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>47.40</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>0.0020</t>
+          <t>0.1603</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>39.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>961.20฿</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>补胎贴，3件</t>
         </is>
       </c>
     </row>
@@ -1697,7 +1689,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>435342988112655</t>
+          <t>773440822655698</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1707,38 +1699,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>UN-INV260916-00003</t>
+          <t>UN-INV260918-00012</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18743-3-34</t>
+ รถ lot18758-4-31</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>0.0014</t>
+          <t>0.0022</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1748,17 +1740,17 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>18.00฿</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>10.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>橡胶垫圈</t>
+          <t>钻头</t>
         </is>
       </c>
     </row>
@@ -1768,7 +1760,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>435343890137834</t>
+          <t>YT7642998390994</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1778,38 +1770,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>UN-INV260916-00003</t>
+          <t>UN-INV260918-00012</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18743-7-25</t>
+ รถ lot18769-3-57</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>21.40</t>
+          <t>5.80</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0.0080</t>
+          <t>0.0070</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1819,7 +1811,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>321.00฿</t>
+          <t>87.00฿</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1829,7 +1821,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>扒胎机包胶撬棍</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -1839,7 +1831,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>YT7642670434639</t>
+          <t>DPK212614057101</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1855,17 +1847,17 @@
       <c r="E21" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18743-2-8</t>
+ รถ lot18749-4-3</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1875,12 +1867,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>9.60</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.0010</t>
+          <t>0.0060</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1890,7 +1882,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>12.00฿</t>
+          <t>144.00฿</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1900,7 +1892,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>片片</t>
+          <t>轮胎气门嘴</t>
         </is>
       </c>
     </row>
@@ -1910,7 +1902,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>93015797092</t>
+          <t>79031204783305</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1920,38 +1912,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>UN-INV260914-00014</t>
+          <t>UN-INV260916-00003</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18735-4-40</t>
+ รถ lot18744-6-15</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>12/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>8.60</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.0148</t>
+          <t>0.0020</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1961,7 +1953,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>129.00฿</t>
+          <t>39.00฿</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1971,7 +1963,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>仪表</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -1981,7 +1973,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>YT7642390374765</t>
+          <t>435342988112655</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1991,18 +1983,18 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>UN-INV260914-00015</t>
+          <t>UN-INV260916-00003</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18735-4-20</t>
+ รถ lot18743-3-34</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2012,17 +2004,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>12/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>20.80</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.0598</t>
+          <t>0.0014</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2037,12 +2029,12 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>358.80฿</t>
+          <t>10.00฿</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>打磨机</t>
+          <t>橡胶垫圈</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2044,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>435342255104130</t>
+          <t>435343890137834</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2062,18 +2054,18 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>UN-INV260914-00014</t>
+          <t>UN-INV260916-00003</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18735-43</t>
+ รถ lot18743-7-25</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2083,17 +2075,17 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>12/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>4.90</t>
+          <t>21.40</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.0172</t>
+          <t>0.0080</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2103,17 +2095,17 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>321.00฿</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>103.20฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>轮毂保护套</t>
+          <t>扒胎机包胶撬棍</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2115,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>773440312345715</t>
+          <t>YT7642670434639</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2133,18 +2125,18 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>UN-INV260914-00014</t>
+          <t>UN-INV260916-00003</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18735-3-78</t>
+ รถ lot18743-2-8</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2154,17 +2146,17 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>12/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.0013</t>
+          <t>0.0010</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2174,7 +2166,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>19.50฿</t>
+          <t>12.00฿</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2184,7 +2176,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>片片</t>
         </is>
       </c>
     </row>
@@ -2194,7 +2186,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>773440291470393</t>
+          <t>93015797092</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2210,7 +2202,7 @@
       <c r="E26" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18735-34</t>
+ รถ lot18735-4-40</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2230,12 +2222,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>8.60</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>0.0029</t>
+          <t>0.0148</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2245,7 +2237,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>48.00฿</t>
+          <t>129.00฿</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2255,7 +2247,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>球阀</t>
+          <t>仪表</t>
         </is>
       </c>
     </row>
@@ -2265,7 +2257,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>435342261175750</t>
+          <t>YT7642390374765</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2281,7 +2273,7 @@
       <c r="E27" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18736-13</t>
+ รถ lot18735-4-20</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2291,7 +2283,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2301,12 +2293,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>13.90</t>
+          <t>20.80</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.0137</t>
+          <t>0.0598</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2316,17 +2308,17 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>208.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>358.80฿</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>打磨机</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2328,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ZY202461195200</t>
+          <t>435342255104130</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2346,13 +2338,13 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>UN-INV260914-00015</t>
+          <t>UN-INV260914-00014</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18728-7-13</t>
+ รถ lot18735-43</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2362,22 +2354,22 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>13/09/2026</t>
+          <t>12/09/2026</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>47.40</t>
+          <t>4.90</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.0116</t>
+          <t>0.0172</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2387,17 +2379,17 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>711.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>103.20฿</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>轮毂保护套</t>
         </is>
       </c>
     </row>
@@ -2407,7 +2399,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>79030687835952</t>
+          <t>773440312345715</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2423,7 +2415,7 @@
       <c r="E29" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18728-3-64</t>
+ รถ lot18735-3-78</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2433,22 +2425,22 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>13/09/2026</t>
+          <t>12/09/2026</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>4.30</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0.0030</t>
+          <t>0.0013</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2458,7 +2450,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>64.50฿</t>
+          <t>19.50฿</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2468,7 +2460,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>接头配件</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -2478,7 +2470,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>LJ20722214#3</t>
+          <t>773440291470393</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2488,38 +2480,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>UN-INV260912-00011</t>
+          <t>UN-INV260914-00014</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18726-7-8</t>
+ รถ lot18735-34</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>12/09/2026</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>14.00</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.0171</t>
+          <t>0.0029</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2529,7 +2521,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>210.00฿</t>
+          <t>48.00฿</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2537,7 +2529,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>球阀</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2545,7 +2541,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>LJ20722214#2</t>
+          <t>435342261175750</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2555,38 +2551,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>UN-INV260912-00011</t>
+          <t>UN-INV260914-00015</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18726-7-7</t>
+ รถ lot18736-13</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>12/09/2026</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>11.90</t>
+          <t>13.90</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.0089</t>
+          <t>0.0137</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2596,7 +2592,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>178.50฿</t>
+          <t>208.50฿</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2604,7 +2600,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>配件</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>LJ20722214</t>
+          <t>ZY202461195200</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2622,38 +2622,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>UN-INV260912-00011</t>
+          <t>UN-INV260914-00015</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18726-7-6</t>
+ รถ lot18728-7-13</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>13/09/2026</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>16.00</t>
+          <t>47.40</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.0144</t>
+          <t>0.0116</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2663,7 +2663,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>240.00฿</t>
+          <t>711.00฿</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>电板套筒配件/3件</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>YT7641966426761</t>
+          <t>79030687835952</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2693,38 +2693,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>UN-INV260912-00011</t>
+          <t>UN-INV260914-00014</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18714-9-23</t>
+ รถ lot18728-3-64</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>13/09/2026</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>13.60</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.0422</t>
+          <t>0.0030</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2734,17 +2734,17 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>64.50฿</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>253.20฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>带表汽车轮胎打气嘴</t>
+          <t>接头配件</t>
         </is>
       </c>
     </row>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ZY202471681117#2</t>
+          <t>LJ20722214#3</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2770,17 +2770,17 @@
       <c r="E34" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18714-9-8</t>
+ รถ lot18726-7-8</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2790,12 +2790,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>11.80</t>
+          <t>14.00</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.0832</t>
+          <t>0.0171</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>210.00฿</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>499.20฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -2821,7 +2821,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ZY202471681117</t>
+          <t>LJ20722214#2</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2837,17 +2837,17 @@
       <c r="E35" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18714-9-7</t>
+ รถ lot18726-7-7</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>7.70</t>
+          <t>11.90</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.0493</t>
+          <t>0.0089</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2872,19 +2872,15 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>178.50฿</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>295.80฿</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>补胎胶片/2件</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2892,7 +2888,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>302285502767#2</t>
+          <t>LJ20722214</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2908,17 +2904,17 @@
       <c r="E36" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18714-8-10</t>
+ รถ lot18726-7-6</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2928,12 +2924,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>33.70</t>
+          <t>16.00</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.0145</t>
+          <t>0.0144</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2943,7 +2939,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>505.50฿</t>
+          <t>240.00฿</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2951,7 +2947,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>电板套筒配件/3件</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>302285502767</t>
+          <t>YT7641966426761</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2975,7 +2975,7 @@
       <c r="E37" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18714-8-9</t>
+ รถ lot18714-9-23</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2995,12 +2995,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>23.40</t>
+          <t>13.60</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.0123</t>
+          <t>0.0422</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -3010,17 +3010,17 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>351.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>253.20฿</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>扳手</t>
+          <t>带表汽车轮胎打气嘴</t>
         </is>
       </c>
     </row>
@@ -3030,7 +3030,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>LJ20716178#2</t>
+          <t>ZY202471681117#2</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3040,18 +3040,18 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>UN-INV260911-00013</t>
+          <t>UN-INV260912-00011</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18713-6-65</t>
+ รถ lot18714-9-8</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -3061,17 +3061,17 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>19.50</t>
+          <t>11.80</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.0075</t>
+          <t>0.0832</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -3081,12 +3081,12 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>292.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>499.20฿</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -3097,7 +3097,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>LJ20716178</t>
+          <t>ZY202471681117</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3107,18 +3107,18 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>UN-INV260911-00013</t>
+          <t>UN-INV260912-00011</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18713-6-64</t>
+ รถ lot18714-9-7</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -3128,17 +3128,17 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>19.60</t>
+          <t>7.70</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.0075</t>
+          <t>0.0493</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -3148,17 +3148,17 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>294.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>295.80฿</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>补胎胶片/2件</t>
         </is>
       </c>
     </row>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>435338972466812</t>
+          <t>302285502767#2</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3178,38 +3178,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>UN-INV260911-00013</t>
+          <t>UN-INV260912-00011</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18710-6-35</t>
+ รถ lot18714-8-10</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>13.10</t>
+          <t>33.70</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.0624</t>
+          <t>0.0145</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -3219,19 +3219,15 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>505.50฿</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>374.40฿</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>修补工具</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -3239,7 +3235,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>435334324045675</t>
+          <t>302285502767</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3249,38 +3245,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>UN-INV260908-00009</t>
+          <t>UN-INV260912-00011</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18696-14</t>
+ รถ lot18714-8-9</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>10.80</t>
+          <t>23.40</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.0088</t>
+          <t>0.0123</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -3290,7 +3286,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>162.00฿</t>
+          <t>351.00฿</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -3300,7 +3296,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>扳手</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3306,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>YT7641276428798</t>
+          <t>LJ20716178#2</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3320,38 +3316,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>UN-INV260908-00009</t>
+          <t>UN-INV260911-00013</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18697-11</t>
+ รถ lot18713-6-65</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>9.50</t>
+          <t>19.50</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.0296</t>
+          <t>0.0075</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3361,19 +3357,15 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>292.50฿</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>177.60฿</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>配件</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -3381,7 +3373,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>79029430531776</t>
+          <t>LJ20716178</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3391,38 +3383,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>UN-INV260907-00015</t>
+          <t>UN-INV260911-00013</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18689-26</t>
+ รถ lot18713-6-64</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>19.60</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.0135</t>
+          <t>0.0075</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3432,17 +3424,17 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>294.00฿</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>81.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>卡套</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -3452,7 +3444,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>113282578128#2</t>
+          <t>435338972466812</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3462,38 +3454,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>UN-INV260907-00015</t>
+          <t>UN-INV260911-00013</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18683-4</t>
+ รถ lot18710-6-35</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>38.00</t>
+          <t>13.10</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.1601</t>
+          <t>0.0624</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3508,10 +3500,14 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>960.60฿</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
+          <t>374.40฿</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>修补工具</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -3519,7 +3515,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>113282578128</t>
+          <t>435334324045675</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3529,38 +3525,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>UN-INV260907-00015</t>
+          <t>UN-INV260908-00009</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18683-3</t>
+ รถ lot18696-14</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>27.50</t>
+          <t>10.80</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.1566</t>
+          <t>0.0088</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3570,17 +3566,17 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>162.00฿</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>939.60฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>压条取出器 一票两件破损件</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3586,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>82730128600#3</t>
+          <t>YT7641276428798</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3600,38 +3596,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>UN-INV260907-00015</t>
+          <t>UN-INV260908-00009</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18678-6-21</t>
+ รถ lot18697-11</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>30/08/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>33.00</t>
+          <t>9.50</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>0.0122</t>
+          <t>0.0296</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3641,15 +3637,19 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>495.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
+          <t>177.60฿</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>配件</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -3657,7 +3657,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>82730128600#2</t>
+          <t>79029430531776</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3673,17 +3673,17 @@
       <c r="E47" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18678-6-20</t>
+ รถ lot18689-26</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>30/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3693,12 +3693,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>27.60</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>0.0095</t>
+          <t>0.0135</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3708,15 +3708,19 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>414.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
+          <t>81.00฿</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>卡套</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -3724,7 +3728,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>82730128600</t>
+          <t>113282578128#2</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3740,12 +3744,12 @@
       <c r="E48" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18678-6-19</t>
+ รถ lot18683-4</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>30/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3760,12 +3764,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>28.10</t>
+          <t>38.00</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>0.0118</t>
+          <t>0.1601</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3775,19 +3779,15 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>421.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>五金配件/3件</t>
-        </is>
-      </c>
+          <t>960.60฿</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -3795,7 +3795,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>113278387839#3</t>
+          <t>113282578128</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3805,38 +3805,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>UN-INV260903-00023</t>
+          <t>UN-INV260907-00015</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18663-8-3</t>
+ รถ lot18683-3</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>25.30</t>
+          <t>27.50</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>0.0404</t>
+          <t>0.1566</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3846,15 +3846,19 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>379.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
+          <t>939.60฿</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>压条取出器 一票两件破损件</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -3862,7 +3866,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>113278387839#2</t>
+          <t>82730128600#3</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3872,38 +3876,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>UN-INV260903-00023</t>
+          <t>UN-INV260907-00015</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18663-8-2</t>
+ รถ lot18678-6-21</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>30/08/2026</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>26.10</t>
+          <t>33.00</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>0.0304</t>
+          <t>0.0122</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3913,7 +3917,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>391.50฿</t>
+          <t>495.00฿</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -3929,7 +3933,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>113278387839</t>
+          <t>82730128600#2</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3939,38 +3943,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>UN-INV260903-00023</t>
+          <t>UN-INV260907-00015</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18663-8-1</t>
+ รถ lot18678-6-20</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>30/08/2026</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>9.10</t>
+          <t>27.60</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>0.0144</t>
+          <t>0.0095</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3980,7 +3984,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>136.50฿</t>
+          <t>414.00฿</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -3988,11 +3992,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>配件/3件</t>
-        </is>
-      </c>
+      <c r="N51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -4000,7 +4000,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>113276098937#3</t>
+          <t>82730128600</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -4010,38 +4010,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>UN-INV260901-00057</t>
+          <t>UN-INV260907-00015</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-45</t>
+ รถ lot18678-6-19</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>30/08/2026</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>17.80</t>
+          <t>28.10</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>0.0302</t>
+          <t>0.0118</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>267.00฿</t>
+          <t>421.50฿</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -4059,7 +4059,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>五金配件/3件</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -4067,7 +4071,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>113276098937#2</t>
+          <t>113278387839#3</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -4077,38 +4081,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>UN-INV260901-00057</t>
+          <t>UN-INV260903-00023</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-44</t>
+ รถ lot18663-8-3</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>10.90</t>
+          <t>25.30</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>0.0313</t>
+          <t>0.0404</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -4118,12 +4122,12 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>379.50฿</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>187.80฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
@@ -4134,7 +4138,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>113276098937</t>
+          <t>113278387839#2</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -4144,38 +4148,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>UN-INV260901-00057</t>
+          <t>UN-INV260903-00023</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-43</t>
+ รถ lot18663-8-2</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>33.60</t>
+          <t>26.10</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>0.0825</t>
+          <t>0.0304</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -4185,7 +4189,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>504.00฿</t>
+          <t>391.50฿</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -4193,11 +4197,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>补胎胶片+配件/3件</t>
-        </is>
-      </c>
+      <c r="N54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -4205,7 +4205,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ZY202464580877#4</t>
+          <t>113278387839</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -4215,38 +4215,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>UN-INV260901-00057</t>
+          <t>UN-INV260903-00023</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-17</t>
+ รถ lot18663-8-1</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>20.10</t>
+          <t>9.10</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>0.0466</t>
+          <t>0.0144</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -4256,7 +4256,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>301.50฿</t>
+          <t>136.50฿</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -4264,7 +4264,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr"/>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>配件/3件</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -4272,7 +4276,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ZY202464580877#7</t>
+          <t>113276098937#3</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -4288,7 +4292,7 @@
       <c r="E56" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-16</t>
+ รถ lot18655-9-45</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -4308,12 +4312,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>16.60</t>
+          <t>17.80</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>0.0430</t>
+          <t>0.0302</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -4323,12 +4327,12 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>267.00฿</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>258.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
@@ -4339,7 +4343,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ZY202464580877#2</t>
+          <t>113276098937#2</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -4355,7 +4359,7 @@
       <c r="E57" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-15</t>
+ รถ lot18655-9-44</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -4375,12 +4379,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>25.10</t>
+          <t>10.90</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>0.0483</t>
+          <t>0.0313</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -4390,12 +4394,12 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>376.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>187.80฿</t>
         </is>
       </c>
       <c r="N57" t="inlineStr"/>
@@ -4406,7 +4410,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ZY202464580877#8</t>
+          <t>113276098937</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -4422,7 +4426,7 @@
       <c r="E58" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-14</t>
+ รถ lot18655-9-43</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -4442,12 +4446,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>28.90</t>
+          <t>33.60</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>0.0800</t>
+          <t>0.0825</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -4457,15 +4461,19 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>504.00฿</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>480.00฿</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>补胎胶片+配件/3件</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -4473,7 +4481,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ZY202464580877#6</t>
+          <t>ZY202464580877#4</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4489,7 +4497,7 @@
       <c r="E59" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-13</t>
+ รถ lot18655-9-17</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -4509,12 +4517,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>20.90</t>
+          <t>20.10</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>0.0534</t>
+          <t>0.0466</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4524,12 +4532,12 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>301.50฿</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>320.40฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
@@ -4540,7 +4548,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ZY202464580877#5</t>
+          <t>ZY202464580877#7</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4556,7 +4564,7 @@
       <c r="E60" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-12</t>
+ รถ lot18655-9-16</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -4576,12 +4584,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>26.20</t>
+          <t>16.60</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>0.0535</t>
+          <t>0.0430</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -4591,12 +4599,12 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>393.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>258.00฿</t>
         </is>
       </c>
       <c r="N60" t="inlineStr"/>
@@ -4607,7 +4615,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>ZY202464580877</t>
+          <t>ZY202464580877#2</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4623,7 +4631,7 @@
       <c r="E61" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-11</t>
+ รถ lot18655-9-15</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -4643,12 +4651,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>20.70</t>
+          <t>25.10</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>0.0531</t>
+          <t>0.0483</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -4658,12 +4666,12 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>376.50฿</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>318.60฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
@@ -4674,7 +4682,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>ZY202464580877#9</t>
+          <t>ZY202464580877#8</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4690,7 +4698,7 @@
       <c r="E62" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-10</t>
+ รถ lot18655-9-14</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -4710,7 +4718,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>27.70</t>
+          <t>28.90</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -4741,7 +4749,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>ZY202464580877#3</t>
+          <t>ZY202464580877#6</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4757,7 +4765,7 @@
       <c r="E63" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-9</t>
+ รถ lot18655-9-13</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -4777,12 +4785,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>27.10</t>
+          <t>20.90</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>0.0567</t>
+          <t>0.0534</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -4792,19 +4800,15 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>406.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>补胎胶片/9件</t>
-        </is>
-      </c>
+          <t>320.40฿</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -4812,7 +4816,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>S71090288685</t>
+          <t>ZY202464580877#5</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4822,38 +4826,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>UN-INV260831-00017</t>
+          <t>UN-INV260901-00057</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18634-7-3</t>
+ รถ lot18655-9-12</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>29/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>12.10</t>
+          <t>26.20</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>0.0240</t>
+          <t>0.0535</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -4863,7 +4867,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>181.50฿</t>
+          <t>393.00฿</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -4871,11 +4875,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N64" t="inlineStr">
-        <is>
-          <t>配件</t>
-        </is>
-      </c>
+      <c r="N64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -4883,7 +4883,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>YT7638092409979</t>
+          <t>ZY202464580877</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4893,38 +4893,38 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>UN-INV260822-00010</t>
+          <t>UN-INV260901-00057</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18569-7-7</t>
+ รถ lot18655-9-11</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>16/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>16/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>15.00</t>
+          <t>20.70</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>0.0140</t>
+          <t>0.0531</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -4934,19 +4934,15 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>225.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr">
-        <is>
-          <t>配件</t>
-        </is>
-      </c>
+          <t>318.60฿</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -4954,7 +4950,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>435308000517585</t>
+          <t>ZY202464580877#9</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4964,38 +4960,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>UN-INV260822-00010</t>
+          <t>UN-INV260901-00057</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18550-6-11</t>
+ รถ lot18655-9-10</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>27.70</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>0.0032</t>
+          <t>0.0800</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -5005,19 +5001,15 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>54.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr">
-        <is>
-          <t>气门嘴</t>
-        </is>
-      </c>
+          <t>480.00฿</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -5025,7 +5017,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>710094401487</t>
+          <t>ZY202464580877#3</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -5035,58 +5027,58 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>UN-INV260822-00010</t>
+          <t>UN-INV260901-00057</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18544-8-14</t>
+ รถ lot18655-9-9</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>107.10</t>
+          <t>27.10</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>0.4536</t>
+          <t>0.0567</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>406.50฿</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>2,721.60฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>空的高压充气罐/一票10件，仓库实收到9件，已确认收到的9件先发</t>
+          <t>补胎胶片/9件</t>
         </is>
       </c>
     </row>
@@ -5096,7 +5088,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>773435675083665</t>
+          <t>S71090288685</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -5106,38 +5098,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>UN-INV260815-00046</t>
+          <t>UN-INV260831-00017</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18526-6-17</t>
+ รถ lot18634-7-3</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>29/08/2026</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>13.10</t>
+          <t>12.10</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>0.0214</t>
+          <t>0.0240</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -5147,7 +5139,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>196.50฿</t>
+          <t>181.50฿</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -5157,7 +5149,7 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>补胎工具</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -5167,7 +5159,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>YT7637032206975</t>
+          <t>YT7638092409979</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -5177,38 +5169,38 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>UN-INV260819-00010</t>
+          <t>UN-INV260822-00010</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>มอก.
- รถ lot18523-6-30</t>
+          <t>ธรรมดา
+ รถ lot18569-7-7</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>16/08/2026</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>16/08/2026</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>16/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>9.60</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>0.0316</t>
+          <t>0.0140</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -5218,17 +5210,17 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>225.00฿</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>214.88฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>气动模具研磨机+配件</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5230,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>ZY202466648481#5</t>
+          <t>435308000517585</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -5248,38 +5240,38 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>UN-INV260815-00046</t>
+          <t>UN-INV260822-00010</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18519-6-17</t>
+ รถ lot18550-6-11</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>15/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>16.10</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>0.0493</t>
+          <t>0.0032</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -5289,15 +5281,19 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>54.00฿</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>295.80฿</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>气门嘴</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -5305,7 +5301,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>ZY202466648481#4</t>
+          <t>710094401487</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -5315,43 +5311,43 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>UN-INV260815-00046</t>
+          <t>UN-INV260822-00010</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18519-6-16</t>
+ รถ lot18544-8-14</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>15/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>20.50</t>
+          <t>107.10</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>0.0656</t>
+          <t>0.4536</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -5361,10 +5357,14 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>393.60฿</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
+          <t>2,721.60฿</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>空的高压充气罐/一票10件，仓库实收到9件，已确认收到的9件先发</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -5372,7 +5372,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>ZY202466648481#3</t>
+          <t>773435675083665</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -5388,32 +5388,32 @@
       <c r="E72" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18519-6-15</t>
+ รถ lot18526-6-17</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>15/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>15.70</t>
+          <t>13.10</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>0.0508</t>
+          <t>0.0214</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -5423,15 +5423,19 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>196.50฿</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>304.80฿</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>补胎工具</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -5439,7 +5443,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>ZY202466648481#2</t>
+          <t>YT7637032206975</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -5449,13 +5453,13 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>UN-INV260815-00046</t>
+          <t>UN-INV260819-00010</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>ธรรมดา
- รถ lot18519-6-14</t>
+          <t>มอก.
+ รถ lot18523-6-30</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -5470,17 +5474,17 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>15/08/2026</t>
+          <t>16/08/2026</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>20.20</t>
+          <t>9.60</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>0.0660</t>
+          <t>0.0316</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -5495,10 +5499,14 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>396.00฿</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr"/>
+          <t>214.88฿</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>气动模具研磨机+配件</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -5506,7 +5514,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>ZY202466648481</t>
+          <t>ZY202466648481#5</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -5522,7 +5530,7 @@
       <c r="E74" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18519-6-13</t>
+ รถ lot18519-6-17</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -5542,12 +5550,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>15.80</t>
+          <t>16.10</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>0.0522</t>
+          <t>0.0493</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -5562,14 +5570,10 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>313.20฿</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr">
-        <is>
-          <t>补胎胶条/5件</t>
-        </is>
-      </c>
+          <t>295.80฿</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -5577,7 +5581,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>113204676267#2</t>
+          <t>ZY202466648481#4</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -5593,32 +5597,32 @@
       <c r="E75" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18518-5-3</t>
+ รถ lot18519-6-16</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>15/08/2026</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>24.60</t>
+          <t>20.50</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>0.0608</t>
+          <t>0.0656</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -5628,12 +5632,12 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>369.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>393.60฿</t>
         </is>
       </c>
       <c r="N75" t="inlineStr"/>
@@ -5644,7 +5648,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>113204676267</t>
+          <t>ZY202466648481#3</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5660,32 +5664,32 @@
       <c r="E76" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18518-5-2</t>
+ รถ lot18519-6-15</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>15/08/2026</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>25.00</t>
+          <t>15.70</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>0.0566</t>
+          <t>0.0508</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -5695,19 +5699,15 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>375.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr">
-        <is>
-          <t>真空胎冷补胶片</t>
-        </is>
-      </c>
+          <t>304.80฿</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -5715,7 +5715,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>910061892464#2</t>
+          <t>ZY202466648481#2</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -5731,32 +5731,32 @@
       <c r="E77" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18505-5-23</t>
+ รถ lot18519-6-14</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>15/08/2026</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>30.40</t>
+          <t>20.20</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>0.0523</t>
+          <t>0.0660</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -5766,12 +5766,12 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>456.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>396.00฿</t>
         </is>
       </c>
       <c r="N77" t="inlineStr"/>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>910061892464</t>
+          <t>ZY202466648481</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -5798,32 +5798,32 @@
       <c r="E78" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18505-5-22</t>
+ รถ lot18519-6-13</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>15/08/2026</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>15.90</t>
+          <t>15.80</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>0.0353</t>
+          <t>0.0522</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>238.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>313.20฿</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>记号蜡笔</t>
+          <t>补胎胶条/5件</t>
         </is>
       </c>
     </row>
@@ -5853,7 +5853,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>773434709817985</t>
+          <t>113204676267#2</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -5863,38 +5863,38 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>UN-INV260819-00010</t>
+          <t>UN-INV260815-00046</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18535-8</t>
+ รถ lot18518-5-3</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>16/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>24.60</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>0.0184</t>
+          <t>0.0608</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -5904,19 +5904,15 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>369.00฿</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>110.40฿</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr">
-        <is>
-          <t>锅具 二次包装货物变形</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -5924,7 +5920,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>435295775627304</t>
+          <t>113204676267</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -5934,38 +5930,38 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>UN-INV260811-00012</t>
+          <t>UN-INV260815-00046</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18492-2</t>
+ รถ lot18518-5-2</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>5.30</t>
+          <t>25.00</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>0.0090</t>
+          <t>0.0566</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -5975,7 +5971,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>79.50฿</t>
+          <t>375.00฿</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -5985,7 +5981,7 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>配件 破损件</t>
+          <t>真空胎冷补胶片</t>
         </is>
       </c>
     </row>
@@ -5995,7 +5991,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>YT7636332367470</t>
+          <t>910061892464#2</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -6005,38 +6001,38 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>UN-INV260811-00012</t>
+          <t>UN-INV260815-00046</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18487-2-27</t>
+ รถ lot18505-5-23</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>30.40</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>0.0004</t>
+          <t>0.0523</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -6046,19 +6042,15 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>456.00฿</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>10.00฿</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr">
-        <is>
-          <t>立牌</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -6066,7 +6058,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>S35386280517#2</t>
+          <t>910061892464</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -6076,38 +6068,38 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>UN-INV260811-00012</t>
+          <t>UN-INV260815-00046</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18475-24</t>
+ รถ lot18505-5-22</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>8.80</t>
+          <t>15.90</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>0.0045</t>
+          <t>0.0353</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -6117,7 +6109,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>132.00฿</t>
+          <t>238.50฿</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -6125,7 +6117,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N82" t="inlineStr"/>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>记号蜡笔</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -6133,7 +6129,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>S35386280517</t>
+          <t>773434709817985</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -6143,58 +6139,58 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>UN-INV260811-00012</t>
+          <t>UN-INV260819-00010</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18475-23</t>
+ รถ lot18535-8</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>16/08/2026</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>103.50</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>0.2236</t>
+          <t>0.0184</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>1,552.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>110.40฿</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>气门嘴 顺心捷达，一票16件</t>
+          <t>锅具 二次包装货物变形</t>
         </is>
       </c>
     </row>
@@ -6204,7 +6200,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>YT7635787693833</t>
+          <t>435295775627304</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -6220,32 +6216,32 @@
       <c r="E84" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18473-6-41</t>
+ รถ lot18492-2</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>13.80</t>
+          <t>5.30</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>0.0432</t>
+          <t>0.0090</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -6255,17 +6251,17 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>79.50฿</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>259.20฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>气压表/面单没有代码</t>
+          <t>配件 破损件</t>
         </is>
       </c>
     </row>
@@ -6275,7 +6271,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>ZY202465806614</t>
+          <t>YT7636332367470</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -6285,38 +6281,38 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>UN-INV260807-00009</t>
+          <t>UN-INV260811-00012</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>มอก.
- รถ lot18466-5-51</t>
+          <t>ธรรมดา
+ รถ lot18487-2-27</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>11.30</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>0.0655</t>
+          <t>0.0004</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -6331,12 +6327,12 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>445.40฿</t>
+          <t>10.00฿</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>电子数显胎压枪</t>
+          <t>立牌</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6342,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>113177184579#7</t>
+          <t>S35386280517#2</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -6356,38 +6352,38 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>UN-INV260807-00009</t>
+          <t>UN-INV260811-00012</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-17</t>
+ รถ lot18475-24</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>9.70</t>
+          <t>8.80</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>0.0305</t>
+          <t>0.0045</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -6397,12 +6393,12 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>132.00฿</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>183.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N86" t="inlineStr"/>
@@ -6413,7 +6409,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>113177184579#5</t>
+          <t>S35386280517</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -6423,48 +6419,48 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>UN-INV260807-00009</t>
+          <t>UN-INV260811-00012</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-16</t>
+ รถ lot18475-23</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>15.00</t>
+          <t>103.50</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>0.0137</t>
+          <t>0.2236</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>225.00฿</t>
+          <t>1,552.50฿</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -6472,7 +6468,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N87" t="inlineStr"/>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>气门嘴 顺心捷达，一票16件</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -6480,7 +6480,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>113177184579#4</t>
+          <t>YT7635787693833</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -6490,38 +6490,38 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>UN-INV260807-00009</t>
+          <t>UN-INV260811-00012</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-15</t>
+ รถ lot18473-6-41</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>7.30</t>
+          <t>13.80</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>0.0235</t>
+          <t>0.0432</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -6536,10 +6536,14 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>141.00฿</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr"/>
+          <t>259.20฿</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>气压表/面单没有代码</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -6547,7 +6551,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>113177184579#3</t>
+          <t>ZY202465806614</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -6562,18 +6566,18 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>ธรรมดา
- รถ lot18463-14</t>
+          <t>มอก.
+ รถ lot18466-5-51</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -6583,12 +6587,12 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>11.90</t>
+          <t>11.30</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>0.0302</t>
+          <t>0.0655</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -6603,10 +6607,14 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>181.20฿</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr"/>
+          <t>445.40฿</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>电子数显胎压枪</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -6614,7 +6622,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>113177184579#6</t>
+          <t>113177184579#7</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -6630,7 +6638,7 @@
       <c r="E90" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-13</t>
+ รถ lot18463-17</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -6650,12 +6658,12 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>26.10</t>
+          <t>9.70</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>0.0673</t>
+          <t>0.0305</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -6670,7 +6678,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>403.80฿</t>
+          <t>183.00฿</t>
         </is>
       </c>
       <c r="N90" t="inlineStr"/>
@@ -6681,7 +6689,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>435289604798626</t>
+          <t>113177184579#5</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -6697,7 +6705,7 @@
       <c r="E91" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18462-6-6</t>
+ รถ lot18463-16</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -6707,7 +6715,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -6717,12 +6725,12 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>9.60</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>0.0090</t>
+          <t>0.0137</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -6732,7 +6740,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>144.00฿</t>
+          <t>225.00฿</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -6740,11 +6748,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N91" t="inlineStr">
-        <is>
-          <t>螺丝配件</t>
-        </is>
-      </c>
+      <c r="N91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -6752,7 +6756,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>113177184579#2</t>
+          <t>113177184579#4</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -6768,7 +6772,7 @@
       <c r="E92" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-12</t>
+ รถ lot18463-15</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -6788,12 +6792,12 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>5.30</t>
+          <t>7.30</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>0.0635</t>
+          <t>0.0235</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -6808,7 +6812,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>381.00฿</t>
+          <t>141.00฿</t>
         </is>
       </c>
       <c r="N92" t="inlineStr"/>
@@ -6819,7 +6823,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>113177184579</t>
+          <t>113177184579#3</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -6835,7 +6839,7 @@
       <c r="E93" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-11</t>
+ รถ lot18463-14</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -6855,12 +6859,12 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>13.30</t>
+          <t>11.90</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>0.1176</t>
+          <t>0.0302</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -6875,14 +6879,10 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>705.60฿</t>
-        </is>
-      </c>
-      <c r="N93" t="inlineStr">
-        <is>
-          <t>蘑菇钉补胎贴</t>
-        </is>
-      </c>
+          <t>181.20฿</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -6890,7 +6890,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>435289604798722</t>
+          <t>113177184579#6</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -6906,7 +6906,7 @@
       <c r="E94" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18462-3</t>
+ รถ lot18463-13</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -6916,7 +6916,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6926,12 +6926,12 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>4.30</t>
+          <t>26.10</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>0.0029</t>
+          <t>0.0673</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -6941,19 +6941,15 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>64.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N94" t="inlineStr">
-        <is>
-          <t>气门嘴</t>
-        </is>
-      </c>
+          <t>403.80฿</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -6961,7 +6957,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>ZY202471573119#2</t>
+          <t>435289604798626</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -6977,7 +6973,7 @@
       <c r="E95" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-6</t>
+ รถ lot18462-6-6</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -6987,7 +6983,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6997,12 +6993,12 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>8.70</t>
+          <t>9.60</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>0.0441</t>
+          <t>0.0090</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -7012,15 +7008,19 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>144.00฿</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>264.60฿</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>螺丝配件</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -7028,7 +7028,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>ZY202471573119</t>
+          <t>113177184579#2</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -7044,7 +7044,7 @@
       <c r="E96" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-5</t>
+ รถ lot18463-12</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -7064,12 +7064,12 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>11.90</t>
+          <t>5.30</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>0.0832</t>
+          <t>0.0635</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -7084,14 +7084,10 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>499.20฿</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr">
-        <is>
-          <t>蘑菇钉补胎</t>
-        </is>
-      </c>
+          <t>381.00฿</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -7099,7 +7095,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>YT7635427281240</t>
+          <t>113177184579</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -7115,7 +7111,7 @@
       <c r="E97" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18458-21</t>
+ รถ lot18463-11</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -7135,12 +7131,12 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>13.30</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>0.0117</t>
+          <t>0.1176</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -7155,12 +7151,12 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>70.20฿</t>
+          <t>705.60฿</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>气阀</t>
+          <t>蘑菇钉补胎贴</t>
         </is>
       </c>
     </row>
@@ -7170,7 +7166,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>79021262374216</t>
+          <t>435289604798722</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -7180,38 +7176,38 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>UN-INV260804-00019</t>
+          <t>UN-INV260807-00009</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18435-5-73</t>
+ รถ lot18462-3</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>12.20</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>0.0352</t>
+          <t>0.0029</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -7221,17 +7217,17 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>64.50฿</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>211.20฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>加长弯头</t>
+          <t>气门嘴</t>
         </is>
       </c>
     </row>
@@ -7241,7 +7237,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>113162219964#3</t>
+          <t>ZY202471573119#2</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -7251,38 +7247,38 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>UN-INV260804-00019</t>
+          <t>UN-INV260807-00009</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18434-9-28</t>
+ รถ lot18463-6</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>18.70</t>
+          <t>8.70</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>0.0443</t>
+          <t>0.0441</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -7292,12 +7288,12 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>280.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>264.60฿</t>
         </is>
       </c>
       <c r="N99" t="inlineStr"/>
@@ -7308,7 +7304,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>113162219964#2</t>
+          <t>ZY202471573119</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -7318,38 +7314,38 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>UN-INV260804-00019</t>
+          <t>UN-INV260807-00009</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18434-9-27</t>
+ รถ lot18463-5</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>22.90</t>
+          <t>11.90</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>0.0522</t>
+          <t>0.0832</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -7359,15 +7355,19 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>343.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N100" t="inlineStr"/>
+          <t>499.20฿</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>蘑菇钉补胎</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -7375,7 +7375,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>113162219964</t>
+          <t>YT7635427281240</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -7385,38 +7385,38 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>UN-INV260804-00019</t>
+          <t>UN-INV260807-00009</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18434-9-26</t>
+ รถ lot18458-21</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>25.60</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>0.0574</t>
+          <t>0.0117</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -7426,17 +7426,17 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>384.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>70.20฿</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>补胎胶片/3件</t>
+          <t>气阀</t>
         </is>
       </c>
     </row>

--- a/cargo_packages_p1-5.xlsx
+++ b/cargo_packages_p1-5.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>S35386291018</t>
+          <t>ZY202466680891#5</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -522,17 +522,17 @@
       <c r="E2" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18901-6-32</t>
+ รถ lot18917-7-7</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -542,34 +542,30 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>82.80</t>
+          <t>19.70</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.1641</t>
+          <t>0.0715</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>1,242.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>配件，12件</t>
-        </is>
-      </c>
+          <t>429.00฿</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -577,7 +573,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>113405301091#3</t>
+          <t>ZY202466680891#4</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -593,17 +589,17 @@
       <c r="E3" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18901-7-3</t>
+ รถ lot18917-7-6</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -613,12 +609,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>13.10</t>
+          <t>20.00</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.0347</t>
+          <t>0.0640</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -633,7 +629,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>208.20฿</t>
+          <t>384.00฿</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -644,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>113405301091#2</t>
+          <t>ZY202466680891#3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -660,17 +656,17 @@
       <c r="E4" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18901-7-2</t>
+ รถ lot18917-7-5</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -680,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>16.10</t>
+          <t>15.80</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.0397</t>
+          <t>0.0492</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -695,12 +691,12 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>241.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>295.20฿</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -711,7 +707,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>113405301091</t>
+          <t>ZY202466680891#2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -727,17 +723,17 @@
       <c r="E5" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18901-7-1</t>
+ รถ lot18917-7-4</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -747,12 +743,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>33.60</t>
+          <t>16.20</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.0832</t>
+          <t>0.0492</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -762,19 +758,15 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>504.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>补胎胶片/3件</t>
-        </is>
-      </c>
+          <t>295.20฿</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -782,7 +774,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>YT7646197126750</t>
+          <t>ZY202466680891</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -798,17 +790,17 @@
       <c r="E6" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18887-50</t>
+ รถ lot18917-7-3</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>26/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>26/09/2026</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -818,12 +810,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>8.30</t>
+          <t>15.90</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.0127</t>
+          <t>0.0492</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -833,17 +825,17 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>124.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>295.20฿</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>补胎胶片/5件</t>
         </is>
       </c>
     </row>
@@ -853,7 +845,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ZY202462495078</t>
+          <t>S35386291018</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -863,58 +855,58 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>UN-INV260926-00006</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18844-9-4</t>
+ รถ lot18901-6-32</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>14.30</t>
+          <t>82.80</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.0624</t>
+          <t>0.1641</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1,242.00฿</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>374.40฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>胎压表</t>
+          <t>配件，12件</t>
         </is>
       </c>
     </row>
@@ -924,7 +916,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>S71749075994</t>
+          <t>113405301091#3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -934,38 +926,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>UN-INV260924-00056</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18830-6-30</t>
+ รถ lot18901-7-3</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>119.00</t>
+          <t>13.10</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.2302</t>
+          <t>0.0347</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -975,19 +967,15 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>1,785.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>真空胎扒胎机配件/木箱</t>
-        </is>
-      </c>
+          <t>208.20฿</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -995,7 +983,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>435358249576981</t>
+          <t>113405301091#2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1005,38 +993,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>UN-INV260924-00056</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18815-4-6</t>
+ รถ lot18901-7-2</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>5.20</t>
+          <t>16.10</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.0044</t>
+          <t>0.0397</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1046,7 +1034,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>78.00฿</t>
+          <t>241.50฿</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1054,11 +1042,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>气门嘴</t>
-        </is>
-      </c>
+      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1066,7 +1050,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>S71195667064</t>
+          <t>113405301091</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1076,58 +1060,58 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>UN-INV260924-00056</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18810-6-3</t>
+ รถ lot18901-7-1</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>165.00</t>
+          <t>33.60</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.8568</t>
+          <t>0.0832</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>504.00฿</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>5,140.80฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>千斤顶，3件，客户不打木架发</t>
+          <t>补胎胶片/3件</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1121,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>113350746029#4</t>
+          <t>YT7646197126750</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1147,38 +1131,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>UN-INV260924-00056</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18799-6-32</t>
+ รถ lot18887-50</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>26/09/2026</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>26/09/2026</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>27.70</t>
+          <t>8.30</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.0800</t>
+          <t>0.0127</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1188,15 +1172,19 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>124.50฿</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>480.00฿</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>配件</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1204,7 +1192,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>113350746029#3</t>
+          <t>ZY202462495078</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1214,38 +1202,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>UN-INV260924-00056</t>
+          <t>UN-INV260926-00006</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18799-6-31</t>
+ รถ lot18844-9-4</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>10.90</t>
+          <t>14.30</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0.0377</t>
+          <t>0.0624</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1260,10 +1248,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>226.20฿</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
+          <t>374.40฿</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>胎压表</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1271,7 +1263,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>113350746029#2</t>
+          <t>S71749075994</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1287,32 +1279,32 @@
       <c r="E13" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18799-6-30</t>
+ รถ lot18830-6-30</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>15.00</t>
+          <t>119.00</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0.0101</t>
+          <t>0.2302</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1322,7 +1314,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>225.00฿</t>
+          <t>1,785.00฿</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1330,7 +1322,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>真空胎扒胎机配件/木箱</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1338,7 +1334,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>113350746029</t>
+          <t>435358249576981</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1354,32 +1350,32 @@
       <c r="E14" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18799-6-29</t>
+ รถ lot18815-4-6</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>16.50</t>
+          <t>5.20</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.0127</t>
+          <t>0.0044</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1389,7 +1385,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>247.50฿</t>
+          <t>78.00฿</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1399,7 +1395,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>真空胎加固修理补片</t>
+          <t>气门嘴</t>
         </is>
       </c>
     </row>
@@ -1409,7 +1405,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>760246657062</t>
+          <t>S71195667064</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1425,17 +1421,17 @@
       <c r="E15" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18799-7-3</t>
+ รถ lot18810-6-3</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1445,17 +1441,17 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>165.00</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.0005</t>
+          <t>0.8568</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1465,12 +1461,12 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>10.00฿</t>
+          <t>5,140.80฿</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>气门嘴，轮胎修补工具，气门芯宣传册</t>
+          <t>千斤顶，3件，客户不打木架发</t>
         </is>
       </c>
     </row>
@@ -1480,7 +1476,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>113348267192#2</t>
+          <t>113350746029#4</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1490,38 +1486,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>UN-INV260921-00019</t>
+          <t>UN-INV260924-00056</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18795-2-7</t>
+ รถ lot18799-6-32</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>28.10</t>
+          <t>27.70</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>0.0628</t>
+          <t>0.0800</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1531,12 +1527,12 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>421.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>480.00฿</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1547,7 +1543,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>113348267192</t>
+          <t>113350746029#3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1557,38 +1553,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>UN-INV260921-00019</t>
+          <t>UN-INV260924-00056</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18795-2-6</t>
+ รถ lot18799-6-31</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>19.50</t>
+          <t>10.90</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.0505</t>
+          <t>0.0377</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1603,14 +1599,10 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>303.00฿</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>补胎胶片</t>
-        </is>
-      </c>
+          <t>226.20฿</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1618,7 +1610,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ZY202472578299</t>
+          <t>113350746029#2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1628,60 +1620,56 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>UN-INV260918-00012</t>
+          <t>UN-INV260924-00056</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18758-7-43</t>
+ รถ lot18799-6-30</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>47.40</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>0.1603</t>
+          <t>0.0101</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>225.00฿</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>961.20฿</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>补胎贴，3件</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1689,7 +1677,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>773440822655698</t>
+          <t>113350746029</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1699,38 +1687,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>UN-INV260918-00012</t>
+          <t>UN-INV260924-00056</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18758-4-31</t>
+ รถ lot18799-6-29</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>16.50</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>0.0022</t>
+          <t>0.0127</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1740,7 +1728,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>18.00฿</t>
+          <t>247.50฿</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1750,7 +1738,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>钻头</t>
+          <t>真空胎加固修理补片</t>
         </is>
       </c>
     </row>
@@ -1760,7 +1748,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>YT7642998390994</t>
+          <t>760246657062</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1770,38 +1758,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>UN-INV260918-00012</t>
+          <t>UN-INV260924-00056</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18769-3-57</t>
+ รถ lot18799-7-3</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>5.80</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0.0070</t>
+          <t>0.0005</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1811,17 +1799,17 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>87.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10.00฿</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>气门嘴，轮胎修补工具，气门芯宣传册</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1819,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>DPK212614057101</t>
+          <t>113348267192#2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1841,38 +1829,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>UN-INV260916-00003</t>
+          <t>UN-INV260921-00019</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18749-4-3</t>
+ รถ lot18795-2-7</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>9.60</t>
+          <t>28.10</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.0060</t>
+          <t>0.0628</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1882,7 +1870,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>144.00฿</t>
+          <t>421.50฿</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1890,11 +1878,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>轮胎气门嘴</t>
-        </is>
-      </c>
+      <c r="N21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1902,7 +1886,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>79031204783305</t>
+          <t>113348267192</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1912,38 +1896,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>UN-INV260916-00003</t>
+          <t>UN-INV260921-00019</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18744-6-15</t>
+ รถ lot18795-2-6</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>19.50</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.0020</t>
+          <t>0.0505</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1953,17 +1937,17 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>39.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>303.00฿</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>补胎胶片</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1957,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>435342988112655</t>
+          <t>ZY202472578299</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1983,43 +1967,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>UN-INV260916-00003</t>
+          <t>UN-INV260918-00012</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18743-3-34</t>
+ รถ lot18758-7-43</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>47.40</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.0014</t>
+          <t>0.1603</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2029,12 +2013,12 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>10.00฿</t>
+          <t>961.20฿</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>橡胶垫圈</t>
+          <t>补胎贴，3件</t>
         </is>
       </c>
     </row>
@@ -2044,7 +2028,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>435343890137834</t>
+          <t>773440822655698</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2054,38 +2038,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>UN-INV260916-00003</t>
+          <t>UN-INV260918-00012</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18743-7-25</t>
+ รถ lot18758-4-31</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>21.40</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.0080</t>
+          <t>0.0022</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2095,7 +2079,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>321.00฿</t>
+          <t>18.00฿</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2105,7 +2089,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>扒胎机包胶撬棍</t>
+          <t>钻头</t>
         </is>
       </c>
     </row>
@@ -2115,7 +2099,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>YT7642670434639</t>
+          <t>YT7642998390994</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2125,38 +2109,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>UN-INV260916-00003</t>
+          <t>UN-INV260918-00012</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18743-2-8</t>
+ รถ lot18769-3-57</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>5.80</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.0010</t>
+          <t>0.0070</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2166,7 +2150,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>12.00฿</t>
+          <t>87.00฿</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2176,7 +2160,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>片片</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -2186,7 +2170,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>93015797092</t>
+          <t>DPK212614057101</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2196,38 +2180,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>UN-INV260914-00014</t>
+          <t>UN-INV260916-00003</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18735-4-40</t>
+ รถ lot18749-4-3</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>12/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>8.60</t>
+          <t>9.60</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>0.0148</t>
+          <t>0.0060</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2237,7 +2221,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>129.00฿</t>
+          <t>144.00฿</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2247,7 +2231,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>仪表</t>
+          <t>轮胎气门嘴</t>
         </is>
       </c>
     </row>
@@ -2257,7 +2241,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>YT7642390374765</t>
+          <t>79031204783305</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2267,38 +2251,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>UN-INV260914-00015</t>
+          <t>UN-INV260916-00003</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18735-4-20</t>
+ รถ lot18744-6-15</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>12/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>20.80</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.0598</t>
+          <t>0.0020</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2308,17 +2292,17 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>39.00฿</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>358.80฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>打磨机</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -2328,7 +2312,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>435342255104130</t>
+          <t>435342988112655</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2338,18 +2322,18 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>UN-INV260914-00014</t>
+          <t>UN-INV260916-00003</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18735-43</t>
+ รถ lot18743-3-34</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2359,17 +2343,17 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>12/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>4.90</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.0172</t>
+          <t>0.0014</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2384,12 +2368,12 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>103.20฿</t>
+          <t>10.00฿</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>轮毂保护套</t>
+          <t>橡胶垫圈</t>
         </is>
       </c>
     </row>
@@ -2399,7 +2383,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>773440312345715</t>
+          <t>435343890137834</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2409,18 +2393,18 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>UN-INV260914-00014</t>
+          <t>UN-INV260916-00003</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18735-3-78</t>
+ รถ lot18743-7-25</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2430,17 +2414,17 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>12/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>21.40</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0.0013</t>
+          <t>0.0080</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2450,7 +2434,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>19.50฿</t>
+          <t>321.00฿</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2460,7 +2444,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>扒胎机包胶撬棍</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2454,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>773440291470393</t>
+          <t>YT7642670434639</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2480,18 +2464,18 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>UN-INV260914-00014</t>
+          <t>UN-INV260916-00003</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18735-34</t>
+ รถ lot18743-2-8</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2501,17 +2485,17 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>12/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.0029</t>
+          <t>0.0010</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2521,7 +2505,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>48.00฿</t>
+          <t>12.00฿</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2531,7 +2515,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>球阀</t>
+          <t>片片</t>
         </is>
       </c>
     </row>
@@ -2541,7 +2525,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>435342261175750</t>
+          <t>93015797092</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2551,13 +2535,13 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>UN-INV260914-00015</t>
+          <t>UN-INV260914-00014</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18736-13</t>
+ รถ lot18735-4-40</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2567,7 +2551,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2577,12 +2561,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>13.90</t>
+          <t>8.60</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.0137</t>
+          <t>0.0148</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2592,7 +2576,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>208.50฿</t>
+          <t>129.00฿</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2602,7 +2586,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>仪表</t>
         </is>
       </c>
     </row>
@@ -2612,7 +2596,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ZY202461195200</t>
+          <t>YT7642390374765</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2628,7 +2612,7 @@
       <c r="E32" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18728-7-13</t>
+ รถ lot18735-4-20</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2638,22 +2622,22 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>13/09/2026</t>
+          <t>12/09/2026</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>47.40</t>
+          <t>20.80</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.0116</t>
+          <t>0.0598</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2663,17 +2647,17 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>711.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>358.80฿</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>打磨机</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2667,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>79030687835952</t>
+          <t>435342255104130</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2699,7 +2683,7 @@
       <c r="E33" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18728-3-64</t>
+ รถ lot18735-43</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2709,22 +2693,22 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>13/09/2026</t>
+          <t>12/09/2026</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>4.30</t>
+          <t>4.90</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.0030</t>
+          <t>0.0172</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2734,17 +2718,17 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>64.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>103.20฿</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>接头配件</t>
+          <t>轮毂保护套</t>
         </is>
       </c>
     </row>
@@ -2754,7 +2738,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>LJ20722214#3</t>
+          <t>773440312345715</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2764,38 +2748,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>UN-INV260912-00011</t>
+          <t>UN-INV260914-00014</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18726-7-8</t>
+ รถ lot18735-3-78</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>12/09/2026</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>14.00</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.0171</t>
+          <t>0.0013</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2805,7 +2789,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>210.00฿</t>
+          <t>19.50฿</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2813,7 +2797,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>配件</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2821,7 +2809,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>LJ20722214#2</t>
+          <t>773440291470393</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2831,38 +2819,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>UN-INV260912-00011</t>
+          <t>UN-INV260914-00014</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18726-7-7</t>
+ รถ lot18735-34</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>12/09/2026</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>11.90</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.0089</t>
+          <t>0.0029</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2872,7 +2860,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>178.50฿</t>
+          <t>48.00฿</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2880,7 +2868,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>球阀</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2888,7 +2880,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>LJ20722214</t>
+          <t>435342261175750</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2898,38 +2890,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>UN-INV260912-00011</t>
+          <t>UN-INV260914-00015</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18726-7-6</t>
+ รถ lot18736-13</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>12/09/2026</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>16.00</t>
+          <t>13.90</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.0144</t>
+          <t>0.0137</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2939,7 +2931,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>240.00฿</t>
+          <t>208.50฿</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2949,7 +2941,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>电板套筒配件/3件</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -2959,7 +2951,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>YT7641966426761</t>
+          <t>ZY202461195200</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2969,38 +2961,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>UN-INV260912-00011</t>
+          <t>UN-INV260914-00015</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18714-9-23</t>
+ รถ lot18728-7-13</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>13/09/2026</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>13.60</t>
+          <t>47.40</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.0422</t>
+          <t>0.0116</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -3010,17 +3002,17 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>711.00฿</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>253.20฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>带表汽车轮胎打气嘴</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -3030,7 +3022,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ZY202471681117#2</t>
+          <t>79030687835952</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3040,38 +3032,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>UN-INV260912-00011</t>
+          <t>UN-INV260914-00014</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18714-9-8</t>
+ รถ lot18728-3-64</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>13/09/2026</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>11.80</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.0832</t>
+          <t>0.0030</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -3081,15 +3073,19 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>64.50฿</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>499.20฿</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>接头配件</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -3097,7 +3093,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>ZY202471681117</t>
+          <t>LJ20722214#3</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3113,17 +3109,17 @@
       <c r="E39" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18714-9-7</t>
+ รถ lot18726-7-8</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3133,12 +3129,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>7.70</t>
+          <t>14.00</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.0493</t>
+          <t>0.0171</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -3148,19 +3144,15 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>210.00฿</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>295.80฿</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>补胎胶片/2件</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -3168,7 +3160,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>302285502767#2</t>
+          <t>LJ20722214#2</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3184,17 +3176,17 @@
       <c r="E40" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18714-8-10</t>
+ รถ lot18726-7-7</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3204,12 +3196,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>33.70</t>
+          <t>11.90</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.0145</t>
+          <t>0.0089</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -3219,7 +3211,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>505.50฿</t>
+          <t>178.50฿</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -3235,7 +3227,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>302285502767</t>
+          <t>LJ20722214</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3251,17 +3243,17 @@
       <c r="E41" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18714-8-9</t>
+ รถ lot18726-7-6</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3271,12 +3263,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>23.40</t>
+          <t>16.00</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.0123</t>
+          <t>0.0144</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -3286,7 +3278,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>351.00฿</t>
+          <t>240.00฿</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -3296,7 +3288,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>扳手</t>
+          <t>电板套筒配件/3件</t>
         </is>
       </c>
     </row>
@@ -3306,7 +3298,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>LJ20716178#2</t>
+          <t>YT7641966426761</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3316,18 +3308,18 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>UN-INV260911-00013</t>
+          <t>UN-INV260912-00011</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18713-6-65</t>
+ รถ lot18714-9-23</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -3337,17 +3329,17 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>19.50</t>
+          <t>13.60</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.0075</t>
+          <t>0.0422</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3357,15 +3349,19 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>292.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
+          <t>253.20฿</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>带表汽车轮胎打气嘴</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -3373,7 +3369,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>LJ20716178</t>
+          <t>ZY202471681117#2</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3383,18 +3379,18 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>UN-INV260911-00013</t>
+          <t>UN-INV260912-00011</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18713-6-64</t>
+ รถ lot18714-9-8</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -3404,17 +3400,17 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>19.60</t>
+          <t>11.80</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.0075</t>
+          <t>0.0832</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3424,19 +3420,15 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>294.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>配件</t>
-        </is>
-      </c>
+          <t>499.20฿</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -3444,7 +3436,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>435338972466812</t>
+          <t>ZY202471681117</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3454,38 +3446,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>UN-INV260911-00013</t>
+          <t>UN-INV260912-00011</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18710-6-35</t>
+ รถ lot18714-9-7</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>13.10</t>
+          <t>7.70</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.0624</t>
+          <t>0.0493</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3500,12 +3492,12 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>374.40฿</t>
+          <t>295.80฿</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>修补工具</t>
+          <t>补胎胶片/2件</t>
         </is>
       </c>
     </row>
@@ -3515,7 +3507,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>435334324045675</t>
+          <t>302285502767#2</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3525,38 +3517,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>UN-INV260908-00009</t>
+          <t>UN-INV260912-00011</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18696-14</t>
+ รถ lot18714-8-10</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>10.80</t>
+          <t>33.70</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.0088</t>
+          <t>0.0145</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3566,7 +3558,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>162.00฿</t>
+          <t>505.50฿</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3574,11 +3566,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>配件</t>
-        </is>
-      </c>
+      <c r="N45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -3586,7 +3574,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>YT7641276428798</t>
+          <t>302285502767</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3596,38 +3584,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>UN-INV260908-00009</t>
+          <t>UN-INV260912-00011</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18697-11</t>
+ รถ lot18714-8-9</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>9.50</t>
+          <t>23.40</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>0.0296</t>
+          <t>0.0123</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3637,17 +3625,17 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>351.00฿</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>177.60฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>扳手</t>
         </is>
       </c>
     </row>
@@ -3657,7 +3645,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>79029430531776</t>
+          <t>LJ20716178#2</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3667,38 +3655,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>UN-INV260907-00015</t>
+          <t>UN-INV260911-00013</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18689-26</t>
+ รถ lot18713-6-65</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>19.50</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>0.0135</t>
+          <t>0.0075</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3708,19 +3696,15 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>292.50฿</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>81.00฿</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>卡套</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -3728,7 +3712,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>113282578128#2</t>
+          <t>LJ20716178</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3738,38 +3722,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>UN-INV260907-00015</t>
+          <t>UN-INV260911-00013</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18683-4</t>
+ รถ lot18713-6-64</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>38.00</t>
+          <t>19.60</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>0.1601</t>
+          <t>0.0075</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3779,15 +3763,19 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>294.00฿</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>960.60฿</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>配件</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -3795,7 +3783,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>113282578128</t>
+          <t>435338972466812</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3805,38 +3793,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>UN-INV260907-00015</t>
+          <t>UN-INV260911-00013</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18683-3</t>
+ รถ lot18710-6-35</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>27.50</t>
+          <t>13.10</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>0.1566</t>
+          <t>0.0624</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3851,12 +3839,12 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>939.60฿</t>
+          <t>374.40฿</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>压条取出器 一票两件破损件</t>
+          <t>修补工具</t>
         </is>
       </c>
     </row>
@@ -3866,7 +3854,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>82730128600#3</t>
+          <t>435334324045675</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3876,38 +3864,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>UN-INV260907-00015</t>
+          <t>UN-INV260908-00009</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18678-6-21</t>
+ รถ lot18696-14</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>30/08/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>33.00</t>
+          <t>10.80</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>0.0122</t>
+          <t>0.0088</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3917,7 +3905,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>495.00฿</t>
+          <t>162.00฿</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -3925,7 +3913,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>配件</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -3933,7 +3925,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>82730128600#2</t>
+          <t>YT7641276428798</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3943,38 +3935,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>UN-INV260907-00015</t>
+          <t>UN-INV260908-00009</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18678-6-20</t>
+ รถ lot18697-11</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>30/08/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>27.60</t>
+          <t>9.50</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>0.0095</t>
+          <t>0.0296</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3984,15 +3976,19 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>414.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
+          <t>177.60฿</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>配件</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -4000,7 +3996,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>82730128600</t>
+          <t>79029430531776</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -4016,17 +4012,17 @@
       <c r="E52" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18678-6-19</t>
+ รถ lot18689-26</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>30/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4036,12 +4032,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>28.10</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>0.0118</t>
+          <t>0.0135</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -4051,17 +4047,17 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>421.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>81.00฿</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>五金配件/3件</t>
+          <t>卡套</t>
         </is>
       </c>
     </row>
@@ -4071,7 +4067,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>113278387839#3</t>
+          <t>113282578128#2</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -4081,38 +4077,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>UN-INV260903-00023</t>
+          <t>UN-INV260907-00015</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18663-8-3</t>
+ รถ lot18683-4</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>25.30</t>
+          <t>38.00</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>0.0404</t>
+          <t>0.1601</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -4122,12 +4118,12 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>379.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>960.60฿</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
@@ -4138,7 +4134,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>113278387839#2</t>
+          <t>113282578128</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -4148,38 +4144,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>UN-INV260903-00023</t>
+          <t>UN-INV260907-00015</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18663-8-2</t>
+ รถ lot18683-3</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>26.10</t>
+          <t>27.50</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>0.0304</t>
+          <t>0.1566</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -4189,15 +4185,19 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>391.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
+          <t>939.60฿</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>压条取出器 一票两件破损件</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -4205,7 +4205,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>113278387839</t>
+          <t>82730128600#3</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -4215,38 +4215,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>UN-INV260903-00023</t>
+          <t>UN-INV260907-00015</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18663-8-1</t>
+ รถ lot18678-6-21</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>30/08/2026</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>9.10</t>
+          <t>33.00</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>0.0144</t>
+          <t>0.0122</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -4256,7 +4256,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>136.50฿</t>
+          <t>495.00฿</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -4264,11 +4264,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>配件/3件</t>
-        </is>
-      </c>
+      <c r="N55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -4276,7 +4272,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>113276098937#3</t>
+          <t>82730128600#2</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -4286,38 +4282,38 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>UN-INV260901-00057</t>
+          <t>UN-INV260907-00015</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-45</t>
+ รถ lot18678-6-20</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>30/08/2026</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>17.80</t>
+          <t>27.60</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>0.0302</t>
+          <t>0.0095</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -4327,7 +4323,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>267.00฿</t>
+          <t>414.00฿</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -4343,7 +4339,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>113276098937#2</t>
+          <t>82730128600</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -4353,38 +4349,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>UN-INV260901-00057</t>
+          <t>UN-INV260907-00015</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-44</t>
+ รถ lot18678-6-19</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>30/08/2026</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>10.90</t>
+          <t>28.10</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>0.0313</t>
+          <t>0.0118</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -4394,15 +4390,19 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>421.50฿</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>187.80฿</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>五金配件/3件</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -4410,7 +4410,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>113276098937</t>
+          <t>113278387839#3</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -4420,38 +4420,38 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>UN-INV260901-00057</t>
+          <t>UN-INV260903-00023</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-43</t>
+ รถ lot18663-8-3</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>33.60</t>
+          <t>25.30</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>0.0825</t>
+          <t>0.0404</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -4461,7 +4461,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>504.00฿</t>
+          <t>379.50฿</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -4469,11 +4469,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>补胎胶片+配件/3件</t>
-        </is>
-      </c>
+      <c r="N58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -4481,7 +4477,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ZY202464580877#4</t>
+          <t>113278387839#2</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4491,38 +4487,38 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>UN-INV260901-00057</t>
+          <t>UN-INV260903-00023</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-17</t>
+ รถ lot18663-8-2</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>20.10</t>
+          <t>26.10</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>0.0466</t>
+          <t>0.0304</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4532,7 +4528,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>301.50฿</t>
+          <t>391.50฿</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -4548,7 +4544,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ZY202464580877#7</t>
+          <t>113278387839</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4558,38 +4554,38 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>UN-INV260901-00057</t>
+          <t>UN-INV260903-00023</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-16</t>
+ รถ lot18663-8-1</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>16.60</t>
+          <t>9.10</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>0.0430</t>
+          <t>0.0144</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -4599,15 +4595,19 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>136.50฿</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>258.00฿</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>配件/3件</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -4615,7 +4615,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>ZY202464580877#2</t>
+          <t>113276098937#3</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4631,7 +4631,7 @@
       <c r="E61" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-15</t>
+ รถ lot18655-9-45</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>25.10</t>
+          <t>17.80</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>0.0483</t>
+          <t>0.0302</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>376.50฿</t>
+          <t>267.00฿</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>ZY202464580877#8</t>
+          <t>113276098937#2</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4698,7 +4698,7 @@
       <c r="E62" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-14</t>
+ รถ lot18655-9-44</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -4718,12 +4718,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>28.90</t>
+          <t>10.90</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>0.0800</t>
+          <t>0.0313</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>480.00฿</t>
+          <t>187.80฿</t>
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
@@ -4749,7 +4749,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>ZY202464580877#6</t>
+          <t>113276098937</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4765,7 +4765,7 @@
       <c r="E63" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-13</t>
+ รถ lot18655-9-43</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -4785,12 +4785,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>20.90</t>
+          <t>33.60</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>0.0534</t>
+          <t>0.0825</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -4800,15 +4800,19 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>504.00฿</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>320.40฿</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>补胎胶片+配件/3件</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -4816,7 +4820,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>ZY202464580877#5</t>
+          <t>ZY202464580877#4</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4832,7 +4836,7 @@
       <c r="E64" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-12</t>
+ รถ lot18655-9-17</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -4852,12 +4856,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>26.20</t>
+          <t>20.10</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>0.0535</t>
+          <t>0.0466</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -4867,7 +4871,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>393.00฿</t>
+          <t>301.50฿</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -4883,7 +4887,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>ZY202464580877</t>
+          <t>ZY202464580877#7</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4899,7 +4903,7 @@
       <c r="E65" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-11</t>
+ รถ lot18655-9-16</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -4919,12 +4923,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>20.70</t>
+          <t>16.60</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>0.0531</t>
+          <t>0.0430</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -4939,7 +4943,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>318.60฿</t>
+          <t>258.00฿</t>
         </is>
       </c>
       <c r="N65" t="inlineStr"/>
@@ -4950,7 +4954,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>ZY202464580877#9</t>
+          <t>ZY202464580877#2</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4966,7 +4970,7 @@
       <c r="E66" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-10</t>
+ รถ lot18655-9-15</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -4986,12 +4990,12 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>27.70</t>
+          <t>25.10</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>0.0800</t>
+          <t>0.0483</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -5001,12 +5005,12 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>376.50฿</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>480.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N66" t="inlineStr"/>
@@ -5017,7 +5021,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>ZY202464580877#3</t>
+          <t>ZY202464580877#8</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -5033,7 +5037,7 @@
       <c r="E67" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-9</t>
+ รถ lot18655-9-14</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -5053,12 +5057,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>27.10</t>
+          <t>28.90</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>0.0567</t>
+          <t>0.0800</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -5068,19 +5072,15 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>406.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr">
-        <is>
-          <t>补胎胶片/9件</t>
-        </is>
-      </c>
+          <t>480.00฿</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -5088,7 +5088,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>S71090288685</t>
+          <t>ZY202464580877#6</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -5098,38 +5098,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>UN-INV260831-00017</t>
+          <t>UN-INV260901-00057</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18634-7-3</t>
+ รถ lot18655-9-13</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>29/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>12.10</t>
+          <t>20.90</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>0.0240</t>
+          <t>0.0534</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -5139,19 +5139,15 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>181.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>配件</t>
-        </is>
-      </c>
+          <t>320.40฿</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -5159,7 +5155,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>YT7638092409979</t>
+          <t>ZY202464580877#5</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -5169,38 +5165,38 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>UN-INV260822-00010</t>
+          <t>UN-INV260901-00057</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18569-7-7</t>
+ รถ lot18655-9-12</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>16/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>16/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>15.00</t>
+          <t>26.20</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>0.0140</t>
+          <t>0.0535</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -5210,7 +5206,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>225.00฿</t>
+          <t>393.00฿</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -5218,11 +5214,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N69" t="inlineStr">
-        <is>
-          <t>配件</t>
-        </is>
-      </c>
+      <c r="N69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -5230,7 +5222,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>435308000517585</t>
+          <t>ZY202464580877</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -5240,38 +5232,38 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>UN-INV260822-00010</t>
+          <t>UN-INV260901-00057</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18550-6-11</t>
+ รถ lot18655-9-11</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>20.70</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>0.0032</t>
+          <t>0.0531</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -5281,19 +5273,15 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>54.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t>气门嘴</t>
-        </is>
-      </c>
+          <t>318.60฿</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -5301,7 +5289,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>710094401487</t>
+          <t>ZY202464580877#9</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -5311,43 +5299,43 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>UN-INV260822-00010</t>
+          <t>UN-INV260901-00057</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18544-8-14</t>
+ รถ lot18655-9-10</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>107.10</t>
+          <t>27.70</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>0.4536</t>
+          <t>0.0800</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -5357,14 +5345,10 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>2,721.60฿</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr">
-        <is>
-          <t>空的高压充气罐/一票10件，仓库实收到9件，已确认收到的9件先发</t>
-        </is>
-      </c>
+          <t>480.00฿</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -5372,7 +5356,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>773435675083665</t>
+          <t>ZY202464580877#3</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -5382,38 +5366,38 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>UN-INV260815-00046</t>
+          <t>UN-INV260901-00057</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18526-6-17</t>
+ รถ lot18655-9-9</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>13.10</t>
+          <t>27.10</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>0.0214</t>
+          <t>0.0567</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -5423,7 +5407,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>196.50฿</t>
+          <t>406.50฿</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -5433,7 +5417,7 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>补胎工具</t>
+          <t>补胎胶片/9件</t>
         </is>
       </c>
     </row>
@@ -5443,7 +5427,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>YT7637032206975</t>
+          <t>S71090288685</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -5453,38 +5437,38 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>UN-INV260819-00010</t>
+          <t>UN-INV260831-00017</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>มอก.
- รถ lot18523-6-30</t>
+          <t>ธรรมดา
+ รถ lot18634-7-3</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>16/08/2026</t>
+          <t>29/08/2026</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>9.60</t>
+          <t>12.10</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>0.0316</t>
+          <t>0.0240</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -5494,17 +5478,17 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>181.50฿</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>214.88฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>气动模具研磨机+配件</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -5514,7 +5498,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>ZY202466648481#5</t>
+          <t>YT7638092409979</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -5524,38 +5508,38 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>UN-INV260815-00046</t>
+          <t>UN-INV260822-00010</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18519-6-17</t>
+ รถ lot18569-7-7</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>16/08/2026</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>16/08/2026</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>15/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>16.10</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>0.0493</t>
+          <t>0.0140</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -5565,15 +5549,19 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>225.00฿</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>295.80฿</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>配件</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -5581,7 +5569,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>ZY202466648481#4</t>
+          <t>435308000517585</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -5591,38 +5579,38 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>UN-INV260815-00046</t>
+          <t>UN-INV260822-00010</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18519-6-16</t>
+ รถ lot18550-6-11</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>15/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>20.50</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>0.0656</t>
+          <t>0.0032</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -5632,15 +5620,19 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>54.00฿</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>393.60฿</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>气门嘴</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -5648,7 +5640,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>ZY202466648481#3</t>
+          <t>710094401487</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5658,43 +5650,43 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>UN-INV260815-00046</t>
+          <t>UN-INV260822-00010</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18519-6-15</t>
+ รถ lot18544-8-14</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>15/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>15.70</t>
+          <t>107.10</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>0.0508</t>
+          <t>0.4536</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -5704,10 +5696,14 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>304.80฿</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr"/>
+          <t>2,721.60฿</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>空的高压充气罐/一票10件，仓库实收到9件，已确认收到的9件先发</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -5715,7 +5711,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>ZY202466648481#2</t>
+          <t>773435675083665</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -5731,32 +5727,32 @@
       <c r="E77" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18519-6-14</t>
+ รถ lot18526-6-17</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>15/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>20.20</t>
+          <t>13.10</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>0.0660</t>
+          <t>0.0214</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -5766,15 +5762,19 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>196.50฿</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>396.00฿</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>补胎工具</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -5782,7 +5782,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>ZY202466648481</t>
+          <t>YT7637032206975</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -5792,13 +5792,13 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>UN-INV260815-00046</t>
+          <t>UN-INV260819-00010</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>ธรรมดา
- รถ lot18519-6-13</t>
+          <t>มอก.
+ รถ lot18523-6-30</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -5813,17 +5813,17 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>15/08/2026</t>
+          <t>16/08/2026</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>15.80</t>
+          <t>9.60</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>0.0522</t>
+          <t>0.0316</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>313.20฿</t>
+          <t>214.88฿</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>补胎胶条/5件</t>
+          <t>气动模具研磨机+配件</t>
         </is>
       </c>
     </row>
@@ -5853,7 +5853,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>113204676267#2</t>
+          <t>ZY202466648481#5</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -5869,32 +5869,32 @@
       <c r="E79" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18518-5-3</t>
+ รถ lot18519-6-17</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>15/08/2026</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>24.60</t>
+          <t>16.10</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>0.0608</t>
+          <t>0.0493</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -5904,12 +5904,12 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>369.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>295.80฿</t>
         </is>
       </c>
       <c r="N79" t="inlineStr"/>
@@ -5920,7 +5920,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>113204676267</t>
+          <t>ZY202466648481#4</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -5936,32 +5936,32 @@
       <c r="E80" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18518-5-2</t>
+ รถ lot18519-6-16</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>15/08/2026</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>25.00</t>
+          <t>20.50</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>0.0566</t>
+          <t>0.0656</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -5971,19 +5971,15 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>375.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr">
-        <is>
-          <t>真空胎冷补胶片</t>
-        </is>
-      </c>
+          <t>393.60฿</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -5991,7 +5987,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>910061892464#2</t>
+          <t>ZY202466648481#3</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -6007,32 +6003,32 @@
       <c r="E81" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18505-5-23</t>
+ รถ lot18519-6-15</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>15/08/2026</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>30.40</t>
+          <t>15.70</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>0.0523</t>
+          <t>0.0508</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -6042,12 +6038,12 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>456.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>304.80฿</t>
         </is>
       </c>
       <c r="N81" t="inlineStr"/>
@@ -6058,7 +6054,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>910061892464</t>
+          <t>ZY202466648481#2</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -6074,32 +6070,32 @@
       <c r="E82" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18505-5-22</t>
+ รถ lot18519-6-14</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>15/08/2026</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>15.90</t>
+          <t>20.20</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>0.0353</t>
+          <t>0.0660</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -6109,19 +6105,15 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>238.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr">
-        <is>
-          <t>记号蜡笔</t>
-        </is>
-      </c>
+          <t>396.00฿</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -6129,7 +6121,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>773434709817985</t>
+          <t>ZY202466648481</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -6139,38 +6131,38 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>UN-INV260819-00010</t>
+          <t>UN-INV260815-00046</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18535-8</t>
+ รถ lot18519-6-13</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>16/08/2026</t>
+          <t>15/08/2026</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>15.80</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>0.0184</t>
+          <t>0.0522</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -6185,12 +6177,12 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>110.40฿</t>
+          <t>313.20฿</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>锅具 二次包装货物变形</t>
+          <t>补胎胶条/5件</t>
         </is>
       </c>
     </row>
@@ -6200,7 +6192,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>435295775627304</t>
+          <t>113204676267#2</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -6210,38 +6202,38 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>UN-INV260811-00012</t>
+          <t>UN-INV260815-00046</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18492-2</t>
+ รถ lot18518-5-3</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>5.30</t>
+          <t>24.60</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>0.0090</t>
+          <t>0.0608</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -6251,7 +6243,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>79.50฿</t>
+          <t>369.00฿</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -6259,11 +6251,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N84" t="inlineStr">
-        <is>
-          <t>配件 破损件</t>
-        </is>
-      </c>
+      <c r="N84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -6271,7 +6259,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>YT7636332367470</t>
+          <t>113204676267</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -6281,38 +6269,38 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>UN-INV260811-00012</t>
+          <t>UN-INV260815-00046</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18487-2-27</t>
+ รถ lot18518-5-2</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>25.00</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>0.0004</t>
+          <t>0.0566</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -6322,17 +6310,17 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>375.00฿</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>10.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>立牌</t>
+          <t>真空胎冷补胶片</t>
         </is>
       </c>
     </row>
@@ -6342,7 +6330,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>S35386280517#2</t>
+          <t>910061892464#2</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -6352,38 +6340,38 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>UN-INV260811-00012</t>
+          <t>UN-INV260815-00046</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18475-24</t>
+ รถ lot18505-5-23</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>8.80</t>
+          <t>30.40</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>0.0045</t>
+          <t>0.0523</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -6393,7 +6381,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>132.00฿</t>
+          <t>456.00฿</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -6409,7 +6397,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>S35386280517</t>
+          <t>910061892464</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -6419,48 +6407,48 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>UN-INV260811-00012</t>
+          <t>UN-INV260815-00046</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18475-23</t>
+ รถ lot18505-5-22</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>103.50</t>
+          <t>15.90</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>0.2236</t>
+          <t>0.0353</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>1,552.50฿</t>
+          <t>238.50฿</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -6470,7 +6458,7 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>气门嘴 顺心捷达，一票16件</t>
+          <t>记号蜡笔</t>
         </is>
       </c>
     </row>
@@ -6480,7 +6468,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>YT7635787693833</t>
+          <t>773434709817985</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -6490,38 +6478,38 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>UN-INV260811-00012</t>
+          <t>UN-INV260819-00010</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18473-6-41</t>
+ รถ lot18535-8</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>16/08/2026</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>13.80</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>0.0432</t>
+          <t>0.0184</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -6536,12 +6524,12 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>259.20฿</t>
+          <t>110.40฿</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>气压表/面单没有代码</t>
+          <t>锅具 二次包装货物变形</t>
         </is>
       </c>
     </row>
@@ -6551,7 +6539,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>ZY202465806614</t>
+          <t>435295775627304</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -6561,38 +6549,38 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>UN-INV260807-00009</t>
+          <t>UN-INV260811-00012</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>มอก.
- รถ lot18466-5-51</t>
+          <t>ธรรมดา
+ รถ lot18492-2</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>11.30</t>
+          <t>5.30</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>0.0655</t>
+          <t>0.0090</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -6602,17 +6590,17 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>79.50฿</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>445.40฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>电子数显胎压枪</t>
+          <t>配件 破损件</t>
         </is>
       </c>
     </row>
@@ -6622,7 +6610,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>113177184579#7</t>
+          <t>YT7636332367470</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -6632,38 +6620,38 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>UN-INV260807-00009</t>
+          <t>UN-INV260811-00012</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-17</t>
+ รถ lot18487-2-27</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>9.70</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>0.0305</t>
+          <t>0.0004</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -6678,10 +6666,14 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>183.00฿</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr"/>
+          <t>10.00฿</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>立牌</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -6689,7 +6681,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>113177184579#5</t>
+          <t>S35386280517#2</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -6699,38 +6691,38 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>UN-INV260807-00009</t>
+          <t>UN-INV260811-00012</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-16</t>
+ รถ lot18475-24</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>15.00</t>
+          <t>8.80</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>0.0137</t>
+          <t>0.0045</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -6740,7 +6732,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>225.00฿</t>
+          <t>132.00฿</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -6756,7 +6748,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>113177184579#4</t>
+          <t>S35386280517</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -6766,56 +6758,60 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>UN-INV260807-00009</t>
+          <t>UN-INV260811-00012</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-15</t>
+ รถ lot18475-23</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>7.30</t>
+          <t>103.50</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>0.0235</t>
+          <t>0.2236</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1,552.50฿</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>141.00฿</t>
-        </is>
-      </c>
-      <c r="N92" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>气门嘴 顺心捷达，一票16件</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -6823,7 +6819,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>113177184579#3</t>
+          <t>YT7635787693833</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -6833,38 +6829,38 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>UN-INV260807-00009</t>
+          <t>UN-INV260811-00012</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-14</t>
+ รถ lot18473-6-41</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>11.90</t>
+          <t>13.80</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>0.0302</t>
+          <t>0.0432</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -6879,10 +6875,14 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>181.20฿</t>
-        </is>
-      </c>
-      <c r="N93" t="inlineStr"/>
+          <t>259.20฿</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>气压表/面单没有代码</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -6890,7 +6890,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>113177184579#6</t>
+          <t>ZY202465806614</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -6905,18 +6905,18 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>ธรรมดา
- รถ lot18463-13</t>
+          <t>มอก.
+ รถ lot18466-5-51</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6926,12 +6926,12 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>26.10</t>
+          <t>11.30</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>0.0673</t>
+          <t>0.0655</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -6946,10 +6946,14 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>403.80฿</t>
-        </is>
-      </c>
-      <c r="N94" t="inlineStr"/>
+          <t>445.40฿</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>电子数显胎压枪</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -6957,7 +6961,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>435289604798626</t>
+          <t>113177184579#7</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -6973,7 +6977,7 @@
       <c r="E95" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18462-6-6</t>
+ รถ lot18463-17</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -6983,7 +6987,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6993,12 +6997,12 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>9.60</t>
+          <t>9.70</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>0.0090</t>
+          <t>0.0305</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -7008,19 +7012,15 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>144.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr">
-        <is>
-          <t>螺丝配件</t>
-        </is>
-      </c>
+          <t>183.00฿</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -7028,7 +7028,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>113177184579#2</t>
+          <t>113177184579#5</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -7044,7 +7044,7 @@
       <c r="E96" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-12</t>
+ รถ lot18463-16</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -7064,12 +7064,12 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>5.30</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>0.0635</t>
+          <t>0.0137</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -7079,12 +7079,12 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>225.00฿</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>381.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N96" t="inlineStr"/>
@@ -7095,7 +7095,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>113177184579</t>
+          <t>113177184579#4</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -7111,7 +7111,7 @@
       <c r="E97" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-11</t>
+ รถ lot18463-15</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -7131,12 +7131,12 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>13.30</t>
+          <t>7.30</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>0.1176</t>
+          <t>0.0235</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -7151,14 +7151,10 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>705.60฿</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr">
-        <is>
-          <t>蘑菇钉补胎贴</t>
-        </is>
-      </c>
+          <t>141.00฿</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -7166,7 +7162,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>435289604798722</t>
+          <t>113177184579#3</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -7182,7 +7178,7 @@
       <c r="E98" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18462-3</t>
+ รถ lot18463-14</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -7192,7 +7188,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -7202,12 +7198,12 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>4.30</t>
+          <t>11.90</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>0.0029</t>
+          <t>0.0302</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -7217,19 +7213,15 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>64.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr">
-        <is>
-          <t>气门嘴</t>
-        </is>
-      </c>
+          <t>181.20฿</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -7237,7 +7229,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>ZY202471573119#2</t>
+          <t>113177184579#6</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -7253,7 +7245,7 @@
       <c r="E99" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-6</t>
+ รถ lot18463-13</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -7273,12 +7265,12 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>8.70</t>
+          <t>26.10</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>0.0441</t>
+          <t>0.0673</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -7293,7 +7285,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>264.60฿</t>
+          <t>403.80฿</t>
         </is>
       </c>
       <c r="N99" t="inlineStr"/>
@@ -7304,7 +7296,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>ZY202471573119</t>
+          <t>435289604798626</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -7320,7 +7312,7 @@
       <c r="E100" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-5</t>
+ รถ lot18462-6-6</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -7330,7 +7322,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -7340,12 +7332,12 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>11.90</t>
+          <t>9.60</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>0.0832</t>
+          <t>0.0090</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -7355,17 +7347,17 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>144.00฿</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>499.20฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>蘑菇钉补胎</t>
+          <t>螺丝配件</t>
         </is>
       </c>
     </row>
@@ -7375,7 +7367,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>YT7635427281240</t>
+          <t>113177184579#2</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -7391,7 +7383,7 @@
       <c r="E101" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18458-21</t>
+ รถ lot18463-12</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -7411,12 +7403,12 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>5.30</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>0.0117</t>
+          <t>0.0635</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -7431,14 +7423,10 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>70.20฿</t>
-        </is>
-      </c>
-      <c r="N101" t="inlineStr">
-        <is>
-          <t>气阀</t>
-        </is>
-      </c>
+          <t>381.00฿</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/cargo_packages_p1-5.xlsx
+++ b/cargo_packages_p1-5.xlsx
@@ -522,7 +522,7 @@
       <c r="E2" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18917-7-7</t>
+ รถ lot18919-2-7</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -532,7 +532,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -589,7 +589,7 @@
       <c r="E3" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18917-7-6</t>
+ รถ lot18919-2-6</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -599,7 +599,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -656,7 +656,7 @@
       <c r="E4" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18917-7-5</t>
+ รถ lot18919-2-5</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -723,7 +723,7 @@
       <c r="E5" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18917-7-4</t>
+ รถ lot18919-2-4</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -733,7 +733,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -790,7 +790,7 @@
       <c r="E6" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18917-7-3</t>
+ รถ lot18919-2-3</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -800,7 +800,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">

--- a/cargo_packages_p1-5.xlsx
+++ b/cargo_packages_p1-5.xlsx
@@ -1152,7 +1152,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">

--- a/cargo_packages_p1-5.xlsx
+++ b/cargo_packages_p1-5.xlsx
@@ -876,7 +876,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">

--- a/cargo_packages_p1-5.xlsx
+++ b/cargo_packages_p1-5.xlsx
@@ -855,7 +855,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>UN-INV261005-00021</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>UN-INV261005-00021</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>UN-INV261005-00021</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1060,7 +1060,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>UN-INV261005-00021</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>UN-INV261005-00021</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">

--- a/cargo_packages_p1-5.xlsx
+++ b/cargo_packages_p1-5.xlsx
@@ -537,7 +537,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -604,7 +604,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -805,7 +805,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">

--- a/cargo_packages_p1-5.xlsx
+++ b/cargo_packages_p1-5.xlsx
@@ -516,7 +516,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>UN-INV261008-00007</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -583,7 +583,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>UN-INV261008-00007</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>UN-INV261008-00007</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>UN-INV261008-00007</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>UN-INV261008-00007</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">

--- a/cargo_packages_p1-5.xlsx
+++ b/cargo_packages_p1-5.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ZY202466680891#5</t>
+          <t>435387211695084</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -516,38 +516,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>UN-INV261008-00007</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18919-2-7</t>
+ รถ lot18966-4-53</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>19.70</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.0715</t>
+          <t>0.0116</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -562,10 +562,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>429.00฿</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>69.60฿</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>宠物用品</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -573,7 +577,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ZY202466680891#4</t>
+          <t>ZY202466680891#5</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -589,7 +593,7 @@
       <c r="E3" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18919-2-6</t>
+ รถ lot18919-2-7</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -609,12 +613,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>20.00</t>
+          <t>19.70</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.0640</t>
+          <t>0.0715</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -629,7 +633,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>384.00฿</t>
+          <t>429.00฿</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -640,7 +644,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ZY202466680891#3</t>
+          <t>ZY202466680891#4</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -656,7 +660,7 @@
       <c r="E4" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18919-2-5</t>
+ รถ lot18919-2-6</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -676,12 +680,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>15.80</t>
+          <t>20.00</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.0492</t>
+          <t>0.0640</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -696,7 +700,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>295.20฿</t>
+          <t>384.00฿</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -707,7 +711,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ZY202466680891#2</t>
+          <t>ZY202466680891#3</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -723,7 +727,7 @@
       <c r="E5" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18919-2-4</t>
+ รถ lot18919-2-5</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -743,7 +747,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>16.20</t>
+          <t>15.80</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -774,7 +778,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ZY202466680891</t>
+          <t>ZY202466680891#2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -790,7 +794,7 @@
       <c r="E6" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18919-2-3</t>
+ รถ lot18919-2-4</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -810,7 +814,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>15.90</t>
+          <t>16.20</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -833,11 +837,7 @@
           <t>295.20฿</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>补胎胶片/5件</t>
-        </is>
-      </c>
+      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -845,7 +845,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>S35386291018</t>
+          <t>ZY202466680891</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -855,58 +855,58 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>UN-INV261005-00021</t>
+          <t>UN-INV261008-00007</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18901-6-32</t>
+ รถ lot18919-2-3</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>82.80</t>
+          <t>15.90</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.1641</t>
+          <t>0.0492</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>1,242.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>295.20฿</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>配件，12件</t>
+          <t>补胎胶片/5件</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>113405301091#3</t>
+          <t>S35386291018</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -932,7 +932,7 @@
       <c r="E8" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18901-7-3</t>
+ รถ lot18901-6-32</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -952,30 +952,34 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>13.10</t>
+          <t>82.80</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.0347</t>
+          <t>0.1641</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1,242.00฿</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>208.20฿</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>配件，12件</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -983,7 +987,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>113405301091#2</t>
+          <t>113405301091#3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -999,7 +1003,7 @@
       <c r="E9" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18901-7-2</t>
+ รถ lot18901-7-3</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1019,12 +1023,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>16.10</t>
+          <t>13.10</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.0397</t>
+          <t>0.0347</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1034,12 +1038,12 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>241.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>208.20฿</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1050,7 +1054,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>113405301091</t>
+          <t>113405301091#2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1066,7 +1070,7 @@
       <c r="E10" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18901-7-1</t>
+ รถ lot18901-7-2</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1086,12 +1090,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>33.60</t>
+          <t>16.10</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.0832</t>
+          <t>0.0397</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1101,7 +1105,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>504.00฿</t>
+          <t>241.50฿</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1109,11 +1113,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>补胎胶片/3件</t>
-        </is>
-      </c>
+      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>YT7646197126750</t>
+          <t>113405301091</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1137,32 +1137,32 @@
       <c r="E11" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18887-50</t>
+ รถ lot18901-7-1</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>26/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>26/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>8.30</t>
+          <t>33.60</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.0127</t>
+          <t>0.0832</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>124.50฿</t>
+          <t>504.00฿</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>补胎胶片/3件</t>
         </is>
       </c>
     </row>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ZY202462495078</t>
+          <t>YT7646197126750</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1202,38 +1202,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>UN-INV260926-00006</t>
+          <t>UN-INV261005-00021</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18844-9-4</t>
+ รถ lot18887-50</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>26/09/2026</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>26/09/2026</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>14.30</t>
+          <t>8.30</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0.0624</t>
+          <t>0.0127</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1243,17 +1243,17 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>124.50฿</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>374.40฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>胎压表</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>S71749075994</t>
+          <t>ZY202462495078</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1273,38 +1273,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>UN-INV260924-00056</t>
+          <t>UN-INV260926-00006</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18830-6-30</t>
+ รถ lot18844-9-4</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>119.00</t>
+          <t>14.30</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0.2302</t>
+          <t>0.0624</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1314,17 +1314,17 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>1,785.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>374.40฿</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>真空胎扒胎机配件/木箱</t>
+          <t>胎压表</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>435358249576981</t>
+          <t>S71749075994</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1350,17 +1350,17 @@
       <c r="E14" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18815-4-6</t>
+ รถ lot18830-6-30</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1370,12 +1370,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>5.20</t>
+          <t>119.00</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.0044</t>
+          <t>0.2302</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1385,7 +1385,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>78.00฿</t>
+          <t>1,785.00฿</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>气门嘴</t>
+          <t>真空胎扒胎机配件/木箱</t>
         </is>
       </c>
     </row>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>S71195667064</t>
+          <t>435358249576981</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1421,12 +1421,12 @@
       <c r="E15" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18810-6-3</t>
+ รถ lot18815-4-6</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1436,37 +1436,37 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>165.00</t>
+          <t>5.20</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.8568</t>
+          <t>0.0044</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>78.00฿</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>5,140.80฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>千斤顶，3件，客户不打木架发</t>
+          <t>气门嘴</t>
         </is>
       </c>
     </row>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>113350746029#4</t>
+          <t>S71195667064</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1492,17 +1492,17 @@
       <c r="E16" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18799-6-32</t>
+ รถ lot18810-6-3</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1512,17 +1512,17 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>27.70</t>
+          <t>165.00</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>0.0800</t>
+          <t>0.8568</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1532,10 +1532,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>480.00฿</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+          <t>5,140.80฿</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>千斤顶，3件，客户不打木架发</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1543,7 +1547,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>113350746029#3</t>
+          <t>113350746029#4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1559,7 +1563,7 @@
       <c r="E17" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18799-6-31</t>
+ รถ lot18799-6-32</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1579,12 +1583,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>10.90</t>
+          <t>27.70</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.0377</t>
+          <t>0.0800</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1599,7 +1603,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>226.20฿</t>
+          <t>480.00฿</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -1610,7 +1614,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>113350746029#2</t>
+          <t>113350746029#3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1626,7 +1630,7 @@
       <c r="E18" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18799-6-30</t>
+ รถ lot18799-6-31</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1646,12 +1650,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>15.00</t>
+          <t>10.90</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>0.0101</t>
+          <t>0.0377</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1661,12 +1665,12 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>225.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>226.20฿</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -1677,7 +1681,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>113350746029</t>
+          <t>113350746029#2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1693,7 +1697,7 @@
       <c r="E19" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18799-6-29</t>
+ รถ lot18799-6-30</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1713,12 +1717,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>16.50</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>0.0127</t>
+          <t>0.0101</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1728,7 +1732,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>247.50฿</t>
+          <t>225.00฿</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1736,11 +1740,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>真空胎加固修理补片</t>
-        </is>
-      </c>
+      <c r="N19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1748,7 +1748,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>760246657062</t>
+          <t>113350746029</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1764,7 +1764,7 @@
       <c r="E20" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18799-7-3</t>
+ รถ lot18799-6-29</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1784,12 +1784,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>16.50</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0.0005</t>
+          <t>0.0127</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1799,17 +1799,17 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>247.50฿</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>10.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>气门嘴，轮胎修补工具，气门芯宣传册</t>
+          <t>真空胎加固修理补片</t>
         </is>
       </c>
     </row>
@@ -1819,7 +1819,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>113348267192#2</t>
+          <t>760246657062</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1829,38 +1829,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>UN-INV260921-00019</t>
+          <t>UN-INV260924-00056</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18795-2-7</t>
+ รถ lot18799-7-3</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>28.10</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.0628</t>
+          <t>0.0005</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1870,15 +1870,19 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>421.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
+          <t>10.00฿</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>气门嘴，轮胎修补工具，气门芯宣传册</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1886,7 +1890,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>113348267192</t>
+          <t>113348267192#2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1902,7 +1906,7 @@
       <c r="E22" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18795-2-6</t>
+ รถ lot18795-2-7</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1922,12 +1926,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>19.50</t>
+          <t>28.10</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.0505</t>
+          <t>0.0628</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1937,19 +1941,15 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>421.50฿</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>303.00฿</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>补胎胶片</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ZY202472578299</t>
+          <t>113348267192</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1967,43 +1967,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>UN-INV260918-00012</t>
+          <t>UN-INV260921-00019</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18758-7-43</t>
+ รถ lot18795-2-6</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>47.40</t>
+          <t>19.50</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.1603</t>
+          <t>0.0505</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2013,12 +2013,12 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>961.20฿</t>
+          <t>303.00฿</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>补胎贴，3件</t>
+          <t>补胎胶片</t>
         </is>
       </c>
     </row>
@@ -2028,7 +2028,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>773440822655698</t>
+          <t>ZY202472578299</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2044,7 +2044,7 @@
       <c r="E24" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18758-4-31</t>
+ รถ lot18758-7-43</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2064,32 +2064,32 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>47.40</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.0022</t>
+          <t>0.1603</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>18.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>961.20฿</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>钻头</t>
+          <t>补胎贴，3件</t>
         </is>
       </c>
     </row>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>YT7642998390994</t>
+          <t>773440822655698</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2115,7 +2115,7 @@
       <c r="E25" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18769-3-57</t>
+ รถ lot18758-4-31</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>5.80</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.0070</t>
+          <t>0.0022</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>87.00฿</t>
+          <t>18.00฿</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>钻头</t>
         </is>
       </c>
     </row>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>DPK212614057101</t>
+          <t>YT7642998390994</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2180,38 +2180,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>UN-INV260916-00003</t>
+          <t>UN-INV260918-00012</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18749-4-3</t>
+ รถ lot18769-3-57</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>9.60</t>
+          <t>5.80</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>0.0060</t>
+          <t>0.0070</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2221,7 +2221,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>144.00฿</t>
+          <t>87.00฿</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>轮胎气门嘴</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -2241,7 +2241,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>79031204783305</t>
+          <t>DPK212614057101</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2257,7 +2257,7 @@
       <c r="E27" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18744-6-15</t>
+ รถ lot18749-4-3</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>9.60</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.0020</t>
+          <t>0.0060</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2292,7 +2292,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>39.00฿</t>
+          <t>144.00฿</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>轮胎气门嘴</t>
         </is>
       </c>
     </row>
@@ -2312,7 +2312,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>435342988112655</t>
+          <t>79031204783305</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2328,17 +2328,17 @@
       <c r="E28" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18743-3-34</t>
+ รถ lot18744-6-15</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2348,12 +2348,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.0014</t>
+          <t>0.0020</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2363,17 +2363,17 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>39.00฿</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>10.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>橡胶垫圈</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>435343890137834</t>
+          <t>435342988112655</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2399,7 +2399,7 @@
       <c r="E29" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18743-7-25</t>
+ รถ lot18743-3-34</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2419,12 +2419,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>21.40</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0.0080</t>
+          <t>0.0014</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2434,17 +2434,17 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>321.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10.00฿</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>扒胎机包胶撬棍</t>
+          <t>橡胶垫圈</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>YT7642670434639</t>
+          <t>435343890137834</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2470,7 +2470,7 @@
       <c r="E30" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18743-2-8</t>
+ รถ lot18743-7-25</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>21.40</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.0010</t>
+          <t>0.0080</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>12.00฿</t>
+          <t>321.00฿</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>片片</t>
+          <t>扒胎机包胶撬棍</t>
         </is>
       </c>
     </row>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>93015797092</t>
+          <t>YT7642670434639</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2535,18 +2535,18 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>UN-INV260914-00014</t>
+          <t>UN-INV260916-00003</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18735-4-40</t>
+ รถ lot18743-2-8</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2556,17 +2556,17 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>12/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>8.60</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.0148</t>
+          <t>0.0010</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>129.00฿</t>
+          <t>12.00฿</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>仪表</t>
+          <t>片片</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>YT7642390374765</t>
+          <t>93015797092</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2606,13 +2606,13 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>UN-INV260914-00015</t>
+          <t>UN-INV260914-00014</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18735-4-20</t>
+ รถ lot18735-4-40</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>20.80</t>
+          <t>8.60</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.0598</t>
+          <t>0.0148</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2647,17 +2647,17 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>129.00฿</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>358.80฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>打磨机</t>
+          <t>仪表</t>
         </is>
       </c>
     </row>
@@ -2667,7 +2667,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>435342255104130</t>
+          <t>YT7642390374765</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2677,13 +2677,13 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>UN-INV260914-00014</t>
+          <t>UN-INV260914-00015</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18735-43</t>
+ รถ lot18735-4-20</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2703,12 +2703,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>4.90</t>
+          <t>20.80</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.0172</t>
+          <t>0.0598</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2723,12 +2723,12 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>103.20฿</t>
+          <t>358.80฿</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>轮毂保护套</t>
+          <t>打磨机</t>
         </is>
       </c>
     </row>
@@ -2738,7 +2738,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>773440312345715</t>
+          <t>435342255104130</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2754,7 +2754,7 @@
       <c r="E34" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18735-3-78</t>
+ รถ lot18735-43</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2774,12 +2774,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>4.90</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.0013</t>
+          <t>0.0172</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2789,17 +2789,17 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>19.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>103.20฿</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>轮毂保护套</t>
         </is>
       </c>
     </row>
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>773440291470393</t>
+          <t>773440312345715</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2825,7 +2825,7 @@
       <c r="E35" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18735-34</t>
+ รถ lot18735-3-78</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2845,12 +2845,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.0029</t>
+          <t>0.0013</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2860,7 +2860,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>48.00฿</t>
+          <t>19.50฿</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>球阀</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -2880,7 +2880,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>435342261175750</t>
+          <t>773440291470393</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2890,13 +2890,13 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>UN-INV260914-00015</t>
+          <t>UN-INV260914-00014</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18736-13</t>
+ รถ lot18735-34</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>13.90</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.0137</t>
+          <t>0.0029</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>208.50฿</t>
+          <t>48.00฿</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2941,7 +2941,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>球阀</t>
         </is>
       </c>
     </row>
@@ -2951,7 +2951,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>ZY202461195200</t>
+          <t>435342261175750</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2967,7 +2967,7 @@
       <c r="E37" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18728-7-13</t>
+ รถ lot18736-13</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2982,17 +2982,17 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>13/09/2026</t>
+          <t>12/09/2026</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>47.40</t>
+          <t>13.90</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.0116</t>
+          <t>0.0137</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>711.00฿</t>
+          <t>208.50฿</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3022,7 +3022,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>79030687835952</t>
+          <t>ZY202461195200</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3032,13 +3032,13 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>UN-INV260914-00014</t>
+          <t>UN-INV260914-00015</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18728-3-64</t>
+ รถ lot18728-7-13</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>4.30</t>
+          <t>47.40</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.0030</t>
+          <t>0.0116</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -3073,7 +3073,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>64.50฿</t>
+          <t>711.00฿</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3083,7 +3083,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>接头配件</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -3093,7 +3093,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>LJ20722214#3</t>
+          <t>79030687835952</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3103,38 +3103,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>UN-INV260912-00011</t>
+          <t>UN-INV260914-00014</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18726-7-8</t>
+ รถ lot18728-3-64</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>13/09/2026</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>14.00</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.0171</t>
+          <t>0.0030</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -3144,7 +3144,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>210.00฿</t>
+          <t>64.50฿</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3152,7 +3152,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>接头配件</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -3160,7 +3164,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>LJ20722214#2</t>
+          <t>LJ20722214#3</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3176,7 +3180,7 @@
       <c r="E40" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18726-7-7</t>
+ รถ lot18726-7-8</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -3196,12 +3200,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>11.90</t>
+          <t>14.00</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.0089</t>
+          <t>0.0171</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -3211,7 +3215,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>178.50฿</t>
+          <t>210.00฿</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -3227,7 +3231,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>LJ20722214</t>
+          <t>LJ20722214#2</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3243,7 +3247,7 @@
       <c r="E41" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18726-7-6</t>
+ รถ lot18726-7-7</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -3263,12 +3267,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>16.00</t>
+          <t>11.90</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.0144</t>
+          <t>0.0089</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -3278,7 +3282,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>240.00฿</t>
+          <t>178.50฿</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -3286,11 +3290,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>电板套筒配件/3件</t>
-        </is>
-      </c>
+      <c r="N41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -3298,7 +3298,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>YT7641966426761</t>
+          <t>LJ20722214</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3314,17 +3314,17 @@
       <c r="E42" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18714-9-23</t>
+ รถ lot18726-7-6</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3334,12 +3334,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>13.60</t>
+          <t>16.00</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.0422</t>
+          <t>0.0144</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3349,17 +3349,17 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>240.00฿</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>253.20฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>带表汽车轮胎打气嘴</t>
+          <t>电板套筒配件/3件</t>
         </is>
       </c>
     </row>
@@ -3369,7 +3369,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ZY202471681117#2</t>
+          <t>YT7641966426761</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3385,7 +3385,7 @@
       <c r="E43" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18714-9-8</t>
+ รถ lot18714-9-23</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -3405,12 +3405,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>11.80</t>
+          <t>13.60</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.0832</t>
+          <t>0.0422</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3425,10 +3425,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>499.20฿</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
+          <t>253.20฿</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>带表汽车轮胎打气嘴</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -3436,7 +3440,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ZY202471681117</t>
+          <t>ZY202471681117#2</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3452,7 +3456,7 @@
       <c r="E44" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18714-9-7</t>
+ รถ lot18714-9-8</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -3472,12 +3476,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>7.70</t>
+          <t>11.80</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.0493</t>
+          <t>0.0832</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3492,14 +3496,10 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>295.80฿</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>补胎胶片/2件</t>
-        </is>
-      </c>
+          <t>499.20฿</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -3507,7 +3507,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>302285502767#2</t>
+          <t>ZY202471681117</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3523,7 +3523,7 @@
       <c r="E45" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18714-8-10</t>
+ รถ lot18714-9-7</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>33.70</t>
+          <t>7.70</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.0145</t>
+          <t>0.0493</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3558,15 +3558,19 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>505.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
+          <t>295.80฿</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>补胎胶片/2件</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -3574,7 +3578,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>302285502767</t>
+          <t>302285502767#2</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3590,7 +3594,7 @@
       <c r="E46" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18714-8-9</t>
+ รถ lot18714-8-10</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -3610,12 +3614,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>23.40</t>
+          <t>33.70</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>0.0123</t>
+          <t>0.0145</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3625,7 +3629,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>351.00฿</t>
+          <t>505.50฿</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3633,11 +3637,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>扳手</t>
-        </is>
-      </c>
+      <c r="N46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -3645,7 +3645,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>LJ20716178#2</t>
+          <t>302285502767</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3655,18 +3655,18 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>UN-INV260911-00013</t>
+          <t>UN-INV260912-00011</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18713-6-65</t>
+ รถ lot18714-8-9</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3676,17 +3676,17 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>19.50</t>
+          <t>23.40</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>0.0075</t>
+          <t>0.0123</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>292.50฿</t>
+          <t>351.00฿</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3704,7 +3704,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>扳手</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -3712,7 +3716,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>LJ20716178</t>
+          <t>LJ20716178#2</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3728,7 +3732,7 @@
       <c r="E48" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18713-6-64</t>
+ รถ lot18713-6-65</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -3748,7 +3752,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>19.60</t>
+          <t>19.50</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3763,7 +3767,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>294.00฿</t>
+          <t>292.50฿</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3771,11 +3775,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>配件</t>
-        </is>
-      </c>
+      <c r="N48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>435338972466812</t>
+          <t>LJ20716178</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3799,7 +3799,7 @@
       <c r="E49" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18710-6-35</t>
+ รถ lot18713-6-64</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3809,7 +3809,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>13.10</t>
+          <t>19.60</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>0.0624</t>
+          <t>0.0075</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3834,17 +3834,17 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>294.00฿</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>374.40฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>修补工具</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -3854,7 +3854,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>435334324045675</t>
+          <t>435338972466812</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3864,38 +3864,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>UN-INV260908-00009</t>
+          <t>UN-INV260911-00013</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18696-14</t>
+ รถ lot18710-6-35</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>10.80</t>
+          <t>13.10</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>0.0088</t>
+          <t>0.0624</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3905,17 +3905,17 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>162.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>374.40฿</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>修补工具</t>
         </is>
       </c>
     </row>
@@ -3925,7 +3925,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>YT7641276428798</t>
+          <t>435334324045675</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3941,7 +3941,7 @@
       <c r="E51" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18697-11</t>
+ รถ lot18696-14</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>9.50</t>
+          <t>10.80</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>0.0296</t>
+          <t>0.0088</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>162.00฿</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>177.60฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>79029430531776</t>
+          <t>YT7641276428798</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -4006,18 +4006,18 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>UN-INV260907-00015</t>
+          <t>UN-INV260908-00009</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18689-26</t>
+ รถ lot18697-11</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -4027,17 +4027,17 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>9.50</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>0.0135</t>
+          <t>0.0296</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -4052,12 +4052,12 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>81.00฿</t>
+          <t>177.60฿</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>卡套</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -4067,7 +4067,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>113282578128#2</t>
+          <t>79029430531776</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -4083,17 +4083,17 @@
       <c r="E53" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18683-4</t>
+ รถ lot18689-26</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -4103,12 +4103,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>38.00</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>0.1601</t>
+          <t>0.0135</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -4123,10 +4123,14 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>960.60฿</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
+          <t>81.00฿</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>卡套</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -4134,7 +4138,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>113282578128</t>
+          <t>113282578128#2</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -4150,7 +4154,7 @@
       <c r="E54" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18683-3</t>
+ รถ lot18683-4</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -4170,12 +4174,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>27.50</t>
+          <t>38.00</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>0.1566</t>
+          <t>0.1601</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -4190,14 +4194,10 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>939.60฿</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>压条取出器 一票两件破损件</t>
-        </is>
-      </c>
+          <t>960.60฿</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -4205,7 +4205,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>82730128600#3</t>
+          <t>113282578128</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -4221,12 +4221,12 @@
       <c r="E55" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18678-6-21</t>
+ รถ lot18683-3</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>30/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>33.00</t>
+          <t>27.50</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>0.0122</t>
+          <t>0.1566</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -4256,15 +4256,19 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>495.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
+          <t>939.60฿</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>压条取出器 一票两件破损件</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -4272,7 +4276,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>82730128600#2</t>
+          <t>82730128600#3</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -4288,7 +4292,7 @@
       <c r="E56" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18678-6-20</t>
+ รถ lot18678-6-21</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -4308,12 +4312,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>27.60</t>
+          <t>33.00</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>0.0095</t>
+          <t>0.0122</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -4323,7 +4327,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>414.00฿</t>
+          <t>495.00฿</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -4339,7 +4343,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>82730128600</t>
+          <t>82730128600#2</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -4355,7 +4359,7 @@
       <c r="E57" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18678-6-19</t>
+ รถ lot18678-6-20</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -4375,12 +4379,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>28.10</t>
+          <t>27.60</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>0.0118</t>
+          <t>0.0095</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -4390,7 +4394,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>421.50฿</t>
+          <t>414.00฿</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -4398,11 +4402,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>五金配件/3件</t>
-        </is>
-      </c>
+      <c r="N57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -4410,7 +4410,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>113278387839#3</t>
+          <t>82730128600</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -4420,38 +4420,38 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>UN-INV260903-00023</t>
+          <t>UN-INV260907-00015</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18663-8-3</t>
+ รถ lot18678-6-19</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>30/08/2026</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>25.30</t>
+          <t>28.10</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>0.0404</t>
+          <t>0.0118</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -4461,7 +4461,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>379.50฿</t>
+          <t>421.50฿</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -4469,7 +4469,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr"/>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>五金配件/3件</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -4477,7 +4481,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>113278387839#2</t>
+          <t>113278387839#3</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4493,7 +4497,7 @@
       <c r="E59" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18663-8-2</t>
+ รถ lot18663-8-3</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -4513,12 +4517,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>26.10</t>
+          <t>25.30</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>0.0304</t>
+          <t>0.0404</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4528,7 +4532,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>391.50฿</t>
+          <t>379.50฿</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -4544,7 +4548,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>113278387839</t>
+          <t>113278387839#2</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4560,7 +4564,7 @@
       <c r="E60" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18663-8-1</t>
+ รถ lot18663-8-2</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -4580,12 +4584,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>9.10</t>
+          <t>26.10</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>0.0144</t>
+          <t>0.0304</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -4595,7 +4599,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>136.50฿</t>
+          <t>391.50฿</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -4603,11 +4607,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>配件/3件</t>
-        </is>
-      </c>
+      <c r="N60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -4615,7 +4615,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>113276098937#3</t>
+          <t>113278387839</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4625,38 +4625,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>UN-INV260901-00057</t>
+          <t>UN-INV260903-00023</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-45</t>
+ รถ lot18663-8-1</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>17.80</t>
+          <t>9.10</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>0.0302</t>
+          <t>0.0144</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>267.00฿</t>
+          <t>136.50฿</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -4674,7 +4674,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr"/>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>配件/3件</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -4682,7 +4686,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>113276098937#2</t>
+          <t>113276098937#3</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4698,7 +4702,7 @@
       <c r="E62" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-44</t>
+ รถ lot18655-9-45</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -4718,12 +4722,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>10.90</t>
+          <t>17.80</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>0.0313</t>
+          <t>0.0302</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -4733,12 +4737,12 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>267.00฿</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>187.80฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
@@ -4749,7 +4753,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>113276098937</t>
+          <t>113276098937#2</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4765,7 +4769,7 @@
       <c r="E63" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-43</t>
+ รถ lot18655-9-44</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -4785,12 +4789,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>33.60</t>
+          <t>10.90</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>0.0825</t>
+          <t>0.0313</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -4800,19 +4804,15 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>504.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>补胎胶片+配件/3件</t>
-        </is>
-      </c>
+          <t>187.80฿</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -4820,7 +4820,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>ZY202464580877#4</t>
+          <t>113276098937</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4836,7 +4836,7 @@
       <c r="E64" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-17</t>
+ รถ lot18655-9-43</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -4856,12 +4856,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>20.10</t>
+          <t>33.60</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>0.0466</t>
+          <t>0.0825</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>301.50฿</t>
+          <t>504.00฿</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -4879,7 +4879,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N64" t="inlineStr"/>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>补胎胶片+配件/3件</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -4887,7 +4891,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>ZY202464580877#7</t>
+          <t>ZY202464580877#4</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4903,7 +4907,7 @@
       <c r="E65" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-16</t>
+ รถ lot18655-9-17</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -4923,12 +4927,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>16.60</t>
+          <t>20.10</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>0.0430</t>
+          <t>0.0466</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -4938,12 +4942,12 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>301.50฿</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>258.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N65" t="inlineStr"/>
@@ -4954,7 +4958,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>ZY202464580877#2</t>
+          <t>ZY202464580877#7</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4970,7 +4974,7 @@
       <c r="E66" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-15</t>
+ รถ lot18655-9-16</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -4990,12 +4994,12 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>25.10</t>
+          <t>16.60</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>0.0483</t>
+          <t>0.0430</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -5005,12 +5009,12 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>376.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>258.00฿</t>
         </is>
       </c>
       <c r="N66" t="inlineStr"/>
@@ -5021,7 +5025,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>ZY202464580877#8</t>
+          <t>ZY202464580877#2</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -5037,7 +5041,7 @@
       <c r="E67" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-14</t>
+ รถ lot18655-9-15</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -5057,12 +5061,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>28.90</t>
+          <t>25.10</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>0.0800</t>
+          <t>0.0483</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -5072,12 +5076,12 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>376.50฿</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>480.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N67" t="inlineStr"/>
@@ -5088,7 +5092,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>ZY202464580877#6</t>
+          <t>ZY202464580877#8</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -5104,7 +5108,7 @@
       <c r="E68" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-13</t>
+ รถ lot18655-9-14</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -5124,12 +5128,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>20.90</t>
+          <t>28.90</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>0.0534</t>
+          <t>0.0800</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -5144,7 +5148,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>320.40฿</t>
+          <t>480.00฿</t>
         </is>
       </c>
       <c r="N68" t="inlineStr"/>
@@ -5155,7 +5159,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>ZY202464580877#5</t>
+          <t>ZY202464580877#6</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -5171,7 +5175,7 @@
       <c r="E69" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-12</t>
+ รถ lot18655-9-13</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -5191,12 +5195,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>26.20</t>
+          <t>20.90</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>0.0535</t>
+          <t>0.0534</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -5206,12 +5210,12 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>393.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>320.40฿</t>
         </is>
       </c>
       <c r="N69" t="inlineStr"/>
@@ -5222,7 +5226,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>ZY202464580877</t>
+          <t>ZY202464580877#5</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -5238,7 +5242,7 @@
       <c r="E70" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-11</t>
+ รถ lot18655-9-12</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -5258,12 +5262,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>20.70</t>
+          <t>26.20</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>0.0531</t>
+          <t>0.0535</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -5273,12 +5277,12 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>393.00฿</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>318.60฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N70" t="inlineStr"/>
@@ -5289,7 +5293,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>ZY202464580877#9</t>
+          <t>ZY202464580877</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -5305,7 +5309,7 @@
       <c r="E71" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-10</t>
+ รถ lot18655-9-11</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -5325,12 +5329,12 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>27.70</t>
+          <t>20.70</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>0.0800</t>
+          <t>0.0531</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -5345,7 +5349,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>480.00฿</t>
+          <t>318.60฿</t>
         </is>
       </c>
       <c r="N71" t="inlineStr"/>
@@ -5356,7 +5360,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>ZY202464580877#3</t>
+          <t>ZY202464580877#9</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -5372,7 +5376,7 @@
       <c r="E72" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-9</t>
+ รถ lot18655-9-10</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -5392,12 +5396,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>27.10</t>
+          <t>27.70</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>0.0567</t>
+          <t>0.0800</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -5407,19 +5411,15 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>406.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr">
-        <is>
-          <t>补胎胶片/9件</t>
-        </is>
-      </c>
+          <t>480.00฿</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -5427,7 +5427,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>S71090288685</t>
+          <t>ZY202464580877#3</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -5437,38 +5437,38 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>UN-INV260831-00017</t>
+          <t>UN-INV260901-00057</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18634-7-3</t>
+ รถ lot18655-9-9</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>29/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>12.10</t>
+          <t>27.10</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>0.0240</t>
+          <t>0.0567</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -5478,7 +5478,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>181.50฿</t>
+          <t>406.50฿</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -5488,7 +5488,7 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>补胎胶片/9件</t>
         </is>
       </c>
     </row>
@@ -5498,7 +5498,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>YT7638092409979</t>
+          <t>S71090288685</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -5508,38 +5508,38 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>UN-INV260822-00010</t>
+          <t>UN-INV260831-00017</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18569-7-7</t>
+ รถ lot18634-7-3</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>16/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>16/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>29/08/2026</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>15.00</t>
+          <t>12.10</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>0.0140</t>
+          <t>0.0240</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -5549,7 +5549,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>225.00฿</t>
+          <t>181.50฿</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -5569,7 +5569,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>435308000517585</t>
+          <t>YT7638092409979</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -5585,32 +5585,32 @@
       <c r="E75" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18550-6-11</t>
+ รถ lot18569-7-7</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>16/08/2026</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>16/08/2026</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>0.0032</t>
+          <t>0.0140</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -5620,7 +5620,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>54.00฿</t>
+          <t>225.00฿</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -5630,7 +5630,7 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>气门嘴</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -5640,7 +5640,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>710094401487</t>
+          <t>435308000517585</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5656,17 +5656,17 @@
       <c r="E76" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18544-8-14</t>
+ รถ lot18550-6-11</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5676,32 +5676,32 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>107.10</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>0.4536</t>
+          <t>0.0032</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>54.00฿</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>2,721.60฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>空的高压充气罐/一票10件，仓库实收到9件，已确认收到的9件先发</t>
+          <t>气门嘴</t>
         </is>
       </c>
     </row>
@@ -5711,7 +5711,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>773435675083665</t>
+          <t>710094401487</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -5721,58 +5721,58 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>UN-INV260815-00046</t>
+          <t>UN-INV260822-00010</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18526-6-17</t>
+ รถ lot18544-8-14</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>13.10</t>
+          <t>107.10</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>0.0214</t>
+          <t>0.4536</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>196.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2,721.60฿</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>补胎工具</t>
+          <t>空的高压充气罐/一票10件，仓库实收到9件，已确认收到的9件先发</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>YT7637032206975</t>
+          <t>773435675083665</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -5792,38 +5792,38 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>UN-INV260819-00010</t>
+          <t>UN-INV260815-00046</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>มอก.
- รถ lot18523-6-30</t>
+          <t>ธรรมดา
+ รถ lot18526-6-17</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>16/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>9.60</t>
+          <t>13.10</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>0.0316</t>
+          <t>0.0214</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>196.50฿</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>214.88฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>气动模具研磨机+配件</t>
+          <t>补胎工具</t>
         </is>
       </c>
     </row>
@@ -5853,7 +5853,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>ZY202466648481#5</t>
+          <t>YT7637032206975</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -5863,13 +5863,13 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>UN-INV260815-00046</t>
+          <t>UN-INV260819-00010</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>ธรรมดา
- รถ lot18519-6-17</t>
+          <t>มอก.
+ รถ lot18523-6-30</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -5884,17 +5884,17 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>15/08/2026</t>
+          <t>16/08/2026</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>16.10</t>
+          <t>9.60</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>0.0493</t>
+          <t>0.0316</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -5909,10 +5909,14 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>295.80฿</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr"/>
+          <t>214.88฿</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>气动模具研磨机+配件</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -5920,7 +5924,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>ZY202466648481#4</t>
+          <t>ZY202466648481#5</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -5936,7 +5940,7 @@
       <c r="E80" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18519-6-16</t>
+ รถ lot18519-6-17</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -5956,12 +5960,12 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>20.50</t>
+          <t>16.10</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>0.0656</t>
+          <t>0.0493</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -5976,7 +5980,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>393.60฿</t>
+          <t>295.80฿</t>
         </is>
       </c>
       <c r="N80" t="inlineStr"/>
@@ -5987,7 +5991,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>ZY202466648481#3</t>
+          <t>ZY202466648481#4</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -6003,7 +6007,7 @@
       <c r="E81" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18519-6-15</t>
+ รถ lot18519-6-16</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -6023,12 +6027,12 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>15.70</t>
+          <t>20.50</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>0.0508</t>
+          <t>0.0656</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -6043,7 +6047,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>304.80฿</t>
+          <t>393.60฿</t>
         </is>
       </c>
       <c r="N81" t="inlineStr"/>
@@ -6054,7 +6058,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>ZY202466648481#2</t>
+          <t>ZY202466648481#3</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -6070,7 +6074,7 @@
       <c r="E82" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18519-6-14</t>
+ รถ lot18519-6-15</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -6090,12 +6094,12 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>20.20</t>
+          <t>15.70</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>0.0660</t>
+          <t>0.0508</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -6110,7 +6114,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>396.00฿</t>
+          <t>304.80฿</t>
         </is>
       </c>
       <c r="N82" t="inlineStr"/>
@@ -6121,7 +6125,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>ZY202466648481</t>
+          <t>ZY202466648481#2</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -6137,7 +6141,7 @@
       <c r="E83" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18519-6-13</t>
+ รถ lot18519-6-14</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -6157,12 +6161,12 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>15.80</t>
+          <t>20.20</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>0.0522</t>
+          <t>0.0660</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -6177,14 +6181,10 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>313.20฿</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr">
-        <is>
-          <t>补胎胶条/5件</t>
-        </is>
-      </c>
+          <t>396.00฿</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -6192,7 +6192,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>113204676267#2</t>
+          <t>ZY202466648481</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -6208,32 +6208,32 @@
       <c r="E84" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18518-5-3</t>
+ รถ lot18519-6-13</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>15/08/2026</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>24.60</t>
+          <t>15.80</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>0.0608</t>
+          <t>0.0522</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -6243,15 +6243,19 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>369.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr"/>
+          <t>313.20฿</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>补胎胶条/5件</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -6259,7 +6263,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>113204676267</t>
+          <t>113204676267#2</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -6275,7 +6279,7 @@
       <c r="E85" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18518-5-2</t>
+ รถ lot18518-5-3</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -6295,12 +6299,12 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>25.00</t>
+          <t>24.60</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>0.0566</t>
+          <t>0.0608</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -6310,7 +6314,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>375.00฿</t>
+          <t>369.00฿</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -6318,11 +6322,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N85" t="inlineStr">
-        <is>
-          <t>真空胎冷补胶片</t>
-        </is>
-      </c>
+      <c r="N85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -6330,7 +6330,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>910061892464#2</t>
+          <t>113204676267</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -6346,32 +6346,32 @@
       <c r="E86" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18505-5-23</t>
+ รถ lot18518-5-2</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>30.40</t>
+          <t>25.00</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>0.0523</t>
+          <t>0.0566</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -6381,7 +6381,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>456.00฿</t>
+          <t>375.00฿</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -6389,7 +6389,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N86" t="inlineStr"/>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>真空胎冷补胶片</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -6397,7 +6401,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>910061892464</t>
+          <t>910061892464#2</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -6413,7 +6417,7 @@
       <c r="E87" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18505-5-22</t>
+ รถ lot18505-5-23</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -6433,12 +6437,12 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>15.90</t>
+          <t>30.40</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>0.0353</t>
+          <t>0.0523</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -6448,7 +6452,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>238.50฿</t>
+          <t>456.00฿</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -6456,11 +6460,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N87" t="inlineStr">
-        <is>
-          <t>记号蜡笔</t>
-        </is>
-      </c>
+      <c r="N87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -6468,7 +6468,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>773434709817985</t>
+          <t>910061892464</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -6478,38 +6478,38 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>UN-INV260819-00010</t>
+          <t>UN-INV260815-00046</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18535-8</t>
+ รถ lot18505-5-22</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>16/08/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>15.90</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>0.0184</t>
+          <t>0.0353</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>238.50฿</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>110.40฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>锅具 二次包装货物变形</t>
+          <t>记号蜡笔</t>
         </is>
       </c>
     </row>
@@ -6539,7 +6539,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>435295775627304</t>
+          <t>773434709817985</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -6549,38 +6549,38 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>UN-INV260811-00012</t>
+          <t>UN-INV260819-00010</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18492-2</t>
+ รถ lot18535-8</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>16/08/2026</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>5.30</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>0.0090</t>
+          <t>0.0184</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -6590,17 +6590,17 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>79.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>110.40฿</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>配件 破损件</t>
+          <t>锅具 二次包装货物变形</t>
         </is>
       </c>
     </row>
@@ -6610,7 +6610,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>YT7636332367470</t>
+          <t>435295775627304</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -6626,7 +6626,7 @@
       <c r="E90" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18487-2-27</t>
+ รถ lot18492-2</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -6646,12 +6646,12 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>5.30</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>0.0004</t>
+          <t>0.0090</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -6661,17 +6661,17 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>79.50฿</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>10.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>立牌</t>
+          <t>配件 破损件</t>
         </is>
       </c>
     </row>
@@ -6681,7 +6681,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>S35386280517#2</t>
+          <t>YT7636332367470</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -6697,32 +6697,32 @@
       <c r="E91" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18475-24</t>
+ รถ lot18487-2-27</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>8.80</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>0.0045</t>
+          <t>0.0004</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -6732,15 +6732,19 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>132.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N91" t="inlineStr"/>
+          <t>10.00฿</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>立牌</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -6748,7 +6752,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>S35386280517</t>
+          <t>S35386280517#2</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -6764,7 +6768,7 @@
       <c r="E92" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18475-23</t>
+ รถ lot18475-24</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -6784,22 +6788,22 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>103.50</t>
+          <t>8.80</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>0.2236</t>
+          <t>0.0045</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>1,552.50฿</t>
+          <t>132.00฿</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -6807,11 +6811,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N92" t="inlineStr">
-        <is>
-          <t>气门嘴 顺心捷达，一票16件</t>
-        </is>
-      </c>
+      <c r="N92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>YT7635787693833</t>
+          <t>S35386280517</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -6835,7 +6835,7 @@
       <c r="E93" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18473-6-41</t>
+ รถ lot18475-23</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -6850,37 +6850,37 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>13.80</t>
+          <t>103.50</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>0.0432</t>
+          <t>0.2236</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1,552.50฿</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>259.20฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>气压表/面单没有代码</t>
+          <t>气门嘴 顺心捷达，一票16件</t>
         </is>
       </c>
     </row>
@@ -6890,7 +6890,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>ZY202465806614</t>
+          <t>YT7635787693833</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -6900,38 +6900,38 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>UN-INV260807-00009</t>
+          <t>UN-INV260811-00012</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>มอก.
- รถ lot18466-5-51</t>
+          <t>ธรรมดา
+ รถ lot18473-6-41</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>11.30</t>
+          <t>13.80</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>0.0655</t>
+          <t>0.0432</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>445.40฿</t>
+          <t>259.20฿</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>电子数显胎压枪</t>
+          <t>气压表/面单没有代码</t>
         </is>
       </c>
     </row>
@@ -6961,7 +6961,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>113177184579#7</t>
+          <t>ZY202465806614</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -6976,18 +6976,18 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>ธรรมดา
- รถ lot18463-17</t>
+          <t>มอก.
+ รถ lot18466-5-51</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6997,12 +6997,12 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>9.70</t>
+          <t>11.30</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>0.0305</t>
+          <t>0.0655</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -7017,10 +7017,14 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>183.00฿</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr"/>
+          <t>445.40฿</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>电子数显胎压枪</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -7028,7 +7032,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>113177184579#5</t>
+          <t>113177184579#7</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -7044,7 +7048,7 @@
       <c r="E96" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-16</t>
+ รถ lot18463-17</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -7064,12 +7068,12 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>15.00</t>
+          <t>9.70</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>0.0137</t>
+          <t>0.0305</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -7079,12 +7083,12 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>225.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>183.00฿</t>
         </is>
       </c>
       <c r="N96" t="inlineStr"/>
@@ -7095,7 +7099,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>113177184579#4</t>
+          <t>113177184579#5</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -7111,7 +7115,7 @@
       <c r="E97" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-15</t>
+ รถ lot18463-16</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -7131,12 +7135,12 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>7.30</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>0.0235</t>
+          <t>0.0137</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -7146,12 +7150,12 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>225.00฿</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>141.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N97" t="inlineStr"/>
@@ -7162,7 +7166,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>113177184579#3</t>
+          <t>113177184579#4</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -7178,7 +7182,7 @@
       <c r="E98" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-14</t>
+ รถ lot18463-15</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -7198,12 +7202,12 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>11.90</t>
+          <t>7.30</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>0.0302</t>
+          <t>0.0235</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -7218,7 +7222,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>181.20฿</t>
+          <t>141.00฿</t>
         </is>
       </c>
       <c r="N98" t="inlineStr"/>
@@ -7229,7 +7233,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>113177184579#6</t>
+          <t>113177184579#3</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -7245,7 +7249,7 @@
       <c r="E99" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-13</t>
+ รถ lot18463-14</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -7265,12 +7269,12 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>26.10</t>
+          <t>11.90</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>0.0673</t>
+          <t>0.0302</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -7285,7 +7289,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>403.80฿</t>
+          <t>181.20฿</t>
         </is>
       </c>
       <c r="N99" t="inlineStr"/>
@@ -7296,7 +7300,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>435289604798626</t>
+          <t>113177184579#6</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -7312,7 +7316,7 @@
       <c r="E100" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18462-6-6</t>
+ รถ lot18463-13</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -7322,7 +7326,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -7332,12 +7336,12 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>9.60</t>
+          <t>26.10</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>0.0090</t>
+          <t>0.0673</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -7347,19 +7351,15 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>144.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N100" t="inlineStr">
-        <is>
-          <t>螺丝配件</t>
-        </is>
-      </c>
+          <t>403.80฿</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -7367,7 +7367,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>113177184579#2</t>
+          <t>435289604798626</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -7383,7 +7383,7 @@
       <c r="E101" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-12</t>
+ รถ lot18462-6-6</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -7393,7 +7393,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -7403,12 +7403,12 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>5.30</t>
+          <t>9.60</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>0.0635</t>
+          <t>0.0090</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -7418,15 +7418,19 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>144.00฿</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>381.00฿</t>
-        </is>
-      </c>
-      <c r="N101" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>螺丝配件</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/cargo_packages_p1-5.xlsx
+++ b/cargo_packages_p1-5.xlsx
@@ -532,7 +532,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">

--- a/cargo_packages_p1-5.xlsx
+++ b/cargo_packages_p1-5.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>435387211695084</t>
+          <t>ZY202466680649#5</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -522,17 +522,17 @@
       <c r="E2" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18966-4-53</t>
+ รถ lot18984-7-12</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -542,12 +542,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>28.50</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.0116</t>
+          <t>0.0816</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -562,14 +562,10 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>69.60฿</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>宠物用品</t>
-        </is>
-      </c>
+          <t>489.60฿</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -577,7 +573,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ZY202466680891#5</t>
+          <t>ZY202466680649#4</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -587,38 +583,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>UN-INV261008-00007</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18919-2-7</t>
+ รถ lot18984-7-11</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>19.70</t>
+          <t>8.70</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.0715</t>
+          <t>0.0446</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -633,7 +629,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>429.00฿</t>
+          <t>267.60฿</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -644,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ZY202466680891#4</t>
+          <t>ZY202466680649#3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -654,38 +650,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>UN-INV261008-00007</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18919-2-6</t>
+ รถ lot18984-7-10</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>20.00</t>
+          <t>11.80</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.0640</t>
+          <t>0.0811</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -700,7 +696,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>384.00฿</t>
+          <t>486.60฿</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -711,7 +707,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ZY202466680891#3</t>
+          <t>ZY202466680649#2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -721,38 +717,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>UN-INV261008-00007</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18919-2-5</t>
+ รถ lot18984-7-9</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>15.80</t>
+          <t>27.60</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.0492</t>
+          <t>0.0800</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -767,7 +763,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>295.20฿</t>
+          <t>480.00฿</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -778,7 +774,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ZY202466680891#2</t>
+          <t>ZY202466680649</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -788,38 +784,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>UN-INV261008-00007</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18919-2-4</t>
+ รถ lot18984-7-8</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>16.20</t>
+          <t>8.20</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.0492</t>
+          <t>0.0203</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -829,15 +825,19 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>123.00฿</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>295.20฿</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>补胎贴</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -845,7 +845,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ZY202466680891</t>
+          <t>435387211695084</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -855,38 +855,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>UN-INV261008-00007</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18919-2-3</t>
+ รถ lot18966-4-53</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>15.90</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.0492</t>
+          <t>0.0116</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>295.20฿</t>
+          <t>69.60฿</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>补胎胶片/5件</t>
+          <t>宠物用品</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>S35386291018</t>
+          <t>ZY202466680891#5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -926,60 +926,56 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>UN-INV261005-00021</t>
+          <t>UN-INV261008-00007</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18901-6-32</t>
+ รถ lot18919-2-7</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>82.80</t>
+          <t>19.70</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.1641</t>
+          <t>0.0715</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>1,242.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>配件，12件</t>
-        </is>
-      </c>
+          <t>429.00฿</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -987,7 +983,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>113405301091#3</t>
+          <t>ZY202466680891#4</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -997,38 +993,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>UN-INV261005-00021</t>
+          <t>UN-INV261008-00007</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18901-7-3</t>
+ รถ lot18919-2-6</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>13.10</t>
+          <t>20.00</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.0347</t>
+          <t>0.0640</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1043,7 +1039,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>208.20฿</t>
+          <t>384.00฿</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1054,7 +1050,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>113405301091#2</t>
+          <t>ZY202466680891#3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1064,38 +1060,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>UN-INV261005-00021</t>
+          <t>UN-INV261008-00007</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18901-7-2</t>
+ รถ lot18919-2-5</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>16.10</t>
+          <t>15.80</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.0397</t>
+          <t>0.0492</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1105,12 +1101,12 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>241.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>295.20฿</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1121,7 +1117,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>113405301091</t>
+          <t>ZY202466680891#2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1131,38 +1127,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>UN-INV261005-00021</t>
+          <t>UN-INV261008-00007</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18901-7-1</t>
+ รถ lot18919-2-4</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>33.60</t>
+          <t>16.20</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.0832</t>
+          <t>0.0492</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1172,19 +1168,15 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>504.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>补胎胶片/3件</t>
-        </is>
-      </c>
+          <t>295.20฿</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1192,7 +1184,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>YT7646197126750</t>
+          <t>ZY202466680891</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1202,38 +1194,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>UN-INV261005-00021</t>
+          <t>UN-INV261008-00007</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18887-50</t>
+ รถ lot18919-2-3</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>26/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>26/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>8.30</t>
+          <t>15.90</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0.0127</t>
+          <t>0.0492</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1243,17 +1235,17 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>124.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>295.20฿</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>补胎胶片/5件</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1255,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ZY202462495078</t>
+          <t>S35386291018</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1273,58 +1265,58 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>UN-INV260926-00006</t>
+          <t>UN-INV261005-00021</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18844-9-4</t>
+ รถ lot18901-6-32</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>14.30</t>
+          <t>82.80</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0.0624</t>
+          <t>0.1641</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1,242.00฿</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>374.40฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>胎压表</t>
+          <t>配件，12件</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1326,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>S71749075994</t>
+          <t>113405301091#3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1344,38 +1336,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>UN-INV260924-00056</t>
+          <t>UN-INV261005-00021</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18830-6-30</t>
+ รถ lot18901-7-3</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>119.00</t>
+          <t>13.10</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.2302</t>
+          <t>0.0347</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1385,19 +1377,15 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>1,785.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>真空胎扒胎机配件/木箱</t>
-        </is>
-      </c>
+          <t>208.20฿</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1405,7 +1393,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>435358249576981</t>
+          <t>113405301091#2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1415,38 +1403,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>UN-INV260924-00056</t>
+          <t>UN-INV261005-00021</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18815-4-6</t>
+ รถ lot18901-7-2</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>5.20</t>
+          <t>16.10</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.0044</t>
+          <t>0.0397</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1456,7 +1444,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>78.00฿</t>
+          <t>241.50฿</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1464,11 +1452,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>气门嘴</t>
-        </is>
-      </c>
+      <c r="N15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1476,7 +1460,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>S71195667064</t>
+          <t>113405301091</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1486,58 +1470,58 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>UN-INV260924-00056</t>
+          <t>UN-INV261005-00021</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18810-6-3</t>
+ รถ lot18901-7-1</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>165.00</t>
+          <t>33.60</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>0.8568</t>
+          <t>0.0832</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>504.00฿</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>5,140.80฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>千斤顶，3件，客户不打木架发</t>
+          <t>补胎胶片/3件</t>
         </is>
       </c>
     </row>
@@ -1547,7 +1531,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>113350746029#4</t>
+          <t>YT7646197126750</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1557,38 +1541,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>UN-INV260924-00056</t>
+          <t>UN-INV261005-00021</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18799-6-32</t>
+ รถ lot18887-50</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>26/09/2026</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>26/09/2026</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>27.70</t>
+          <t>8.30</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.0800</t>
+          <t>0.0127</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1598,15 +1582,19 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>124.50฿</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>480.00฿</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>配件</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1614,7 +1602,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>113350746029#3</t>
+          <t>ZY202462495078</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1624,38 +1612,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>UN-INV260924-00056</t>
+          <t>UN-INV260926-00006</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18799-6-31</t>
+ รถ lot18844-9-4</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>10.90</t>
+          <t>14.30</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>0.0377</t>
+          <t>0.0624</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1670,10 +1658,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>226.20฿</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
+          <t>374.40฿</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>胎压表</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1681,7 +1673,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>113350746029#2</t>
+          <t>S71749075994</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1697,32 +1689,32 @@
       <c r="E19" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18799-6-30</t>
+ รถ lot18830-6-30</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>15.00</t>
+          <t>119.00</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>0.0101</t>
+          <t>0.2302</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1732,7 +1724,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>225.00฿</t>
+          <t>1,785.00฿</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1740,7 +1732,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>真空胎扒胎机配件/木箱</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1748,7 +1744,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>113350746029</t>
+          <t>435358249576981</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1764,32 +1760,32 @@
       <c r="E20" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18799-6-29</t>
+ รถ lot18815-4-6</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>16.50</t>
+          <t>5.20</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0.0127</t>
+          <t>0.0044</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1799,7 +1795,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>247.50฿</t>
+          <t>78.00฿</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1809,7 +1805,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>真空胎加固修理补片</t>
+          <t>气门嘴</t>
         </is>
       </c>
     </row>
@@ -1819,7 +1815,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>760246657062</t>
+          <t>S71195667064</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1835,17 +1831,17 @@
       <c r="E21" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18799-7-3</t>
+ รถ lot18810-6-3</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1855,17 +1851,17 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>165.00</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.0005</t>
+          <t>0.8568</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1875,12 +1871,12 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>10.00฿</t>
+          <t>5,140.80฿</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>气门嘴，轮胎修补工具，气门芯宣传册</t>
+          <t>千斤顶，3件，客户不打木架发</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1886,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>113348267192#2</t>
+          <t>113350746029#4</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1900,38 +1896,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>UN-INV260921-00019</t>
+          <t>UN-INV260924-00056</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18795-2-7</t>
+ รถ lot18799-6-32</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>28.10</t>
+          <t>27.70</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.0628</t>
+          <t>0.0800</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1941,12 +1937,12 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>421.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>480.00฿</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -1957,7 +1953,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>113348267192</t>
+          <t>113350746029#3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1967,38 +1963,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>UN-INV260921-00019</t>
+          <t>UN-INV260924-00056</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18795-2-6</t>
+ รถ lot18799-6-31</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>19.50</t>
+          <t>10.90</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.0505</t>
+          <t>0.0377</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2013,14 +2009,10 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>303.00฿</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>补胎胶片</t>
-        </is>
-      </c>
+          <t>226.20฿</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2028,7 +2020,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ZY202472578299</t>
+          <t>113350746029#2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2038,60 +2030,56 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>UN-INV260918-00012</t>
+          <t>UN-INV260924-00056</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18758-7-43</t>
+ รถ lot18799-6-30</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>47.40</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.1603</t>
+          <t>0.0101</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>225.00฿</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>961.20฿</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>补胎贴，3件</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -2099,7 +2087,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>773440822655698</t>
+          <t>113350746029</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2109,38 +2097,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>UN-INV260918-00012</t>
+          <t>UN-INV260924-00056</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18758-4-31</t>
+ รถ lot18799-6-29</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>16.50</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.0022</t>
+          <t>0.0127</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2150,7 +2138,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>18.00฿</t>
+          <t>247.50฿</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2160,7 +2148,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>钻头</t>
+          <t>真空胎加固修理补片</t>
         </is>
       </c>
     </row>
@@ -2170,7 +2158,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>YT7642998390994</t>
+          <t>760246657062</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2180,38 +2168,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>UN-INV260918-00012</t>
+          <t>UN-INV260924-00056</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18769-3-57</t>
+ รถ lot18799-7-3</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>5.80</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>0.0070</t>
+          <t>0.0005</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2221,17 +2209,17 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>87.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10.00฿</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>气门嘴，轮胎修补工具，气门芯宣传册</t>
         </is>
       </c>
     </row>
@@ -2241,7 +2229,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>DPK212614057101</t>
+          <t>113348267192#2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2251,38 +2239,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>UN-INV260916-00003</t>
+          <t>UN-INV260921-00019</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18749-4-3</t>
+ รถ lot18795-2-7</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>9.60</t>
+          <t>28.10</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.0060</t>
+          <t>0.0628</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2292,7 +2280,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>144.00฿</t>
+          <t>421.50฿</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2300,11 +2288,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>轮胎气门嘴</t>
-        </is>
-      </c>
+      <c r="N27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2312,7 +2296,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>79031204783305</t>
+          <t>113348267192</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2322,38 +2306,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>UN-INV260916-00003</t>
+          <t>UN-INV260921-00019</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18744-6-15</t>
+ รถ lot18795-2-6</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>19.50</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.0020</t>
+          <t>0.0505</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2363,17 +2347,17 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>39.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>303.00฿</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>补胎胶片</t>
         </is>
       </c>
     </row>
@@ -2383,7 +2367,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>435342988112655</t>
+          <t>ZY202472578299</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2393,43 +2377,43 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>UN-INV260916-00003</t>
+          <t>UN-INV260918-00012</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18743-3-34</t>
+ รถ lot18758-7-43</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>47.40</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0.0014</t>
+          <t>0.1603</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2439,12 +2423,12 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>10.00฿</t>
+          <t>961.20฿</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>橡胶垫圈</t>
+          <t>补胎贴，3件</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2438,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>435343890137834</t>
+          <t>773440822655698</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2464,38 +2448,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>UN-INV260916-00003</t>
+          <t>UN-INV260918-00012</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18743-7-25</t>
+ รถ lot18758-4-31</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>21.40</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.0080</t>
+          <t>0.0022</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2505,7 +2489,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>321.00฿</t>
+          <t>18.00฿</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2515,7 +2499,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>扒胎机包胶撬棍</t>
+          <t>钻头</t>
         </is>
       </c>
     </row>
@@ -2525,7 +2509,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>YT7642670434639</t>
+          <t>YT7642998390994</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2535,38 +2519,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>UN-INV260916-00003</t>
+          <t>UN-INV260918-00012</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18743-2-8</t>
+ รถ lot18769-3-57</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>5.80</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.0010</t>
+          <t>0.0070</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2576,7 +2560,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>12.00฿</t>
+          <t>87.00฿</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2586,7 +2570,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>片片</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2580,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>93015797092</t>
+          <t>DPK212614057101</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2606,38 +2590,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>UN-INV260914-00014</t>
+          <t>UN-INV260916-00003</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18735-4-40</t>
+ รถ lot18749-4-3</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>12/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>8.60</t>
+          <t>9.60</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.0148</t>
+          <t>0.0060</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2647,7 +2631,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>129.00฿</t>
+          <t>144.00฿</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2657,7 +2641,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>仪表</t>
+          <t>轮胎气门嘴</t>
         </is>
       </c>
     </row>
@@ -2667,7 +2651,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>YT7642390374765</t>
+          <t>79031204783305</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2677,38 +2661,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>UN-INV260914-00015</t>
+          <t>UN-INV260916-00003</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18735-4-20</t>
+ รถ lot18744-6-15</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>12/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>20.80</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.0598</t>
+          <t>0.0020</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2718,17 +2702,17 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>39.00฿</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>358.80฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>打磨机</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -2738,7 +2722,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>435342255104130</t>
+          <t>435342988112655</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2748,18 +2732,18 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>UN-INV260914-00014</t>
+          <t>UN-INV260916-00003</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18735-43</t>
+ รถ lot18743-3-34</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2769,17 +2753,17 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>12/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>4.90</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.0172</t>
+          <t>0.0014</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2794,12 +2778,12 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>103.20฿</t>
+          <t>10.00฿</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>轮毂保护套</t>
+          <t>橡胶垫圈</t>
         </is>
       </c>
     </row>
@@ -2809,7 +2793,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>773440312345715</t>
+          <t>435343890137834</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2819,18 +2803,18 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>UN-INV260914-00014</t>
+          <t>UN-INV260916-00003</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18735-3-78</t>
+ รถ lot18743-7-25</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2840,17 +2824,17 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>12/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>21.40</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.0013</t>
+          <t>0.0080</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2860,7 +2844,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>19.50฿</t>
+          <t>321.00฿</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2870,7 +2854,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>扒胎机包胶撬棍</t>
         </is>
       </c>
     </row>
@@ -2880,7 +2864,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>773440291470393</t>
+          <t>YT7642670434639</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2890,18 +2874,18 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>UN-INV260914-00014</t>
+          <t>UN-INV260916-00003</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18735-34</t>
+ รถ lot18743-2-8</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2911,17 +2895,17 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>12/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.0029</t>
+          <t>0.0010</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2931,7 +2915,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>48.00฿</t>
+          <t>12.00฿</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2941,7 +2925,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>球阀</t>
+          <t>片片</t>
         </is>
       </c>
     </row>
@@ -2951,7 +2935,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>435342261175750</t>
+          <t>93015797092</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2961,13 +2945,13 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>UN-INV260914-00015</t>
+          <t>UN-INV260914-00014</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18736-13</t>
+ รถ lot18735-4-40</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2977,7 +2961,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2987,12 +2971,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>13.90</t>
+          <t>8.60</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.0137</t>
+          <t>0.0148</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -3002,7 +2986,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>208.50฿</t>
+          <t>129.00฿</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3012,7 +2996,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>仪表</t>
         </is>
       </c>
     </row>
@@ -3022,7 +3006,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ZY202461195200</t>
+          <t>YT7642390374765</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3038,7 +3022,7 @@
       <c r="E38" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18728-7-13</t>
+ รถ lot18735-4-20</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -3048,22 +3032,22 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>13/09/2026</t>
+          <t>12/09/2026</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>47.40</t>
+          <t>20.80</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.0116</t>
+          <t>0.0598</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -3073,17 +3057,17 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>711.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>358.80฿</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>打磨机</t>
         </is>
       </c>
     </row>
@@ -3093,7 +3077,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>79030687835952</t>
+          <t>435342255104130</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3109,7 +3093,7 @@
       <c r="E39" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18728-3-64</t>
+ รถ lot18735-43</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -3119,22 +3103,22 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>13/09/2026</t>
+          <t>12/09/2026</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>4.30</t>
+          <t>4.90</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.0030</t>
+          <t>0.0172</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -3144,17 +3128,17 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>64.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>103.20฿</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>接头配件</t>
+          <t>轮毂保护套</t>
         </is>
       </c>
     </row>
@@ -3164,7 +3148,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>LJ20722214#3</t>
+          <t>773440312345715</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3174,38 +3158,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>UN-INV260912-00011</t>
+          <t>UN-INV260914-00014</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18726-7-8</t>
+ รถ lot18735-3-78</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>12/09/2026</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>14.00</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.0171</t>
+          <t>0.0013</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -3215,7 +3199,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>210.00฿</t>
+          <t>19.50฿</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -3223,7 +3207,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>配件</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -3231,7 +3219,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>LJ20722214#2</t>
+          <t>773440291470393</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3241,38 +3229,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>UN-INV260912-00011</t>
+          <t>UN-INV260914-00014</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18726-7-7</t>
+ รถ lot18735-34</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>12/09/2026</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>11.90</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.0089</t>
+          <t>0.0029</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -3282,7 +3270,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>178.50฿</t>
+          <t>48.00฿</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -3290,7 +3278,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>球阀</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -3298,7 +3290,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>LJ20722214</t>
+          <t>435342261175750</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3308,38 +3300,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>UN-INV260912-00011</t>
+          <t>UN-INV260914-00015</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18726-7-6</t>
+ รถ lot18736-13</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>12/09/2026</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>16.00</t>
+          <t>13.90</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.0144</t>
+          <t>0.0137</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3349,7 +3341,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>240.00฿</t>
+          <t>208.50฿</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3359,7 +3351,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>电板套筒配件/3件</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -3369,7 +3361,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>YT7641966426761</t>
+          <t>ZY202461195200</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3379,38 +3371,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>UN-INV260912-00011</t>
+          <t>UN-INV260914-00015</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18714-9-23</t>
+ รถ lot18728-7-13</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>13/09/2026</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>13.60</t>
+          <t>47.40</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.0422</t>
+          <t>0.0116</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3420,17 +3412,17 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>711.00฿</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>253.20฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>带表汽车轮胎打气嘴</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -3440,7 +3432,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ZY202471681117#2</t>
+          <t>79030687835952</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3450,38 +3442,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>UN-INV260912-00011</t>
+          <t>UN-INV260914-00014</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18714-9-8</t>
+ รถ lot18728-3-64</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>13/09/2026</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>11.80</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.0832</t>
+          <t>0.0030</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3491,15 +3483,19 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>64.50฿</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>499.20฿</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>接头配件</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -3507,7 +3503,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ZY202471681117</t>
+          <t>LJ20722214#3</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3523,17 +3519,17 @@
       <c r="E45" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18714-9-7</t>
+ รถ lot18726-7-8</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3543,12 +3539,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>7.70</t>
+          <t>14.00</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.0493</t>
+          <t>0.0171</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3558,19 +3554,15 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>210.00฿</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>295.80฿</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>补胎胶片/2件</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -3578,7 +3570,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>302285502767#2</t>
+          <t>LJ20722214#2</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3594,17 +3586,17 @@
       <c r="E46" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18714-8-10</t>
+ รถ lot18726-7-7</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3614,12 +3606,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>33.70</t>
+          <t>11.90</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>0.0145</t>
+          <t>0.0089</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3629,7 +3621,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>505.50฿</t>
+          <t>178.50฿</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3645,7 +3637,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>302285502767</t>
+          <t>LJ20722214</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3661,17 +3653,17 @@
       <c r="E47" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18714-8-9</t>
+ รถ lot18726-7-6</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3681,12 +3673,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>23.40</t>
+          <t>16.00</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>0.0123</t>
+          <t>0.0144</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3696,7 +3688,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>351.00฿</t>
+          <t>240.00฿</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3706,7 +3698,7 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>扳手</t>
+          <t>电板套筒配件/3件</t>
         </is>
       </c>
     </row>
@@ -3716,7 +3708,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>LJ20716178#2</t>
+          <t>YT7641966426761</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3726,18 +3718,18 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>UN-INV260911-00013</t>
+          <t>UN-INV260912-00011</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18713-6-65</t>
+ รถ lot18714-9-23</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3747,17 +3739,17 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>19.50</t>
+          <t>13.60</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>0.0075</t>
+          <t>0.0422</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3767,15 +3759,19 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>292.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
+          <t>253.20฿</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>带表汽车轮胎打气嘴</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -3783,7 +3779,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>LJ20716178</t>
+          <t>ZY202471681117#2</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3793,18 +3789,18 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>UN-INV260911-00013</t>
+          <t>UN-INV260912-00011</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18713-6-64</t>
+ รถ lot18714-9-8</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3814,17 +3810,17 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>19.60</t>
+          <t>11.80</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>0.0075</t>
+          <t>0.0832</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3834,19 +3830,15 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>294.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>配件</t>
-        </is>
-      </c>
+          <t>499.20฿</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -3854,7 +3846,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>435338972466812</t>
+          <t>ZY202471681117</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3864,38 +3856,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>UN-INV260911-00013</t>
+          <t>UN-INV260912-00011</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18710-6-35</t>
+ รถ lot18714-9-7</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>13.10</t>
+          <t>7.70</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>0.0624</t>
+          <t>0.0493</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3910,12 +3902,12 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>374.40฿</t>
+          <t>295.80฿</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>修补工具</t>
+          <t>补胎胶片/2件</t>
         </is>
       </c>
     </row>
@@ -3925,7 +3917,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>435334324045675</t>
+          <t>302285502767#2</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3935,38 +3927,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>UN-INV260908-00009</t>
+          <t>UN-INV260912-00011</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18696-14</t>
+ รถ lot18714-8-10</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>10.80</t>
+          <t>33.70</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>0.0088</t>
+          <t>0.0145</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3976,7 +3968,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>162.00฿</t>
+          <t>505.50฿</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -3984,11 +3976,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>配件</t>
-        </is>
-      </c>
+      <c r="N51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -3996,7 +3984,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>YT7641276428798</t>
+          <t>302285502767</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -4006,38 +3994,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>UN-INV260908-00009</t>
+          <t>UN-INV260912-00011</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18697-11</t>
+ รถ lot18714-8-9</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>9.50</t>
+          <t>23.40</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>0.0296</t>
+          <t>0.0123</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -4047,17 +4035,17 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>351.00฿</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>177.60฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>扳手</t>
         </is>
       </c>
     </row>
@@ -4067,7 +4055,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>79029430531776</t>
+          <t>LJ20716178#2</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -4077,38 +4065,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>UN-INV260907-00015</t>
+          <t>UN-INV260911-00013</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18689-26</t>
+ รถ lot18713-6-65</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>19.50</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>0.0135</t>
+          <t>0.0075</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -4118,19 +4106,15 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>292.50฿</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>81.00฿</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>卡套</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -4138,7 +4122,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>113282578128#2</t>
+          <t>LJ20716178</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -4148,38 +4132,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>UN-INV260907-00015</t>
+          <t>UN-INV260911-00013</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18683-4</t>
+ รถ lot18713-6-64</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>38.00</t>
+          <t>19.60</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>0.1601</t>
+          <t>0.0075</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -4189,15 +4173,19 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>294.00฿</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>960.60฿</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>配件</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -4205,7 +4193,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>113282578128</t>
+          <t>435338972466812</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -4215,38 +4203,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>UN-INV260907-00015</t>
+          <t>UN-INV260911-00013</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18683-3</t>
+ รถ lot18710-6-35</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>27.50</t>
+          <t>13.10</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>0.1566</t>
+          <t>0.0624</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -4261,12 +4249,12 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>939.60฿</t>
+          <t>374.40฿</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>压条取出器 一票两件破损件</t>
+          <t>修补工具</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4264,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>82730128600#3</t>
+          <t>435334324045675</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -4286,38 +4274,38 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>UN-INV260907-00015</t>
+          <t>UN-INV260908-00009</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18678-6-21</t>
+ รถ lot18696-14</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>30/08/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>33.00</t>
+          <t>10.80</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>0.0122</t>
+          <t>0.0088</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -4327,7 +4315,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>495.00฿</t>
+          <t>162.00฿</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -4335,7 +4323,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr"/>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>配件</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -4343,7 +4335,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>82730128600#2</t>
+          <t>YT7641276428798</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -4353,38 +4345,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>UN-INV260907-00015</t>
+          <t>UN-INV260908-00009</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18678-6-20</t>
+ รถ lot18697-11</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>30/08/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>27.60</t>
+          <t>9.50</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>0.0095</t>
+          <t>0.0296</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -4394,15 +4386,19 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>414.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
+          <t>177.60฿</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>配件</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -4410,7 +4406,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>82730128600</t>
+          <t>79029430531776</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -4426,17 +4422,17 @@
       <c r="E58" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18678-6-19</t>
+ รถ lot18689-26</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>30/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4446,12 +4442,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>28.10</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>0.0118</t>
+          <t>0.0135</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -4461,17 +4457,17 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>421.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>81.00฿</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>五金配件/3件</t>
+          <t>卡套</t>
         </is>
       </c>
     </row>
@@ -4481,7 +4477,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>113278387839#3</t>
+          <t>113282578128#2</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4491,38 +4487,38 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>UN-INV260903-00023</t>
+          <t>UN-INV260907-00015</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18663-8-3</t>
+ รถ lot18683-4</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>25.30</t>
+          <t>38.00</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>0.0404</t>
+          <t>0.1601</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4532,12 +4528,12 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>379.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>960.60฿</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
@@ -4548,7 +4544,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>113278387839#2</t>
+          <t>113282578128</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4558,38 +4554,38 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>UN-INV260903-00023</t>
+          <t>UN-INV260907-00015</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18663-8-2</t>
+ รถ lot18683-3</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>26.10</t>
+          <t>27.50</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>0.0304</t>
+          <t>0.1566</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -4599,15 +4595,19 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>391.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
+          <t>939.60฿</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>压条取出器 一票两件破损件</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -4615,7 +4615,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>113278387839</t>
+          <t>82730128600#3</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4625,38 +4625,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>UN-INV260903-00023</t>
+          <t>UN-INV260907-00015</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18663-8-1</t>
+ รถ lot18678-6-21</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>30/08/2026</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>9.10</t>
+          <t>33.00</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>0.0144</t>
+          <t>0.0122</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>136.50฿</t>
+          <t>495.00฿</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -4674,11 +4674,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>配件/3件</t>
-        </is>
-      </c>
+      <c r="N61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -4686,7 +4682,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>113276098937#3</t>
+          <t>82730128600#2</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4696,38 +4692,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>UN-INV260901-00057</t>
+          <t>UN-INV260907-00015</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-45</t>
+ รถ lot18678-6-20</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>30/08/2026</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>17.80</t>
+          <t>27.60</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>0.0302</t>
+          <t>0.0095</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -4737,7 +4733,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>267.00฿</t>
+          <t>414.00฿</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -4753,7 +4749,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>113276098937#2</t>
+          <t>82730128600</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4763,38 +4759,38 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>UN-INV260901-00057</t>
+          <t>UN-INV260907-00015</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-44</t>
+ รถ lot18678-6-19</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>30/08/2026</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>10.90</t>
+          <t>28.10</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>0.0313</t>
+          <t>0.0118</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -4804,15 +4800,19 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>421.50฿</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>187.80฿</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>五金配件/3件</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -4820,7 +4820,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>113276098937</t>
+          <t>113278387839#3</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4830,38 +4830,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>UN-INV260901-00057</t>
+          <t>UN-INV260903-00023</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-43</t>
+ รถ lot18663-8-3</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>33.60</t>
+          <t>25.30</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>0.0825</t>
+          <t>0.0404</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>504.00฿</t>
+          <t>379.50฿</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -4879,11 +4879,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N64" t="inlineStr">
-        <is>
-          <t>补胎胶片+配件/3件</t>
-        </is>
-      </c>
+      <c r="N64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -4891,7 +4887,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>ZY202464580877#4</t>
+          <t>113278387839#2</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4901,38 +4897,38 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>UN-INV260901-00057</t>
+          <t>UN-INV260903-00023</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-17</t>
+ รถ lot18663-8-2</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>20.10</t>
+          <t>26.10</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>0.0466</t>
+          <t>0.0304</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -4942,7 +4938,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>301.50฿</t>
+          <t>391.50฿</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -4958,7 +4954,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>ZY202464580877#7</t>
+          <t>113278387839</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4968,38 +4964,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>UN-INV260901-00057</t>
+          <t>UN-INV260903-00023</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-16</t>
+ รถ lot18663-8-1</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>16.60</t>
+          <t>9.10</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>0.0430</t>
+          <t>0.0144</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -5009,15 +5005,19 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>136.50฿</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>258.00฿</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>配件/3件</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -5025,7 +5025,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>ZY202464580877#2</t>
+          <t>113276098937#3</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -5041,7 +5041,7 @@
       <c r="E67" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-15</t>
+ รถ lot18655-9-45</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -5061,12 +5061,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>25.10</t>
+          <t>17.80</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>0.0483</t>
+          <t>0.0302</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>376.50฿</t>
+          <t>267.00฿</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -5092,7 +5092,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>ZY202464580877#8</t>
+          <t>113276098937#2</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -5108,7 +5108,7 @@
       <c r="E68" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-14</t>
+ รถ lot18655-9-44</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -5128,12 +5128,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>28.90</t>
+          <t>10.90</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>0.0800</t>
+          <t>0.0313</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>480.00฿</t>
+          <t>187.80฿</t>
         </is>
       </c>
       <c r="N68" t="inlineStr"/>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>ZY202464580877#6</t>
+          <t>113276098937</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -5175,7 +5175,7 @@
       <c r="E69" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-13</t>
+ รถ lot18655-9-43</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -5195,12 +5195,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>20.90</t>
+          <t>33.60</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>0.0534</t>
+          <t>0.0825</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -5210,15 +5210,19 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>504.00฿</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>320.40฿</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>补胎胶片+配件/3件</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -5226,7 +5230,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>ZY202464580877#5</t>
+          <t>ZY202464580877#4</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -5242,7 +5246,7 @@
       <c r="E70" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-12</t>
+ รถ lot18655-9-17</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -5262,12 +5266,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>26.20</t>
+          <t>20.10</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>0.0535</t>
+          <t>0.0466</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -5277,7 +5281,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>393.00฿</t>
+          <t>301.50฿</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -5293,7 +5297,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>ZY202464580877</t>
+          <t>ZY202464580877#7</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -5309,7 +5313,7 @@
       <c r="E71" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-11</t>
+ รถ lot18655-9-16</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -5329,12 +5333,12 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>20.70</t>
+          <t>16.60</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>0.0531</t>
+          <t>0.0430</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -5349,7 +5353,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>318.60฿</t>
+          <t>258.00฿</t>
         </is>
       </c>
       <c r="N71" t="inlineStr"/>
@@ -5360,7 +5364,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>ZY202464580877#9</t>
+          <t>ZY202464580877#2</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -5376,7 +5380,7 @@
       <c r="E72" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-10</t>
+ รถ lot18655-9-15</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -5396,12 +5400,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>27.70</t>
+          <t>25.10</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>0.0800</t>
+          <t>0.0483</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -5411,12 +5415,12 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>376.50฿</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>480.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N72" t="inlineStr"/>
@@ -5427,7 +5431,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>ZY202464580877#3</t>
+          <t>ZY202464580877#8</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -5443,7 +5447,7 @@
       <c r="E73" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-9</t>
+ รถ lot18655-9-14</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -5463,12 +5467,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>27.10</t>
+          <t>28.90</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>0.0567</t>
+          <t>0.0800</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -5478,19 +5482,15 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>406.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t>补胎胶片/9件</t>
-        </is>
-      </c>
+          <t>480.00฿</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -5498,7 +5498,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>S71090288685</t>
+          <t>ZY202464580877#6</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -5508,38 +5508,38 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>UN-INV260831-00017</t>
+          <t>UN-INV260901-00057</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18634-7-3</t>
+ รถ lot18655-9-13</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>29/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>12.10</t>
+          <t>20.90</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>0.0240</t>
+          <t>0.0534</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -5549,19 +5549,15 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>181.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr">
-        <is>
-          <t>配件</t>
-        </is>
-      </c>
+          <t>320.40฿</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -5569,7 +5565,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>YT7638092409979</t>
+          <t>ZY202464580877#5</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -5579,38 +5575,38 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>UN-INV260822-00010</t>
+          <t>UN-INV260901-00057</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18569-7-7</t>
+ รถ lot18655-9-12</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>16/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>16/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>15.00</t>
+          <t>26.20</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>0.0140</t>
+          <t>0.0535</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -5620,7 +5616,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>225.00฿</t>
+          <t>393.00฿</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -5628,11 +5624,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N75" t="inlineStr">
-        <is>
-          <t>配件</t>
-        </is>
-      </c>
+      <c r="N75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -5640,7 +5632,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>435308000517585</t>
+          <t>ZY202464580877</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5650,38 +5642,38 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>UN-INV260822-00010</t>
+          <t>UN-INV260901-00057</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18550-6-11</t>
+ รถ lot18655-9-11</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>20.70</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>0.0032</t>
+          <t>0.0531</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -5691,19 +5683,15 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>54.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr">
-        <is>
-          <t>气门嘴</t>
-        </is>
-      </c>
+          <t>318.60฿</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -5711,7 +5699,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>710094401487</t>
+          <t>ZY202464580877#9</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -5721,43 +5709,43 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>UN-INV260822-00010</t>
+          <t>UN-INV260901-00057</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18544-8-14</t>
+ รถ lot18655-9-10</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>107.10</t>
+          <t>27.70</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>0.4536</t>
+          <t>0.0800</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -5767,14 +5755,10 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>2,721.60฿</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr">
-        <is>
-          <t>空的高压充气罐/一票10件，仓库实收到9件，已确认收到的9件先发</t>
-        </is>
-      </c>
+          <t>480.00฿</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -5782,7 +5766,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>773435675083665</t>
+          <t>ZY202464580877#3</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -5792,38 +5776,38 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>UN-INV260815-00046</t>
+          <t>UN-INV260901-00057</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18526-6-17</t>
+ รถ lot18655-9-9</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>13.10</t>
+          <t>27.10</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>0.0214</t>
+          <t>0.0567</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -5833,7 +5817,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>196.50฿</t>
+          <t>406.50฿</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -5843,7 +5827,7 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>补胎工具</t>
+          <t>补胎胶片/9件</t>
         </is>
       </c>
     </row>
@@ -5853,7 +5837,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>YT7637032206975</t>
+          <t>S71090288685</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -5863,38 +5847,38 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>UN-INV260819-00010</t>
+          <t>UN-INV260831-00017</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>มอก.
- รถ lot18523-6-30</t>
+          <t>ธรรมดา
+ รถ lot18634-7-3</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>16/08/2026</t>
+          <t>29/08/2026</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>9.60</t>
+          <t>12.10</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>0.0316</t>
+          <t>0.0240</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -5904,17 +5888,17 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>181.50฿</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>214.88฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>气动模具研磨机+配件</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -5924,7 +5908,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>ZY202466648481#5</t>
+          <t>YT7638092409979</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -5934,38 +5918,38 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>UN-INV260815-00046</t>
+          <t>UN-INV260822-00010</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18519-6-17</t>
+ รถ lot18569-7-7</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>16/08/2026</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>16/08/2026</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>15/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>16.10</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>0.0493</t>
+          <t>0.0140</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -5975,15 +5959,19 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>225.00฿</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>295.80฿</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>配件</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -5991,7 +5979,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>ZY202466648481#4</t>
+          <t>435308000517585</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -6001,38 +5989,38 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>UN-INV260815-00046</t>
+          <t>UN-INV260822-00010</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18519-6-16</t>
+ รถ lot18550-6-11</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>15/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>20.50</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>0.0656</t>
+          <t>0.0032</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -6042,15 +6030,19 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>54.00฿</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>393.60฿</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>气门嘴</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -6058,7 +6050,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>ZY202466648481#3</t>
+          <t>710094401487</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -6068,43 +6060,43 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>UN-INV260815-00046</t>
+          <t>UN-INV260822-00010</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18519-6-15</t>
+ รถ lot18544-8-14</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>15/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>15.70</t>
+          <t>107.10</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>0.0508</t>
+          <t>0.4536</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -6114,10 +6106,14 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>304.80฿</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
+          <t>2,721.60฿</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>空的高压充气罐/一票10件，仓库实收到9件，已确认收到的9件先发</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -6125,7 +6121,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>ZY202466648481#2</t>
+          <t>773435675083665</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -6141,32 +6137,32 @@
       <c r="E83" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18519-6-14</t>
+ รถ lot18526-6-17</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>15/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>20.20</t>
+          <t>13.10</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>0.0660</t>
+          <t>0.0214</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -6176,15 +6172,19 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>196.50฿</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>396.00฿</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>补胎工具</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -6192,7 +6192,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>ZY202466648481</t>
+          <t>YT7637032206975</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -6202,13 +6202,13 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>UN-INV260815-00046</t>
+          <t>UN-INV260819-00010</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>ธรรมดา
- รถ lot18519-6-13</t>
+          <t>มอก.
+ รถ lot18523-6-30</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -6223,17 +6223,17 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>15/08/2026</t>
+          <t>16/08/2026</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>15.80</t>
+          <t>9.60</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>0.0522</t>
+          <t>0.0316</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -6248,12 +6248,12 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>313.20฿</t>
+          <t>214.88฿</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>补胎胶条/5件</t>
+          <t>气动模具研磨机+配件</t>
         </is>
       </c>
     </row>
@@ -6263,7 +6263,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>113204676267#2</t>
+          <t>ZY202466648481#5</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -6279,32 +6279,32 @@
       <c r="E85" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18518-5-3</t>
+ รถ lot18519-6-17</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>15/08/2026</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>24.60</t>
+          <t>16.10</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>0.0608</t>
+          <t>0.0493</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -6314,12 +6314,12 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>369.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>295.80฿</t>
         </is>
       </c>
       <c r="N85" t="inlineStr"/>
@@ -6330,7 +6330,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>113204676267</t>
+          <t>ZY202466648481#4</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -6346,32 +6346,32 @@
       <c r="E86" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18518-5-2</t>
+ รถ lot18519-6-16</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>15/08/2026</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>25.00</t>
+          <t>20.50</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>0.0566</t>
+          <t>0.0656</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -6381,19 +6381,15 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>375.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr">
-        <is>
-          <t>真空胎冷补胶片</t>
-        </is>
-      </c>
+          <t>393.60฿</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -6401,7 +6397,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>910061892464#2</t>
+          <t>ZY202466648481#3</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -6417,32 +6413,32 @@
       <c r="E87" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18505-5-23</t>
+ รถ lot18519-6-15</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>15/08/2026</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>30.40</t>
+          <t>15.70</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>0.0523</t>
+          <t>0.0508</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -6452,12 +6448,12 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>456.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>304.80฿</t>
         </is>
       </c>
       <c r="N87" t="inlineStr"/>
@@ -6468,7 +6464,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>910061892464</t>
+          <t>ZY202466648481#2</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -6484,32 +6480,32 @@
       <c r="E88" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18505-5-22</t>
+ รถ lot18519-6-14</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>15/08/2026</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>15.90</t>
+          <t>20.20</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>0.0353</t>
+          <t>0.0660</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -6519,19 +6515,15 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>238.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr">
-        <is>
-          <t>记号蜡笔</t>
-        </is>
-      </c>
+          <t>396.00฿</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -6539,7 +6531,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>773434709817985</t>
+          <t>ZY202466648481</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -6549,38 +6541,38 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>UN-INV260819-00010</t>
+          <t>UN-INV260815-00046</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18535-8</t>
+ รถ lot18519-6-13</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>16/08/2026</t>
+          <t>15/08/2026</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>15.80</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>0.0184</t>
+          <t>0.0522</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -6595,12 +6587,12 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>110.40฿</t>
+          <t>313.20฿</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>锅具 二次包装货物变形</t>
+          <t>补胎胶条/5件</t>
         </is>
       </c>
     </row>
@@ -6610,7 +6602,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>435295775627304</t>
+          <t>113204676267#2</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -6620,38 +6612,38 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>UN-INV260811-00012</t>
+          <t>UN-INV260815-00046</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18492-2</t>
+ รถ lot18518-5-3</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>5.30</t>
+          <t>24.60</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>0.0090</t>
+          <t>0.0608</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -6661,7 +6653,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>79.50฿</t>
+          <t>369.00฿</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -6669,11 +6661,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N90" t="inlineStr">
-        <is>
-          <t>配件 破损件</t>
-        </is>
-      </c>
+      <c r="N90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -6681,7 +6669,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>YT7636332367470</t>
+          <t>113204676267</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -6691,38 +6679,38 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>UN-INV260811-00012</t>
+          <t>UN-INV260815-00046</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18487-2-27</t>
+ รถ lot18518-5-2</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>25.00</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>0.0004</t>
+          <t>0.0566</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -6732,17 +6720,17 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>375.00฿</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>10.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>立牌</t>
+          <t>真空胎冷补胶片</t>
         </is>
       </c>
     </row>
@@ -6752,7 +6740,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>S35386280517#2</t>
+          <t>910061892464#2</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -6762,38 +6750,38 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>UN-INV260811-00012</t>
+          <t>UN-INV260815-00046</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18475-24</t>
+ รถ lot18505-5-23</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>8.80</t>
+          <t>30.40</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>0.0045</t>
+          <t>0.0523</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -6803,7 +6791,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>132.00฿</t>
+          <t>456.00฿</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -6819,7 +6807,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>S35386280517</t>
+          <t>910061892464</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -6829,48 +6817,48 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>UN-INV260811-00012</t>
+          <t>UN-INV260815-00046</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18475-23</t>
+ รถ lot18505-5-22</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>103.50</t>
+          <t>15.90</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>0.2236</t>
+          <t>0.0353</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>1,552.50฿</t>
+          <t>238.50฿</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
@@ -6880,7 +6868,7 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>气门嘴 顺心捷达，一票16件</t>
+          <t>记号蜡笔</t>
         </is>
       </c>
     </row>
@@ -6890,7 +6878,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>YT7635787693833</t>
+          <t>773434709817985</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -6900,38 +6888,38 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>UN-INV260811-00012</t>
+          <t>UN-INV260819-00010</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18473-6-41</t>
+ รถ lot18535-8</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>16/08/2026</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>13.80</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>0.0432</t>
+          <t>0.0184</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -6946,12 +6934,12 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>259.20฿</t>
+          <t>110.40฿</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>气压表/面单没有代码</t>
+          <t>锅具 二次包装货物变形</t>
         </is>
       </c>
     </row>
@@ -6961,7 +6949,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>ZY202465806614</t>
+          <t>435295775627304</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -6971,38 +6959,38 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>UN-INV260807-00009</t>
+          <t>UN-INV260811-00012</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>มอก.
- รถ lot18466-5-51</t>
+          <t>ธรรมดา
+ รถ lot18492-2</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>11.30</t>
+          <t>5.30</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>0.0655</t>
+          <t>0.0090</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -7012,17 +7000,17 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>79.50฿</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>445.40฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>电子数显胎压枪</t>
+          <t>配件 破损件</t>
         </is>
       </c>
     </row>
@@ -7032,7 +7020,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>113177184579#7</t>
+          <t>YT7636332367470</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -7042,38 +7030,38 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>UN-INV260807-00009</t>
+          <t>UN-INV260811-00012</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-17</t>
+ รถ lot18487-2-27</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>9.70</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>0.0305</t>
+          <t>0.0004</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -7088,10 +7076,14 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>183.00฿</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr"/>
+          <t>10.00฿</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>立牌</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -7099,7 +7091,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>113177184579#5</t>
+          <t>S35386280517#2</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -7109,38 +7101,38 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>UN-INV260807-00009</t>
+          <t>UN-INV260811-00012</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-16</t>
+ รถ lot18475-24</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>15.00</t>
+          <t>8.80</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>0.0137</t>
+          <t>0.0045</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -7150,7 +7142,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>225.00฿</t>
+          <t>132.00฿</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -7166,7 +7158,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>113177184579#4</t>
+          <t>S35386280517</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -7176,56 +7168,60 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>UN-INV260807-00009</t>
+          <t>UN-INV260811-00012</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-15</t>
+ รถ lot18475-23</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>7.30</t>
+          <t>103.50</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>0.0235</t>
+          <t>0.2236</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1,552.50฿</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>141.00฿</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>气门嘴 顺心捷达，一票16件</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -7233,7 +7229,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>113177184579#3</t>
+          <t>YT7635787693833</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -7243,38 +7239,38 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>UN-INV260807-00009</t>
+          <t>UN-INV260811-00012</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-14</t>
+ รถ lot18473-6-41</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>11.90</t>
+          <t>13.80</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>0.0302</t>
+          <t>0.0432</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -7289,10 +7285,14 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>181.20฿</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr"/>
+          <t>259.20฿</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>气压表/面单没有代码</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -7300,7 +7300,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>113177184579#6</t>
+          <t>ZY202465806614</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -7315,18 +7315,18 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>ธรรมดา
- รถ lot18463-13</t>
+          <t>มอก.
+ รถ lot18466-5-51</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -7336,12 +7336,12 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>26.10</t>
+          <t>11.30</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>0.0673</t>
+          <t>0.0655</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -7356,10 +7356,14 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>403.80฿</t>
-        </is>
-      </c>
-      <c r="N100" t="inlineStr"/>
+          <t>445.40฿</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>电子数显胎压枪</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -7367,7 +7371,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>435289604798626</t>
+          <t>113177184579#7</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -7383,7 +7387,7 @@
       <c r="E101" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18462-6-6</t>
+ รถ lot18463-17</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -7393,7 +7397,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -7403,12 +7407,12 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>9.60</t>
+          <t>9.70</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>0.0090</t>
+          <t>0.0305</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -7418,19 +7422,15 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>144.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N101" t="inlineStr">
-        <is>
-          <t>螺丝配件</t>
-        </is>
-      </c>
+          <t>183.00฿</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/cargo_packages_p1-5.xlsx
+++ b/cargo_packages_p1-5.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ZY202466680649#5</t>
+          <t>773445635488295</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -522,7 +522,7 @@
       <c r="E2" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18984-7-12</t>
+ รถ lot18986-4-60</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -542,12 +542,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>28.50</t>
+          <t>5.50</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.0816</t>
+          <t>0.0128</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -557,15 +557,19 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>82.50฿</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>489.60฿</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>配件</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -573,7 +577,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ZY202466680649#4</t>
+          <t>ZY202466680649#5</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -589,7 +593,7 @@
       <c r="E3" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18984-7-11</t>
+ รถ lot18984-7-12</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -599,7 +603,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -609,12 +613,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>8.70</t>
+          <t>28.50</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.0446</t>
+          <t>0.0816</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -629,7 +633,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>267.60฿</t>
+          <t>489.60฿</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -640,7 +644,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ZY202466680649#3</t>
+          <t>ZY202466680649#4</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -656,7 +660,7 @@
       <c r="E4" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18984-7-10</t>
+ รถ lot18984-7-11</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -666,7 +670,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +680,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>11.80</t>
+          <t>8.70</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.0811</t>
+          <t>0.0446</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -696,7 +700,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>486.60฿</t>
+          <t>267.60฿</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -707,7 +711,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ZY202466680649#2</t>
+          <t>ZY202466680649#3</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -723,7 +727,7 @@
       <c r="E5" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18984-7-9</t>
+ รถ lot18984-7-10</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -733,7 +737,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -743,12 +747,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>27.60</t>
+          <t>11.80</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.0800</t>
+          <t>0.0811</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -763,7 +767,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>480.00฿</t>
+          <t>486.60฿</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -774,7 +778,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ZY202466680649</t>
+          <t>ZY202466680649#2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -790,7 +794,7 @@
       <c r="E6" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18984-7-8</t>
+ รถ lot18984-7-9</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -800,7 +804,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -810,12 +814,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>8.20</t>
+          <t>27.60</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.0203</t>
+          <t>0.0800</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -825,19 +829,15 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>123.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>补胎贴</t>
-        </is>
-      </c>
+          <t>480.00฿</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -845,7 +845,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>435387211695084</t>
+          <t>ZY202466680649</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -861,17 +861,17 @@
       <c r="E7" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18966-4-53</t>
+ รถ lot18984-7-8</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>8.20</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.0116</t>
+          <t>0.0203</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -896,17 +896,17 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>123.00฿</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>69.60฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>宠物用品</t>
+          <t>补胎贴</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ZY202466680891#5</t>
+          <t>435387211695084</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -926,38 +926,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>UN-INV261008-00007</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18919-2-7</t>
+ รถ lot18966-4-53</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>19.70</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.0715</t>
+          <t>0.0116</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -972,10 +972,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>429.00฿</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>69.60฿</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>宠物用品</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -983,7 +987,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ZY202466680891#4</t>
+          <t>ZY202466680891#5</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -999,7 +1003,7 @@
       <c r="E9" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18919-2-6</t>
+ รถ lot18919-2-7</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1019,12 +1023,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>20.00</t>
+          <t>19.70</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.0640</t>
+          <t>0.0715</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1039,7 +1043,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>384.00฿</t>
+          <t>429.00฿</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1050,7 +1054,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ZY202466680891#3</t>
+          <t>ZY202466680891#4</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1066,7 +1070,7 @@
       <c r="E10" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18919-2-5</t>
+ รถ lot18919-2-6</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1086,12 +1090,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>15.80</t>
+          <t>20.00</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.0492</t>
+          <t>0.0640</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1106,7 +1110,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>295.20฿</t>
+          <t>384.00฿</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1117,7 +1121,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ZY202466680891#2</t>
+          <t>ZY202466680891#3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1133,7 +1137,7 @@
       <c r="E11" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18919-2-4</t>
+ รถ lot18919-2-5</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1153,7 +1157,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>16.20</t>
+          <t>15.80</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1184,7 +1188,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ZY202466680891</t>
+          <t>ZY202466680891#2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1200,7 +1204,7 @@
       <c r="E12" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18919-2-3</t>
+ รถ lot18919-2-4</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1220,7 +1224,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>15.90</t>
+          <t>16.20</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1243,11 +1247,7 @@
           <t>295.20฿</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>补胎胶片/5件</t>
-        </is>
-      </c>
+      <c r="N12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>S35386291018</t>
+          <t>ZY202466680891</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1265,58 +1265,58 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>UN-INV261005-00021</t>
+          <t>UN-INV261008-00007</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18901-6-32</t>
+ รถ lot18919-2-3</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>82.80</t>
+          <t>15.90</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0.1641</t>
+          <t>0.0492</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>1,242.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>295.20฿</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>配件，12件</t>
+          <t>补胎胶片/5件</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>113405301091#3</t>
+          <t>S35386291018</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1342,7 +1342,7 @@
       <c r="E14" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18901-7-3</t>
+ รถ lot18901-6-32</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1362,30 +1362,34 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>13.10</t>
+          <t>82.80</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.0347</t>
+          <t>0.1641</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1,242.00฿</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>208.20฿</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>配件，12件</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1393,7 +1397,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>113405301091#2</t>
+          <t>113405301091#3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1409,7 +1413,7 @@
       <c r="E15" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18901-7-2</t>
+ รถ lot18901-7-3</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1429,12 +1433,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>16.10</t>
+          <t>13.10</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.0397</t>
+          <t>0.0347</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1444,12 +1448,12 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>241.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>208.20฿</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1460,7 +1464,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>113405301091</t>
+          <t>113405301091#2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1476,7 +1480,7 @@
       <c r="E16" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18901-7-1</t>
+ รถ lot18901-7-2</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1496,12 +1500,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>33.60</t>
+          <t>16.10</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>0.0832</t>
+          <t>0.0397</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1511,7 +1515,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>504.00฿</t>
+          <t>241.50฿</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1519,11 +1523,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>补胎胶片/3件</t>
-        </is>
-      </c>
+      <c r="N16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>YT7646197126750</t>
+          <t>113405301091</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1547,32 +1547,32 @@
       <c r="E17" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18887-50</t>
+ รถ lot18901-7-1</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>26/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>26/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>8.30</t>
+          <t>33.60</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.0127</t>
+          <t>0.0832</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>124.50฿</t>
+          <t>504.00฿</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1592,7 +1592,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>补胎胶片/3件</t>
         </is>
       </c>
     </row>
@@ -1602,7 +1602,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ZY202462495078</t>
+          <t>YT7646197126750</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1612,38 +1612,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>UN-INV260926-00006</t>
+          <t>UN-INV261005-00021</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18844-9-4</t>
+ รถ lot18887-50</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>26/09/2026</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>26/09/2026</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>14.30</t>
+          <t>8.30</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>0.0624</t>
+          <t>0.0127</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1653,17 +1653,17 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>124.50฿</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>374.40฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>胎压表</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -1673,7 +1673,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>S71749075994</t>
+          <t>ZY202462495078</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1683,38 +1683,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>UN-INV260924-00056</t>
+          <t>UN-INV260926-00006</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18830-6-30</t>
+ รถ lot18844-9-4</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>119.00</t>
+          <t>14.30</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>0.2302</t>
+          <t>0.0624</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1724,17 +1724,17 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>1,785.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>374.40฿</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>真空胎扒胎机配件/木箱</t>
+          <t>胎压表</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>435358249576981</t>
+          <t>S71749075994</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1760,17 +1760,17 @@
       <c r="E20" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18815-4-6</t>
+ รถ lot18830-6-30</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1780,12 +1780,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>5.20</t>
+          <t>119.00</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0.0044</t>
+          <t>0.2302</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>78.00฿</t>
+          <t>1,785.00฿</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1805,7 +1805,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>气门嘴</t>
+          <t>真空胎扒胎机配件/木箱</t>
         </is>
       </c>
     </row>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>S71195667064</t>
+          <t>435358249576981</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1831,12 +1831,12 @@
       <c r="E21" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18810-6-3</t>
+ รถ lot18815-4-6</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1846,37 +1846,37 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>165.00</t>
+          <t>5.20</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.8568</t>
+          <t>0.0044</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>78.00฿</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>5,140.80฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>千斤顶，3件，客户不打木架发</t>
+          <t>气门嘴</t>
         </is>
       </c>
     </row>
@@ -1886,7 +1886,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>113350746029#4</t>
+          <t>S71195667064</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1902,17 +1902,17 @@
       <c r="E22" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18799-6-32</t>
+ รถ lot18810-6-3</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1922,17 +1922,17 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>27.70</t>
+          <t>165.00</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.0800</t>
+          <t>0.8568</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1942,10 +1942,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>480.00฿</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
+          <t>5,140.80฿</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>千斤顶，3件，客户不打木架发</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1953,7 +1957,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>113350746029#3</t>
+          <t>113350746029#4</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1969,7 +1973,7 @@
       <c r="E23" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18799-6-31</t>
+ รถ lot18799-6-32</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1989,12 +1993,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>10.90</t>
+          <t>27.70</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.0377</t>
+          <t>0.0800</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2009,7 +2013,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>226.20฿</t>
+          <t>480.00฿</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -2020,7 +2024,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>113350746029#2</t>
+          <t>113350746029#3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2036,7 +2040,7 @@
       <c r="E24" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18799-6-30</t>
+ รถ lot18799-6-31</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2056,12 +2060,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>15.00</t>
+          <t>10.90</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.0101</t>
+          <t>0.0377</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2071,12 +2075,12 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>225.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>226.20฿</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -2087,7 +2091,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>113350746029</t>
+          <t>113350746029#2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2103,7 +2107,7 @@
       <c r="E25" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18799-6-29</t>
+ รถ lot18799-6-30</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2123,12 +2127,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>16.50</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.0127</t>
+          <t>0.0101</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2138,7 +2142,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>247.50฿</t>
+          <t>225.00฿</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2146,11 +2150,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>真空胎加固修理补片</t>
-        </is>
-      </c>
+      <c r="N25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -2158,7 +2158,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>760246657062</t>
+          <t>113350746029</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2174,7 +2174,7 @@
       <c r="E26" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18799-7-3</t>
+ รถ lot18799-6-29</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2194,12 +2194,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>16.50</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>0.0005</t>
+          <t>0.0127</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2209,17 +2209,17 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>247.50฿</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>10.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>气门嘴，轮胎修补工具，气门芯宣传册</t>
+          <t>真空胎加固修理补片</t>
         </is>
       </c>
     </row>
@@ -2229,7 +2229,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>113348267192#2</t>
+          <t>760246657062</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2239,38 +2239,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>UN-INV260921-00019</t>
+          <t>UN-INV260924-00056</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18795-2-7</t>
+ รถ lot18799-7-3</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>28.10</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.0628</t>
+          <t>0.0005</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2280,15 +2280,19 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>421.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
+          <t>10.00฿</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>气门嘴，轮胎修补工具，气门芯宣传册</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2296,7 +2300,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>113348267192</t>
+          <t>113348267192#2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2312,7 +2316,7 @@
       <c r="E28" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18795-2-6</t>
+ รถ lot18795-2-7</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2332,12 +2336,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>19.50</t>
+          <t>28.10</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.0505</t>
+          <t>0.0628</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2347,19 +2351,15 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>421.50฿</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>303.00฿</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>补胎胶片</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2367,7 +2367,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ZY202472578299</t>
+          <t>113348267192</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2377,43 +2377,43 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>UN-INV260918-00012</t>
+          <t>UN-INV260921-00019</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18758-7-43</t>
+ รถ lot18795-2-6</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>47.40</t>
+          <t>19.50</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0.1603</t>
+          <t>0.0505</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2423,12 +2423,12 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>961.20฿</t>
+          <t>303.00฿</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>补胎贴，3件</t>
+          <t>补胎胶片</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>773440822655698</t>
+          <t>ZY202472578299</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2454,7 +2454,7 @@
       <c r="E30" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18758-4-31</t>
+ รถ lot18758-7-43</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2474,32 +2474,32 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>47.40</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.0022</t>
+          <t>0.1603</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>18.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>961.20฿</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>钻头</t>
+          <t>补胎贴，3件</t>
         </is>
       </c>
     </row>
@@ -2509,7 +2509,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>YT7642998390994</t>
+          <t>773440822655698</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2525,7 +2525,7 @@
       <c r="E31" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18769-3-57</t>
+ รถ lot18758-4-31</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2535,7 +2535,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2545,12 +2545,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>5.80</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.0070</t>
+          <t>0.0022</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2560,7 +2560,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>87.00฿</t>
+          <t>18.00฿</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2570,7 +2570,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>钻头</t>
         </is>
       </c>
     </row>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>DPK212614057101</t>
+          <t>YT7642998390994</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2590,38 +2590,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>UN-INV260916-00003</t>
+          <t>UN-INV260918-00012</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18749-4-3</t>
+ รถ lot18769-3-57</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>9.60</t>
+          <t>5.80</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.0060</t>
+          <t>0.0070</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>144.00฿</t>
+          <t>87.00฿</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2641,7 +2641,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>轮胎气门嘴</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -2651,7 +2651,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>79031204783305</t>
+          <t>DPK212614057101</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2667,7 +2667,7 @@
       <c r="E33" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18744-6-15</t>
+ รถ lot18749-4-3</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2687,12 +2687,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>9.60</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.0020</t>
+          <t>0.0060</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>39.00฿</t>
+          <t>144.00฿</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>轮胎气门嘴</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>435342988112655</t>
+          <t>79031204783305</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2738,17 +2738,17 @@
       <c r="E34" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18743-3-34</t>
+ รถ lot18744-6-15</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2758,12 +2758,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.0014</t>
+          <t>0.0020</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2773,17 +2773,17 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>39.00฿</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>10.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>橡胶垫圈</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>435343890137834</t>
+          <t>435342988112655</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2809,7 +2809,7 @@
       <c r="E35" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18743-7-25</t>
+ รถ lot18743-3-34</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>21.40</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.0080</t>
+          <t>0.0014</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2844,17 +2844,17 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>321.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10.00฿</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>扒胎机包胶撬棍</t>
+          <t>橡胶垫圈</t>
         </is>
       </c>
     </row>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>YT7642670434639</t>
+          <t>435343890137834</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2880,7 +2880,7 @@
       <c r="E36" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18743-2-8</t>
+ รถ lot18743-7-25</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2900,12 +2900,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>21.40</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.0010</t>
+          <t>0.0080</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2915,7 +2915,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>12.00฿</t>
+          <t>321.00฿</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2925,7 +2925,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>片片</t>
+          <t>扒胎机包胶撬棍</t>
         </is>
       </c>
     </row>
@@ -2935,7 +2935,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>93015797092</t>
+          <t>YT7642670434639</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2945,18 +2945,18 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>UN-INV260914-00014</t>
+          <t>UN-INV260916-00003</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18735-4-40</t>
+ รถ lot18743-2-8</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2966,17 +2966,17 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>12/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>8.60</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.0148</t>
+          <t>0.0010</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2986,7 +2986,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>129.00฿</t>
+          <t>12.00฿</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>仪表</t>
+          <t>片片</t>
         </is>
       </c>
     </row>
@@ -3006,7 +3006,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>YT7642390374765</t>
+          <t>93015797092</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3016,13 +3016,13 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>UN-INV260914-00015</t>
+          <t>UN-INV260914-00014</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18735-4-20</t>
+ รถ lot18735-4-40</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -3042,12 +3042,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>20.80</t>
+          <t>8.60</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.0598</t>
+          <t>0.0148</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -3057,17 +3057,17 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>129.00฿</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>358.80฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>打磨机</t>
+          <t>仪表</t>
         </is>
       </c>
     </row>
@@ -3077,7 +3077,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>435342255104130</t>
+          <t>YT7642390374765</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3087,13 +3087,13 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>UN-INV260914-00014</t>
+          <t>UN-INV260914-00015</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18735-43</t>
+ รถ lot18735-4-20</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -3113,12 +3113,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>4.90</t>
+          <t>20.80</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.0172</t>
+          <t>0.0598</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>103.20฿</t>
+          <t>358.80฿</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>轮毂保护套</t>
+          <t>打磨机</t>
         </is>
       </c>
     </row>
@@ -3148,7 +3148,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>773440312345715</t>
+          <t>435342255104130</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3164,7 +3164,7 @@
       <c r="E40" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18735-3-78</t>
+ รถ lot18735-43</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>4.90</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.0013</t>
+          <t>0.0172</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -3199,17 +3199,17 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>19.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>103.20฿</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>轮毂保护套</t>
         </is>
       </c>
     </row>
@@ -3219,7 +3219,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>773440291470393</t>
+          <t>773440312345715</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3235,7 +3235,7 @@
       <c r="E41" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18735-34</t>
+ รถ lot18735-3-78</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -3255,12 +3255,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.0029</t>
+          <t>0.0013</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -3270,7 +3270,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>48.00฿</t>
+          <t>19.50฿</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>球阀</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -3290,7 +3290,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>435342261175750</t>
+          <t>773440291470393</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3300,13 +3300,13 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>UN-INV260914-00015</t>
+          <t>UN-INV260914-00014</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18736-13</t>
+ รถ lot18735-34</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3326,12 +3326,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>13.90</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.0137</t>
+          <t>0.0029</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>208.50฿</t>
+          <t>48.00฿</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>球阀</t>
         </is>
       </c>
     </row>
@@ -3361,7 +3361,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ZY202461195200</t>
+          <t>435342261175750</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3377,7 +3377,7 @@
       <c r="E43" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18728-7-13</t>
+ รถ lot18736-13</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -3392,17 +3392,17 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>13/09/2026</t>
+          <t>12/09/2026</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>47.40</t>
+          <t>13.90</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.0116</t>
+          <t>0.0137</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>711.00฿</t>
+          <t>208.50฿</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3432,7 +3432,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>79030687835952</t>
+          <t>ZY202461195200</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3442,13 +3442,13 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>UN-INV260914-00014</t>
+          <t>UN-INV260914-00015</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18728-3-64</t>
+ รถ lot18728-7-13</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -3468,12 +3468,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>4.30</t>
+          <t>47.40</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.0030</t>
+          <t>0.0116</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3483,7 +3483,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>64.50฿</t>
+          <t>711.00฿</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>接头配件</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -3503,7 +3503,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>LJ20722214#3</t>
+          <t>79030687835952</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3513,38 +3513,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>UN-INV260912-00011</t>
+          <t>UN-INV260914-00014</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18726-7-8</t>
+ รถ lot18728-3-64</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>13/09/2026</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>14.00</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.0171</t>
+          <t>0.0030</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3554,7 +3554,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>210.00฿</t>
+          <t>64.50฿</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3562,7 +3562,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>接头配件</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -3570,7 +3574,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>LJ20722214#2</t>
+          <t>LJ20722214#3</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3586,7 +3590,7 @@
       <c r="E46" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18726-7-7</t>
+ รถ lot18726-7-8</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -3606,12 +3610,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>11.90</t>
+          <t>14.00</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>0.0089</t>
+          <t>0.0171</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3621,7 +3625,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>178.50฿</t>
+          <t>210.00฿</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3637,7 +3641,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>LJ20722214</t>
+          <t>LJ20722214#2</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3653,7 +3657,7 @@
       <c r="E47" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18726-7-6</t>
+ รถ lot18726-7-7</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -3673,12 +3677,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>16.00</t>
+          <t>11.90</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>0.0144</t>
+          <t>0.0089</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3688,7 +3692,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>240.00฿</t>
+          <t>178.50฿</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3696,11 +3700,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>电板套筒配件/3件</t>
-        </is>
-      </c>
+      <c r="N47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>YT7641966426761</t>
+          <t>LJ20722214</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3724,17 +3724,17 @@
       <c r="E48" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18714-9-23</t>
+ รถ lot18726-7-6</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>13.60</t>
+          <t>16.00</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>0.0422</t>
+          <t>0.0144</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3759,17 +3759,17 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>240.00฿</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>253.20฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>带表汽车轮胎打气嘴</t>
+          <t>电板套筒配件/3件</t>
         </is>
       </c>
     </row>
@@ -3779,7 +3779,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ZY202471681117#2</t>
+          <t>YT7641966426761</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3795,7 +3795,7 @@
       <c r="E49" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18714-9-8</t>
+ รถ lot18714-9-23</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3815,12 +3815,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>11.80</t>
+          <t>13.60</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>0.0832</t>
+          <t>0.0422</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3835,10 +3835,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>499.20฿</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
+          <t>253.20฿</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>带表汽车轮胎打气嘴</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -3846,7 +3850,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ZY202471681117</t>
+          <t>ZY202471681117#2</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3862,7 +3866,7 @@
       <c r="E50" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18714-9-7</t>
+ รถ lot18714-9-8</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3882,12 +3886,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>7.70</t>
+          <t>11.80</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>0.0493</t>
+          <t>0.0832</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3902,14 +3906,10 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>295.80฿</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>补胎胶片/2件</t>
-        </is>
-      </c>
+          <t>499.20฿</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -3917,7 +3917,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>302285502767#2</t>
+          <t>ZY202471681117</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3933,7 +3933,7 @@
       <c r="E51" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18714-8-10</t>
+ รถ lot18714-9-7</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>33.70</t>
+          <t>7.70</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>0.0145</t>
+          <t>0.0493</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3968,15 +3968,19 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>505.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
+          <t>295.80฿</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>补胎胶片/2件</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -3984,7 +3988,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>302285502767</t>
+          <t>302285502767#2</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -4000,7 +4004,7 @@
       <c r="E52" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18714-8-9</t>
+ รถ lot18714-8-10</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -4020,12 +4024,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>23.40</t>
+          <t>33.70</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>0.0123</t>
+          <t>0.0145</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -4035,7 +4039,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>351.00฿</t>
+          <t>505.50฿</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -4043,11 +4047,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>扳手</t>
-        </is>
-      </c>
+      <c r="N52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -4055,7 +4055,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>LJ20716178#2</t>
+          <t>302285502767</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -4065,18 +4065,18 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>UN-INV260911-00013</t>
+          <t>UN-INV260912-00011</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18713-6-65</t>
+ รถ lot18714-8-9</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -4086,17 +4086,17 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>19.50</t>
+          <t>23.40</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>0.0075</t>
+          <t>0.0123</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>292.50฿</t>
+          <t>351.00฿</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -4114,7 +4114,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr"/>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>扳手</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -4122,7 +4126,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>LJ20716178</t>
+          <t>LJ20716178#2</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -4138,7 +4142,7 @@
       <c r="E54" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18713-6-64</t>
+ รถ lot18713-6-65</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -4158,7 +4162,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>19.60</t>
+          <t>19.50</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -4173,7 +4177,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>294.00฿</t>
+          <t>292.50฿</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -4181,11 +4185,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>配件</t>
-        </is>
-      </c>
+      <c r="N54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>435338972466812</t>
+          <t>LJ20716178</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -4209,7 +4209,7 @@
       <c r="E55" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18710-6-35</t>
+ รถ lot18713-6-64</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>13.10</t>
+          <t>19.60</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>0.0624</t>
+          <t>0.0075</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -4244,17 +4244,17 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>294.00฿</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>374.40฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>修补工具</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -4264,7 +4264,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>435334324045675</t>
+          <t>435338972466812</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -4274,38 +4274,38 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>UN-INV260908-00009</t>
+          <t>UN-INV260911-00013</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18696-14</t>
+ รถ lot18710-6-35</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>10.80</t>
+          <t>13.10</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>0.0088</t>
+          <t>0.0624</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -4315,17 +4315,17 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>162.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>374.40฿</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>修补工具</t>
         </is>
       </c>
     </row>
@@ -4335,7 +4335,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>YT7641276428798</t>
+          <t>435334324045675</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -4351,7 +4351,7 @@
       <c r="E57" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18697-11</t>
+ รถ lot18696-14</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>9.50</t>
+          <t>10.80</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>0.0296</t>
+          <t>0.0088</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -4386,12 +4386,12 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>162.00฿</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>177.60฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>79029430531776</t>
+          <t>YT7641276428798</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -4416,18 +4416,18 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>UN-INV260907-00015</t>
+          <t>UN-INV260908-00009</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18689-26</t>
+ รถ lot18697-11</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -4437,17 +4437,17 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>9.50</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>0.0135</t>
+          <t>0.0296</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -4462,12 +4462,12 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>81.00฿</t>
+          <t>177.60฿</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>卡套</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -4477,7 +4477,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>113282578128#2</t>
+          <t>79029430531776</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4493,17 +4493,17 @@
       <c r="E59" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18683-4</t>
+ รถ lot18689-26</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>38.00</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>0.1601</t>
+          <t>0.0135</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4533,10 +4533,14 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>960.60฿</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
+          <t>81.00฿</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>卡套</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -4544,7 +4548,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>113282578128</t>
+          <t>113282578128#2</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4560,7 +4564,7 @@
       <c r="E60" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18683-3</t>
+ รถ lot18683-4</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -4580,12 +4584,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>27.50</t>
+          <t>38.00</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>0.1566</t>
+          <t>0.1601</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -4600,14 +4604,10 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>939.60฿</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>压条取出器 一票两件破损件</t>
-        </is>
-      </c>
+          <t>960.60฿</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -4615,7 +4615,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>82730128600#3</t>
+          <t>113282578128</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4631,12 +4631,12 @@
       <c r="E61" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18678-6-21</t>
+ รถ lot18683-3</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>30/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>33.00</t>
+          <t>27.50</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>0.0122</t>
+          <t>0.1566</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -4666,15 +4666,19 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>495.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
+          <t>939.60฿</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>压条取出器 一票两件破损件</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -4682,7 +4686,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>82730128600#2</t>
+          <t>82730128600#3</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4698,7 +4702,7 @@
       <c r="E62" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18678-6-20</t>
+ รถ lot18678-6-21</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -4718,12 +4722,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>27.60</t>
+          <t>33.00</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>0.0095</t>
+          <t>0.0122</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -4733,7 +4737,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>414.00฿</t>
+          <t>495.00฿</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -4749,7 +4753,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>82730128600</t>
+          <t>82730128600#2</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4765,7 +4769,7 @@
       <c r="E63" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18678-6-19</t>
+ รถ lot18678-6-20</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -4785,12 +4789,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>28.10</t>
+          <t>27.60</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>0.0118</t>
+          <t>0.0095</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -4800,7 +4804,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>421.50฿</t>
+          <t>414.00฿</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -4808,11 +4812,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>五金配件/3件</t>
-        </is>
-      </c>
+      <c r="N63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -4820,7 +4820,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>113278387839#3</t>
+          <t>82730128600</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4830,38 +4830,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>UN-INV260903-00023</t>
+          <t>UN-INV260907-00015</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18663-8-3</t>
+ รถ lot18678-6-19</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>30/08/2026</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>25.30</t>
+          <t>28.10</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>0.0404</t>
+          <t>0.0118</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>379.50฿</t>
+          <t>421.50฿</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -4879,7 +4879,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N64" t="inlineStr"/>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>五金配件/3件</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -4887,7 +4891,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>113278387839#2</t>
+          <t>113278387839#3</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4903,7 +4907,7 @@
       <c r="E65" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18663-8-2</t>
+ รถ lot18663-8-3</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -4923,12 +4927,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>26.10</t>
+          <t>25.30</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>0.0304</t>
+          <t>0.0404</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -4938,7 +4942,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>391.50฿</t>
+          <t>379.50฿</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -4954,7 +4958,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>113278387839</t>
+          <t>113278387839#2</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4970,7 +4974,7 @@
       <c r="E66" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18663-8-1</t>
+ รถ lot18663-8-2</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -4990,12 +4994,12 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>9.10</t>
+          <t>26.10</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>0.0144</t>
+          <t>0.0304</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -5005,7 +5009,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>136.50฿</t>
+          <t>391.50฿</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -5013,11 +5017,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N66" t="inlineStr">
-        <is>
-          <t>配件/3件</t>
-        </is>
-      </c>
+      <c r="N66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -5025,7 +5025,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>113276098937#3</t>
+          <t>113278387839</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -5035,38 +5035,38 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>UN-INV260901-00057</t>
+          <t>UN-INV260903-00023</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-45</t>
+ รถ lot18663-8-1</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>17.80</t>
+          <t>9.10</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>0.0302</t>
+          <t>0.0144</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>267.00฿</t>
+          <t>136.50฿</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -5084,7 +5084,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N67" t="inlineStr"/>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>配件/3件</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -5092,7 +5096,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>113276098937#2</t>
+          <t>113276098937#3</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -5108,7 +5112,7 @@
       <c r="E68" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-44</t>
+ รถ lot18655-9-45</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -5128,12 +5132,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>10.90</t>
+          <t>17.80</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>0.0313</t>
+          <t>0.0302</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -5143,12 +5147,12 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>267.00฿</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>187.80฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N68" t="inlineStr"/>
@@ -5159,7 +5163,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>113276098937</t>
+          <t>113276098937#2</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -5175,7 +5179,7 @@
       <c r="E69" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-43</t>
+ รถ lot18655-9-44</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -5195,12 +5199,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>33.60</t>
+          <t>10.90</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>0.0825</t>
+          <t>0.0313</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -5210,19 +5214,15 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>504.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr">
-        <is>
-          <t>补胎胶片+配件/3件</t>
-        </is>
-      </c>
+          <t>187.80฿</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -5230,7 +5230,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>ZY202464580877#4</t>
+          <t>113276098937</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -5246,7 +5246,7 @@
       <c r="E70" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-17</t>
+ รถ lot18655-9-43</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>20.10</t>
+          <t>33.60</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>0.0466</t>
+          <t>0.0825</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>301.50฿</t>
+          <t>504.00฿</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -5289,7 +5289,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N70" t="inlineStr"/>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>补胎胶片+配件/3件</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -5297,7 +5301,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>ZY202464580877#7</t>
+          <t>ZY202464580877#4</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -5313,7 +5317,7 @@
       <c r="E71" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-16</t>
+ รถ lot18655-9-17</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -5333,12 +5337,12 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>16.60</t>
+          <t>20.10</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>0.0430</t>
+          <t>0.0466</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -5348,12 +5352,12 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>301.50฿</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>258.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N71" t="inlineStr"/>
@@ -5364,7 +5368,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>ZY202464580877#2</t>
+          <t>ZY202464580877#7</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -5380,7 +5384,7 @@
       <c r="E72" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-15</t>
+ รถ lot18655-9-16</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -5400,12 +5404,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>25.10</t>
+          <t>16.60</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>0.0483</t>
+          <t>0.0430</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -5415,12 +5419,12 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>376.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>258.00฿</t>
         </is>
       </c>
       <c r="N72" t="inlineStr"/>
@@ -5431,7 +5435,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>ZY202464580877#8</t>
+          <t>ZY202464580877#2</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -5447,7 +5451,7 @@
       <c r="E73" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-14</t>
+ รถ lot18655-9-15</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -5467,12 +5471,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>28.90</t>
+          <t>25.10</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>0.0800</t>
+          <t>0.0483</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -5482,12 +5486,12 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>376.50฿</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>480.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N73" t="inlineStr"/>
@@ -5498,7 +5502,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>ZY202464580877#6</t>
+          <t>ZY202464580877#8</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -5514,7 +5518,7 @@
       <c r="E74" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-13</t>
+ รถ lot18655-9-14</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -5534,12 +5538,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>20.90</t>
+          <t>28.90</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>0.0534</t>
+          <t>0.0800</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -5554,7 +5558,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>320.40฿</t>
+          <t>480.00฿</t>
         </is>
       </c>
       <c r="N74" t="inlineStr"/>
@@ -5565,7 +5569,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>ZY202464580877#5</t>
+          <t>ZY202464580877#6</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -5581,7 +5585,7 @@
       <c r="E75" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-12</t>
+ รถ lot18655-9-13</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -5601,12 +5605,12 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>26.20</t>
+          <t>20.90</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>0.0535</t>
+          <t>0.0534</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -5616,12 +5620,12 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>393.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>320.40฿</t>
         </is>
       </c>
       <c r="N75" t="inlineStr"/>
@@ -5632,7 +5636,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>ZY202464580877</t>
+          <t>ZY202464580877#5</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5648,7 +5652,7 @@
       <c r="E76" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-11</t>
+ รถ lot18655-9-12</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -5668,12 +5672,12 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>20.70</t>
+          <t>26.20</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>0.0531</t>
+          <t>0.0535</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -5683,12 +5687,12 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>393.00฿</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>318.60฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N76" t="inlineStr"/>
@@ -5699,7 +5703,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>ZY202464580877#9</t>
+          <t>ZY202464580877</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -5715,7 +5719,7 @@
       <c r="E77" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-10</t>
+ รถ lot18655-9-11</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -5735,12 +5739,12 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>27.70</t>
+          <t>20.70</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>0.0800</t>
+          <t>0.0531</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -5755,7 +5759,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>480.00฿</t>
+          <t>318.60฿</t>
         </is>
       </c>
       <c r="N77" t="inlineStr"/>
@@ -5766,7 +5770,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>ZY202464580877#3</t>
+          <t>ZY202464580877#9</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -5782,7 +5786,7 @@
       <c r="E78" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-9</t>
+ รถ lot18655-9-10</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -5802,12 +5806,12 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>27.10</t>
+          <t>27.70</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>0.0567</t>
+          <t>0.0800</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -5817,19 +5821,15 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>406.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr">
-        <is>
-          <t>补胎胶片/9件</t>
-        </is>
-      </c>
+          <t>480.00฿</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -5837,7 +5837,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>S71090288685</t>
+          <t>ZY202464580877#3</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -5847,38 +5847,38 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>UN-INV260831-00017</t>
+          <t>UN-INV260901-00057</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18634-7-3</t>
+ รถ lot18655-9-9</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>29/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>12.10</t>
+          <t>27.10</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>0.0240</t>
+          <t>0.0567</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>181.50฿</t>
+          <t>406.50฿</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -5898,7 +5898,7 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>补胎胶片/9件</t>
         </is>
       </c>
     </row>
@@ -5908,7 +5908,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>YT7638092409979</t>
+          <t>S71090288685</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -5918,38 +5918,38 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>UN-INV260822-00010</t>
+          <t>UN-INV260831-00017</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18569-7-7</t>
+ รถ lot18634-7-3</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>16/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>16/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>29/08/2026</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>15.00</t>
+          <t>12.10</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>0.0140</t>
+          <t>0.0240</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -5959,7 +5959,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>225.00฿</t>
+          <t>181.50฿</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -5979,7 +5979,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>435308000517585</t>
+          <t>YT7638092409979</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -5995,32 +5995,32 @@
       <c r="E81" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18550-6-11</t>
+ รถ lot18569-7-7</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>16/08/2026</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>16/08/2026</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>0.0032</t>
+          <t>0.0140</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -6030,7 +6030,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>54.00฿</t>
+          <t>225.00฿</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -6040,7 +6040,7 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>气门嘴</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -6050,7 +6050,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>710094401487</t>
+          <t>435308000517585</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -6066,17 +6066,17 @@
       <c r="E82" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18544-8-14</t>
+ รถ lot18550-6-11</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -6086,32 +6086,32 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>107.10</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>0.4536</t>
+          <t>0.0032</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>54.00฿</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>2,721.60฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>空的高压充气罐/一票10件，仓库实收到9件，已确认收到的9件先发</t>
+          <t>气门嘴</t>
         </is>
       </c>
     </row>
@@ -6121,7 +6121,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>773435675083665</t>
+          <t>710094401487</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -6131,58 +6131,58 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>UN-INV260815-00046</t>
+          <t>UN-INV260822-00010</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18526-6-17</t>
+ รถ lot18544-8-14</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>13.10</t>
+          <t>107.10</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>0.0214</t>
+          <t>0.4536</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>196.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2,721.60฿</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>补胎工具</t>
+          <t>空的高压充气罐/一票10件，仓库实收到9件，已确认收到的9件先发</t>
         </is>
       </c>
     </row>
@@ -6192,7 +6192,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>YT7637032206975</t>
+          <t>773435675083665</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -6202,38 +6202,38 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>UN-INV260819-00010</t>
+          <t>UN-INV260815-00046</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>มอก.
- รถ lot18523-6-30</t>
+          <t>ธรรมดา
+ รถ lot18526-6-17</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>16/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>9.60</t>
+          <t>13.10</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>0.0316</t>
+          <t>0.0214</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -6243,17 +6243,17 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>196.50฿</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>214.88฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>气动模具研磨机+配件</t>
+          <t>补胎工具</t>
         </is>
       </c>
     </row>
@@ -6263,7 +6263,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>ZY202466648481#5</t>
+          <t>YT7637032206975</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -6273,13 +6273,13 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>UN-INV260815-00046</t>
+          <t>UN-INV260819-00010</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>ธรรมดา
- รถ lot18519-6-17</t>
+          <t>มอก.
+ รถ lot18523-6-30</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -6294,17 +6294,17 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>15/08/2026</t>
+          <t>16/08/2026</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>16.10</t>
+          <t>9.60</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>0.0493</t>
+          <t>0.0316</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -6319,10 +6319,14 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>295.80฿</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr"/>
+          <t>214.88฿</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>气动模具研磨机+配件</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -6330,7 +6334,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>ZY202466648481#4</t>
+          <t>ZY202466648481#5</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -6346,7 +6350,7 @@
       <c r="E86" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18519-6-16</t>
+ รถ lot18519-6-17</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -6366,12 +6370,12 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>20.50</t>
+          <t>16.10</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>0.0656</t>
+          <t>0.0493</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -6386,7 +6390,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>393.60฿</t>
+          <t>295.80฿</t>
         </is>
       </c>
       <c r="N86" t="inlineStr"/>
@@ -6397,7 +6401,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>ZY202466648481#3</t>
+          <t>ZY202466648481#4</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -6413,7 +6417,7 @@
       <c r="E87" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18519-6-15</t>
+ รถ lot18519-6-16</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -6433,12 +6437,12 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>15.70</t>
+          <t>20.50</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>0.0508</t>
+          <t>0.0656</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -6453,7 +6457,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>304.80฿</t>
+          <t>393.60฿</t>
         </is>
       </c>
       <c r="N87" t="inlineStr"/>
@@ -6464,7 +6468,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>ZY202466648481#2</t>
+          <t>ZY202466648481#3</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -6480,7 +6484,7 @@
       <c r="E88" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18519-6-14</t>
+ รถ lot18519-6-15</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -6500,12 +6504,12 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>20.20</t>
+          <t>15.70</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>0.0660</t>
+          <t>0.0508</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -6520,7 +6524,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>396.00฿</t>
+          <t>304.80฿</t>
         </is>
       </c>
       <c r="N88" t="inlineStr"/>
@@ -6531,7 +6535,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>ZY202466648481</t>
+          <t>ZY202466648481#2</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -6547,7 +6551,7 @@
       <c r="E89" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18519-6-13</t>
+ รถ lot18519-6-14</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -6567,12 +6571,12 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>15.80</t>
+          <t>20.20</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>0.0522</t>
+          <t>0.0660</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -6587,14 +6591,10 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>313.20฿</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr">
-        <is>
-          <t>补胎胶条/5件</t>
-        </is>
-      </c>
+          <t>396.00฿</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -6602,7 +6602,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>113204676267#2</t>
+          <t>ZY202466648481</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -6618,32 +6618,32 @@
       <c r="E90" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18518-5-3</t>
+ รถ lot18519-6-13</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>15/08/2026</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>24.60</t>
+          <t>15.80</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>0.0608</t>
+          <t>0.0522</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -6653,15 +6653,19 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>369.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr"/>
+          <t>313.20฿</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>补胎胶条/5件</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -6669,7 +6673,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>113204676267</t>
+          <t>113204676267#2</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -6685,7 +6689,7 @@
       <c r="E91" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18518-5-2</t>
+ รถ lot18518-5-3</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -6705,12 +6709,12 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>25.00</t>
+          <t>24.60</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>0.0566</t>
+          <t>0.0608</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -6720,7 +6724,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>375.00฿</t>
+          <t>369.00฿</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -6728,11 +6732,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N91" t="inlineStr">
-        <is>
-          <t>真空胎冷补胶片</t>
-        </is>
-      </c>
+      <c r="N91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -6740,7 +6740,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>910061892464#2</t>
+          <t>113204676267</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -6756,32 +6756,32 @@
       <c r="E92" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18505-5-23</t>
+ รถ lot18518-5-2</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>30.40</t>
+          <t>25.00</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>0.0523</t>
+          <t>0.0566</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>456.00฿</t>
+          <t>375.00฿</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -6799,7 +6799,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N92" t="inlineStr"/>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>真空胎冷补胶片</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -6807,7 +6811,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>910061892464</t>
+          <t>910061892464#2</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -6823,7 +6827,7 @@
       <c r="E93" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18505-5-22</t>
+ รถ lot18505-5-23</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -6843,12 +6847,12 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>15.90</t>
+          <t>30.40</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>0.0353</t>
+          <t>0.0523</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -6858,7 +6862,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>238.50฿</t>
+          <t>456.00฿</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
@@ -6866,11 +6870,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N93" t="inlineStr">
-        <is>
-          <t>记号蜡笔</t>
-        </is>
-      </c>
+      <c r="N93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -6878,7 +6878,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>773434709817985</t>
+          <t>910061892464</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -6888,38 +6888,38 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>UN-INV260819-00010</t>
+          <t>UN-INV260815-00046</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18535-8</t>
+ รถ lot18505-5-22</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>16/08/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>15.90</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>0.0184</t>
+          <t>0.0353</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -6929,17 +6929,17 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>238.50฿</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>110.40฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>锅具 二次包装货物变形</t>
+          <t>记号蜡笔</t>
         </is>
       </c>
     </row>
@@ -6949,7 +6949,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>435295775627304</t>
+          <t>773434709817985</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -6959,38 +6959,38 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>UN-INV260811-00012</t>
+          <t>UN-INV260819-00010</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18492-2</t>
+ รถ lot18535-8</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>16/08/2026</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>5.30</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>0.0090</t>
+          <t>0.0184</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -7000,17 +7000,17 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>79.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>110.40฿</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>配件 破损件</t>
+          <t>锅具 二次包装货物变形</t>
         </is>
       </c>
     </row>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>YT7636332367470</t>
+          <t>435295775627304</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -7036,7 +7036,7 @@
       <c r="E96" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18487-2-27</t>
+ รถ lot18492-2</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -7056,12 +7056,12 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>5.30</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>0.0004</t>
+          <t>0.0090</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -7071,17 +7071,17 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>79.50฿</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>10.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>立牌</t>
+          <t>配件 破损件</t>
         </is>
       </c>
     </row>
@@ -7091,7 +7091,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>S35386280517#2</t>
+          <t>YT7636332367470</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -7107,32 +7107,32 @@
       <c r="E97" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18475-24</t>
+ รถ lot18487-2-27</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>8.80</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>0.0045</t>
+          <t>0.0004</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -7142,15 +7142,19 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>132.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr"/>
+          <t>10.00฿</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>立牌</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -7158,7 +7162,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>S35386280517</t>
+          <t>S35386280517#2</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -7174,7 +7178,7 @@
       <c r="E98" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18475-23</t>
+ รถ lot18475-24</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -7194,22 +7198,22 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>103.50</t>
+          <t>8.80</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>0.2236</t>
+          <t>0.0045</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>1,552.50฿</t>
+          <t>132.00฿</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -7217,11 +7221,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N98" t="inlineStr">
-        <is>
-          <t>气门嘴 顺心捷达，一票16件</t>
-        </is>
-      </c>
+      <c r="N98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -7229,7 +7229,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>YT7635787693833</t>
+          <t>S35386280517</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -7245,7 +7245,7 @@
       <c r="E99" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18473-6-41</t>
+ รถ lot18475-23</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -7260,37 +7260,37 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>13.80</t>
+          <t>103.50</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>0.0432</t>
+          <t>0.2236</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1,552.50฿</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>259.20฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>气压表/面单没有代码</t>
+          <t>气门嘴 顺心捷达，一票16件</t>
         </is>
       </c>
     </row>
@@ -7300,7 +7300,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>ZY202465806614</t>
+          <t>YT7635787693833</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -7310,38 +7310,38 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>UN-INV260807-00009</t>
+          <t>UN-INV260811-00012</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>มอก.
- รถ lot18466-5-51</t>
+          <t>ธรรมดา
+ รถ lot18473-6-41</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>11.30</t>
+          <t>13.80</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>0.0655</t>
+          <t>0.0432</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -7356,12 +7356,12 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>445.40฿</t>
+          <t>259.20฿</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>电子数显胎压枪</t>
+          <t>气压表/面单没有代码</t>
         </is>
       </c>
     </row>
@@ -7371,7 +7371,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>113177184579#7</t>
+          <t>ZY202465806614</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -7386,18 +7386,18 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>ธรรมดา
- รถ lot18463-17</t>
+          <t>มอก.
+ รถ lot18466-5-51</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -7407,12 +7407,12 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>9.70</t>
+          <t>11.30</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>0.0305</t>
+          <t>0.0655</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -7427,10 +7427,14 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>183.00฿</t>
-        </is>
-      </c>
-      <c r="N101" t="inlineStr"/>
+          <t>445.40฿</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>电子数显胎压枪</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/cargo_packages_p1-5.xlsx
+++ b/cargo_packages_p1-5.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>773445635488295</t>
+          <t>113449148325#3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -522,12 +522,12 @@
       <c r="E2" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18986-4-60</t>
+ รถ lot18994-8-9</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>12/10/2026</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -542,12 +542,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5.50</t>
+          <t>26.20</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.0128</t>
+          <t>0.0396</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -557,7 +557,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>82.50฿</t>
+          <t>393.00฿</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -565,11 +565,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>配件</t>
-        </is>
-      </c>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -577,7 +573,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ZY202466680649#5</t>
+          <t>113449148325#2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -593,17 +589,17 @@
       <c r="E3" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18984-7-12</t>
+ รถ lot18994-8-8</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>12/10/2026</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -613,12 +609,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>28.50</t>
+          <t>26.20</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.0816</t>
+          <t>0.0367</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -628,12 +624,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>393.00฿</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>489.60฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -644,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ZY202466680649#4</t>
+          <t>113449148325</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -660,17 +656,17 @@
       <c r="E4" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18984-7-11</t>
+ รถ lot18994-8-7</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>12/10/2026</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -680,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>8.70</t>
+          <t>17.80</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.0446</t>
+          <t>0.0254</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -695,15 +691,19 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>267.00฿</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>267.60฿</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>配件</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -711,7 +711,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ZY202466680649#3</t>
+          <t>79038771455808</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -726,18 +726,18 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ธรรมดา
- รถ lot18984-7-10</t>
+          <t>มอก.
+ รถ lot18992-9-4</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>12/10/2026</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>12/10/2026</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>11.80</t>
+          <t>6.90</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.0811</t>
+          <t>0.0777</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -767,10 +767,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>486.60฿</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>528.36฿</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>智能无线干湿两用吸尘器</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -778,7 +782,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ZY202466680649#2</t>
+          <t>DPK202830769852</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -794,17 +798,17 @@
       <c r="E6" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18984-7-9</t>
+ รถ lot18986-7-52</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>12/10/2026</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>12/10/2026</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -814,12 +818,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>27.60</t>
+          <t>18.50</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.0800</t>
+          <t>0.0479</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -834,10 +838,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>480.00฿</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>287.40฿</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>真空胎冷补胶片</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -845,7 +853,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ZY202466680649</t>
+          <t>773445635488295</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -861,7 +869,7 @@
       <c r="E7" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18984-7-8</t>
+ รถ lot18986-4-60</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -871,7 +879,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>12/10/2026</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -881,12 +889,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>8.20</t>
+          <t>5.50</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.0203</t>
+          <t>0.0128</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -896,7 +904,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>123.00฿</t>
+          <t>82.50฿</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -906,7 +914,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>补胎贴</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -916,7 +924,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>435387211695084</t>
+          <t>ZY202466680649#5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -932,17 +940,17 @@
       <c r="E8" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18966-4-53</t>
+ รถ lot18984-7-12</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -952,12 +960,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>28.50</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.0116</t>
+          <t>0.0816</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -972,14 +980,10 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>69.60฿</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>宠物用品</t>
-        </is>
-      </c>
+          <t>489.60฿</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -987,7 +991,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ZY202466680891#5</t>
+          <t>ZY202466680649#4</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -997,38 +1001,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>UN-INV261008-00007</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18919-2-7</t>
+ รถ lot18984-7-11</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>19.70</t>
+          <t>8.70</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.0715</t>
+          <t>0.0446</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1043,7 +1047,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>429.00฿</t>
+          <t>267.60฿</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1054,7 +1058,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ZY202466680891#4</t>
+          <t>ZY202466680649#3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1064,38 +1068,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>UN-INV261008-00007</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18919-2-6</t>
+ รถ lot18984-7-10</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>20.00</t>
+          <t>11.80</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.0640</t>
+          <t>0.0811</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1110,7 +1114,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>384.00฿</t>
+          <t>486.60฿</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1121,7 +1125,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ZY202466680891#3</t>
+          <t>ZY202466680649#2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1131,38 +1135,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>UN-INV261008-00007</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18919-2-5</t>
+ รถ lot18984-7-9</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>15.80</t>
+          <t>27.60</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.0492</t>
+          <t>0.0800</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1177,7 +1181,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>295.20฿</t>
+          <t>480.00฿</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1188,7 +1192,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ZY202466680891#2</t>
+          <t>ZY202466680649</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1198,38 +1202,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>UN-INV261008-00007</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18919-2-4</t>
+ รถ lot18984-7-8</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>16.20</t>
+          <t>8.20</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0.0492</t>
+          <t>0.0203</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1239,15 +1243,19 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>123.00฿</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>295.20฿</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>补胎贴</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1255,7 +1263,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ZY202466680891</t>
+          <t>435387211695084</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1265,38 +1273,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>UN-INV261008-00007</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18919-2-3</t>
+ รถ lot18966-4-53</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>15.90</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0.0492</t>
+          <t>0.0116</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1311,12 +1319,12 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>295.20฿</t>
+          <t>69.60฿</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>补胎胶片/5件</t>
+          <t>宠物用品</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1334,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>S35386291018</t>
+          <t>ZY202466680891#5</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1336,60 +1344,56 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>UN-INV261005-00021</t>
+          <t>UN-INV261008-00007</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18901-6-32</t>
+ รถ lot18919-2-7</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>82.80</t>
+          <t>19.70</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.1641</t>
+          <t>0.0715</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>1,242.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>配件，12件</t>
-        </is>
-      </c>
+          <t>429.00฿</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1397,7 +1401,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>113405301091#3</t>
+          <t>ZY202466680891#4</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1407,38 +1411,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>UN-INV261005-00021</t>
+          <t>UN-INV261008-00007</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18901-7-3</t>
+ รถ lot18919-2-6</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>13.10</t>
+          <t>20.00</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.0347</t>
+          <t>0.0640</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1453,7 +1457,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>208.20฿</t>
+          <t>384.00฿</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1464,7 +1468,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>113405301091#2</t>
+          <t>ZY202466680891#3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1474,38 +1478,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>UN-INV261005-00021</t>
+          <t>UN-INV261008-00007</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18901-7-2</t>
+ รถ lot18919-2-5</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>16.10</t>
+          <t>15.80</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>0.0397</t>
+          <t>0.0492</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1515,12 +1519,12 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>241.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>295.20฿</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1531,7 +1535,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>113405301091</t>
+          <t>ZY202466680891#2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1541,38 +1545,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>UN-INV261005-00021</t>
+          <t>UN-INV261008-00007</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18901-7-1</t>
+ รถ lot18919-2-4</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>33.60</t>
+          <t>16.20</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.0832</t>
+          <t>0.0492</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1582,19 +1586,15 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>504.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>补胎胶片/3件</t>
-        </is>
-      </c>
+          <t>295.20฿</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>YT7646197126750</t>
+          <t>ZY202466680891</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1612,38 +1612,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>UN-INV261005-00021</t>
+          <t>UN-INV261008-00007</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18887-50</t>
+ รถ lot18919-2-3</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>26/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>26/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>8.30</t>
+          <t>15.90</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>0.0127</t>
+          <t>0.0492</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1653,17 +1653,17 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>124.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>295.20฿</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>补胎胶片/5件</t>
         </is>
       </c>
     </row>
@@ -1673,7 +1673,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ZY202462495078</t>
+          <t>S35386291018</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1683,58 +1683,58 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>UN-INV260926-00006</t>
+          <t>UN-INV261005-00021</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18844-9-4</t>
+ รถ lot18901-6-32</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>14.30</t>
+          <t>82.80</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>0.0624</t>
+          <t>0.1641</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1,242.00฿</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>374.40฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>胎压表</t>
+          <t>配件，12件</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>S71749075994</t>
+          <t>113405301091#3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1754,38 +1754,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>UN-INV260924-00056</t>
+          <t>UN-INV261005-00021</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18830-6-30</t>
+ รถ lot18901-7-3</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>119.00</t>
+          <t>13.10</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0.2302</t>
+          <t>0.0347</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1795,19 +1795,15 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>1,785.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>真空胎扒胎机配件/木箱</t>
-        </is>
-      </c>
+          <t>208.20฿</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1815,7 +1811,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>435358249576981</t>
+          <t>113405301091#2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1825,38 +1821,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>UN-INV260924-00056</t>
+          <t>UN-INV261005-00021</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18815-4-6</t>
+ รถ lot18901-7-2</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>5.20</t>
+          <t>16.10</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.0044</t>
+          <t>0.0397</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1866,7 +1862,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>78.00฿</t>
+          <t>241.50฿</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1874,11 +1870,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>气门嘴</t>
-        </is>
-      </c>
+      <c r="N21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1886,7 +1878,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>S71195667064</t>
+          <t>113405301091</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1896,58 +1888,58 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>UN-INV260924-00056</t>
+          <t>UN-INV261005-00021</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18810-6-3</t>
+ รถ lot18901-7-1</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>165.00</t>
+          <t>33.60</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.8568</t>
+          <t>0.0832</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>504.00฿</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>5,140.80฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>千斤顶，3件，客户不打木架发</t>
+          <t>补胎胶片/3件</t>
         </is>
       </c>
     </row>
@@ -1957,7 +1949,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>113350746029#4</t>
+          <t>YT7646197126750</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1967,38 +1959,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>UN-INV260924-00056</t>
+          <t>UN-INV261005-00021</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18799-6-32</t>
+ รถ lot18887-50</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>26/09/2026</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>26/09/2026</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>27.70</t>
+          <t>8.30</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.0800</t>
+          <t>0.0127</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2008,15 +2000,19 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>124.50฿</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>480.00฿</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>配件</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2024,7 +2020,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>113350746029#3</t>
+          <t>ZY202462495078</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2034,38 +2030,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>UN-INV260924-00056</t>
+          <t>UN-INV260926-00006</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18799-6-31</t>
+ รถ lot18844-9-4</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>10.90</t>
+          <t>14.30</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.0377</t>
+          <t>0.0624</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2080,10 +2076,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>226.20฿</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
+          <t>374.40฿</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>胎压表</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -2091,7 +2091,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>113350746029#2</t>
+          <t>S71749075994</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2107,32 +2107,32 @@
       <c r="E25" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18799-6-30</t>
+ รถ lot18830-6-30</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>15.00</t>
+          <t>119.00</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.0101</t>
+          <t>0.2302</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>225.00฿</t>
+          <t>1,785.00฿</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2150,7 +2150,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>真空胎扒胎机配件/木箱</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -2158,7 +2162,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>113350746029</t>
+          <t>435358249576981</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2174,32 +2178,32 @@
       <c r="E26" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18799-6-29</t>
+ รถ lot18815-4-6</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>16.50</t>
+          <t>5.20</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>0.0127</t>
+          <t>0.0044</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2209,7 +2213,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>247.50฿</t>
+          <t>78.00฿</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2219,7 +2223,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>真空胎加固修理补片</t>
+          <t>气门嘴</t>
         </is>
       </c>
     </row>
@@ -2229,7 +2233,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>760246657062</t>
+          <t>S71195667064</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2245,17 +2249,17 @@
       <c r="E27" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18799-7-3</t>
+ รถ lot18810-6-3</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2265,17 +2269,17 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>165.00</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.0005</t>
+          <t>0.8568</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2285,12 +2289,12 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>10.00฿</t>
+          <t>5,140.80฿</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>气门嘴，轮胎修补工具，气门芯宣传册</t>
+          <t>千斤顶，3件，客户不打木架发</t>
         </is>
       </c>
     </row>
@@ -2300,7 +2304,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>113348267192#2</t>
+          <t>113350746029#4</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2310,38 +2314,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>UN-INV260921-00019</t>
+          <t>UN-INV260924-00056</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18795-2-7</t>
+ รถ lot18799-6-32</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>28.10</t>
+          <t>27.70</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.0628</t>
+          <t>0.0800</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2351,12 +2355,12 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>421.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>480.00฿</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -2367,7 +2371,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>113348267192</t>
+          <t>113350746029#3</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2377,38 +2381,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>UN-INV260921-00019</t>
+          <t>UN-INV260924-00056</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18795-2-6</t>
+ รถ lot18799-6-31</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>19.50</t>
+          <t>10.90</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0.0505</t>
+          <t>0.0377</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2423,14 +2427,10 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>303.00฿</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>补胎胶片</t>
-        </is>
-      </c>
+          <t>226.20฿</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ZY202472578299</t>
+          <t>113350746029#2</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2448,60 +2448,56 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>UN-INV260918-00012</t>
+          <t>UN-INV260924-00056</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18758-7-43</t>
+ รถ lot18799-6-30</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>47.40</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.1603</t>
+          <t>0.0101</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>225.00฿</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>961.20฿</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>补胎贴，3件</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2509,7 +2505,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>773440822655698</t>
+          <t>113350746029</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2519,38 +2515,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>UN-INV260918-00012</t>
+          <t>UN-INV260924-00056</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18758-4-31</t>
+ รถ lot18799-6-29</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>16.50</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.0022</t>
+          <t>0.0127</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2560,7 +2556,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>18.00฿</t>
+          <t>247.50฿</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2570,7 +2566,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>钻头</t>
+          <t>真空胎加固修理补片</t>
         </is>
       </c>
     </row>
@@ -2580,7 +2576,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>YT7642998390994</t>
+          <t>760246657062</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2590,38 +2586,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>UN-INV260918-00012</t>
+          <t>UN-INV260924-00056</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18769-3-57</t>
+ รถ lot18799-7-3</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>5.80</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.0070</t>
+          <t>0.0005</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2631,17 +2627,17 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>87.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10.00฿</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>气门嘴，轮胎修补工具，气门芯宣传册</t>
         </is>
       </c>
     </row>
@@ -2651,7 +2647,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>DPK212614057101</t>
+          <t>113348267192#2</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2661,38 +2657,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>UN-INV260916-00003</t>
+          <t>UN-INV260921-00019</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18749-4-3</t>
+ รถ lot18795-2-7</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>9.60</t>
+          <t>28.10</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.0060</t>
+          <t>0.0628</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2702,7 +2698,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>144.00฿</t>
+          <t>421.50฿</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2710,11 +2706,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>轮胎气门嘴</t>
-        </is>
-      </c>
+      <c r="N33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2722,7 +2714,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>79031204783305</t>
+          <t>113348267192</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2732,38 +2724,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>UN-INV260916-00003</t>
+          <t>UN-INV260921-00019</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18744-6-15</t>
+ รถ lot18795-2-6</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>19.50</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.0020</t>
+          <t>0.0505</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2773,17 +2765,17 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>39.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>303.00฿</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>补胎胶片</t>
         </is>
       </c>
     </row>
@@ -2793,7 +2785,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>435342988112655</t>
+          <t>ZY202472578299</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2803,43 +2795,43 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>UN-INV260916-00003</t>
+          <t>UN-INV260918-00012</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18743-3-34</t>
+ รถ lot18758-7-43</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>47.40</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.0014</t>
+          <t>0.1603</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2849,12 +2841,12 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>10.00฿</t>
+          <t>961.20฿</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>橡胶垫圈</t>
+          <t>补胎贴，3件</t>
         </is>
       </c>
     </row>
@@ -2864,7 +2856,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>435343890137834</t>
+          <t>773440822655698</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2874,38 +2866,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>UN-INV260916-00003</t>
+          <t>UN-INV260918-00012</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18743-7-25</t>
+ รถ lot18758-4-31</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>21.40</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.0080</t>
+          <t>0.0022</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2915,7 +2907,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>321.00฿</t>
+          <t>18.00฿</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2925,7 +2917,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>扒胎机包胶撬棍</t>
+          <t>钻头</t>
         </is>
       </c>
     </row>
@@ -2935,7 +2927,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>YT7642670434639</t>
+          <t>YT7642998390994</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2945,38 +2937,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>UN-INV260916-00003</t>
+          <t>UN-INV260918-00012</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18743-2-8</t>
+ รถ lot18769-3-57</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>5.80</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.0010</t>
+          <t>0.0070</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2986,7 +2978,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>12.00฿</t>
+          <t>87.00฿</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2996,7 +2988,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>片片</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -3006,7 +2998,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>93015797092</t>
+          <t>DPK212614057101</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3016,38 +3008,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>UN-INV260914-00014</t>
+          <t>UN-INV260916-00003</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18735-4-40</t>
+ รถ lot18749-4-3</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>12/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>8.60</t>
+          <t>9.60</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.0148</t>
+          <t>0.0060</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -3057,7 +3049,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>129.00฿</t>
+          <t>144.00฿</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3067,7 +3059,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>仪表</t>
+          <t>轮胎气门嘴</t>
         </is>
       </c>
     </row>
@@ -3077,7 +3069,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>YT7642390374765</t>
+          <t>79031204783305</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3087,38 +3079,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>UN-INV260914-00015</t>
+          <t>UN-INV260916-00003</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18735-4-20</t>
+ รถ lot18744-6-15</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>12/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>20.80</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.0598</t>
+          <t>0.0020</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -3128,17 +3120,17 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>39.00฿</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>358.80฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>打磨机</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -3148,7 +3140,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>435342255104130</t>
+          <t>435342988112655</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3158,18 +3150,18 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>UN-INV260914-00014</t>
+          <t>UN-INV260916-00003</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18735-43</t>
+ รถ lot18743-3-34</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -3179,17 +3171,17 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>12/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>4.90</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.0172</t>
+          <t>0.0014</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -3204,12 +3196,12 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>103.20฿</t>
+          <t>10.00฿</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>轮毂保护套</t>
+          <t>橡胶垫圈</t>
         </is>
       </c>
     </row>
@@ -3219,7 +3211,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>773440312345715</t>
+          <t>435343890137834</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3229,18 +3221,18 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>UN-INV260914-00014</t>
+          <t>UN-INV260916-00003</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18735-3-78</t>
+ รถ lot18743-7-25</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -3250,17 +3242,17 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>12/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>21.40</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.0013</t>
+          <t>0.0080</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -3270,7 +3262,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>19.50฿</t>
+          <t>321.00฿</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -3280,7 +3272,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>扒胎机包胶撬棍</t>
         </is>
       </c>
     </row>
@@ -3290,7 +3282,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>773440291470393</t>
+          <t>YT7642670434639</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3300,18 +3292,18 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>UN-INV260914-00014</t>
+          <t>UN-INV260916-00003</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18735-34</t>
+ รถ lot18743-2-8</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -3321,17 +3313,17 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>12/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.0029</t>
+          <t>0.0010</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3341,7 +3333,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>48.00฿</t>
+          <t>12.00฿</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3351,7 +3343,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>球阀</t>
+          <t>片片</t>
         </is>
       </c>
     </row>
@@ -3361,7 +3353,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>435342261175750</t>
+          <t>93015797092</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3371,13 +3363,13 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>UN-INV260914-00015</t>
+          <t>UN-INV260914-00014</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18736-13</t>
+ รถ lot18735-4-40</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -3387,7 +3379,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3397,12 +3389,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>13.90</t>
+          <t>8.60</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.0137</t>
+          <t>0.0148</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3412,7 +3404,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>208.50฿</t>
+          <t>129.00฿</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3422,7 +3414,7 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>仪表</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3424,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ZY202461195200</t>
+          <t>YT7642390374765</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3448,7 +3440,7 @@
       <c r="E44" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18728-7-13</t>
+ รถ lot18735-4-20</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -3458,22 +3450,22 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>13/09/2026</t>
+          <t>12/09/2026</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>47.40</t>
+          <t>20.80</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.0116</t>
+          <t>0.0598</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3483,17 +3475,17 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>711.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>358.80฿</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>打磨机</t>
         </is>
       </c>
     </row>
@@ -3503,7 +3495,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>79030687835952</t>
+          <t>435342255104130</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3519,7 +3511,7 @@
       <c r="E45" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18728-3-64</t>
+ รถ lot18735-43</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -3529,22 +3521,22 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>13/09/2026</t>
+          <t>12/09/2026</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>4.30</t>
+          <t>4.90</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.0030</t>
+          <t>0.0172</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3554,17 +3546,17 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>64.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>103.20฿</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>接头配件</t>
+          <t>轮毂保护套</t>
         </is>
       </c>
     </row>
@@ -3574,7 +3566,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>LJ20722214#3</t>
+          <t>773440312345715</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3584,38 +3576,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>UN-INV260912-00011</t>
+          <t>UN-INV260914-00014</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18726-7-8</t>
+ รถ lot18735-3-78</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>12/09/2026</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>14.00</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>0.0171</t>
+          <t>0.0013</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3625,7 +3617,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>210.00฿</t>
+          <t>19.50฿</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3633,7 +3625,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>配件</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -3641,7 +3637,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>LJ20722214#2</t>
+          <t>773440291470393</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3651,38 +3647,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>UN-INV260912-00011</t>
+          <t>UN-INV260914-00014</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18726-7-7</t>
+ รถ lot18735-34</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>12/09/2026</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>11.90</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>0.0089</t>
+          <t>0.0029</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3692,7 +3688,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>178.50฿</t>
+          <t>48.00฿</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3700,7 +3696,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>球阀</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>LJ20722214</t>
+          <t>435342261175750</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3718,38 +3718,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>UN-INV260912-00011</t>
+          <t>UN-INV260914-00015</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18726-7-6</t>
+ รถ lot18736-13</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>12/09/2026</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>16.00</t>
+          <t>13.90</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>0.0144</t>
+          <t>0.0137</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3759,7 +3759,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>240.00฿</t>
+          <t>208.50฿</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3769,7 +3769,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>电板套筒配件/3件</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -3779,7 +3779,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>YT7641966426761</t>
+          <t>ZY202461195200</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3789,38 +3789,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>UN-INV260912-00011</t>
+          <t>UN-INV260914-00015</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18714-9-23</t>
+ รถ lot18728-7-13</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>13/09/2026</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>13.60</t>
+          <t>47.40</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>0.0422</t>
+          <t>0.0116</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3830,17 +3830,17 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>711.00฿</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>253.20฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>带表汽车轮胎打气嘴</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -3850,7 +3850,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ZY202471681117#2</t>
+          <t>79030687835952</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3860,38 +3860,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>UN-INV260912-00011</t>
+          <t>UN-INV260914-00014</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18714-9-8</t>
+ รถ lot18728-3-64</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>13/09/2026</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>11.80</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>0.0832</t>
+          <t>0.0030</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3901,15 +3901,19 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>64.50฿</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>499.20฿</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>接头配件</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -3917,7 +3921,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ZY202471681117</t>
+          <t>LJ20722214#3</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3933,17 +3937,17 @@
       <c r="E51" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18714-9-7</t>
+ รถ lot18726-7-8</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3953,12 +3957,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>7.70</t>
+          <t>14.00</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>0.0493</t>
+          <t>0.0171</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3968,19 +3972,15 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>210.00฿</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>295.80฿</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>补胎胶片/2件</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -3988,7 +3988,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>302285502767#2</t>
+          <t>LJ20722214#2</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -4004,17 +4004,17 @@
       <c r="E52" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18714-8-10</t>
+ รถ lot18726-7-7</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>33.70</t>
+          <t>11.90</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>0